--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -590,12 +590,51 @@
     <t xml:space="preserve">Finanze</t>
   </si>
   <si>
+    <t xml:space="preserve">25.4794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGOV und E-ID. Die Authentifizierung bei Bundes-Applikationen soll vereinheitlicht werden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agov et e-ID. L'authentification pour les applications fédérales doit être uniformisée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGOV ed Id-e. L'autenticazione nelle applicazioni federali deve essere uniformata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;AGOV est un service d’authentification standardisé pour les services numériques de la Confédération, des cantons et des communes. La loi sur l’e-ID ayant été adoptée, une nouvelle possibilité de vérifier l’identité existera pour accéder à une application administrative.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les départements ont actuellement des opinions divergentes quant à l’utilisation de ces possibilités d’authentification. En effet, les coûts liés à la vérification d’identité (p.&amp;nbsp;ex.&amp;nbsp;pour AGOV&amp;nbsp;400) sont à la charge du gestionnaire de l’application administrative, tandis que l’e-ID pourra être utilisée sans coûts supplémentaires. Si ces coûts ne sont pas pris en charge, il y aura de facto une obligation d’utiliser l’e-ID, ce qu’il convient d’éviter en uniformisant l’authentification pour les applications fédérales.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral doit déterminer comment AGOV et l’e-ID devront être utilisés de manière uniforme dans tous les départements s’agissant de l’authentification dans les applications fédérales.&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Il doit décider que l’utilisation de l’e-ID restera facultative et que toutes les applications fédérales offriront également la possibilité d’une authentification au moyen d’AGOV.&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Les coûts liés à la vérification d’identité sont à la charge des gestionnaires des applications fédérales.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;AGOV ist ein standardisierter Authentifizierungsdienst für digitale Angebote von Bund, Kantonen und Gemeinden. Wenn für den Zugriff auf eine Behörden-Applikation eine Identitätsprüfung erforderlich ist, steht seit der Annahme des e-ID Gesetzes eine neue Möglichkeit zur Identitätsüberprüfung zur Verfügung.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die verschiedenen Departemente haben aktuell unterschiedliche Auffassungen über die Verwendung dieser Authentifizierungsmöglichkeiten. Dies weil die Kosten der Identitätsüberprüfung&amp;nbsp;(z.B. für AGOV 400) vom Betreiber der Behörden-Applikation übernommen werden müssen, während die e-ID nach deren Einführung ohne Kostenfolge eingesetzt werden kann. Wenn diese Kosten der Identitätsüberprüfung nicht übernommen werden, führt dies zu einem faktischen e-ID-Zwang, den es zu verhindern gilt mit einer Vereinheitlichung der Authentifizierung bei Bundes-Applikationen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Der Bundesrat hat festzulegen, wie AGOV und die e-ID einheitlich über alle Departemente hinweg bei den Bundes-Applikationen zur Authentifizierung genutzt werden sollen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Der Bundesrat hat festzulegen, dass die Verwendung der e-ID freiwillig bleibt und in allen Bundes-Applikationen auch die Möglichkeit der AGOV Authentifizierung angeboten werden muss.&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Die Kosten der Identitätsüberprüfung sind von den Betreibern der Bundes-Applikationen zu übernehmen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation|Menschenrechte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication|Droits de l'homme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione|Diritti umani</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.4774</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-12-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gewalttätiger Extremismus bei Demonstrationen. Veranstalter sollen die Kosten übernehmen</t>
   </si>
   <si>
@@ -629,45 +668,6 @@
     <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Questioni sociali</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGOV und E-ID. Die Authentifizierung bei Bundes-Applikationen soll vereinheitlicht werden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agov et e-ID. L'authentification pour les applications fédérales doit être uniformisée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGOV ed Id-e. L'autenticazione nelle applicazioni federali deve essere uniformata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;AGOV est un service d’authentification standardisé pour les services numériques de la Confédération, des cantons et des communes. La loi sur l’e-ID ayant été adoptée, une nouvelle possibilité de vérifier l’identité existera pour accéder à une application administrative.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les départements ont actuellement des opinions divergentes quant à l’utilisation de ces possibilités d’authentification. En effet, les coûts liés à la vérification d’identité (p.&amp;nbsp;ex.&amp;nbsp;pour AGOV&amp;nbsp;400) sont à la charge du gestionnaire de l’application administrative, tandis que l’e-ID pourra être utilisée sans coûts supplémentaires. Si ces coûts ne sont pas pris en charge, il y aura de facto une obligation d’utiliser l’e-ID, ce qu’il convient d’éviter en uniformisant l’authentification pour les applications fédérales.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral doit déterminer comment AGOV et l’e-ID devront être utilisés de manière uniforme dans tous les départements s’agissant de l’authentification dans les applications fédérales.&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Il doit décider que l’utilisation de l’e-ID restera facultative et que toutes les applications fédérales offriront également la possibilité d’une authentification au moyen d’AGOV.&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Les coûts liés à la vérification d’identité sont à la charge des gestionnaires des applications fédérales.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;AGOV ist ein standardisierter Authentifizierungsdienst für digitale Angebote von Bund, Kantonen und Gemeinden. Wenn für den Zugriff auf eine Behörden-Applikation eine Identitätsprüfung erforderlich ist, steht seit der Annahme des e-ID Gesetzes eine neue Möglichkeit zur Identitätsüberprüfung zur Verfügung.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die verschiedenen Departemente haben aktuell unterschiedliche Auffassungen über die Verwendung dieser Authentifizierungsmöglichkeiten. Dies weil die Kosten der Identitätsüberprüfung&amp;nbsp;(z.B. für AGOV 400) vom Betreiber der Behörden-Applikation übernommen werden müssen, während die e-ID nach deren Einführung ohne Kostenfolge eingesetzt werden kann. Wenn diese Kosten der Identitätsüberprüfung nicht übernommen werden, führt dies zu einem faktischen e-ID-Zwang, den es zu verhindern gilt mit einer Vereinheitlichung der Authentifizierung bei Bundes-Applikationen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Der Bundesrat hat festzulegen, wie AGOV und die e-ID einheitlich über alle Departemente hinweg bei den Bundes-Applikationen zur Authentifizierung genutzt werden sollen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Der Bundesrat hat festzulegen, dass die Verwendung der e-ID freiwillig bleibt und in allen Bundes-Applikationen auch die Möglichkeit der AGOV Authentifizierung angeboten werden muss.&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Die Kosten der Identitätsüberprüfung sind von den Betreibern der Bundes-Applikationen zu übernehmen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation|Menschenrechte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication|Droits de l'homme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione|Diritti umani</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.4836</t>
   </si>
   <si>
@@ -890,15 +890,45 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254517</t>
   </si>
   <si>
+    <t xml:space="preserve">25.8270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRG-Sparprogramm November 2025. Ist Gebühren-Zuwachs berücksichtigt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programme d’économies de la SSR en novembre 2025. La croissance en volume de la redevance a-t-elle été prise en compte ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;En novembre 2025, la SSR a annoncé son intention de réaliser 270 millions de francs d'économies. L’immigration engendre une hausse de 57&amp;nbsp;000 ménages en moyenne par an.&lt;br&gt;- Le Conseil fédéral peut-il confirmer que la hausse du volume de la redevance qui en découle pour la SSR, soit 170 millions de francs (sur dix ans) n’a pas été intégré au plan d’économies de 270&amp;nbsp;millions de francs&amp;nbsp;?&lt;br&gt;- &amp;nbsp;Dans la négative, à combien s’élèvent les économies potentielles, selon lui&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die SRG hat im November 2025 angekündet, dass sie 270 Mio. Franken einsparen will. Durch Zuwanderung wächst die Schweiz im Durchschnitt um 57'000 Haushalte pro Jahr.&lt;br&gt;- Kann der Bundesrat bestätigen, dass der dadurch entstehende Gebühren-Zuwachs der SRG von 170 Mio. Franken (in zehn Jahren) in diesem Sparbetrag von 270 Mio. Franken nicht enthalten ist?&lt;br&gt;- &amp;nbsp;Falls nein, wie hoch ist der einzusparende Betrag nach Ansicht des Bundesrats?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Médias et communication|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Media e comunicazione|Imposte</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.8254</t>
   </si>
   <si>
     <t xml:space="preserve">Alijaj Islam</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-12-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nationalen Finanzausgleich (NFA) im Bezug auf Sportschulen</t>
   </si>
   <si>
@@ -926,36 +956,6 @@
     <t xml:space="preserve">Finanze|Questioni sociali|Formazione</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRG-Sparprogramm November 2025. Ist Gebühren-Zuwachs berücksichtigt?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programme d’économies de la SSR en novembre 2025. La croissance en volume de la redevance a-t-elle été prise en compte ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;En novembre 2025, la SSR a annoncé son intention de réaliser 270 millions de francs d'économies. L’immigration engendre une hausse de 57&amp;nbsp;000 ménages en moyenne par an.&lt;br&gt;- Le Conseil fédéral peut-il confirmer que la hausse du volume de la redevance qui en découle pour la SSR, soit 170 millions de francs (sur dix ans) n’a pas été intégré au plan d’économies de 270&amp;nbsp;millions de francs&amp;nbsp;?&lt;br&gt;- &amp;nbsp;Dans la négative, à combien s’élèvent les économies potentielles, selon lui&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die SRG hat im November 2025 angekündet, dass sie 270 Mio. Franken einsparen will. Durch Zuwanderung wächst die Schweiz im Durchschnitt um 57'000 Haushalte pro Jahr.&lt;br&gt;- Kann der Bundesrat bestätigen, dass der dadurch entstehende Gebühren-Zuwachs der SRG von 170 Mio. Franken (in zehn Jahren) in diesem Sparbetrag von 270 Mio. Franken nicht enthalten ist?&lt;br&gt;- &amp;nbsp;Falls nein, wie hoch ist der einzusparende Betrag nach Ansicht des Bundesrats?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Médias et communication|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Media e comunicazione|Imposte</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.8286</t>
   </si>
   <si>
@@ -1019,15 +1019,48 @@
     <t xml:space="preserve">Politica nazionale|Cultura|Pianificazione territoriale e alloggi</t>
   </si>
   <si>
+    <t xml:space="preserve">25.4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stärkung der Aufsicht über die SRG unter Wahrung der Programmautonomie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renforcer la surveillance de la SSR tout en préservant l'autonomie des programmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafforzare la vigilanza sulla SSR nel rispetto dell'autonomia in materia di programmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter une modification de la loi fédérale sur la radio et la télévision (LRTV) afin de soumettre la SSR à la haute surveillance financière du Contrôle fédéral des finances (CDF) sans porter atteinte à l’autonomie des programmes.&lt;/p&gt;&lt;p&gt;Il respectera les principes suivants :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Garantir l’autonomie dans la conception des programmes visée à l’art. 93, al. 3, Cst.&lt;/p&gt;&lt;p&gt;L’indépendance de la SSR dans la conception des programmes et dans ses activités rédactionnelles restera entièrement garantie.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Éviter les doublons&lt;/p&gt;&lt;p&gt;La répartition des tâches entre l’OFCOM, le DETEC, l’organe de révision interne de la SSR et le CDF doit être clairement harmonisée et coordonnée, comme c’est le cas pour des entreprises comparables qui sont soumises à la surveillance du CDF (par ex. la Poste, Swisscom et les CFF). Il conviendra d’éviter les doublons lors des contrôles afin de maintenir l’efficacité du processus de contrôle. L’indépendance du CDF, telle qu’elle est définie dans la loi sur le Contrôle des finances, sera garantie en permanence.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Assurer une surveillance complémentaire par le CDF&lt;/p&gt;&lt;p&gt;La surveillance actuelle par le DETEC et l’OFCOM et le contrôle des états financiers selon le droit de la société anonyme seront maintenus sans être remplacés. Lors du contrôle, le CDF agira de manière complémentaire et ciblée et interviendra de manière autonome et indépendante là où sa position particulière et sa spécialisation (par ex. contrôles de l’économicité) lui permettent de créer une plus-value, comme c’est le cas par rapport aux révisions internes, quand il définit lui-même l’accent qu’il va mettre.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine Änderung des Bundesgesetzes über Radio und Fernsehen (RTVG) vorzulegen, damit die SRG der finanziellen Oberaufsicht der eidgenössischen Finanzkontrolle (EFK) ohne Beeinträchtigung der Programmautonomie, unterstellt wird.&lt;/p&gt;&lt;p&gt;Folgende Bedingungen sollen dabei berücksichtigt werden:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Programmautonomie gemäss Bundesverfassung (Art. 93 Abs. 3 BV):&lt;/p&gt;&lt;p&gt;Die Unabhängigkeit der SRG in der Programmgestaltung und redaktionellen Tätigkeit bleibt vollständig gewährleistet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Vermeidung von Doppelspurigkeiten:&lt;/p&gt;&lt;p&gt;Die Aufgabenverteilung zwischen BAKOM, UVEK, interner Revision SRG und EFK ist klar abzustimmen und zu koordinieren, wie das bei vergleichbaren Unternehmen, welche der Aufsicht der EFK unterstehen (z.B. Post, Swisscom, SBB der Fall ist. Doppelspurigkeiten bei der Prüfung sollen vermieden werden, um den Prüfungsprozess effizient zu halten. Die Unabhängigkeit der EFK gemäss Finanzkontrollgesetz bleibt hierbei jederzeit gewahrt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Ergänzende Aufsicht durch die EFK:&lt;/p&gt;&lt;p&gt;Die bestehende Aufsicht durch UVEK/BAKOM und die aktienrechtliche Abschlussprüfung bleiben erhalten und werden nicht ersetzt. Die EFK wirkt bei der Prüfung gezielt ergänzend und wird selbständig und unabhängig dort eingesetzt, wo sie durch ihre Sonderstellung und Spezialisierung (z.B. Wirtschaftlichkeitsprüfungen) einen Mehrwert schaffen kann, wie zum Beispiel gegenüber internen Revisionen wo der Fokus selbst definiert wird.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Media e comunicazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.4263</t>
   </si>
   <si>
     <t xml:space="preserve">Germann Hannes</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-09-26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vollumfänglicher Abzug der Krankenversicherungsprämien von der direkten Bundessteuer</t>
   </si>
   <si>
@@ -1056,39 +1089,6 @@
   </si>
   <si>
     <t xml:space="preserve">Imposte|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stärkung der Aufsicht über die SRG unter Wahrung der Programmautonomie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renforcer la surveillance de la SSR tout en préservant l'autonomie des programmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafforzare la vigilanza sulla SSR nel rispetto dell'autonomia in materia di programmi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter une modification de la loi fédérale sur la radio et la télévision (LRTV) afin de soumettre la SSR à la haute surveillance financière du Contrôle fédéral des finances (CDF) sans porter atteinte à l’autonomie des programmes.&lt;/p&gt;&lt;p&gt;Il respectera les principes suivants :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Garantir l’autonomie dans la conception des programmes visée à l’art. 93, al. 3, Cst.&lt;/p&gt;&lt;p&gt;L’indépendance de la SSR dans la conception des programmes et dans ses activités rédactionnelles restera entièrement garantie.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Éviter les doublons&lt;/p&gt;&lt;p&gt;La répartition des tâches entre l’OFCOM, le DETEC, l’organe de révision interne de la SSR et le CDF doit être clairement harmonisée et coordonnée, comme c’est le cas pour des entreprises comparables qui sont soumises à la surveillance du CDF (par ex. la Poste, Swisscom et les CFF). Il conviendra d’éviter les doublons lors des contrôles afin de maintenir l’efficacité du processus de contrôle. L’indépendance du CDF, telle qu’elle est définie dans la loi sur le Contrôle des finances, sera garantie en permanence.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Assurer une surveillance complémentaire par le CDF&lt;/p&gt;&lt;p&gt;La surveillance actuelle par le DETEC et l’OFCOM et le contrôle des états financiers selon le droit de la société anonyme seront maintenus sans être remplacés. Lors du contrôle, le CDF agira de manière complémentaire et ciblée et interviendra de manière autonome et indépendante là où sa position particulière et sa spécialisation (par ex. contrôles de l’économicité) lui permettent de créer une plus-value, comme c’est le cas par rapport aux révisions internes, quand il définit lui-même l’accent qu’il va mettre.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine Änderung des Bundesgesetzes über Radio und Fernsehen (RTVG) vorzulegen, damit die SRG der finanziellen Oberaufsicht der eidgenössischen Finanzkontrolle (EFK) ohne Beeinträchtigung der Programmautonomie, unterstellt wird.&lt;/p&gt;&lt;p&gt;Folgende Bedingungen sollen dabei berücksichtigt werden:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Programmautonomie gemäss Bundesverfassung (Art. 93 Abs. 3 BV):&lt;/p&gt;&lt;p&gt;Die Unabhängigkeit der SRG in der Programmgestaltung und redaktionellen Tätigkeit bleibt vollständig gewährleistet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Vermeidung von Doppelspurigkeiten:&lt;/p&gt;&lt;p&gt;Die Aufgabenverteilung zwischen BAKOM, UVEK, interner Revision SRG und EFK ist klar abzustimmen und zu koordinieren, wie das bei vergleichbaren Unternehmen, welche der Aufsicht der EFK unterstehen (z.B. Post, Swisscom, SBB der Fall ist. Doppelspurigkeiten bei der Prüfung sollen vermieden werden, um den Prüfungsprozess effizient zu halten. Die Unabhängigkeit der EFK gemäss Finanzkontrollgesetz bleibt hierbei jederzeit gewahrt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Ergänzende Aufsicht durch die EFK:&lt;/p&gt;&lt;p&gt;Die bestehende Aufsicht durch UVEK/BAKOM und die aktienrechtliche Abschlussprüfung bleiben erhalten und werden nicht ersetzt. Die EFK wirkt bei der Prüfung gezielt ergänzend und wird selbständig und unabhängig dort eingesetzt, wo sie durch ihre Sonderstellung und Spezialisierung (z.B. Wirtschaftlichkeitsprüfungen) einen Mehrwert schaffen kann, wie zum Beispiel gegenüber internen Revisionen wo der Fokus selbst definiert wird.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Media e comunicazione</t>
   </si>
   <si>
     <t xml:space="preserve">25.4320</t>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20254774</v>
+        <v>20254794</v>
       </c>
       <c r="B17" t="s">
         <v>192</v>
@@ -5984,55 +5984,55 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F17" t="s">
         <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="I17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q17" t="s">
         <v>47</v>
       </c>
       <c r="R17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U17" t="s">
         <v>37</v>
@@ -6040,28 +6040,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20254794</v>
+        <v>20254774</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
         <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H18" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="I18" t="s">
         <v>207</v>
@@ -6144,7 +6144,7 @@
         <v>225</v>
       </c>
       <c r="N19" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O19" t="s">
         <v>226</v>
@@ -6209,7 +6209,7 @@
         <v>239</v>
       </c>
       <c r="N20" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O20" t="s">
         <v>240</v>
@@ -6274,7 +6274,7 @@
         <v>252</v>
       </c>
       <c r="N21" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O21" t="s">
         <v>253</v>
@@ -6469,7 +6469,7 @@
         <v>289</v>
       </c>
       <c r="N24" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O24" t="s">
         <v>290</v>
@@ -6495,7 +6495,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20258254</v>
+        <v>20258270</v>
       </c>
       <c r="B25" t="s">
         <v>292</v>
@@ -6504,53 +6504,53 @@
         <v>120</v>
       </c>
       <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" t="s">
         <v>293</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" t="s">
-        <v>294</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="I25" t="s">
+        <v>294</v>
+      </c>
+      <c r="J25" t="s">
         <v>295</v>
-      </c>
-      <c r="J25" t="s">
-        <v>296</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
+        <v>296</v>
+      </c>
+      <c r="M25" t="s">
         <v>297</v>
-      </c>
-      <c r="M25" t="s">
-        <v>298</v>
       </c>
       <c r="N25" t="s">
         <v>129</v>
       </c>
       <c r="O25" t="s">
+        <v>298</v>
+      </c>
+      <c r="P25" t="s">
         <v>299</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
+        <v>47</v>
+      </c>
+      <c r="R25" t="s">
         <v>300</v>
       </c>
-      <c r="Q25" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>301</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>302</v>
-      </c>
-      <c r="T25" t="s">
-        <v>303</v>
       </c>
       <c r="U25" t="s">
         <v>37</v>
@@ -6558,28 +6558,28 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20258270</v>
+        <v>20258254</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C26" t="s">
         <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>304</v>
       </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="I26" t="s">
         <v>305</v>
@@ -6604,7 +6604,7 @@
         <v>310</v>
       </c>
       <c r="Q26" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="R26" t="s">
         <v>311</v>
@@ -6636,7 +6636,7 @@
         <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20254263</v>
+        <v>20254317</v>
       </c>
       <c r="B29" t="s">
         <v>335</v>
@@ -6756,55 +6756,55 @@
         <v>22</v>
       </c>
       <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
         <v>336</v>
       </c>
-      <c r="E29" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I29" t="s">
         <v>337</v>
       </c>
-      <c r="G29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" t="s">
-        <v>124</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>338</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>339</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>340</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>341</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
+        <v>200</v>
+      </c>
+      <c r="O29" t="s">
         <v>342</v>
       </c>
-      <c r="N29" t="s">
-        <v>129</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>343</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
+        <v>47</v>
+      </c>
+      <c r="R29" t="s">
         <v>344</v>
       </c>
-      <c r="Q29" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>345</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>346</v>
-      </c>
-      <c r="T29" t="s">
-        <v>347</v>
       </c>
       <c r="U29" t="s">
         <v>37</v>
@@ -6812,28 +6812,28 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20254317</v>
+        <v>20254263</v>
       </c>
       <c r="B30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>348</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H30" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="I30" t="s">
         <v>349</v>
@@ -6851,7 +6851,7 @@
         <v>353</v>
       </c>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="O30" t="s">
         <v>354</v>
@@ -6860,7 +6860,7 @@
         <v>355</v>
       </c>
       <c r="Q30" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="R30" t="s">
         <v>356</v>
@@ -6892,7 +6892,7 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
@@ -6916,7 +6916,7 @@
         <v>365</v>
       </c>
       <c r="N31" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O31" t="s">
         <v>366</v>
@@ -6957,7 +6957,7 @@
         <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
@@ -6981,7 +6981,7 @@
         <v>373</v>
       </c>
       <c r="N32" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O32" t="s">
         <v>374</v>
@@ -7022,7 +7022,7 @@
         <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G33" t="s">
         <v>41</v>
@@ -7046,7 +7046,7 @@
         <v>381</v>
       </c>
       <c r="N33" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O33" t="s">
         <v>382</v>
@@ -7241,7 +7241,7 @@
         <v>416</v>
       </c>
       <c r="N36" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O36" t="s">
         <v>417</v>
@@ -7436,7 +7436,7 @@
         <v>456</v>
       </c>
       <c r="N39" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O39" t="s">
         <v>457</v>
@@ -7753,7 +7753,7 @@
         <v>511</v>
       </c>
       <c r="N44" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O44" t="s">
         <v>512</v>
@@ -7877,7 +7877,7 @@
         <v>536</v>
       </c>
       <c r="N46" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O46" t="s">
         <v>537</v>
@@ -7936,7 +7936,7 @@
         <v>546</v>
       </c>
       <c r="N47" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O47" t="s">
         <v>547</v>
@@ -8001,7 +8001,7 @@
         <v>558</v>
       </c>
       <c r="N48" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O48" t="s">
         <v>559</v>
@@ -8129,7 +8129,7 @@
         <v>583</v>
       </c>
       <c r="N50" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O50" t="s">
         <v>584</v>
@@ -8387,7 +8387,7 @@
         <v>628</v>
       </c>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O54" t="s">
         <v>629</v>
@@ -8517,7 +8517,7 @@
         <v>651</v>
       </c>
       <c r="N56" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O56" t="s">
         <v>652</v>
@@ -8582,7 +8582,7 @@
         <v>662</v>
       </c>
       <c r="N57" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O57" t="s">
         <v>663</v>
@@ -8647,7 +8647,7 @@
         <v>673</v>
       </c>
       <c r="N58" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O58" t="s">
         <v>674</v>
@@ -8840,7 +8840,7 @@
         <v>708</v>
       </c>
       <c r="N61" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O61" t="s">
         <v>709</v>
@@ -8905,7 +8905,7 @@
         <v>720</v>
       </c>
       <c r="N62" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O62" t="s">
         <v>721</v>
@@ -9035,7 +9035,7 @@
         <v>741</v>
       </c>
       <c r="N64" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O64" t="s">
         <v>742</v>
@@ -9165,7 +9165,7 @@
         <v>762</v>
       </c>
       <c r="N66" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O66" t="s">
         <v>763</v>
@@ -9468,7 +9468,7 @@
         <v>817</v>
       </c>
       <c r="N71" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O71" t="s">
         <v>818</v>
@@ -9515,7 +9515,7 @@
         <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="I72" t="s">
         <v>825</v>
@@ -9663,7 +9663,7 @@
         <v>852</v>
       </c>
       <c r="N74" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O74" t="s">
         <v>853</v>
@@ -9728,7 +9728,7 @@
         <v>864</v>
       </c>
       <c r="N75" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O75" t="s">
         <v>865</v>
@@ -9858,7 +9858,7 @@
         <v>888</v>
       </c>
       <c r="N77" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O77" t="s">
         <v>889</v>
@@ -9963,7 +9963,7 @@
         <v>124</v>
       </c>
       <c r="I79" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="J79" t="s">
         <v>905</v>
@@ -9990,13 +9990,13 @@
         <v>33</v>
       </c>
       <c r="R79" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="S79" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="T79" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="U79" t="s">
         <v>37</v>
@@ -10346,7 +10346,7 @@
         <v>971</v>
       </c>
       <c r="N85" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O85" t="s">
         <v>972</v>
@@ -10411,7 +10411,7 @@
         <v>984</v>
       </c>
       <c r="N86" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O86" t="s">
         <v>985</v>
@@ -10606,7 +10606,7 @@
         <v>1017</v>
       </c>
       <c r="N89" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O89" t="s">
         <v>1018</v>
@@ -10671,7 +10671,7 @@
         <v>1027</v>
       </c>
       <c r="N90" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O90" t="s">
         <v>1028</v>
@@ -10683,13 +10683,13 @@
         <v>153</v>
       </c>
       <c r="R90" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="S90" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="T90" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="U90" t="s">
         <v>37</v>
@@ -11116,7 +11116,7 @@
         <v>1078</v>
       </c>
       <c r="N97" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O97" t="s">
         <v>1079</v>
@@ -11246,7 +11246,7 @@
         <v>1099</v>
       </c>
       <c r="N99" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O99" t="s">
         <v>1100</v>
@@ -11258,13 +11258,13 @@
         <v>33</v>
       </c>
       <c r="R99" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="S99" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="T99" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="U99" t="s">
         <v>37</v>
@@ -11311,7 +11311,7 @@
         <v>1108</v>
       </c>
       <c r="N100" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O100" t="s">
         <v>1109</v>
@@ -11437,7 +11437,7 @@
         <v>1131</v>
       </c>
       <c r="N102" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O102" t="s">
         <v>1132</v>
@@ -11502,7 +11502,7 @@
         <v>1143</v>
       </c>
       <c r="N103" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O103" t="s">
         <v>1144</v>
@@ -11632,7 +11632,7 @@
         <v>1163</v>
       </c>
       <c r="N105" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O105" t="s">
         <v>1164</v>
@@ -12018,7 +12018,7 @@
         <v>1224</v>
       </c>
       <c r="N111" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="O111" t="s">
         <v>1225</v>
@@ -12459,7 +12459,7 @@
         <v>1299</v>
       </c>
       <c r="N118" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O118" t="s">
         <v>1300</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -455,15 +455,39 @@
     <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Energia</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sollberger Sandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.7151</t>
   </si>
   <si>
     <t xml:space="preserve">Feller Olivier</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">EJPD</t>
   </si>
   <si>
@@ -495,30 +519,6 @@
   </si>
   <si>
     <t xml:space="preserve">Economia|Diritto penale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sollberger Sandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
   </si>
   <si>
     <t xml:space="preserve">26.030</t>
@@ -5797,19 +5797,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20267151</v>
+        <v>20263069</v>
       </c>
       <c r="B13" t="s">
         <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
         <v>149</v>
@@ -5817,42 +5817,42 @@
       <c r="G13" t="s">
         <v>25</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13"/>
+      <c r="I13" t="s">
         <v>150</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>151</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" t="s">
         <v>152</v>
       </c>
-      <c r="K13"/>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>153</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" t="s">
         <v>154</v>
       </c>
-      <c r="N13" t="s">
-        <v>129</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>155</v>
       </c>
-      <c r="P13" t="s">
-        <v>156</v>
-      </c>
       <c r="Q13" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="R13" t="s">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="S13" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="T13" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="U13" t="s">
         <v>37</v>
@@ -5860,19 +5860,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263069</v>
+        <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
         <v>149</v>
@@ -5880,42 +5880,42 @@
       <c r="G14" t="s">
         <v>25</v>
       </c>
-      <c r="H14"/>
+      <c r="H14" t="s">
+        <v>158</v>
+      </c>
       <c r="I14" t="s">
+        <v>159</v>
+      </c>
+      <c r="J14" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14" t="s">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s">
+        <v>162</v>
+      </c>
+      <c r="N14" t="s">
+        <v>129</v>
+      </c>
+      <c r="O14" t="s">
         <v>163</v>
       </c>
-      <c r="J14" t="s">
+      <c r="P14" t="s">
         <v>164</v>
       </c>
-      <c r="K14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="Q14" t="s">
         <v>165</v>
       </c>
-      <c r="M14" t="s">
+      <c r="R14" t="s">
         <v>166</v>
       </c>
-      <c r="N14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>167</v>
       </c>
-      <c r="P14" t="s">
+      <c r="T14" t="s">
         <v>168</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" t="s">
-        <v>59</v>
-      </c>
-      <c r="S14" t="s">
-        <v>60</v>
-      </c>
-      <c r="T14" t="s">
-        <v>61</v>
       </c>
       <c r="U14" t="s">
         <v>37</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I15" t="s">
         <v>172</v>
@@ -6190,7 +6190,7 @@
         <v>41</v>
       </c>
       <c r="H19" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I19" t="s">
         <v>219</v>
@@ -6347,7 +6347,7 @@
         <v>253</v>
       </c>
       <c r="Q21" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R21" t="s">
         <v>254</v>
@@ -6450,7 +6450,7 @@
         <v>41</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I23" t="s">
         <v>271</v>
@@ -6542,7 +6542,7 @@
         <v>291</v>
       </c>
       <c r="Q24" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R24" t="s">
         <v>292</v>
@@ -6607,7 +6607,7 @@
         <v>303</v>
       </c>
       <c r="Q25" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R25" t="s">
         <v>201</v>
@@ -6836,7 +6836,7 @@
         <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I29" t="s">
         <v>339</v>
@@ -7444,7 +7444,7 @@
         <v>440</v>
       </c>
       <c r="Q38" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R38" t="s">
         <v>441</v>
@@ -7765,7 +7765,7 @@
         <v>500</v>
       </c>
       <c r="Q43" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R43" t="s">
         <v>501</v>
@@ -7866,7 +7866,7 @@
         <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
         <v>517</v>
@@ -8139,7 +8139,7 @@
         <v>570</v>
       </c>
       <c r="Q49" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R49" t="s">
         <v>571</v>
@@ -8397,7 +8397,7 @@
         <v>619</v>
       </c>
       <c r="Q53" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R53" t="s">
         <v>620</v>
@@ -8785,7 +8785,7 @@
         <v>686</v>
       </c>
       <c r="Q59" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R59" t="s">
         <v>687</v>
@@ -9108,7 +9108,7 @@
         <v>744</v>
       </c>
       <c r="Q64" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R64" t="s">
         <v>481</v>
@@ -9303,7 +9303,7 @@
         <v>774</v>
       </c>
       <c r="Q67" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R67" t="s">
         <v>775</v>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G70"/>
       <c r="H70" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I70" t="s">
         <v>554</v>
@@ -9514,7 +9514,7 @@
         <v>41</v>
       </c>
       <c r="H71" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I71" t="s">
         <v>812</v>
@@ -9736,7 +9736,7 @@
         <v>853</v>
       </c>
       <c r="Q74" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R74" t="s">
         <v>854</v>
@@ -9839,7 +9839,7 @@
         <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I76" t="s">
         <v>870</v>
@@ -9866,7 +9866,7 @@
         <v>876</v>
       </c>
       <c r="Q76" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R76" t="s">
         <v>877</v>
@@ -10061,7 +10061,7 @@
         <v>912</v>
       </c>
       <c r="Q79" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R79" t="s">
         <v>913</v>
@@ -10219,7 +10219,7 @@
         <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I82" t="s">
         <v>936</v>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="G84"/>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I84" t="s">
         <v>956</v>
@@ -10549,7 +10549,7 @@
         <v>995</v>
       </c>
       <c r="Q87" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R87" t="s">
         <v>996</v>
@@ -10614,7 +10614,7 @@
         <v>1008</v>
       </c>
       <c r="Q88" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R88" t="s">
         <v>1009</v>
@@ -10874,7 +10874,7 @@
         <v>1051</v>
       </c>
       <c r="Q92" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R92" t="s">
         <v>334</v>
@@ -10912,7 +10912,7 @@
         <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I93" t="s">
         <v>1054</v>
@@ -11103,7 +11103,7 @@
         <v>25</v>
       </c>
       <c r="H96" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I96" t="s">
         <v>1078</v>
@@ -11166,7 +11166,7 @@
         <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I97" t="s">
         <v>1078</v>
@@ -11229,7 +11229,7 @@
         <v>25</v>
       </c>
       <c r="H98" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I98" t="s">
         <v>1078</v>
@@ -11514,7 +11514,7 @@
         <v>1132</v>
       </c>
       <c r="Q102" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R102" t="s">
         <v>1133</v>
@@ -11640,7 +11640,7 @@
         <v>1155</v>
       </c>
       <c r="Q104" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R104" t="s">
         <v>1156</v>
@@ -11705,7 +11705,7 @@
         <v>1167</v>
       </c>
       <c r="Q105" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R105" t="s">
         <v>1168</v>
@@ -11835,7 +11835,7 @@
         <v>1187</v>
       </c>
       <c r="Q107" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R107" t="s">
         <v>1188</v>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="G114"/>
       <c r="H114" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I114" t="s">
         <v>1251</v>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="G115"/>
       <c r="H115" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I115" t="s">
         <v>1262</v>
@@ -12597,7 +12597,7 @@
         <v>1314</v>
       </c>
       <c r="Q119" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R119" t="s">
         <v>1145</v>
@@ -12727,7 +12727,7 @@
         <v>1336</v>
       </c>
       <c r="Q121" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R121" t="s">
         <v>1337</v>
@@ -12922,7 +12922,7 @@
         <v>1369</v>
       </c>
       <c r="Q124" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R124" t="s">
         <v>1370</v>
@@ -12987,7 +12987,7 @@
         <v>1382</v>
       </c>
       <c r="Q125" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R125" t="s">
         <v>698</v>
@@ -13436,7 +13436,7 @@
         <v>1448</v>
       </c>
       <c r="Q132" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R132" t="s">
         <v>1449</v>
@@ -13501,7 +13501,7 @@
         <v>1459</v>
       </c>
       <c r="Q133" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R133" t="s">
         <v>1460</v>
@@ -13566,7 +13566,7 @@
         <v>1472</v>
       </c>
       <c r="Q134" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R134" t="s">
         <v>1473</v>
@@ -13631,7 +13631,7 @@
         <v>1478</v>
       </c>
       <c r="Q135" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R135" t="s">
         <v>1479</v>
@@ -13696,7 +13696,7 @@
         <v>1491</v>
       </c>
       <c r="Q136" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R136" t="s">
         <v>481</v>
@@ -13889,7 +13889,7 @@
         <v>1523</v>
       </c>
       <c r="Q139" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R139" t="s">
         <v>1513</v>
@@ -14078,7 +14078,7 @@
         <v>1547</v>
       </c>
       <c r="Q142" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="R142" t="s">
         <v>1548</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -9650,7 +9650,7 @@
         <v>871</v>
       </c>
       <c r="N75" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="O75" t="s">
         <v>872</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1516">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -320,6 +320,9 @@
     <t xml:space="preserve">Von Dänemark lernen: Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
   </si>
   <si>
+    <t xml:space="preserve">Imparare dalla Danimarca: espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
@@ -416,6 +419,33 @@
     <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Energia</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sollberger Sandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.7151</t>
   </si>
   <si>
@@ -425,9 +455,6 @@
     <t xml:space="preserve">PLR</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">EJPD</t>
   </si>
   <si>
@@ -461,30 +488,6 @@
     <t xml:space="preserve">Economia|Diritto penale</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sollberger Sandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.030</t>
   </si>
   <si>
@@ -650,7 +653,7 @@
     <t xml:space="preserve">pvl</t>
   </si>
   <si>
-    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA Optimierungen durch die Kantone?</t>
+    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA-Optimierungen durch die Kantone?</t>
   </si>
   <si>
     <t xml:space="preserve">Les facturations provisoires de l’impôt manquantes permettent-elles aux cantons d'optimiser la RPT ?</t>
@@ -5433,32 +5436,32 @@
         <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="L9"/>
       <c r="M9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="s">
         <v>30</v>
       </c>
       <c r="O9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q9" t="s">
         <v>33</v>
       </c>
       <c r="R9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U9" t="s">
         <v>37</v>
@@ -5469,10 +5472,10 @@
         <v>20263099</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -5481,7 +5484,7 @@
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -5491,35 +5494,35 @@
         <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M10"/>
       <c r="N10" t="s">
         <v>30</v>
       </c>
       <c r="O10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q10" t="s">
         <v>47</v>
       </c>
       <c r="R10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U10" t="s">
         <v>37</v>
@@ -5530,59 +5533,59 @@
         <v>20267194</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11"/>
       <c r="L11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q11" t="s">
         <v>47</v>
       </c>
       <c r="R11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U11" t="s">
         <v>37</v>
@@ -5590,19 +5593,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20267151</v>
+        <v>20263069</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
         <v>137</v>
@@ -5610,42 +5613,42 @@
       <c r="G12" t="s">
         <v>25</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12"/>
+      <c r="I12" t="s">
         <v>138</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>139</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s">
         <v>140</v>
       </c>
-      <c r="K12"/>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>141</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
         <v>142</v>
       </c>
-      <c r="N12" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>143</v>
       </c>
-      <c r="P12" t="s">
-        <v>144</v>
-      </c>
       <c r="Q12" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="R12" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="S12" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="T12" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="U12" t="s">
         <v>37</v>
@@ -5653,19 +5656,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263069</v>
+        <v>20267151</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="F13" t="s">
         <v>137</v>
@@ -5673,42 +5676,42 @@
       <c r="G13" t="s">
         <v>25</v>
       </c>
-      <c r="H13"/>
+      <c r="H13" t="s">
+        <v>147</v>
+      </c>
       <c r="I13" t="s">
+        <v>148</v>
+      </c>
+      <c r="J13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13"/>
+      <c r="L13" t="s">
+        <v>150</v>
+      </c>
+      <c r="M13" t="s">
         <v>151</v>
       </c>
-      <c r="J13" t="s">
+      <c r="N13" t="s">
+        <v>129</v>
+      </c>
+      <c r="O13" t="s">
         <v>152</v>
       </c>
-      <c r="K13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="P13" t="s">
         <v>153</v>
       </c>
-      <c r="M13" t="s">
+      <c r="Q13" t="s">
         <v>154</v>
       </c>
-      <c r="N13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>155</v>
       </c>
-      <c r="P13" t="s">
+      <c r="S13" t="s">
         <v>156</v>
       </c>
-      <c r="Q13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" t="s">
-        <v>59</v>
-      </c>
-      <c r="S13" t="s">
-        <v>60</v>
-      </c>
       <c r="T13" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="U13" t="s">
         <v>37</v>
@@ -5719,51 +5722,51 @@
         <v>20260030</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q14" t="s">
         <v>47</v>
       </c>
       <c r="R14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U14" t="s">
         <v>37</v>
@@ -5774,59 +5777,59 @@
         <v>20267032</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
         <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K15"/>
       <c r="L15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q15" t="s">
         <v>33</v>
       </c>
       <c r="R15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U15" t="s">
         <v>37</v>
@@ -5837,59 +5840,59 @@
         <v>20263006</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q16" t="s">
         <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U16" t="s">
         <v>37</v>
@@ -5900,7 +5903,7 @@
         <v>20254774</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -5912,49 +5915,49 @@
         <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G17" t="s">
         <v>41</v>
       </c>
       <c r="H17" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q17" t="s">
         <v>47</v>
       </c>
       <c r="R17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U17" t="s">
         <v>37</v>
@@ -5965,61 +5968,61 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U18" t="s">
         <v>37</v>
@@ -6030,61 +6033,61 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s">
         <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q19" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U19" t="s">
         <v>37</v>
@@ -6095,7 +6098,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -6107,49 +6110,49 @@
         <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q20" t="s">
         <v>47</v>
       </c>
       <c r="R20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U20" t="s">
         <v>37</v>
@@ -6160,10 +6163,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
         <v>93</v>
@@ -6172,49 +6175,49 @@
         <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G21" t="s">
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q21" t="s">
         <v>47</v>
       </c>
       <c r="R21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U21" t="s">
         <v>37</v>
@@ -6225,61 +6228,61 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" t="s">
         <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G22" t="s">
         <v>41</v>
       </c>
       <c r="H22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q22" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="U22" t="s">
         <v>37</v>
@@ -6290,7 +6293,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -6302,49 +6305,49 @@
         <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q23" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U23" t="s">
         <v>37</v>
@@ -6355,61 +6358,61 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C24" t="s">
         <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
         <v>40</v>
       </c>
       <c r="F24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O24" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P24" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q24" t="s">
         <v>47</v>
       </c>
       <c r="R24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U24" t="s">
         <v>37</v>
@@ -6420,59 +6423,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E25" t="s">
         <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q25" t="s">
         <v>33</v>
       </c>
       <c r="R25" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U25" t="s">
         <v>37</v>
@@ -6483,59 +6486,59 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E26" t="s">
         <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q26" t="s">
         <v>33</v>
       </c>
       <c r="R26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U26" t="s">
         <v>37</v>
@@ -6546,59 +6549,59 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J27" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L27" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q27" t="s">
         <v>33</v>
       </c>
       <c r="R27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="U27" t="s">
         <v>37</v>
@@ -6609,61 +6612,61 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E28" t="s">
         <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G28" t="s">
         <v>41</v>
       </c>
       <c r="H28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J28" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O28" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q28" t="s">
         <v>33</v>
       </c>
       <c r="R28" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T28" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U28" t="s">
         <v>37</v>
@@ -6674,61 +6677,61 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E29" t="s">
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q29" t="s">
         <v>33</v>
       </c>
       <c r="R29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U29" t="s">
         <v>37</v>
@@ -6739,7 +6742,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C30" t="s">
         <v>52</v>
@@ -6751,40 +6754,40 @@
         <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L30" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R30" t="s">
         <v>59</v>
@@ -6804,7 +6807,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -6816,49 +6819,49 @@
         <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G31" t="s">
         <v>41</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I31" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L31" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M31" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O31" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P31" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q31" t="s">
         <v>47</v>
       </c>
       <c r="R31" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="T31" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="U31" t="s">
         <v>37</v>
@@ -6869,61 +6872,61 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C32" t="s">
         <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E32" t="s">
         <v>94</v>
       </c>
       <c r="F32" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K32" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P32" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U32" t="s">
         <v>37</v>
@@ -6934,7 +6937,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C33" t="s">
         <v>52</v>
@@ -6946,49 +6949,49 @@
         <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G33" t="s">
         <v>41</v>
       </c>
       <c r="H33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J33" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O33" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P33" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R33" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="T33" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="U33" t="s">
         <v>37</v>
@@ -6999,61 +7002,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C34" t="s">
         <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E34" t="s">
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I34" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J34" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K34" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L34" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M34" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O34" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P34" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q34" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R34" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="S34" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="T34" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="U34" t="s">
         <v>37</v>
@@ -7064,61 +7067,61 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C35" t="s">
         <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E35" t="s">
         <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G35" t="s">
         <v>41</v>
       </c>
       <c r="H35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I35" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J35" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K35" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L35" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M35" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P35" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R35" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="S35" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T35" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="U35" t="s">
         <v>37</v>
@@ -7129,10 +7132,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C36" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D36" t="s">
         <v>53</v>
@@ -7141,49 +7144,49 @@
         <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I36" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J36" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K36" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L36" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M36" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N36" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O36" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P36" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q36" t="s">
         <v>47</v>
       </c>
       <c r="R36" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="S36" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="T36" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U36" t="s">
         <v>37</v>
@@ -7194,61 +7197,61 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C37" t="s">
         <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F37" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I37" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J37" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K37" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L37" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M37" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O37" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P37" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q37" t="s">
         <v>33</v>
       </c>
       <c r="R37" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S37" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T37" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U37" t="s">
         <v>37</v>
@@ -7259,59 +7262,59 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E38" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F38" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I38" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J38" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M38" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P38" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U38" t="s">
         <v>37</v>
@@ -7322,59 +7325,59 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E39" t="s">
         <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I39" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J39" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M39" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O39" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P39" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q39" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R39" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="S39" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="T39" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="U39" t="s">
         <v>37</v>
@@ -7385,59 +7388,59 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E40" t="s">
         <v>54</v>
       </c>
       <c r="F40" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I40" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J40" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M40" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O40" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P40" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R40" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="S40" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="T40" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="U40" t="s">
         <v>37</v>
@@ -7448,61 +7451,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C41" t="s">
         <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E41" t="s">
         <v>54</v>
       </c>
       <c r="F41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I41" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K41" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L41" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M41" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N41" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O41" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P41" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q41" t="s">
         <v>33</v>
       </c>
       <c r="R41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="S41" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="T41" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="U41" t="s">
         <v>37</v>
@@ -7513,59 +7516,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E42" t="s">
         <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I42" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J42" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M42" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O42" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P42" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q42" t="s">
         <v>33</v>
       </c>
       <c r="R42" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="S42" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T42" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="U42" t="s">
         <v>37</v>
@@ -7576,45 +7579,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C43" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D43" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I43" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J43" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K43" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L43" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M43" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O43" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P43" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q43" t="s">
         <v>33</v>
@@ -7631,61 +7634,61 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C44" t="s">
         <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E44" t="s">
         <v>40</v>
       </c>
       <c r="F44" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I44" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J44" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K44" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L44" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M44" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O44" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P44" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q44" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R44" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T44" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="U44" t="s">
         <v>37</v>
@@ -7696,61 +7699,61 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C45" t="s">
         <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E45" t="s">
         <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I45" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J45" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K45" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L45" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M45" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O45" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P45" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q45" t="s">
         <v>33</v>
       </c>
       <c r="R45" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="S45" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="T45" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="U45" t="s">
         <v>37</v>
@@ -7761,61 +7764,61 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E46" t="s">
         <v>94</v>
       </c>
       <c r="F46" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I46" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J46" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K46" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L46" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M46" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N46" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O46" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P46" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q46" t="s">
         <v>33</v>
       </c>
       <c r="R46" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S46" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T46" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U46" t="s">
         <v>37</v>
@@ -7826,7 +7829,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C47" t="s">
         <v>22</v>
@@ -7836,49 +7839,49 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I47" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J47" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K47" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L47" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M47" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O47" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P47" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R47" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="S47" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="T47" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="U47" t="s">
         <v>37</v>
@@ -7889,61 +7892,61 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C48" t="s">
         <v>52</v>
       </c>
       <c r="D48" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E48" t="s">
         <v>40</v>
       </c>
       <c r="F48" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
       </c>
       <c r="H48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J48" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K48" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L48" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M48" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O48" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P48" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Q48" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R48" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="S48" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T48" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="U48" t="s">
         <v>37</v>
@@ -7954,52 +7957,52 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C49" t="s">
         <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E49" t="s">
         <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I49" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J49" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K49" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L49" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M49" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O49" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P49" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R49" t="s">
         <v>59</v>
@@ -8019,59 +8022,59 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I50" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J50" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K50" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L50" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M50" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O50" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P50" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Q50" t="s">
         <v>33</v>
       </c>
       <c r="R50" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="S50" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="T50" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="U50" t="s">
         <v>37</v>
@@ -8082,61 +8085,61 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C51" t="s">
         <v>52</v>
       </c>
       <c r="D51" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E51" t="s">
         <v>74</v>
       </c>
       <c r="F51" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I51" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J51" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K51" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L51" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M51" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O51" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P51" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Q51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R51" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="S51" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="T51" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="U51" t="s">
         <v>37</v>
@@ -8147,61 +8150,61 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C52" t="s">
         <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E52" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F52" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G52" t="s">
         <v>41</v>
       </c>
       <c r="H52" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I52" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J52" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K52" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L52" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M52" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O52" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P52" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Q52" t="s">
         <v>33</v>
       </c>
       <c r="R52" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S52" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T52" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="U52" t="s">
         <v>37</v>
@@ -8212,49 +8215,49 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C53" t="s">
         <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E53" t="s">
         <v>54</v>
       </c>
       <c r="F53" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
       </c>
       <c r="H53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I53" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J53" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K53" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L53" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M53" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O53" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P53" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Q53" t="s">
         <v>33</v>
@@ -8277,61 +8280,61 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
       </c>
       <c r="D54" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E54" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F54" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
       </c>
       <c r="H54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J54" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K54" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L54" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M54" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O54" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P54" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q54" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R54" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="S54" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="T54" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="U54" t="s">
         <v>37</v>
@@ -8342,61 +8345,61 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E55" t="s">
         <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
       </c>
       <c r="H55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I55" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J55" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K55" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L55" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M55" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O55" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P55" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R55" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S55" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T55" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U55" t="s">
         <v>37</v>
@@ -8407,59 +8410,59 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C56" t="s">
         <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
       </c>
       <c r="H56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I56" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J56" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K56" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L56" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M56" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N56" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O56" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P56" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R56" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S56" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T56" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U56" t="s">
         <v>37</v>
@@ -8470,61 +8473,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E57" t="s">
         <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
       </c>
       <c r="H57" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I57" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J57" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K57" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L57" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M57" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O57" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P57" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Q57" t="s">
         <v>33</v>
       </c>
       <c r="R57" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="S57" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="T57" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="U57" t="s">
         <v>37</v>
@@ -8535,61 +8538,61 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C58" t="s">
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E58" t="s">
         <v>94</v>
       </c>
       <c r="F58" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
       </c>
       <c r="H58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I58" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J58" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="K58" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L58" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M58" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N58" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O58" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P58" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q58" t="s">
         <v>33</v>
       </c>
       <c r="R58" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S58" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="T58" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="U58" t="s">
         <v>37</v>
@@ -8600,61 +8603,61 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C59" t="s">
         <v>52</v>
       </c>
       <c r="D59" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E59" t="s">
         <v>74</v>
       </c>
       <c r="F59" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
       </c>
       <c r="H59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I59" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J59" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K59" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L59" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M59" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N59" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O59" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P59" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Q59" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R59" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S59" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T59" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U59" t="s">
         <v>37</v>
@@ -8665,61 +8668,61 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E60" t="s">
         <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G60" t="s">
         <v>41</v>
       </c>
       <c r="H60" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I60" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J60" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="K60" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L60" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M60" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O60" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P60" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R60" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="S60" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="T60" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="U60" t="s">
         <v>37</v>
@@ -8730,7 +8733,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C61" t="s">
         <v>22</v>
@@ -8742,49 +8745,49 @@
         <v>94</v>
       </c>
       <c r="F61" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G61" t="s">
         <v>41</v>
       </c>
       <c r="H61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I61" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J61" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K61" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L61" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M61" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O61" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P61" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Q61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R61" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S61" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T61" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U61" t="s">
         <v>37</v>
@@ -8795,61 +8798,61 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C62" t="s">
         <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E62" t="s">
         <v>94</v>
       </c>
       <c r="F62" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G62" t="s">
         <v>41</v>
       </c>
       <c r="H62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I62" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J62" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K62" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L62" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M62" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N62" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O62" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P62" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q62" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R62" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="S62" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="T62" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="U62" t="s">
         <v>37</v>
@@ -8860,61 +8863,61 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C63" t="s">
         <v>52</v>
       </c>
       <c r="D63" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E63" t="s">
         <v>40</v>
       </c>
       <c r="F63" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
       </c>
       <c r="H63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I63" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J63" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="K63" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L63" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M63" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O63" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P63" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Q63" t="s">
         <v>33</v>
       </c>
       <c r="R63" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="S63" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="T63" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="U63" t="s">
         <v>37</v>
@@ -8925,45 +8928,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C64" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D64" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I64" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J64" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K64" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L64" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M64" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N64" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O64" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="P64" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="Q64" t="s">
         <v>33</v>
@@ -8980,45 +8983,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C65" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D65" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I65" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J65" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K65" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L65" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M65" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N65" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O65" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P65" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="Q65" t="s">
         <v>33</v>
@@ -9035,59 +9038,59 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C66" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D66" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G66" t="s">
         <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I66" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J66" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="K66" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L66" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M66" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N66" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O66" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P66" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Q66" t="s">
         <v>33</v>
       </c>
       <c r="R66" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="S66" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="T66" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="U66" t="s">
         <v>37</v>
@@ -9098,61 +9101,61 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C67" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D67" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E67" t="s">
         <v>40</v>
       </c>
       <c r="F67" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
       </c>
       <c r="H67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I67" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J67" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="K67" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L67" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M67" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O67" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P67" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Q67" t="s">
         <v>33</v>
       </c>
       <c r="R67" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="S67" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="T67" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="U67" t="s">
         <v>37</v>
@@ -9163,61 +9166,61 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C68" t="s">
         <v>52</v>
       </c>
       <c r="D68" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E68" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F68" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
       </c>
       <c r="H68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I68" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J68" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="K68" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L68" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M68" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O68" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P68" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Q68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R68" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="S68" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="T68" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="U68" t="s">
         <v>37</v>
@@ -9228,61 +9231,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C69" t="s">
         <v>52</v>
       </c>
       <c r="D69" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E69" t="s">
         <v>94</v>
       </c>
       <c r="F69" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
       </c>
       <c r="H69" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I69" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="J69" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="K69" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="L69" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M69" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O69" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P69" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="Q69" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R69" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S69" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="T69" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="U69" t="s">
         <v>37</v>
@@ -9293,61 +9296,61 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E70" t="s">
         <v>74</v>
       </c>
       <c r="F70" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
       </c>
       <c r="H70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I70" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J70" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K70" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="L70" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M70" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N70" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O70" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P70" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="Q70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R70" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S70" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="T70" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="U70" t="s">
         <v>37</v>
@@ -9358,61 +9361,61 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E71" t="s">
         <v>40</v>
       </c>
       <c r="F71" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
       </c>
       <c r="H71" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I71" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J71" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="K71" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="L71" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M71" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O71" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P71" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="Q71" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R71" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="S71" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="T71" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="U71" t="s">
         <v>37</v>
@@ -9423,61 +9426,61 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C72" t="s">
         <v>52</v>
       </c>
       <c r="D72" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E72" t="s">
         <v>40</v>
       </c>
       <c r="F72" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I72" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J72" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K72" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L72" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M72" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N72" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O72" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P72" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R72" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="S72" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="T72" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="U72" t="s">
         <v>37</v>
@@ -9488,61 +9491,61 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C73" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E73" t="s">
         <v>94</v>
       </c>
       <c r="F73" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I73" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J73" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K73" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="L73" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M73" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O73" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="P73" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q73" t="s">
         <v>33</v>
       </c>
       <c r="R73" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="S73" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="T73" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="U73" t="s">
         <v>37</v>
@@ -9553,61 +9556,61 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C74" t="s">
         <v>52</v>
       </c>
       <c r="D74" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E74" t="s">
         <v>40</v>
       </c>
       <c r="F74" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I74" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J74" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K74" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="L74" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M74" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O74" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="P74" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q74" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R74" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S74" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="T74" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="U74" t="s">
         <v>37</v>
@@ -9618,45 +9621,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D75" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I75" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J75" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="K75" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L75" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M75" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N75" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O75" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="P75" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q75" t="s">
         <v>33</v>
@@ -9673,7 +9676,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C76" t="s">
         <v>22</v>
@@ -9685,49 +9688,49 @@
         <v>54</v>
       </c>
       <c r="F76" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I76" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J76" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K76" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L76" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M76" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O76" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="P76" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="Q76" t="s">
         <v>33</v>
       </c>
       <c r="R76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U76" t="s">
         <v>37</v>
@@ -9738,59 +9741,59 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D77" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E77" t="s">
         <v>54</v>
       </c>
       <c r="F77" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I77" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J77" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M77" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N77" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O77" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P77" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="Q77" t="s">
         <v>33</v>
       </c>
       <c r="R77" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="S77" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="T77" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="U77" t="s">
         <v>37</v>
@@ -9801,59 +9804,59 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D78" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E78" t="s">
         <v>40</v>
       </c>
       <c r="F78" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="G78" t="s">
         <v>25</v>
       </c>
       <c r="H78" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I78" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J78" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M78" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N78" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O78" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="P78" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="Q78" t="s">
         <v>33</v>
       </c>
       <c r="R78" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="S78" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="T78" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="U78" t="s">
         <v>37</v>
@@ -9864,51 +9867,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I79" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J79" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="K79" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O79" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="P79" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
       </c>
       <c r="R79" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="S79" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="T79" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="U79" t="s">
         <v>37</v>
@@ -9919,57 +9922,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C80" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D80" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I80" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J80" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="K80" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L80" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M80" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N80" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O80" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="P80" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="Q80" t="s">
         <v>33</v>
       </c>
       <c r="R80" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="S80" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="T80" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="U80" t="s">
         <v>37</v>
@@ -9980,57 +9983,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C81" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D81" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I81" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J81" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="K81" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L81" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M81" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="N81" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O81" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="P81" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="Q81" t="s">
         <v>33</v>
       </c>
       <c r="R81" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="S81" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="T81" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="U81" t="s">
         <v>37</v>
@@ -10041,61 +10044,61 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
       </c>
       <c r="D82" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E82" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F82" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G82" t="s">
         <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I82" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="J82" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K82" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="L82" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M82" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="N82" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O82" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="P82" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="Q82" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R82" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="S82" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="T82" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="U82" t="s">
         <v>37</v>
@@ -10106,61 +10109,61 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C83" t="s">
         <v>22</v>
       </c>
       <c r="D83" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E83" t="s">
         <v>94</v>
       </c>
       <c r="F83" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G83" t="s">
         <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I83" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J83" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K83" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="L83" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M83" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="N83" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O83" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="P83" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="Q83" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R83" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="S83" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="T83" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="U83" t="s">
         <v>37</v>
@@ -10171,61 +10174,61 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C84" t="s">
         <v>52</v>
       </c>
       <c r="D84" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E84" t="s">
         <v>54</v>
       </c>
       <c r="F84" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G84" t="s">
         <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I84" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="J84" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="K84" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="L84" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M84" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="N84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O84" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="P84" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q84" t="s">
         <v>33</v>
       </c>
       <c r="R84" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="S84" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="T84" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="U84" t="s">
         <v>37</v>
@@ -10236,61 +10239,61 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C85" t="s">
         <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E85" t="s">
         <v>40</v>
       </c>
       <c r="F85" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G85" t="s">
         <v>25</v>
       </c>
       <c r="H85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I85" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="J85" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="K85" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="L85" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M85" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="N85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O85" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P85" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Q85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R85" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="S85" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="T85" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="U85" t="s">
         <v>37</v>
@@ -10301,61 +10304,61 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C86" t="s">
         <v>52</v>
       </c>
       <c r="D86" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E86" t="s">
         <v>94</v>
       </c>
       <c r="F86" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G86" t="s">
         <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I86" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="J86" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="K86" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="L86" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M86" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O86" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="P86" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="Q86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R86" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S86" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T86" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="U86" t="s">
         <v>37</v>
@@ -10366,61 +10369,61 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C87" t="s">
         <v>22</v>
       </c>
       <c r="D87" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E87" t="s">
         <v>74</v>
       </c>
       <c r="F87" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G87" t="s">
         <v>25</v>
       </c>
       <c r="H87" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I87" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J87" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="K87" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="L87" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M87" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="N87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O87" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P87" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="Q87" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R87" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S87" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T87" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U87" t="s">
         <v>37</v>
@@ -10431,59 +10434,59 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C88" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E88" t="s">
         <v>54</v>
       </c>
       <c r="F88" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G88" t="s">
         <v>25</v>
       </c>
       <c r="H88" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I88" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="J88" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M88" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="N88" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O88" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="P88" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="Q88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U88" t="s">
         <v>37</v>
@@ -10494,7 +10497,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C89" t="s">
         <v>52</v>
@@ -10506,40 +10509,40 @@
         <v>74</v>
       </c>
       <c r="F89" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
       </c>
       <c r="H89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I89" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="J89" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K89" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L89" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M89" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="N89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O89" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="P89" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="Q89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R89" t="s">
         <v>59</v>
@@ -10559,59 +10562,59 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D90" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E90" t="s">
         <v>94</v>
       </c>
       <c r="F90" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G90" t="s">
         <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I90" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J90" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M90" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N90" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O90" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="P90" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q90" t="s">
         <v>33</v>
       </c>
       <c r="R90" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S90" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T90" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U90" t="s">
         <v>37</v>
@@ -10622,59 +10625,59 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C91" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E91" t="s">
         <v>54</v>
       </c>
       <c r="F91" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G91" t="s">
         <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I91" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J91" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="M91" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="N91" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O91" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="P91" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R91" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S91" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T91" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U91" t="s">
         <v>37</v>
@@ -10685,59 +10688,59 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C92" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D92" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E92" t="s">
         <v>54</v>
       </c>
       <c r="F92" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G92" t="s">
         <v>25</v>
       </c>
       <c r="H92" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I92" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J92" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M92" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="N92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O92" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="P92" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="Q92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T92" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U92" t="s">
         <v>37</v>
@@ -10748,59 +10751,59 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C93" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E93" t="s">
         <v>54</v>
       </c>
       <c r="F93" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G93" t="s">
         <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I93" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J93" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M93" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="N93" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O93" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P93" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="Q93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R93" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T93" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U93" t="s">
         <v>37</v>
@@ -10811,61 +10814,61 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C94" t="s">
         <v>52</v>
       </c>
       <c r="D94" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E94" t="s">
         <v>54</v>
       </c>
       <c r="F94" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G94" t="s">
         <v>25</v>
       </c>
       <c r="H94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I94" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="J94" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K94" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="L94" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="M94" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="N94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O94" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P94" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="Q94" t="s">
         <v>33</v>
       </c>
       <c r="R94" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="S94" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="T94" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="U94" t="s">
         <v>37</v>
@@ -10876,49 +10879,49 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C95" t="s">
         <v>52</v>
       </c>
       <c r="D95" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E95" t="s">
         <v>94</v>
       </c>
       <c r="F95" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G95" t="s">
         <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I95" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J95" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K95" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L95" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M95" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N95" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O95" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P95" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="Q95" t="s">
         <v>33</v>
@@ -10941,61 +10944,61 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C96" t="s">
         <v>52</v>
       </c>
       <c r="D96" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E96" t="s">
         <v>54</v>
       </c>
       <c r="F96" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G96" t="s">
         <v>25</v>
       </c>
       <c r="H96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I96" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J96" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="K96" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="L96" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="M96" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O96" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="P96" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="Q96" t="s">
         <v>33</v>
       </c>
       <c r="R96" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="S96" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="T96" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="U96" t="s">
         <v>37</v>
@@ -11006,61 +11009,61 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C97" t="s">
         <v>52</v>
       </c>
       <c r="D97" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E97" t="s">
         <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G97" t="s">
         <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I97" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J97" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K97" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="L97" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="M97" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N97" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O97" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="P97" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="Q97" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R97" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="S97" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="T97" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="U97" t="s">
         <v>37</v>
@@ -11071,57 +11074,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C98" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D98" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I98" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J98" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K98" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L98" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="M98" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N98" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O98" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P98" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="Q98" t="s">
         <v>33</v>
       </c>
       <c r="R98" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="S98" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="T98" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="U98" t="s">
         <v>37</v>
@@ -11132,61 +11135,61 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C99" t="s">
         <v>22</v>
       </c>
       <c r="D99" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E99" t="s">
         <v>94</v>
       </c>
       <c r="F99" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G99" t="s">
         <v>25</v>
       </c>
       <c r="H99" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I99" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J99" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K99" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L99" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="M99" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O99" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="P99" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="Q99" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R99" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="S99" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="T99" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="U99" t="s">
         <v>37</v>
@@ -11197,61 +11200,61 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C100" t="s">
         <v>22</v>
       </c>
       <c r="D100" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E100" t="s">
         <v>74</v>
       </c>
       <c r="F100" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G100" t="s">
         <v>25</v>
       </c>
       <c r="H100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I100" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="J100" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K100" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="L100" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="M100" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N100" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O100" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="P100" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="Q100" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R100" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="S100" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="T100" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="U100" t="s">
         <v>37</v>
@@ -11262,61 +11265,61 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C101" t="s">
         <v>52</v>
       </c>
       <c r="D101" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E101" t="s">
         <v>40</v>
       </c>
       <c r="F101" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G101" t="s">
         <v>25</v>
       </c>
       <c r="H101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I101" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="J101" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K101" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="L101" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="M101" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N101" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O101" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="P101" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="Q101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R101" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="S101" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="T101" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="U101" t="s">
         <v>37</v>
@@ -11327,61 +11330,61 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C102" t="s">
         <v>22</v>
       </c>
       <c r="D102" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E102" t="s">
         <v>40</v>
       </c>
       <c r="F102" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G102" t="s">
         <v>25</v>
       </c>
       <c r="H102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I102" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="J102" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="K102" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="L102" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="M102" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="N102" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O102" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="P102" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Q102" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R102" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="S102" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="T102" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="U102" t="s">
         <v>37</v>
@@ -11392,61 +11395,61 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C103" t="s">
         <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E103" t="s">
         <v>54</v>
       </c>
       <c r="F103" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G103" t="s">
         <v>25</v>
       </c>
       <c r="H103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I103" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="J103" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K103" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="L103" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="M103" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="N103" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O103" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="P103" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="Q103" t="s">
         <v>33</v>
       </c>
       <c r="R103" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="S103" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="T103" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="U103" t="s">
         <v>37</v>
@@ -11457,7 +11460,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C104" t="s">
         <v>52</v>
@@ -11469,37 +11472,37 @@
         <v>54</v>
       </c>
       <c r="F104" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G104" t="s">
         <v>25</v>
       </c>
       <c r="H104" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I104" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="J104" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="K104" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="L104" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="M104" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N104" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O104" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="P104" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="Q104" t="s">
         <v>33</v>
@@ -11522,61 +11525,61 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C105" t="s">
         <v>22</v>
       </c>
       <c r="D105" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E105" t="s">
         <v>74</v>
       </c>
       <c r="F105" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G105" t="s">
         <v>25</v>
       </c>
       <c r="H105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I105" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J105" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="K105" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="L105" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="M105" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N105" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O105" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="P105" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Q105" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R105" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S105" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T105" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U105" t="s">
         <v>37</v>
@@ -11587,59 +11590,59 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D106" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E106" t="s">
         <v>54</v>
       </c>
       <c r="F106" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G106" t="s">
         <v>25</v>
       </c>
       <c r="H106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I106" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="J106" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="M106" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N106" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O106" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="P106" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q106" t="s">
         <v>33</v>
       </c>
       <c r="R106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S106" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T106" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U106" t="s">
         <v>37</v>
@@ -11650,59 +11653,59 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E107" t="s">
         <v>40</v>
       </c>
       <c r="F107" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G107" t="s">
         <v>25</v>
       </c>
       <c r="H107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I107" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J107" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="M107" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N107" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O107" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P107" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="Q107" t="s">
         <v>33</v>
       </c>
       <c r="R107" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="S107" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="T107" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="U107" t="s">
         <v>37</v>
@@ -11713,10 +11716,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
         <v>63</v>
@@ -11725,49 +11728,49 @@
         <v>40</v>
       </c>
       <c r="F108" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G108" t="s">
         <v>25</v>
       </c>
       <c r="H108" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I108" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="J108" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="K108" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="L108" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="M108" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="N108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O108" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="P108" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="Q108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R108" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="S108" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="T108" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="U108" t="s">
         <v>37</v>
@@ -11778,51 +11781,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C109" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I109" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J109" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="K109" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="O109" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="P109" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="Q109" t="s">
         <v>47</v>
       </c>
       <c r="R109" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="S109" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="T109" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="U109" t="s">
         <v>37</v>
@@ -11833,57 +11836,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C110" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D110" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I110" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J110" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="K110" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="L110" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="M110" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N110" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O110" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="P110" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="Q110" t="s">
         <v>33</v>
       </c>
       <c r="R110" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="S110" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="T110" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="U110" t="s">
         <v>37</v>
@@ -11894,61 +11897,61 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C111" t="s">
         <v>52</v>
       </c>
       <c r="D111" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E111" t="s">
         <v>40</v>
       </c>
       <c r="F111" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="G111" t="s">
         <v>25</v>
       </c>
       <c r="H111" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I111" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="J111" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="K111" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="L111" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="M111" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="N111" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O111" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="P111" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="Q111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R111" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="S111" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="T111" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="U111" t="s">
         <v>37</v>
@@ -11959,61 +11962,61 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C112" t="s">
         <v>52</v>
       </c>
       <c r="D112" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E112" t="s">
         <v>40</v>
       </c>
       <c r="F112" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G112" t="s">
         <v>25</v>
       </c>
       <c r="H112" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I112" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J112" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="K112" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L112" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="M112" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N112" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O112" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="P112" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="Q112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R112" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="S112" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="T112" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="U112" t="s">
         <v>37</v>
@@ -12024,7 +12027,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C113" t="s">
         <v>52</v>
@@ -12036,49 +12039,49 @@
         <v>40</v>
       </c>
       <c r="F113" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G113" t="s">
         <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I113" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="J113" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="K113" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="L113" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M113" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N113" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O113" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="P113" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="Q113" t="s">
         <v>33</v>
       </c>
       <c r="R113" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="S113" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="T113" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="U113" t="s">
         <v>37</v>
@@ -12089,61 +12092,61 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E114" t="s">
         <v>94</v>
       </c>
       <c r="F114" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G114" t="s">
         <v>41</v>
       </c>
       <c r="H114" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I114" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="J114" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="K114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="L114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="M114" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="N114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="P114" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="Q114" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R114" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="S114" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="T114" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="U114" t="s">
         <v>37</v>
@@ -12154,61 +12157,61 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C115" t="s">
         <v>22</v>
       </c>
       <c r="D115" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E115" t="s">
         <v>94</v>
       </c>
       <c r="F115" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G115" t="s">
         <v>25</v>
       </c>
       <c r="H115" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I115" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="J115" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="K115" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="L115" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="M115" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N115" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O115" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="P115" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="Q115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R115" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="S115" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="T115" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="U115" t="s">
         <v>37</v>
@@ -12219,61 +12222,61 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C116" t="s">
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E116" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F116" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G116" t="s">
         <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I116" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="J116" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="K116" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="L116" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="M116" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="N116" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O116" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="P116" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="Q116" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R116" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="S116" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="T116" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="U116" t="s">
         <v>37</v>
@@ -12284,61 +12287,61 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C117" t="s">
         <v>52</v>
       </c>
       <c r="D117" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E117" t="s">
         <v>54</v>
       </c>
       <c r="F117" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G117" t="s">
         <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I117" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="J117" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="K117" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="L117" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="M117" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="N117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O117" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="P117" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="Q117" t="s">
         <v>33</v>
       </c>
       <c r="R117" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="S117" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="T117" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="U117" t="s">
         <v>37</v>
@@ -12349,61 +12352,61 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C118" t="s">
         <v>52</v>
       </c>
       <c r="D118" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E118" t="s">
         <v>94</v>
       </c>
       <c r="F118" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G118" t="s">
         <v>25</v>
       </c>
       <c r="H118" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I118" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="J118" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="K118" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="L118" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="M118" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="N118" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O118" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="P118" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="Q118" t="s">
         <v>33</v>
       </c>
       <c r="R118" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="S118" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="T118" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="U118" t="s">
         <v>37</v>
@@ -12414,61 +12417,61 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C119" t="s">
         <v>52</v>
       </c>
       <c r="D119" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E119" t="s">
         <v>40</v>
       </c>
       <c r="F119" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G119" t="s">
         <v>25</v>
       </c>
       <c r="H119" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I119" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="J119" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="K119" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="L119" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="M119" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="N119" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O119" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="P119" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="Q119" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R119" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="S119" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="T119" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="U119" t="s">
         <v>37</v>
@@ -12479,61 +12482,61 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C120" t="s">
         <v>52</v>
       </c>
       <c r="D120" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E120" t="s">
         <v>94</v>
       </c>
       <c r="F120" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="G120" t="s">
         <v>25</v>
       </c>
       <c r="H120" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I120" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J120" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="K120" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="L120" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="M120" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N120" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O120" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="P120" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="Q120" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R120" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S120" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T120" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U120" t="s">
         <v>37</v>
@@ -12544,7 +12547,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C121" t="s">
         <v>52</v>
@@ -12556,49 +12559,49 @@
         <v>54</v>
       </c>
       <c r="F121" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="G121" t="s">
         <v>25</v>
       </c>
       <c r="H121" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I121" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="J121" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="K121" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="L121" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="M121" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="N121" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O121" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="P121" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="Q121" t="s">
         <v>33</v>
       </c>
       <c r="R121" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S121" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T121" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U121" t="s">
         <v>37</v>
@@ -12609,61 +12612,61 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C122" t="s">
         <v>52</v>
       </c>
       <c r="D122" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E122" t="s">
         <v>40</v>
       </c>
       <c r="F122" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="G122" t="s">
         <v>41</v>
       </c>
       <c r="H122" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I122" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="J122" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="K122" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="L122" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="M122" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="N122" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O122" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="P122" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="Q122" t="s">
         <v>33</v>
       </c>
       <c r="R122" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="S122" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T122" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="U122" t="s">
         <v>37</v>
@@ -12674,61 +12677,61 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D123" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E123" t="s">
         <v>40</v>
       </c>
       <c r="F123" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="G123" t="s">
         <v>41</v>
       </c>
       <c r="H123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I123" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="J123" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="K123" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="L123" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="M123" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="N123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O123" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="P123" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="Q123" t="s">
         <v>33</v>
       </c>
       <c r="R123" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="S123" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="T123" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="U123" t="s">
         <v>37</v>
@@ -12739,50 +12742,50 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D124" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E124" t="s">
         <v>54</v>
       </c>
       <c r="F124" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="G124" t="s">
         <v>25</v>
       </c>
       <c r="H124" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I124" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="J124" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="M124" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N124" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O124" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="P124" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="Q124" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R124" t="s">
         <v>59</v>
@@ -12802,10 +12805,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C125" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D125" t="s">
         <v>63</v>
@@ -12814,35 +12817,35 @@
         <v>40</v>
       </c>
       <c r="F125" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="G125" t="s">
         <v>25</v>
       </c>
       <c r="H125" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I125" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="J125" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="M125" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="N125" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O125" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="P125" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q125" t="s">
         <v>33</v>
@@ -12865,59 +12868,59 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C126" t="s">
         <v>22</v>
       </c>
       <c r="D126" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="G126" t="s">
         <v>25</v>
       </c>
       <c r="H126" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I126" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="J126" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K126" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="L126" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="M126" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="N126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O126" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P126" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="Q126" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R126" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="S126" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="T126" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="U126" t="s">
         <v>37</v>
@@ -12928,61 +12931,61 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C127" t="s">
         <v>52</v>
       </c>
       <c r="D127" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E127" t="s">
         <v>74</v>
       </c>
       <c r="F127" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="G127" t="s">
         <v>25</v>
       </c>
       <c r="H127" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I127" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="J127" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="K127" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="L127" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="M127" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="N127" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O127" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="P127" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="Q127" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R127" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="S127" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="T127" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="U127" t="s">
         <v>37</v>
@@ -12993,61 +12996,61 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
       </c>
       <c r="D128" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E128" t="s">
         <v>40</v>
       </c>
       <c r="F128" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="G128" t="s">
         <v>25</v>
       </c>
       <c r="H128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I128" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J128" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K128" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="L128" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="M128" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="N128" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O128" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="P128" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="Q128" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R128" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="S128" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="T128" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="U128" t="s">
         <v>37</v>
@@ -13058,61 +13061,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C129" t="s">
         <v>22</v>
       </c>
       <c r="D129" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E129" t="s">
         <v>40</v>
       </c>
       <c r="F129" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G129" t="s">
         <v>41</v>
       </c>
       <c r="H129" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I129" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="J129" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="K129" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="L129" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="M129" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="N129" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O129" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="P129" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="Q129" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R129" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="S129" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="T129" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="U129" t="s">
         <v>37</v>
@@ -13123,61 +13126,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C130" t="s">
         <v>22</v>
       </c>
       <c r="D130" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E130" t="s">
         <v>40</v>
       </c>
       <c r="F130" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G130" t="s">
         <v>25</v>
       </c>
       <c r="H130" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I130" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="J130" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="K130" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="L130" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="M130" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="N130" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O130" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="P130" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="Q130" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R130" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="S130" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="T130" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="U130" t="s">
         <v>37</v>
@@ -13188,61 +13191,61 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C131" t="s">
         <v>52</v>
       </c>
       <c r="D131" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E131" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F131" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="G131" t="s">
         <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I131" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="J131" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="K131" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="L131" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="M131" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="N131" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O131" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="P131" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="Q131" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R131" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S131" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T131" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U131" t="s">
         <v>37</v>
@@ -13253,7 +13256,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C132" t="s">
         <v>52</v>
@@ -13265,49 +13268,49 @@
         <v>94</v>
       </c>
       <c r="F132" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
       </c>
       <c r="H132" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I132" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="J132" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="K132" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="L132" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="M132" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="N132" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O132" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="P132" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="Q132" t="s">
         <v>33</v>
       </c>
       <c r="R132" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="S132" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="T132" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="U132" t="s">
         <v>37</v>
@@ -13318,61 +13321,61 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C133" t="s">
         <v>52</v>
       </c>
       <c r="D133" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E133" t="s">
         <v>54</v>
       </c>
       <c r="F133" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G133" t="s">
         <v>25</v>
       </c>
       <c r="H133" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I133" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="J133" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="K133" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="L133" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="M133" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="N133" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O133" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="P133" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="Q133" t="s">
         <v>33</v>
       </c>
       <c r="R133" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="S133" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="T133" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="U133" t="s">
         <v>37</v>
@@ -13383,59 +13386,59 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D134" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E134" t="s">
         <v>74</v>
       </c>
       <c r="F134" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G134" t="s">
         <v>25</v>
       </c>
       <c r="H134" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I134" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="J134" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="M134" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="N134" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O134" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="P134" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="Q134" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R134" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="S134" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="T134" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="U134" t="s">
         <v>37</v>
@@ -13446,59 +13449,59 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C135" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D135" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E135" t="s">
         <v>74</v>
       </c>
       <c r="F135" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G135" t="s">
         <v>25</v>
       </c>
       <c r="H135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I135" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="J135" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="M135" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="N135" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O135" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="P135" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="Q135" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R135" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="S135" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="T135" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="U135" t="s">
         <v>37</v>
@@ -13509,59 +13512,59 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C136" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D136" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E136" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F136" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="G136" t="s">
         <v>25</v>
       </c>
       <c r="H136" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I136" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="J136" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="M136" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="N136" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O136" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="P136" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="Q136" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R136" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S136" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T136" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U136" t="s">
         <v>37</v>
@@ -13572,59 +13575,59 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C137" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D137" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E137" t="s">
         <v>94</v>
       </c>
       <c r="F137" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G137" t="s">
         <v>25</v>
       </c>
       <c r="H137" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I137" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="J137" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M137" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="N137" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O137" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="P137" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="Q137" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="R137" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="S137" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="T137" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="U137" t="s">
         <v>37</v>
@@ -13635,57 +13638,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C138" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D138" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I138" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="J138" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="K138" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="L138" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="M138" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="N138" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O138" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="P138" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="Q138" t="s">
         <v>33</v>
       </c>
       <c r="R138" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="S138" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="T138" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="U138" t="s">
         <v>37</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1525">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -374,6 +374,9 @@
     <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
   </si>
   <si>
+    <t xml:space="preserve">Collegare efficacemente spazi culturali ed economici attraverso una strada nazionale N18 efficiente</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les paramètres du programme « Transports ’45 »dans lequel le projet d’amélioration structurelle de la liaison routière Delémont- Bâle a été retenu. Mais, le report au-delà de 2055 des projets routiers le long de la N18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufen (horizon 2055) – suscite une forte incompréhension de la part des élus, des populations et des milieux économiques en particulier. Ce renoncement de fait à une meilleure accessibilité et à de réelles perspectives de développement économique contredit directement les résultats de l’étude de corridor N18 menée sous la direction de l’OFROU selon les méthodes les plus récentes. C’est aussi une question de crédibilité des institutions par un respect de la cohérence des politiques publiques.&lt;/p&gt;&lt;p&gt;La N18 est un élément essentiel du réseau routier national : elle relie l’agglomération bâloise à l’Arc lémanique et unit deux espaces culturels et&amp;nbsp;économiques majeurs. Elle connecte&amp;nbsp;également le Laufonnais, région dynamique, ainsi que la capitale cantonale Delémont au réseau à haute performance. Elle contribue ainsi&amp;nbsp;à la cohésion nationale et au rapprochement des communautés linguistiques.&lt;/p&gt;&lt;p&gt;Sous l’effet de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, avec l’une des plus fortes densités de bouchons du pays. De plus, le trafic actuel porte atteinte à la qualité de vie dans les centres et compromet la sécurité du trafic motorisé et cycliste. Une modernisation rapide du corridor est donc prioritaire.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il la nécessité d’éliminer les goulets d’étranglement sur la N18 entre Angenstein et Delémont ?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel du Muggenberg comme une mesure durable pour améliorer la sécurité au point noir d’Angenstein ?&lt;/li&gt;&lt;li&gt;Comment apprécie-t-il l’utilité des projets recommandés dans l’étude de corridor N18 (tunnel du Muggenberg, contournements Laufen–Zwingen et Delémont, décharge de Laufen) pour renforcer la connexion des entreprises de la région Laufonnais–Thierstein–Delémont ?&lt;/li&gt;&lt;li&gt;Estime-t-il que les contournements Laufen–Zwingen et Delémont constituent des mesures appropriées pour soulager les zones habitées concernées ?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
@@ -504,6 +507,9 @@
   </si>
   <si>
     <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafforzare la sicurezza stradale con progetti lungo la N18</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
@@ -5490,22 +5496,22 @@
         <v>119</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="L9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
@@ -5529,13 +5535,13 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -5548,38 +5554,38 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10" t="s">
         <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L10"/>
       <c r="M10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q10" t="s">
         <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5591,10 +5597,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5603,7 +5609,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5615,35 +5621,35 @@
         <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="T11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5655,19 +5661,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5676,38 +5682,38 @@
         <v>99</v>
       </c>
       <c r="I12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5719,19 +5725,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5740,28 +5746,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5785,19 +5791,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5806,38 +5812,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="S14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5849,51 +5855,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5905,19 +5911,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
         <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5926,38 +5932,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O16" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -5969,17 +5975,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -5988,40 +5994,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="S17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="T17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6033,16 +6039,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6054,40 +6060,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J18" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6099,13 +6105,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6120,40 +6126,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6165,7 +6171,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6177,49 +6183,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="S20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6231,10 +6237,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6243,7 +6249,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6252,40 +6258,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6297,19 +6303,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6318,40 +6324,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K22" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="T22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6363,7 +6369,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -6375,7 +6381,7 @@
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6384,40 +6390,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P23" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="S23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="T23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6429,19 +6435,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6450,40 +6456,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J24" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K24" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M24" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6495,59 +6501,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="S25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="T25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6559,19 +6565,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6580,38 +6586,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J26" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O26" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P26" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6623,17 +6629,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6642,40 +6648,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K27" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L27" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M27" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N27" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O27" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P27" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6687,19 +6693,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6708,40 +6714,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J28" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K28" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L28" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P28" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S28" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6753,19 +6759,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E29" t="s">
         <v>98</v>
       </c>
       <c r="F29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6774,40 +6780,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N29" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6819,7 +6825,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6831,7 +6837,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6840,31 +6846,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J30" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K30" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L30" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N30" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P30" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6885,7 +6891,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6897,7 +6903,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6906,40 +6912,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="T31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6951,19 +6957,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -6972,40 +6978,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K32" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L32" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O32" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P32" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q32" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R32" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S32" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T32" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7017,7 +7023,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7029,7 +7035,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7038,40 +7044,40 @@
         <v>99</v>
       </c>
       <c r="I33" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J33" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L33" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M33" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O33" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P33" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q33" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="S33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="T33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7083,61 +7089,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I34" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J34" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K34" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N34" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P34" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R34" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="S34" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="T34" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7149,19 +7155,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7170,40 +7176,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J35" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K35" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L35" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M35" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O35" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P35" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R35" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S35" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7215,10 +7221,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C36" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7227,7 +7233,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7236,40 +7242,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J36" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K36" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L36" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="S36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="T36" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7281,19 +7287,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7302,40 +7308,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J37" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O37" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P37" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="S37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="T37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7347,19 +7353,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E38" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F38" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7368,38 +7374,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J38" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M38" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P38" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T38" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7411,19 +7417,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D39" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7432,38 +7438,38 @@
         <v>99</v>
       </c>
       <c r="I39" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J39" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M39" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O39" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P39" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Q39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R39" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="S39" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="T39" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7475,19 +7481,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D40" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7496,38 +7502,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J40" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M40" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O40" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P40" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Q40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="S40" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="T40" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7539,61 +7545,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I41" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J41" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K41" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L41" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M41" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N41" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O41" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="P41" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="S41" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="T41" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7605,59 +7611,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I42" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J42" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M42" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P42" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="S42" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="T42" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7669,45 +7675,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C43" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D43" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I43" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J43" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K43" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L43" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M43" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N43" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O43" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P43" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7725,19 +7731,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7746,40 +7752,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J44" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K44" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L44" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M44" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N44" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O44" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P44" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R44" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S44" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="T44" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7791,19 +7797,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7812,40 +7818,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J45" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K45" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L45" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M45" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O45" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P45" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="S45" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="T45" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7857,19 +7863,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7878,40 +7884,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J46" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K46" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L46" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N46" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O46" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="P46" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="S46" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="T46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7923,7 +7929,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7933,7 +7939,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7942,40 +7948,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J47" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K47" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L47" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M47" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N47" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O47" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="Q47" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R47" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="S47" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="T47" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -7987,19 +7993,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8008,40 +8014,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J48" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K48" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L48" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M48" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O48" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P48" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Q48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R48" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="S48" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="T48" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8053,19 +8059,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8074,31 +8080,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J49" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K49" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L49" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M49" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O49" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P49" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="Q49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8119,17 +8125,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8138,40 +8144,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J50" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K50" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="L50" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M50" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O50" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="P50" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="S50" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8183,19 +8189,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E51" t="s">
         <v>98</v>
       </c>
       <c r="F51" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8204,40 +8210,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J51" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K51" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L51" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M51" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N51" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O51" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="P51" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Q51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R51" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="S51" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="T51" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8249,19 +8255,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E52" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8270,40 +8276,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J52" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="K52" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L52" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M52" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O52" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P52" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S52" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="T52" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8315,19 +8321,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8336,28 +8342,28 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J53" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="K53" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L53" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M53" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N53" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O53" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P53" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
@@ -8381,19 +8387,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E54" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F54" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8402,40 +8408,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J54" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K54" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L54" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M54" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N54" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O54" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="P54" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="Q54" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R54" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="S54" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="T54" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8447,19 +8453,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8468,40 +8474,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J55" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K55" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L55" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M55" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N55" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O55" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P55" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Q55" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R55" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S55" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T55" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8513,17 +8519,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8532,40 +8538,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J56" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K56" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L56" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M56" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N56" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O56" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P56" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="Q56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R56" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S56" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T56" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8577,61 +8583,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I57" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J57" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="K57" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L57" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M57" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N57" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O57" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="P57" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="S57" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="T57" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8643,19 +8649,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8664,40 +8670,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J58" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K58" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L58" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M58" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N58" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O58" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P58" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="S58" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="T58" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8709,19 +8715,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E59" t="s">
         <v>98</v>
       </c>
       <c r="F59" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8730,40 +8736,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J59" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="K59" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="L59" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M59" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O59" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="P59" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="Q59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R59" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="S59" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="T59" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8775,19 +8781,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8796,40 +8802,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="J60" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="K60" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L60" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M60" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O60" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="P60" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="Q60" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R60" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="S60" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="T60" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8841,7 +8847,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8853,7 +8859,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8862,40 +8868,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="J61" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="K61" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L61" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M61" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N61" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O61" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="P61" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="Q61" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R61" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S61" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T61" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8907,19 +8913,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8928,40 +8934,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="J62" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="K62" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="L62" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="M62" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="N62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O62" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P62" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="Q62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R62" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="S62" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="T62" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -8973,19 +8979,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -8994,40 +9000,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="J63" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K63" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="L63" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M63" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="N63" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O63" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="P63" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="S63" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="T63" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9039,45 +9045,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C64" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D64" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J64" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="K64" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="L64" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M64" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="P64" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9095,45 +9101,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C65" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D65" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J65" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K65" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L65" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M65" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N65" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="O65" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="P65" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9151,17 +9157,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D66" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9170,40 +9176,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J66" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="K66" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="L66" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="M66" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="P66" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="S66" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="T66" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9215,19 +9221,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C67" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D67" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9236,40 +9242,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="J67" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K67" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="L67" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M67" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N67" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O67" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="P67" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="S67" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="T67" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9281,19 +9287,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E68" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F68" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9302,40 +9308,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="J68" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="K68" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="L68" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M68" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N68" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O68" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="P68" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="Q68" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R68" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="S68" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="T68" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9347,61 +9353,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="I69" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="J69" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="K69" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="L69" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="M69" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N69" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O69" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="P69" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="Q69" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R69" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="S69" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="T69" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9413,19 +9419,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E70" t="s">
         <v>98</v>
       </c>
       <c r="F70" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9434,40 +9440,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="J70" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="K70" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L70" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M70" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N70" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O70" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P70" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="Q70" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R70" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="S70" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="T70" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9479,19 +9485,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9500,40 +9506,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J71" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="K71" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="L71" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="M71" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N71" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O71" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="P71" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="Q71" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R71" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="S71" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="T71" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9545,19 +9551,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9566,40 +9572,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="J72" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="K72" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="L72" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="M72" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N72" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O72" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="P72" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="Q72" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R72" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="S72" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="T72" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9611,19 +9617,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9632,40 +9638,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J73" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="K73" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="L73" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="M73" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="N73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O73" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="P73" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="S73" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="T73" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9677,19 +9683,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9698,40 +9704,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="J74" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="K74" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="L74" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="M74" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="N74" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O74" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="P74" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="Q74" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R74" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="S74" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="T74" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9743,45 +9749,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C75" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D75" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="J75" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K75" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="L75" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="M75" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="N75" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="O75" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="P75" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9799,7 +9805,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9811,7 +9817,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9820,40 +9826,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J76" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="K76" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="L76" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="M76" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="N76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O76" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="P76" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S76" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T76" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9865,19 +9871,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D77" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9886,38 +9892,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="J77" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="M77" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="N77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O77" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="P77" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="S77" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="T77" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9929,19 +9935,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D78" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9950,38 +9956,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J78" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="M78" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="N78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O78" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="P78" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="S78" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="T78" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -9993,51 +9999,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="J79" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K79" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O79" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="P79" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="S79" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="T79" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10049,57 +10055,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C80" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D80" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="J80" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="K80" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="L80" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="M80" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="P80" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="S80" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="T80" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10111,57 +10117,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C81" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D81" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="J81" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="K81" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="L81" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="M81" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="N81" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="O81" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="P81" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="S81" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="T81" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10173,19 +10179,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E82" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F82" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10194,40 +10200,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="J82" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="K82" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="L82" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="M82" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="N82" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O82" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="P82" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="Q82" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R82" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="S82" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="T82" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10239,19 +10245,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10260,40 +10266,40 @@
         <v>99</v>
       </c>
       <c r="I83" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="J83" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="K83" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="L83" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="M83" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="N83" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O83" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="P83" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="Q83" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R83" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="S83" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="T83" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10305,19 +10311,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10326,40 +10332,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="J84" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="K84" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L84" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="M84" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="N84" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O84" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="P84" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="S84" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="T84" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10371,19 +10377,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10392,40 +10398,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="J85" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="K85" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="L85" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="M85" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="N85" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O85" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="P85" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="Q85" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R85" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="S85" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="T85" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10437,19 +10443,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10458,40 +10464,40 @@
         <v>99</v>
       </c>
       <c r="I86" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="J86" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="K86" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="L86" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="M86" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="N86" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O86" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="P86" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="Q86" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R86" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S86" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="T86" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10503,19 +10509,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="E87" t="s">
         <v>98</v>
       </c>
       <c r="F87" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10524,40 +10530,40 @@
         <v>99</v>
       </c>
       <c r="I87" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="J87" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K87" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="L87" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="M87" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="N87" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O87" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="P87" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="Q87" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R87" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="S87" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="T87" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10569,19 +10575,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10590,38 +10596,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="J88" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="M88" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="N88" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O88" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="P88" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="Q88" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R88" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S88" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T88" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10633,7 +10639,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
@@ -10645,7 +10651,7 @@
         <v>98</v>
       </c>
       <c r="F89" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10654,31 +10660,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="J89" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="K89" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="L89" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="M89" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N89" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O89" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="P89" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="Q89" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10699,19 +10705,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D90" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10720,38 +10726,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="J90" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="M90" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="N90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O90" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="P90" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="S90" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="T90" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10763,19 +10769,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D91" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10784,38 +10790,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="J91" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="M91" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="N91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O91" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="P91" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="Q91" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S91" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10827,19 +10833,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D92" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10848,38 +10854,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="J92" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="M92" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N92" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O92" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="P92" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="Q92" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T92" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10891,19 +10897,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D93" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10912,38 +10918,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="J93" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="M93" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="N93" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O93" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="P93" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="Q93" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R93" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10955,19 +10961,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -10976,40 +10982,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="J94" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="K94" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="L94" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="M94" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="N94" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O94" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="P94" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="S94" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="T94" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11021,19 +11027,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11042,28 +11048,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J95" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="K95" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="L95" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M95" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="N95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O95" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="P95" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11087,19 +11093,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11108,40 +11114,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="J96" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="K96" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="L96" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="M96" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="N96" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O96" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="P96" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="S96" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="T96" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11153,19 +11159,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E97" t="s">
         <v>98</v>
       </c>
       <c r="F97" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11174,40 +11180,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="J97" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="K97" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="L97" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="M97" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="N97" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O97" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="P97" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="Q97" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R97" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="S97" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="T97" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11219,57 +11225,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C98" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D98" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I98" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="J98" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K98" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="L98" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="M98" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="P98" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="S98" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="T98" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11281,19 +11287,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11302,40 +11308,40 @@
         <v>99</v>
       </c>
       <c r="I99" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="J99" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="K99" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="L99" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M99" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="N99" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O99" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="P99" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="Q99" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R99" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="S99" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="T99" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11347,19 +11353,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E100" t="s">
         <v>98</v>
       </c>
       <c r="F100" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11368,40 +11374,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="J100" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="K100" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="L100" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="M100" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="N100" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O100" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="P100" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="Q100" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R100" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="S100" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="T100" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11413,19 +11419,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11434,40 +11440,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="J101" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="K101" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="L101" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="M101" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="N101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O101" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="P101" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="Q101" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R101" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="S101" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="T101" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11479,19 +11485,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11500,40 +11506,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="J102" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="K102" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="L102" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="M102" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="N102" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O102" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="P102" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="Q102" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R102" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="S102" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="T102" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11545,19 +11551,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11566,40 +11572,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="J103" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="K103" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="L103" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="M103" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="N103" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O103" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P103" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="S103" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="T103" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11611,7 +11617,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11623,7 +11629,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11632,28 +11638,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="J104" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="K104" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="L104" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="M104" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="N104" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O104" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="P104" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11677,19 +11683,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E105" t="s">
         <v>98</v>
       </c>
       <c r="F105" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11698,40 +11704,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="J105" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="K105" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="L105" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="M105" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="N105" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O105" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="P105" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="Q105" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R105" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S105" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T105" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11743,19 +11749,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D106" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11764,38 +11770,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="J106" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="M106" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="N106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O106" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="P106" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S106" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T106" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11807,19 +11813,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11828,38 +11834,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="J107" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="M107" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="N107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O107" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="P107" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="S107" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="T107" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11871,10 +11877,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C108" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D108" t="s">
         <v>87</v>
@@ -11883,7 +11889,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11892,40 +11898,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="J108" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="K108" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="L108" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="M108" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="N108" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O108" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="P108" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="Q108" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R108" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="S108" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="T108" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11937,51 +11943,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C109" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="J109" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="K109" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="O109" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="P109" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="S109" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="T109" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -11993,57 +11999,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C110" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D110" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="J110" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K110" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="L110" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="M110" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="N110" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O110" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="P110" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="S110" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="T110" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12055,19 +12061,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12076,40 +12082,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="J111" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="K111" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="L111" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="M111" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="N111" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O111" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="P111" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="Q111" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R111" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="S111" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="T111" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12121,19 +12127,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12142,40 +12148,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="J112" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="K112" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="L112" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="M112" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="N112" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O112" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="P112" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="Q112" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R112" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="S112" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="T112" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12187,7 +12193,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12199,7 +12205,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12208,40 +12214,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="J113" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="K113" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="L113" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="M113" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="N113" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O113" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="P113" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="S113" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="T113" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12253,19 +12259,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C114" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D114" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12274,40 +12280,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="J114" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="K114" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="L114" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="M114" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="N114" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O114" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="P114" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="Q114" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R114" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="S114" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="T114" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12319,19 +12325,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12340,40 +12346,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="J115" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="K115" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="L115" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="M115" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="N115" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O115" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="P115" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="Q115" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R115" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="S115" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="T115" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12385,19 +12391,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E116" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="F116" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12406,40 +12412,40 @@
         <v>99</v>
       </c>
       <c r="I116" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="J116" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="K116" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="L116" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="M116" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="N116" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O116" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="P116" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="Q116" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R116" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="S116" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="T116" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12451,19 +12457,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12472,40 +12478,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="J117" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="K117" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="L117" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="M117" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="N117" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O117" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="P117" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="S117" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="T117" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12517,19 +12523,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12538,40 +12544,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="J118" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="K118" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="L118" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="M118" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="N118" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O118" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="P118" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="S118" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="T118" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12583,19 +12589,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12604,40 +12610,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="J119" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="K119" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="L119" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="M119" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="N119" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O119" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="P119" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="Q119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R119" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="S119" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="T119" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12649,19 +12655,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12670,40 +12676,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="J120" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="K120" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="L120" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="M120" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="N120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O120" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="P120" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="Q120" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R120" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="S120" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T120" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12715,7 +12721,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
@@ -12727,7 +12733,7 @@
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12736,40 +12742,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="J121" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="K121" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="L121" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="M121" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="N121" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O121" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="P121" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S121" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T121" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12781,19 +12787,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12802,40 +12808,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="J122" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="K122" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="L122" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="M122" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="N122" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O122" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="P122" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="S122" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="T122" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12847,19 +12853,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D123" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12868,40 +12874,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="J123" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="K123" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="L123" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="M123" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="N123" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O123" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="P123" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="S123" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="T123" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12913,19 +12919,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C124" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D124" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12934,29 +12940,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J124" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="M124" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="N124" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O124" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="P124" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="Q124" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -12977,10 +12983,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -12989,7 +12995,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -12998,26 +13004,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="J125" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="M125" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="N125" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O125" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="P125" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13041,17 +13047,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13060,40 +13066,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="J126" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="K126" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="L126" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="M126" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="N126" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O126" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="P126" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="Q126" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R126" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="S126" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="T126" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13105,19 +13111,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E127" t="s">
         <v>98</v>
       </c>
       <c r="F127" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13126,40 +13132,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="J127" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="K127" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="L127" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="M127" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="N127" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O127" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="P127" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="Q127" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R127" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="S127" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="T127" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13171,19 +13177,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13192,40 +13198,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="J128" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="K128" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="L128" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="M128" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="N128" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O128" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="P128" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="Q128" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R128" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="S128" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="T128" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13237,61 +13243,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I129" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="J129" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="K129" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="L129" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="M129" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="N129" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O129" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="P129" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="Q129" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R129" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="S129" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="T129" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13303,61 +13309,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I130" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="J130" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="K130" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="L130" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="M130" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="N130" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O130" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="P130" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="Q130" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R130" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="S130" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="T130" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13369,19 +13375,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E131" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F131" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13390,40 +13396,40 @@
         <v>99</v>
       </c>
       <c r="I131" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="J131" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="K131" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="L131" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="M131" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="N131" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O131" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="P131" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="Q131" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R131" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="S131" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="T131" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13435,7 +13441,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13447,7 +13453,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13456,40 +13462,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="J132" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="K132" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="L132" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="M132" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="N132" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O132" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="P132" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="S132" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="T132" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13501,19 +13507,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13522,40 +13528,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="J133" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="K133" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="L133" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="M133" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="N133" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O133" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="P133" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="S133" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="T133" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13567,19 +13573,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D134" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E134" t="s">
         <v>98</v>
       </c>
       <c r="F134" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13588,38 +13594,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="J134" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="M134" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="N134" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O134" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="P134" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="Q134" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R134" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="S134" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="T134" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13631,19 +13637,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D135" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E135" t="s">
         <v>98</v>
       </c>
       <c r="F135" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13652,38 +13658,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="J135" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="M135" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="N135" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O135" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="P135" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="Q135" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R135" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="S135" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="T135" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13695,19 +13701,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D136" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E136" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F136" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13716,38 +13722,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="J136" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="M136" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="N136" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O136" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="P136" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="Q136" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R136" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="S136" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="T136" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13759,19 +13765,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D137" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13780,38 +13786,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="J137" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="M137" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="N137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O137" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="P137" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="Q137" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R137" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="S137" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="T137" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13823,57 +13829,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C138" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D138" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>99</v>
       </c>
       <c r="I138" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="J138" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K138" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="L138" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="M138" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="N138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O138" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="P138" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="S138" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="T138" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1528">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -281,12 +281,18 @@
     <t xml:space="preserve">2026-03-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Bahnplanung: Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat hat Ende Januar 2026 die Eckwerte für den Ausbau der Verkehrsinfrastruktur im Rahmen von «Verkehr 45» veröffentlicht. Obwohl die politischen Instanzen bereits klare Leitlinien festgelegt haben – insbesondere haben beide Kammern am 11. März 2026 die Motion &lt;strong&gt;24.4042&lt;/strong&gt; «Entwicklung eines Angebotskonzepts 2050 auf nationaler und internationaler Ebene» und am 11. März 2024 &lt;strong&gt;die Motion 23.3668&lt;/strong&gt; «Redundanz und Zuverlässigkeit auf der Eisenbahnachse Lausanne–Genf» angenommen – scheint dies im Dossier &lt;strong&gt;«Verkehr 45»&lt;/strong&gt; in keiner Weise berücksichtigt worden zu sein.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Wird sich die Botschaft 2027 auf diese beiden Motionen abstützen und klar aufzeigen, dass prioritär die Redundanz in der Genferseeregion sowie ein Angebotskonzept, das den nationalen Hauptstrecken Vorrang einräumt, schnellstmöglich geprüft und umgesetzt werden müssen? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Wird die Botschaft 2027 eine Erhöhung der Taktfrequenz, kürzere Fahrzeiten, mehr Kapazitäten und eine robustere Eisenbahninfrastruktur vorsehen, insbesondere für die Westschweiz?&lt;/p&gt;&lt;p&gt;3. Wie gedenkt der Bundesrat angesichts bestimmter neuer Projekte, die im Rahmen von «Verkehr&amp;nbsp;45» vorgesehen sind, die Tragfähigkeit des Bahninfrastrukturfonds zu gewährleisten, ohne dabei die Regionen zu benachteiligen, die bereits einen Investitionsrückstand aufweisen (Jura und Genferseeregion)?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Kann der Bundesrat die territorialen und wirtschaftlichen Auswirkungen eines mangelnden Ausbaus des Schienenverkehrs darlegen und die geplanten Massnahmen zur Gewährleistung der Gleichbehandlung erläutern?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Hält es der Bundesrat im Hinblick auf die Eindämmung der öffentlichen Ausgaben nicht für notwendig, die Baustandards der SBB zu vereinfachen?&lt;/p&gt;&lt;p&gt;6. Sind konkret Verbesserungen auf der Strecke Biel–Lausanne/Genf sowie die endgültige Wiederaufnahme der direkten (pünktlichen) Verbindung Basel/Zürich–Biel–Genf (ohne Umsteigen in Renens) vorgesehen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Ist der Bundesrat nicht der Ansicht, dass er neben den Grossprojekten auch Projekten mit hohem Mehrwert und geringen Kosten Vorrang einräumen sollte, wie beispielsweise der &lt;strong&gt;Bahnhaltestelle «Y-Parc» in Yverdon&lt;/strong&gt;? Die Investitionen sind für das Bundesamt für Verkehr lächerlich gering, gewährleisten jedoch eine Verkehrsverlagerung für Tausende von Arbeitsplätzen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Wenn die Beschlüsse des Parlaments bei der technischen Planung ausser Kraft gesetzt werden können, was bringen die Sessionen dann noch?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
   </si>
   <si>
@@ -345,6 +351,9 @@
   </si>
   <si>
     <t xml:space="preserve">Streichung von Art. 22 des Epidemiengesetzes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stralcio dell’articolo 22 della legge sulle epidemie</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, welcher die Streichung von Art. 22 des Epidemiengesetzes (EpG) vorsieht.&amp;nbsp;&lt;/p&gt;</t>
@@ -5298,38 +5307,40 @@
         <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K6" t="s">
         <v>65</v>
       </c>
       <c r="L6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M6"/>
+        <v>91</v>
+      </c>
+      <c r="M6" t="s">
+        <v>92</v>
+      </c>
       <c r="N6" t="s">
         <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="s">
         <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -5341,16 +5352,16 @@
         <v>20263323</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
         <v>88</v>
@@ -5359,10 +5370,10 @@
         <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J7" t="s">
         <v>48</v>
@@ -5372,28 +5383,28 @@
       </c>
       <c r="L7"/>
       <c r="M7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N7" t="s">
         <v>51</v>
       </c>
       <c r="O7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q7" t="s">
         <v>54</v>
       </c>
       <c r="R7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -5405,19 +5416,19 @@
         <v>20263120</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
@@ -5426,38 +5437,38 @@
         <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J8" t="s">
         <v>48</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="L8"/>
       <c r="M8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s">
         <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="s">
         <v>54</v>
       </c>
       <c r="R8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="S8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="T8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -5469,7 +5480,7 @@
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -5481,7 +5492,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -5490,40 +5501,40 @@
         <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="P9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -5535,17 +5546,17 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
         <v>45</v>
@@ -5554,38 +5565,38 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J10" t="s">
         <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L10"/>
       <c r="M10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q10" t="s">
         <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="T10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5597,10 +5608,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5609,7 +5620,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5621,35 +5632,35 @@
         <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="S11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="T11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5661,59 +5672,59 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="S12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="T12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5725,19 +5736,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5746,28 +5757,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5791,19 +5802,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5812,38 +5823,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="S14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5855,51 +5866,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5911,19 +5922,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5932,38 +5943,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="S16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -5975,17 +5986,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -5994,40 +6005,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="N17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O17" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P17" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="S17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="T17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6039,16 +6050,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6060,40 +6071,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J18" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O18" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R18" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="S18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="T18" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6105,13 +6116,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6126,40 +6137,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J19" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K19" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L19" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M19" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N19" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O19" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="P19" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="S19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="T19" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6171,7 +6182,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6183,49 +6194,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K20" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="L20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="S20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="T20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6237,10 +6248,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6249,7 +6260,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6258,40 +6269,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K21" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L21" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M21" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N21" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="P21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="T21" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6303,19 +6314,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6324,40 +6335,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K22" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L22" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N22" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="P22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="S22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="T22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6369,19 +6380,19 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6390,40 +6401,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J23" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K23" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N23" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O23" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="S23" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="T23" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6435,19 +6446,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6456,40 +6467,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L24" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N24" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="P24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="S24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="T24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6501,59 +6512,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D25" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I25" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J25" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M25" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O25" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P25" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S25" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="T25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6565,19 +6576,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6586,38 +6597,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M26" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O26" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P26" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="T26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6629,17 +6640,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6648,40 +6659,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J27" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K27" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L27" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N27" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="P27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="S27" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="T27" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6693,19 +6704,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6714,40 +6725,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J28" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K28" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L28" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M28" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O28" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P28" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="S28" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="T28" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6759,19 +6770,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6780,40 +6791,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J29" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L29" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M29" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N29" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O29" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="P29" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S29" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6825,7 +6836,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6837,7 +6848,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6846,31 +6857,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J30" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K30" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L30" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M30" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N30" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O30" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P30" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6891,7 +6902,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6903,7 +6914,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6912,40 +6923,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J31" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K31" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L31" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M31" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N31" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O31" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P31" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S31" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T31" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6957,19 +6968,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -6978,40 +6989,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J32" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K32" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L32" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O32" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="P32" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q32" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R32" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="S32" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="T32" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7023,7 +7034,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7035,49 +7046,49 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I33" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="K33" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L33" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M33" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O33" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P33" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q33" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R33" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="S33" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="T33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7089,61 +7100,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I34" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J34" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K34" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L34" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M34" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N34" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O34" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P34" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R34" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="S34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="T34" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7155,19 +7166,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7176,40 +7187,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J35" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K35" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L35" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M35" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N35" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O35" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P35" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q35" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R35" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="S35" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="T35" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7221,10 +7232,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C36" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7233,7 +7244,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7242,40 +7253,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J36" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K36" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L36" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M36" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N36" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O36" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P36" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="S36" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="T36" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7287,19 +7298,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7308,40 +7319,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J37" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K37" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L37" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M37" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N37" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O37" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P37" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S37" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="T37" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7353,19 +7364,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E38" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F38" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7374,38 +7385,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="J38" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M38" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O38" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P38" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Q38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R38" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="S38" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="T38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7417,59 +7428,59 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="J39" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M39" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O39" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="P39" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="Q39" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R39" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="S39" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="T39" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7481,19 +7492,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7502,38 +7513,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J40" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M40" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N40" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O40" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P40" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="Q40" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R40" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="S40" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="T40" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7545,61 +7556,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I41" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J41" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K41" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L41" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M41" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N41" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O41" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="P41" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="S41" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="T41" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7611,59 +7622,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I42" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="J42" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M42" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N42" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O42" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P42" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="S42" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="T42" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7675,45 +7686,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C43" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D43" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="I43" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J43" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K43" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L43" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M43" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N43" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O43" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="P43" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7731,19 +7742,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7752,40 +7763,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J44" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K44" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="L44" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M44" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N44" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O44" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="P44" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="Q44" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R44" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="S44" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="T44" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7797,19 +7808,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7818,40 +7829,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J45" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K45" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L45" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M45" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O45" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="P45" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="S45" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="T45" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7863,19 +7874,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7884,40 +7895,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J46" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K46" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L46" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M46" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="N46" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="O46" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="P46" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="S46" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="T46" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7929,7 +7940,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7939,7 +7950,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7948,40 +7959,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J47" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K47" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="L47" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M47" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N47" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O47" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P47" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Q47" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R47" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="S47" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="T47" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -7993,19 +8004,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8014,40 +8025,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J48" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K48" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L48" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="M48" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="N48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O48" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="P48" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="Q48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R48" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="S48" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="T48" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8059,19 +8070,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8080,31 +8091,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J49" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K49" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L49" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M49" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="N49" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O49" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="P49" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="Q49" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8125,17 +8136,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8144,40 +8155,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J50" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K50" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L50" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M50" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="N50" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O50" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P50" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="S50" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="T50" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8189,19 +8200,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8210,40 +8221,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J51" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K51" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L51" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M51" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O51" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P51" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="Q51" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R51" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="S51" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="T51" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8255,19 +8266,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F52" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8276,40 +8287,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="J52" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="K52" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L52" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M52" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N52" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O52" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P52" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="S52" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="T52" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8321,19 +8332,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8342,40 +8353,40 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="J53" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K53" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="L53" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M53" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N53" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O53" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="P53" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
       </c>
       <c r="R53" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U53" t="s">
         <v>58</v>
@@ -8387,19 +8398,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E54" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F54" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8408,40 +8419,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="J54" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="K54" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="L54" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M54" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N54" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O54" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="P54" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="Q54" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R54" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="S54" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="T54" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8453,19 +8464,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8474,40 +8485,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J55" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K55" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="L55" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="M55" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="N55" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O55" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="P55" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="Q55" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R55" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="S55" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="T55" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8519,17 +8530,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8538,40 +8549,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
+        <v>665</v>
+      </c>
+      <c r="J56" t="s">
+        <v>666</v>
+      </c>
+      <c r="K56" t="s">
+        <v>667</v>
+      </c>
+      <c r="L56" t="s">
+        <v>668</v>
+      </c>
+      <c r="M56" t="s">
+        <v>669</v>
+      </c>
+      <c r="N56" t="s">
+        <v>555</v>
+      </c>
+      <c r="O56" t="s">
+        <v>670</v>
+      </c>
+      <c r="P56" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>234</v>
+      </c>
+      <c r="R56" t="s">
+        <v>660</v>
+      </c>
+      <c r="S56" t="s">
+        <v>661</v>
+      </c>
+      <c r="T56" t="s">
         <v>662</v>
-      </c>
-      <c r="J56" t="s">
-        <v>663</v>
-      </c>
-      <c r="K56" t="s">
-        <v>664</v>
-      </c>
-      <c r="L56" t="s">
-        <v>665</v>
-      </c>
-      <c r="M56" t="s">
-        <v>666</v>
-      </c>
-      <c r="N56" t="s">
-        <v>552</v>
-      </c>
-      <c r="O56" t="s">
-        <v>667</v>
-      </c>
-      <c r="P56" t="s">
-        <v>668</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>231</v>
-      </c>
-      <c r="R56" t="s">
-        <v>657</v>
-      </c>
-      <c r="S56" t="s">
-        <v>658</v>
-      </c>
-      <c r="T56" t="s">
-        <v>659</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8583,61 +8594,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I57" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="J57" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K57" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L57" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="M57" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="N57" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O57" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="P57" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="S57" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="T57" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8649,19 +8660,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8670,40 +8681,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="J58" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="K58" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="L58" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="M58" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="N58" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O58" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="P58" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="S58" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="T58" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8715,19 +8726,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8736,40 +8747,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="J59" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="K59" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="L59" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="M59" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="N59" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O59" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="P59" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="Q59" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R59" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S59" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="T59" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8781,19 +8792,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8802,40 +8813,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J60" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="K60" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L60" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="M60" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="N60" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O60" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="P60" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="Q60" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R60" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="S60" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="T60" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8847,7 +8858,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8859,7 +8870,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8868,40 +8879,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="J61" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="K61" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="L61" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="M61" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="N61" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O61" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="P61" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="Q61" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R61" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="S61" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="T61" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8913,19 +8924,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8934,40 +8945,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="J62" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K62" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="L62" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M62" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="N62" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O62" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="P62" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="Q62" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R62" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="S62" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="T62" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -8979,19 +8990,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9000,40 +9011,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="J63" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K63" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L63" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="M63" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="N63" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O63" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="P63" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="S63" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="T63" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9045,45 +9056,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C64" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D64" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="J64" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="K64" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="L64" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="M64" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="P64" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9101,45 +9112,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C65" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D65" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J65" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K65" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L65" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M65" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="N65" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="O65" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="P65" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9157,17 +9168,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C66" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D66" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9176,40 +9187,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="J66" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="K66" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="L66" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="M66" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="P66" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="S66" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="T66" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9221,19 +9232,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C67" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D67" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9242,40 +9253,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="J67" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="K67" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="L67" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="M67" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="N67" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O67" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="P67" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="S67" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="T67" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9287,19 +9298,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E68" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F68" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9308,40 +9319,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="J68" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="K68" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="L68" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="M68" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="N68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O68" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="P68" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="Q68" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R68" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="S68" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="T68" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9353,61 +9364,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="I69" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="J69" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="K69" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="L69" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="M69" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="N69" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O69" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="P69" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="Q69" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R69" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="S69" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="T69" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9419,19 +9430,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9440,40 +9451,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="J70" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="K70" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="L70" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="M70" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="N70" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="O70" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="P70" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="Q70" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R70" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="S70" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="T70" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9485,19 +9496,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9506,40 +9517,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="J71" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="K71" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="L71" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="M71" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="N71" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O71" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="P71" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="Q71" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R71" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="S71" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="T71" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9551,19 +9562,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9572,40 +9583,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="J72" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="K72" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="L72" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M72" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="N72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O72" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="P72" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="Q72" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R72" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="S72" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="T72" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9617,19 +9628,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9638,40 +9649,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="J73" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="K73" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="L73" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="M73" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="N73" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O73" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="P73" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="S73" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="T73" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9683,19 +9694,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9704,40 +9715,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="J74" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="K74" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="L74" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="M74" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="N74" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O74" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="P74" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="Q74" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R74" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="S74" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="T74" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9749,45 +9760,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C75" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D75" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="J75" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="K75" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="L75" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="M75" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="N75" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="O75" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="P75" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9805,7 +9816,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9817,7 +9828,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9826,40 +9837,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J76" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="K76" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="L76" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="M76" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="N76" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O76" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="P76" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="S76" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="T76" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9871,19 +9882,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C77" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D77" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9892,38 +9903,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="J77" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="M77" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="N77" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O77" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="P77" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="S77" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="T77" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9935,19 +9946,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C78" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D78" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9956,38 +9967,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="J78" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="M78" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="N78" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O78" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="P78" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="S78" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="T78" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -9999,51 +10010,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C79" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="J79" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="K79" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O79" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="P79" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="S79" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="T79" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10055,57 +10066,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C80" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D80" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="J80" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="K80" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="L80" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="M80" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="P80" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="S80" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="T80" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10117,57 +10128,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C81" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D81" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="J81" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="K81" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="L81" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="M81" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="N81" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="O81" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="P81" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="S81" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="T81" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10179,19 +10190,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E82" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F82" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10200,40 +10211,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="J82" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="K82" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="L82" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M82" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="N82" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O82" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="P82" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="Q82" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R82" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="S82" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="T82" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10245,61 +10256,61 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I83" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="J83" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="K83" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="L83" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="M83" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="N83" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O83" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="P83" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="Q83" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R83" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="S83" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="T83" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10311,19 +10322,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10332,40 +10343,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="J84" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="K84" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="L84" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="M84" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="N84" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O84" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="P84" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="S84" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="T84" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10377,19 +10388,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10398,40 +10409,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="J85" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="K85" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="L85" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="M85" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="N85" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O85" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="P85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="Q85" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R85" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="S85" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="T85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10443,61 +10454,61 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I86" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="J86" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="K86" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="L86" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="M86" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="N86" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O86" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="P86" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="Q86" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R86" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="S86" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="T86" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10509,61 +10520,61 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I87" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="J87" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="K87" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="L87" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="M87" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="N87" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O87" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="P87" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="Q87" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R87" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S87" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="T87" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10575,19 +10586,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D88" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10596,38 +10607,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="J88" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="M88" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="N88" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O88" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="P88" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="Q88" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R88" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S88" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T88" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10639,19 +10650,19 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F89" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10660,31 +10671,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="J89" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="K89" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="L89" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="M89" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="N89" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O89" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="P89" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="Q89" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10705,19 +10716,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C90" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D90" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10726,38 +10737,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="J90" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="M90" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="N90" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O90" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="P90" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S90" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="T90" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10769,19 +10780,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C91" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D91" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10790,38 +10801,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="J91" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="M91" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="N91" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O91" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="P91" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="Q91" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R91" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S91" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T91" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10833,19 +10844,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D92" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10854,38 +10865,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="J92" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M92" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="N92" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O92" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="P92" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="Q92" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R92" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S92" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T92" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10897,19 +10908,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C93" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10918,38 +10929,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="J93" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="M93" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="N93" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O93" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="P93" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="Q93" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R93" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S93" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T93" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10961,19 +10972,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -10982,40 +10993,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="J94" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="K94" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="L94" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="M94" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="N94" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O94" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="P94" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="S94" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="T94" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11027,19 +11038,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11048,28 +11059,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="J95" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="K95" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="L95" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="M95" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="N95" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O95" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="P95" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11093,19 +11104,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11114,40 +11125,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="J96" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="K96" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="L96" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="M96" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="N96" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O96" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="P96" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="S96" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="T96" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11159,19 +11170,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11180,40 +11191,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="J97" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="K97" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="L97" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="M97" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="N97" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O97" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="P97" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="Q97" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R97" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="S97" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="T97" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11225,57 +11236,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="C98" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D98" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="I98" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="J98" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="K98" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="L98" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="M98" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="P98" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="S98" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="T98" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11287,61 +11298,61 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I99" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="J99" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="K99" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="L99" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="M99" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="N99" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O99" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="P99" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="Q99" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R99" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="S99" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="T99" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11353,19 +11364,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E100" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11374,40 +11385,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="J100" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="K100" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="L100" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="M100" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="N100" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O100" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="P100" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="Q100" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R100" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="S100" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="T100" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11419,19 +11430,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11440,40 +11451,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="J101" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="K101" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="L101" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="M101" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="N101" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O101" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="P101" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="Q101" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R101" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="S101" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="T101" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11485,19 +11496,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11506,40 +11517,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="J102" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="K102" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="L102" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="M102" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="N102" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O102" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="P102" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="Q102" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R102" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="S102" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="T102" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11551,19 +11562,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11572,40 +11583,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="J103" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="K103" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="L103" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="M103" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="N103" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O103" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="P103" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="S103" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="T103" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11617,7 +11628,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11629,7 +11640,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11638,28 +11649,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="J104" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="K104" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="L104" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="M104" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="N104" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O104" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="P104" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11683,19 +11694,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E105" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11704,40 +11715,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="J105" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="K105" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="L105" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="M105" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="N105" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O105" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="P105" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="Q105" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R105" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="S105" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="T105" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11749,19 +11760,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C106" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D106" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11770,38 +11781,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="J106" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="M106" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="N106" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O106" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="P106" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="S106" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="T106" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11813,19 +11824,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="C107" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D107" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11834,38 +11845,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="J107" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="M107" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="N107" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O107" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="P107" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="S107" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="T107" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11877,10 +11888,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="C108" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
         <v>87</v>
@@ -11889,7 +11900,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11898,40 +11909,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="J108" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="K108" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="L108" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="M108" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="N108" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O108" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="P108" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="Q108" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R108" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="S108" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="T108" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11943,51 +11954,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="J109" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K109" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="O109" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="P109" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="S109" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="T109" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -11999,57 +12010,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="C110" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D110" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="J110" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="K110" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="L110" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="M110" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="N110" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O110" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="P110" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="S110" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="T110" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12061,19 +12072,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12082,40 +12093,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="J111" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="K111" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="L111" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="M111" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="N111" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O111" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="P111" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="Q111" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R111" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="S111" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="T111" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12127,19 +12138,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12148,40 +12159,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="J112" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="K112" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="L112" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="M112" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="N112" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O112" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="P112" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="Q112" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R112" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="S112" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="T112" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12193,7 +12204,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12205,7 +12216,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12214,40 +12225,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="J113" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="K113" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="L113" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="M113" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="N113" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O113" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="P113" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="S113" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="T113" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12259,19 +12270,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D114" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12280,40 +12291,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="J114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="K114" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="L114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="M114" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="N114" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O114" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="P114" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="Q114" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R114" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="S114" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="T114" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12325,19 +12336,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12346,40 +12357,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="J115" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="K115" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="L115" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="M115" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="N115" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O115" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="P115" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="Q115" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R115" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="S115" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="T115" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12391,61 +12402,61 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="E116" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="F116" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I116" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="J116" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="K116" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="L116" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="M116" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="N116" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O116" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="P116" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="Q116" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R116" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="S116" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="T116" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12457,19 +12468,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12478,40 +12489,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="J117" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="K117" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="L117" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="M117" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="N117" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O117" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="P117" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="S117" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="T117" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12523,19 +12534,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12544,40 +12555,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="J118" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="K118" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="L118" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="M118" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="N118" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O118" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="P118" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="S118" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="T118" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12589,19 +12600,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12610,40 +12621,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="J119" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="K119" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="L119" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="M119" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="N119" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O119" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="P119" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="Q119" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R119" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="S119" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="T119" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12655,19 +12666,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12676,40 +12687,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="J120" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="K120" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="L120" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="M120" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="N120" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O120" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="P120" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="Q120" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R120" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="S120" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="T120" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12721,19 +12732,19 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E121" t="s">
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12742,40 +12753,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="J121" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="K121" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="L121" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="M121" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="N121" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O121" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="P121" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="S121" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="T121" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12787,19 +12798,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12808,40 +12819,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="J122" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="K122" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="L122" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="M122" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="N122" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O122" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="P122" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="S122" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="T122" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12853,19 +12864,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12874,40 +12885,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="J123" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="K123" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="L123" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="M123" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="N123" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O123" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="P123" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="S123" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="T123" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12919,19 +12930,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="C124" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D124" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12940,29 +12951,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="J124" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="M124" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="N124" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O124" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="P124" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="Q124" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -12983,10 +12994,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C125" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -12995,7 +13006,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13004,26 +13015,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="J125" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="M125" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="N125" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O125" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="P125" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13047,17 +13058,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13066,40 +13077,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="J126" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="K126" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="L126" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="M126" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="N126" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O126" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="P126" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="Q126" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R126" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="S126" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="T126" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13111,19 +13122,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E127" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F127" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13132,40 +13143,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="J127" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="K127" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="L127" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="M127" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="N127" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O127" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="P127" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="Q127" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R127" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="S127" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="T127" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13177,19 +13188,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13198,40 +13209,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="J128" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="K128" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="L128" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="M128" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="N128" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O128" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="P128" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="Q128" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R128" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="S128" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="T128" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13243,61 +13254,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I129" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="J129" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="K129" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="L129" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="M129" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="N129" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O129" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="P129" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="Q129" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R129" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="S129" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="T129" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13309,61 +13320,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I130" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="J130" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="K130" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="L130" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="M130" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="N130" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O130" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="P130" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="Q130" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R130" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="S130" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="T130" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13375,61 +13386,61 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="E131" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F131" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I131" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="J131" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="K131" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="L131" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="M131" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="N131" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O131" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="P131" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="Q131" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R131" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S131" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="T131" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13441,7 +13452,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13453,7 +13464,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13462,40 +13473,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="J132" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="K132" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="L132" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="M132" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="N132" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O132" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="P132" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="S132" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="T132" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13507,19 +13518,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13528,40 +13539,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="J133" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="K133" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="L133" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="M133" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="N133" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O133" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="P133" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="S133" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="T133" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13573,19 +13584,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="C134" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="E134" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F134" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13594,38 +13605,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="J134" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="M134" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="N134" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O134" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="P134" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="Q134" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R134" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="S134" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="T134" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13637,19 +13648,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="C135" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D135" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="E135" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F135" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13658,38 +13669,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="J135" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="M135" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="N135" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O135" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="P135" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="Q135" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R135" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="S135" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="T135" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13701,19 +13712,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="C136" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D136" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F136" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13722,38 +13733,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="J136" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="M136" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="N136" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O136" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="P136" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="Q136" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R136" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S136" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="T136" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13765,19 +13776,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="C137" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D137" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13786,38 +13797,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="J137" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="M137" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="N137" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O137" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="P137" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="Q137" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R137" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="S137" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="T137" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13829,57 +13840,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="C138" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D138" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I138" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="J138" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="K138" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="L138" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="M138" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="N138" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O138" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="P138" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="S138" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="T138" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1530">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -353,7 +353,13 @@
     <t xml:space="preserve">Streichung von Art. 22 des Epidemiengesetzes</t>
   </si>
   <si>
+    <t xml:space="preserve">Abrogation de l’art. 22 de la loi sur les épidémies</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stralcio dell’articolo 22 della legge sulle epidemie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l’Assemblée fédérale un projet d’acte législatif prévoyant l’abrogation de l’art.&amp;nbsp;22 de la loi du 28&amp;nbsp;septembre&amp;nbsp;2012 sur les épidémies (LEp).&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, welcher die Streichung von Art. 22 des Epidemiengesetzes (EpG) vorsieht.&amp;nbsp;&lt;/p&gt;</t>
@@ -5440,35 +5446,37 @@
         <v>112</v>
       </c>
       <c r="J8" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L8"/>
+        <v>114</v>
+      </c>
+      <c r="L8" t="s">
+        <v>115</v>
+      </c>
       <c r="M8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N8" t="s">
         <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q8" t="s">
         <v>54</v>
       </c>
       <c r="R8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="T8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -5480,7 +5488,7 @@
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -5501,28 +5509,28 @@
         <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="P9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
@@ -5546,13 +5554,13 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -5565,38 +5573,38 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J10" t="s">
         <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10"/>
       <c r="M10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q10" t="s">
         <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="S10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5608,10 +5616,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5620,7 +5628,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5632,35 +5640,35 @@
         <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="P11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5672,19 +5680,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5693,38 +5701,38 @@
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="S12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5736,19 +5744,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5757,28 +5765,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5802,19 +5810,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5823,38 +5831,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5866,51 +5874,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5922,19 +5930,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5943,38 +5951,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -5986,17 +5994,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6005,40 +6013,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6050,16 +6058,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6071,40 +6079,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="T18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6116,13 +6124,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6137,40 +6145,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R19" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6182,7 +6190,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6194,49 +6202,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="S20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6248,10 +6256,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6260,7 +6268,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6269,40 +6277,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="S21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6314,19 +6322,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6335,40 +6343,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="S22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6380,7 +6388,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -6392,7 +6400,7 @@
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6401,40 +6409,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J23" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K23" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6446,19 +6454,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6467,40 +6475,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N24" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6512,59 +6520,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O25" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="S25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6576,19 +6584,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D26" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6597,38 +6605,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M26" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P26" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="S26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6640,17 +6648,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6659,40 +6667,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J27" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O27" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P27" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S27" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T27" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6704,19 +6712,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6725,40 +6733,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J28" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L28" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O28" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P28" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="S28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="T28" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6770,19 +6778,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6791,40 +6799,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K29" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N29" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O29" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S29" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6836,7 +6844,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6848,7 +6856,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6857,31 +6865,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J30" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M30" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N30" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P30" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6902,7 +6910,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6914,7 +6922,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6923,40 +6931,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="S31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6968,19 +6976,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -6989,40 +6997,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J32" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L32" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O32" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q32" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R32" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="T32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7034,7 +7042,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7046,7 +7054,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7055,40 +7063,40 @@
         <v>101</v>
       </c>
       <c r="I33" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J33" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R33" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="S33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7100,61 +7108,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J34" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K34" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L34" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M34" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N34" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O34" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P34" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R34" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="S34" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="T34" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7166,19 +7174,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7187,40 +7195,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J35" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K35" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L35" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N35" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O35" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P35" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="S35" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="T35" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7232,10 +7240,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C36" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7244,7 +7252,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7253,40 +7261,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N36" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O36" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="P36" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="S36" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="T36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7298,19 +7306,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7319,40 +7327,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J37" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K37" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S37" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T37" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7364,19 +7372,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D38" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F38" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7385,38 +7393,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J38" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M38" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P38" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Q38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R38" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="T38" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7428,19 +7436,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7449,38 +7457,38 @@
         <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J39" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M39" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O39" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P39" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R39" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="S39" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="T39" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7492,19 +7500,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D40" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7513,38 +7521,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M40" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O40" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P40" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Q40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R40" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="S40" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="T40" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7556,61 +7564,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I41" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J41" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L41" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M41" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O41" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="P41" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="S41" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="T41" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7622,59 +7630,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D42" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I42" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J42" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M42" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O42" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P42" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S42" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="T42" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7686,45 +7694,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C43" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D43" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I43" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J43" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K43" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L43" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M43" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N43" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P43" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7742,19 +7750,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7763,40 +7771,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J44" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K44" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L44" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M44" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N44" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O44" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P44" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Q44" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R44" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="S44" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T44" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7808,19 +7816,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7829,40 +7837,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J45" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K45" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L45" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M45" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N45" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O45" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="P45" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="S45" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="T45" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7874,19 +7882,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7895,40 +7903,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J46" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K46" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M46" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O46" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P46" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="S46" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="T46" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7940,7 +7948,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7950,7 +7958,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7959,40 +7967,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K47" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L47" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M47" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N47" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O47" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P47" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R47" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="S47" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="T47" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -8004,19 +8012,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8025,40 +8033,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J48" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K48" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L48" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M48" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O48" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P48" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q48" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R48" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S48" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T48" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8070,19 +8078,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8091,31 +8099,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J49" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K49" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L49" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M49" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O49" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P49" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Q49" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8136,17 +8144,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8155,40 +8163,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J50" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K50" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L50" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="P50" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="S50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="T50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8200,19 +8208,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E51" t="s">
         <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8221,40 +8229,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J51" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="K51" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L51" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M51" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O51" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="P51" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Q51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R51" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="S51" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="T51" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8266,19 +8274,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F52" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8287,40 +8295,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J52" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="K52" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L52" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M52" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O52" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P52" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="S52" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T52" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8332,19 +8340,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8353,28 +8361,28 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J53" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K53" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L53" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M53" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O53" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P53" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
@@ -8398,19 +8406,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E54" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F54" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8419,40 +8427,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J54" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="K54" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L54" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M54" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O54" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="P54" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="Q54" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R54" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="S54" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="T54" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8464,19 +8472,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8485,40 +8493,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J55" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K55" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L55" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M55" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N55" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O55" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P55" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Q55" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R55" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S55" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T55" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8530,17 +8538,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8549,40 +8557,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="J56" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K56" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L56" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M56" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N56" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O56" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P56" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="Q56" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R56" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S56" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T56" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8594,61 +8602,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I57" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="J57" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="K57" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L57" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M57" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N57" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O57" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P57" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="S57" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="T57" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8660,19 +8668,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8681,40 +8689,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="J58" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K58" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="L58" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M58" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N58" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O58" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P58" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="S58" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="T58" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8726,19 +8734,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E59" t="s">
         <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8747,40 +8755,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="J59" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="K59" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="L59" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="M59" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="N59" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O59" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="P59" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="Q59" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R59" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S59" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T59" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8792,19 +8800,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8813,40 +8821,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J60" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K60" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L60" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M60" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N60" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O60" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="P60" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="Q60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R60" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="S60" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="T60" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8858,7 +8866,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8870,7 +8878,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8879,40 +8887,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="J61" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="K61" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="L61" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M61" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N61" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O61" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P61" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Q61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R61" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S61" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T61" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8924,19 +8932,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8945,40 +8953,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J62" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K62" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L62" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M62" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="N62" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O62" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="P62" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="Q62" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R62" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="S62" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="T62" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -8990,19 +8998,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9011,40 +9019,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="J63" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="K63" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="L63" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="M63" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N63" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O63" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="P63" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="S63" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="T63" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9056,45 +9064,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C64" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D64" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="J64" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="K64" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L64" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M64" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="P64" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9112,45 +9120,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C65" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D65" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J65" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K65" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L65" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="M65" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="N65" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="O65" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="P65" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9168,17 +9176,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C66" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D66" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9187,40 +9195,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J66" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="K66" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="L66" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="M66" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="P66" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="S66" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="T66" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9232,19 +9240,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C67" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D67" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9253,40 +9261,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J67" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="K67" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="L67" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="M67" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N67" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O67" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="P67" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="S67" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="T67" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9298,19 +9306,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E68" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F68" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9319,40 +9327,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="J68" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="K68" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="L68" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="M68" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="N68" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O68" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="P68" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="Q68" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R68" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="S68" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="T68" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9364,61 +9372,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I69" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J69" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="K69" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="L69" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M69" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O69" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="P69" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="Q69" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R69" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="S69" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="T69" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9430,19 +9438,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E70" t="s">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9451,40 +9459,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="J70" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="K70" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="L70" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M70" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N70" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O70" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="P70" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="Q70" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R70" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="S70" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="T70" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9496,19 +9504,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9517,40 +9525,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J71" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="K71" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="L71" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="M71" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="N71" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O71" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="P71" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="Q71" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R71" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="S71" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="T71" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9562,19 +9570,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9583,40 +9591,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="J72" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="K72" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="L72" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M72" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O72" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="P72" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="Q72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R72" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="S72" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="T72" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9628,19 +9636,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9649,40 +9657,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="J73" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="K73" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="L73" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="M73" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="N73" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O73" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="P73" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="S73" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="T73" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9694,19 +9702,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9715,40 +9723,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="J74" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="K74" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="L74" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="M74" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="N74" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O74" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="P74" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="Q74" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R74" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="S74" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="T74" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9760,45 +9768,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C75" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D75" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="J75" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="K75" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="L75" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M75" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="N75" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="O75" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="P75" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9816,7 +9824,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9828,7 +9836,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9837,40 +9845,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J76" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="K76" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="L76" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="M76" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="N76" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O76" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P76" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="S76" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="T76" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9882,19 +9890,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C77" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D77" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9903,38 +9911,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J77" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="M77" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="N77" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O77" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="P77" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="S77" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="T77" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9946,19 +9954,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C78" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D78" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9967,38 +9975,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="J78" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="M78" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="N78" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O78" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="P78" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="S78" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="T78" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -10010,51 +10018,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C79" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J79" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="K79" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O79" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="P79" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="S79" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="T79" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10066,57 +10074,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C80" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D80" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="J80" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="K80" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="L80" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="M80" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="P80" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="S80" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="T80" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10128,57 +10136,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C81" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D81" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="J81" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K81" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="L81" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="M81" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="N81" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="O81" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="P81" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="S81" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="T81" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10190,19 +10198,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E82" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F82" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10211,40 +10219,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="J82" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="K82" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="L82" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="M82" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="N82" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O82" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="P82" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="Q82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R82" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="S82" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="T82" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10256,19 +10264,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10277,40 +10285,40 @@
         <v>101</v>
       </c>
       <c r="I83" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="J83" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="K83" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="L83" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="M83" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="N83" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O83" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="P83" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="Q83" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R83" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="S83" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="T83" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10322,19 +10330,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10343,40 +10351,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="J84" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="K84" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="L84" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="M84" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="N84" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O84" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="P84" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="S84" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="T84" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10388,19 +10396,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10409,40 +10417,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="J85" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K85" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="L85" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="M85" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="N85" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O85" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="P85" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="Q85" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R85" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="S85" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="T85" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10454,19 +10462,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10475,40 +10483,40 @@
         <v>101</v>
       </c>
       <c r="I86" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="J86" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="K86" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="L86" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="M86" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N86" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O86" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="P86" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="Q86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R86" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="S86" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T86" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10520,19 +10528,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="E87" t="s">
         <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10541,40 +10549,40 @@
         <v>101</v>
       </c>
       <c r="I87" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="J87" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="K87" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="L87" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="M87" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="N87" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O87" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="P87" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="Q87" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R87" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="S87" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T87" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10586,19 +10594,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10607,38 +10615,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="J88" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="M88" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="N88" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O88" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="P88" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="Q88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R88" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10650,7 +10658,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
@@ -10662,7 +10670,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10671,31 +10679,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="J89" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="K89" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="L89" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="M89" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="N89" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O89" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="P89" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="Q89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10716,19 +10724,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C90" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D90" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10737,38 +10745,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="J90" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="M90" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="N90" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O90" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="P90" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S90" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T90" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10780,19 +10788,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D91" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10801,38 +10809,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J91" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="M91" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N91" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O91" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="P91" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="Q91" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R91" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S91" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T91" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10844,19 +10852,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C92" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D92" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10865,38 +10873,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J92" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="M92" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="N92" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O92" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="P92" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="Q92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R92" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10908,19 +10916,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C93" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D93" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10929,38 +10937,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J93" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="M93" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="N93" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O93" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="P93" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="Q93" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R93" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S93" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10972,19 +10980,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -10993,40 +11001,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="J94" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="K94" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="L94" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="M94" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="N94" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O94" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="P94" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="S94" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="T94" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11038,19 +11046,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11059,28 +11067,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J95" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="K95" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="L95" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="M95" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="N95" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O95" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="P95" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11104,19 +11112,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11125,40 +11133,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="J96" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="K96" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="L96" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="M96" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="N96" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O96" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="P96" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="S96" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="T96" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11170,19 +11178,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E97" t="s">
         <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11191,40 +11199,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="J97" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="K97" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="L97" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="M97" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="N97" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O97" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="P97" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="Q97" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R97" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="S97" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="T97" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11236,57 +11244,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C98" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D98" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I98" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="J98" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="K98" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="L98" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="M98" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="P98" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="S98" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="T98" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11298,19 +11306,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11319,40 +11327,40 @@
         <v>101</v>
       </c>
       <c r="I99" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="J99" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="K99" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="L99" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="M99" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="N99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O99" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="P99" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="Q99" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R99" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="S99" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="T99" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11364,19 +11372,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E100" t="s">
         <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11385,40 +11393,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="J100" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="K100" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="L100" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="M100" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="N100" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O100" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="P100" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="Q100" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R100" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="S100" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="T100" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11430,19 +11438,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11451,40 +11459,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="J101" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="K101" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="L101" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="M101" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="N101" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O101" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="P101" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="Q101" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R101" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="S101" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="T101" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11496,19 +11504,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11517,40 +11525,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="J102" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="K102" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="L102" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="M102" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="N102" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O102" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="P102" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="Q102" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R102" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="S102" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="T102" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11562,19 +11570,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11583,40 +11591,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="J103" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="K103" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="L103" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="M103" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="N103" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O103" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="P103" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="S103" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="T103" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11628,7 +11636,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11640,7 +11648,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11649,28 +11657,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="J104" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="K104" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="L104" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="M104" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="N104" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O104" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="P104" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11694,19 +11702,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E105" t="s">
         <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11715,40 +11723,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="J105" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="K105" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="L105" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="M105" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N105" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O105" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="P105" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="Q105" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R105" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S105" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T105" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11760,19 +11768,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C106" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D106" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11781,38 +11789,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="J106" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="M106" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="N106" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O106" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="P106" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S106" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T106" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11824,19 +11832,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D107" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11845,38 +11853,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="J107" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="M107" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="N107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O107" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="P107" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="S107" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="T107" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11888,10 +11896,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D108" t="s">
         <v>87</v>
@@ -11900,7 +11908,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11909,40 +11917,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="J108" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="K108" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="L108" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="M108" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="N108" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O108" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="P108" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="Q108" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R108" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="S108" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="T108" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11954,51 +11962,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C109" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="J109" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="K109" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="O109" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="P109" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="S109" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="T109" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -12010,57 +12018,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C110" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D110" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="J110" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="K110" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="L110" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="M110" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="N110" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O110" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="P110" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="S110" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="T110" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12072,19 +12080,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12093,40 +12101,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="J111" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="K111" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="L111" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="M111" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="N111" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O111" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="P111" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="Q111" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R111" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="S111" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="T111" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12138,19 +12146,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12159,40 +12167,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="J112" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="K112" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="L112" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="M112" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="N112" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O112" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="P112" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="Q112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R112" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="S112" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="T112" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12204,7 +12212,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12216,7 +12224,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12225,40 +12233,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="J113" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="K113" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="L113" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="M113" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="N113" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O113" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="P113" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="S113" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="T113" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12270,19 +12278,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12291,40 +12299,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="J114" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="K114" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="L114" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="M114" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="N114" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O114" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="P114" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="Q114" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R114" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="S114" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="T114" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12336,19 +12344,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12357,40 +12365,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="J115" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="K115" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="L115" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M115" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="N115" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O115" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="P115" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="Q115" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R115" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="S115" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="T115" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12402,19 +12410,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E116" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F116" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12423,40 +12431,40 @@
         <v>101</v>
       </c>
       <c r="I116" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="J116" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="K116" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="L116" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M116" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="N116" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O116" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="P116" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="Q116" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R116" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="S116" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="T116" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12468,19 +12476,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12489,40 +12497,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="J117" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="K117" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="L117" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="M117" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="N117" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O117" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="P117" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="S117" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="T117" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12534,19 +12542,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12555,40 +12563,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="J118" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="K118" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="L118" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="M118" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="N118" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O118" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="P118" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="S118" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="T118" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12600,19 +12608,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12621,40 +12629,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="J119" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="K119" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="L119" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="M119" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="N119" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O119" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="P119" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="Q119" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R119" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="S119" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="T119" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12666,19 +12674,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12687,40 +12695,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="J120" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="K120" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="L120" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="M120" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="N120" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O120" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="P120" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="Q120" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R120" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="S120" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T120" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12732,7 +12740,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
@@ -12744,7 +12752,7 @@
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12753,40 +12761,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="J121" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="K121" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="L121" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="M121" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="N121" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O121" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="P121" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="T121" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12798,19 +12806,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12819,40 +12827,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="J122" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="K122" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="L122" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="M122" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="N122" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O122" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="P122" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S122" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T122" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12864,19 +12872,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D123" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12885,40 +12893,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="J123" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="K123" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="L123" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="M123" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="N123" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O123" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="P123" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="S123" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="T123" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12930,19 +12938,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D124" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12951,29 +12959,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="J124" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="M124" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="N124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O124" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="P124" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="Q124" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -12994,10 +13002,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C125" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -13006,7 +13014,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13015,26 +13023,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="J125" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="M125" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="N125" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O125" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="P125" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13058,17 +13066,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13077,40 +13085,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J126" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="K126" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="L126" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="M126" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="N126" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O126" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="P126" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="Q126" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R126" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="S126" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="T126" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13122,19 +13130,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E127" t="s">
         <v>100</v>
       </c>
       <c r="F127" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13143,40 +13151,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="J127" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="K127" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L127" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="M127" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="N127" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O127" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="P127" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="Q127" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R127" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="S127" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="T127" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13188,19 +13196,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13209,40 +13217,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="J128" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="K128" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="L128" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="M128" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="N128" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O128" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="P128" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="Q128" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R128" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="S128" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="T128" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13254,61 +13262,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I129" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="J129" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="K129" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="L129" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="M129" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="N129" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O129" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="P129" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="Q129" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R129" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="S129" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="T129" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13320,61 +13328,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I130" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="J130" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="K130" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="L130" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="M130" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="N130" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O130" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="P130" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="Q130" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R130" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="S130" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="T130" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13386,19 +13394,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="E131" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F131" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13407,40 +13415,40 @@
         <v>101</v>
       </c>
       <c r="I131" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="J131" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="K131" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="L131" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="M131" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="N131" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O131" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="P131" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="Q131" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R131" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S131" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T131" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13452,7 +13460,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13464,7 +13472,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13473,40 +13481,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J132" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="K132" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="L132" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="M132" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="N132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O132" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="P132" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="S132" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="T132" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13518,19 +13526,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13539,40 +13547,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="J133" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="K133" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="L133" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="M133" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="N133" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O133" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="P133" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="S133" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="T133" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13584,19 +13592,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C134" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D134" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E134" t="s">
         <v>100</v>
       </c>
       <c r="F134" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13605,38 +13613,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="J134" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="M134" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="N134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O134" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="P134" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="Q134" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R134" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="S134" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="T134" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13648,19 +13656,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C135" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D135" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E135" t="s">
         <v>100</v>
       </c>
       <c r="F135" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13669,38 +13677,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="J135" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="M135" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="N135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O135" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="P135" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="Q135" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R135" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="S135" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="T135" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13712,19 +13720,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C136" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D136" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="E136" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F136" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13733,38 +13741,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="J136" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="M136" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="N136" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O136" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="P136" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="Q136" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R136" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S136" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T136" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13776,19 +13784,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C137" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D137" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13797,38 +13805,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="J137" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="M137" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="N137" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O137" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="P137" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="Q137" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R137" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="S137" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="T137" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13840,57 +13848,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="C138" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D138" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>101</v>
       </c>
       <c r="I138" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="J138" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K138" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="L138" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="M138" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="N138" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O138" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="P138" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="S138" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="T138" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="1532">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -443,6 +443,9 @@
     <t xml:space="preserve">2026-03-12</t>
   </si>
   <si>
+    <t xml:space="preserve">Rechtliche Abklärungen und Potenzial von künstlicher Intelligenz in den Bereichen Polizei und innere Sicherheit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clarifications juridiques et potentiel de l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police et de la sécurité intérieure</t>
   </si>
   <si>
@@ -450,6 +453,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un rapport concernant l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale exposant le potentiel, les bases légales et les limites constitutionnelles, notamment pour la protection de la vie privée. Sur la base de ces conclusions, il devra soumettre au Parlement des lignes directrices pour une utilisation cohérente et conforme aux droits fondamentaux de l’IA dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale, tout en respectant la souveraineté numérique de la Suisse. Le rapport devra notamment :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Démontrer le potentiel et les domaines d’application des technologies d’IA pour rendre la lutte contre la criminalité plus efficace et contribuer à la sauvegarde de la sécurité intérieure.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Analyser le cadre juridique existant pour l’utilisation des technologies d’IA dans le domaine de la sécurité et identifier les éventuelles lacunes du cadre juridique.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Expliquer les limites constitutionnelles à l’utilisation des technologies d’IA dans les domaines de la police et de la sécurité et définir des conditions cadre et les lignes directrices pour l’utilisation de ces technologies.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Démontrer comment les exigences en matière de protection de la vie privée peuvent être satisfaites lors de l'utilisation des technologies d'IA dans les domaines de la police et de la sécurité.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Expliquer comment la souveraineté numérique de la Suisse peut être préservée et la dépendance vis-à-vis des prestataires externes évitée lors de l'acquisition et de l'exploitation des technologies d'IA dans le secteur de la sécurité.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Bericht über den Einsatz künstlicher Intelligenz (KI) in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorzulegen. Der Bericht soll insbesondere das Potenzial, die rechtlichen Grundlagen sowie die verfassungsrechtlichen Grenzen von KI – namentlich in Bezug auf den Schutz der Privatsphäre – darlegen. Auf der Grundlage des Berichts soll der Bundesrat dem Parlament Leitlinien für einen kohärenten und grundrechtskonformen Einsatz von KI in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorlegen, wobei die digitale Souveränität der Schweiz gewahrt werden soll. Der Bericht soll insbesondere:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. das Potenzial und die Anwendungsbereiche von KI-Technologien aufzeigen, um die Bekämpfung der Kriminalität effizienter zu gestalten und die innere Sicherheit zu stärken;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. den bestehenden Rechtsrahmen für den Einsatz von KI-Technologien im Sicherheitsbereich analysieren und allfällige Lücken identifizieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. die verfassungsrechtlichen Grenzen für den Einsatz von KI-Technologien in den Bereichen Polizei und Sicherheit erläutern sowie Rahmenbedingungen und Leitlinien für den Einsatz von KI definieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. aufzeigen, wie die Anforderungen an den Schutz der Privatsphäre beim Einsatz von KI-Technologien im Polizei- und Sicherheitsbereich erfüllt werden können;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. erläutern, wie die digitale Souveränität der Schweiz gewahrt und Abhängigkeiten von externen Anbietern bei der Beschaffung und beim Betrieb von KI-Technologien im Sicherheitsbereich vermieden werden können.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263099</t>
@@ -5637,38 +5643,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="J11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s">
-        <v>145</v>
-      </c>
-      <c r="M11"/>
+        <v>146</v>
+      </c>
+      <c r="M11" t="s">
+        <v>147</v>
+      </c>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="S11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5680,19 +5688,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5701,38 +5709,38 @@
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="S12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="T12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5744,19 +5752,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5765,28 +5773,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5810,19 +5818,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5831,38 +5839,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="S14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="T14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5874,51 +5882,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5930,19 +5938,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" t="s">
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5951,38 +5959,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="S16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -5994,17 +6002,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6013,40 +6021,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="T17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6058,16 +6066,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6079,40 +6087,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6124,13 +6132,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6145,40 +6153,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O19" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="T19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6190,7 +6198,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6202,49 +6210,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="T20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6256,7 +6264,7 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
         <v>141</v>
@@ -6268,7 +6276,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6277,40 +6285,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6322,19 +6330,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6343,40 +6351,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="S22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="T22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6388,7 +6396,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -6400,7 +6408,7 @@
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6409,40 +6417,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N23" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S23" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="T23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6454,19 +6462,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6475,40 +6483,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="T24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6520,59 +6528,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S25" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6584,19 +6592,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6605,26 +6613,26 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J26" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M26" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O26" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P26" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
@@ -6648,17 +6656,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6667,40 +6675,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L27" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M27" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P27" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S27" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T27" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6712,19 +6720,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6733,40 +6741,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J28" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L28" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M28" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="S28" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="T28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6778,19 +6786,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C29" t="s">
         <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6799,40 +6807,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L29" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O29" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P29" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6844,7 +6852,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6856,7 +6864,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6865,31 +6873,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K30" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M30" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N30" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O30" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P30" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6910,7 +6918,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6922,7 +6930,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6931,40 +6939,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="S31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6976,19 +6984,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -6997,40 +7005,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J32" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L32" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N32" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q32" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S32" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T32" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7042,7 +7050,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7054,7 +7062,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7063,40 +7071,40 @@
         <v>101</v>
       </c>
       <c r="I33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O33" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q33" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="S33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="T33" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7108,61 +7116,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I34" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J34" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K34" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L34" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M34" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O34" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P34" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R34" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="S34" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="T34" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7174,19 +7182,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7195,40 +7203,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J35" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L35" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M35" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P35" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R35" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="T35" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7240,10 +7248,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7252,7 +7260,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7261,40 +7269,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L36" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M36" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N36" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P36" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="S36" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="T36" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7306,19 +7314,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7327,40 +7335,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P37" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S37" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T37" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7372,19 +7380,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D38" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E38" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F38" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7393,38 +7401,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J38" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M38" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N38" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O38" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P38" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Q38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R38" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S38" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7436,19 +7444,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7457,38 +7465,38 @@
         <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J39" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M39" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O39" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="P39" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="Q39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R39" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="S39" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="T39" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7500,19 +7508,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7521,38 +7529,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J40" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M40" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O40" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="P40" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="Q40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R40" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="S40" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="T40" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7564,61 +7572,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J41" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K41" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L41" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M41" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O41" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P41" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="S41" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="T41" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7630,59 +7638,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D42" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I42" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J42" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M42" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N42" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O42" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P42" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="S42" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T42" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7694,45 +7702,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C43" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D43" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I43" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J43" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K43" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M43" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N43" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O43" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P43" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7750,19 +7758,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7771,40 +7779,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J44" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K44" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L44" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M44" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N44" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O44" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P44" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Q44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R44" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="S44" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="T44" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7816,19 +7824,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7837,40 +7845,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J45" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K45" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L45" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M45" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N45" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O45" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="P45" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="S45" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="T45" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7882,19 +7890,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C46" t="s">
         <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7903,40 +7911,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K46" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M46" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N46" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O46" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P46" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="S46" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="T46" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7948,7 +7956,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7958,7 +7966,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7967,40 +7975,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J47" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K47" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L47" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M47" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N47" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O47" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="P47" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Q47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R47" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="S47" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="T47" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -8012,19 +8020,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8033,40 +8041,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J48" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K48" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L48" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M48" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O48" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P48" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="Q48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R48" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="S48" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T48" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8078,19 +8086,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8099,31 +8107,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J49" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K49" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L49" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M49" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O49" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="P49" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Q49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8144,17 +8152,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C50" t="s">
         <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8163,40 +8171,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J50" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M50" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="P50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="S50" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="T50" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8208,19 +8216,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E51" t="s">
         <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8229,40 +8237,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J51" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="K51" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L51" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M51" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N51" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O51" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="P51" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Q51" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R51" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="S51" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="T51" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8274,19 +8282,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F52" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8295,40 +8303,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J52" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="K52" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L52" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M52" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O52" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="P52" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="S52" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="T52" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8340,19 +8348,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8361,28 +8369,28 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J53" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K53" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L53" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M53" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N53" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P53" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
@@ -8406,19 +8414,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E54" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F54" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8427,40 +8435,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J54" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K54" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L54" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M54" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N54" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O54" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="P54" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="Q54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R54" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="S54" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="T54" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8472,19 +8480,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8493,40 +8501,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="J55" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="K55" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L55" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M55" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O55" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="P55" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="Q55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R55" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S55" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T55" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8538,17 +8546,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8557,40 +8565,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J56" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K56" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L56" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="M56" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N56" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O56" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P56" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="Q56" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R56" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S56" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T56" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8602,61 +8610,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C57" t="s">
         <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I57" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="J57" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="K57" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L57" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M57" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N57" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O57" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P57" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="S57" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="T57" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8668,19 +8676,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8689,40 +8697,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J58" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K58" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L58" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M58" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O58" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P58" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="S58" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="T58" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8734,19 +8742,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E59" t="s">
         <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8755,40 +8763,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="J59" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="K59" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L59" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M59" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O59" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="P59" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="Q59" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R59" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S59" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T59" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8800,19 +8808,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8821,40 +8829,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="J60" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K60" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L60" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M60" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N60" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O60" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="P60" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Q60" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R60" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="S60" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="T60" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8866,7 +8874,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8878,7 +8886,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8887,40 +8895,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="J61" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K61" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="L61" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="M61" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="N61" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O61" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="P61" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="Q61" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R61" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S61" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T61" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8932,19 +8940,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8953,40 +8961,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="J62" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K62" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="L62" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M62" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N62" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O62" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="P62" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="Q62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R62" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="S62" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="T62" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -8998,19 +9006,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9019,40 +9027,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J63" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K63" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="L63" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="M63" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N63" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O63" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="P63" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="S63" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="T63" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9064,45 +9072,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C64" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D64" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J64" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K64" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="L64" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M64" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="P64" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9120,45 +9128,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C65" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D65" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J65" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K65" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L65" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M65" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="N65" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O65" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="P65" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9176,17 +9184,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C66" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D66" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9195,40 +9203,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="J66" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="K66" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="L66" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="M66" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="P66" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="S66" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="T66" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9240,19 +9248,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C67" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D67" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9261,40 +9269,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="J67" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="K67" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L67" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="M67" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="N67" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O67" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="P67" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="S67" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="T67" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9306,19 +9314,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E68" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F68" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9327,40 +9335,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="J68" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="K68" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="L68" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="M68" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="N68" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O68" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="P68" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="Q68" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R68" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="S68" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="T68" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9372,61 +9380,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="I69" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="J69" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="K69" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="L69" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M69" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N69" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O69" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="P69" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="Q69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R69" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="S69" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="T69" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9438,19 +9446,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E70" t="s">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9459,40 +9467,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="J70" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="K70" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="L70" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="M70" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="N70" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O70" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="P70" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="Q70" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R70" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="S70" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="T70" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9504,19 +9512,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9525,40 +9533,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J71" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="K71" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="L71" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="M71" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="N71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O71" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="P71" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="Q71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R71" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="S71" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="T71" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9570,19 +9578,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9591,40 +9599,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="J72" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="K72" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L72" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="M72" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="N72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O72" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="P72" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="Q72" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R72" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="S72" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="T72" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9636,19 +9644,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D73" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9657,40 +9665,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="J73" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="K73" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="L73" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="M73" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="N73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O73" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="P73" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="S73" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="T73" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9702,19 +9710,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9723,40 +9731,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="J74" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="K74" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="L74" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="M74" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="N74" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O74" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="P74" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="Q74" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R74" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="S74" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="T74" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9768,45 +9776,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C75" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D75" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="J75" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="K75" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="L75" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="M75" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N75" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O75" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="P75" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9824,7 +9832,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9836,7 +9844,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9845,40 +9853,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J76" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="K76" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="L76" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="M76" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="N76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O76" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="P76" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="S76" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="T76" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9890,19 +9898,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C77" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D77" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9911,38 +9919,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="J77" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="M77" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="N77" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O77" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="P77" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="S77" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="T77" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9954,19 +9962,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C78" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D78" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9975,38 +9983,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="J78" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="M78" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="N78" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O78" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="P78" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="S78" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="T78" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -10018,51 +10026,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="J79" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="K79" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O79" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="P79" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="S79" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="T79" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10074,57 +10082,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C80" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D80" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="J80" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="K80" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="L80" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M80" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="P80" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="S80" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="T80" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10136,57 +10144,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C81" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D81" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J81" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="K81" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="L81" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="M81" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="N81" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O81" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="P81" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="S81" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="T81" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10198,19 +10206,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E82" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F82" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10219,40 +10227,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="J82" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="K82" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="L82" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="M82" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="N82" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O82" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="P82" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="Q82" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R82" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="S82" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="T82" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10264,19 +10272,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10285,40 +10293,40 @@
         <v>101</v>
       </c>
       <c r="I83" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="J83" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K83" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="L83" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="M83" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="N83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O83" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="P83" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="Q83" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R83" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="S83" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="T83" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10330,19 +10338,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10351,40 +10359,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="J84" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="K84" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="L84" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="M84" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="N84" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O84" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="P84" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="S84" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="T84" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10396,19 +10404,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10417,40 +10425,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="J85" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="K85" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="L85" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="M85" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="N85" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O85" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="P85" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="Q85" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R85" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="S85" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="T85" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10462,19 +10470,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10483,40 +10491,40 @@
         <v>101</v>
       </c>
       <c r="I86" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="J86" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="K86" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="L86" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="M86" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="N86" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O86" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="P86" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="Q86" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R86" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="S86" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="T86" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10528,19 +10536,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="E87" t="s">
         <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10549,40 +10557,40 @@
         <v>101</v>
       </c>
       <c r="I87" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="J87" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="K87" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="L87" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="M87" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="N87" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O87" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="P87" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="Q87" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R87" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S87" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T87" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10594,19 +10602,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10615,38 +10623,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="J88" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="M88" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="N88" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O88" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="P88" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="Q88" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T88" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10658,7 +10666,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
@@ -10670,7 +10678,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10679,31 +10687,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="J89" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="K89" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="L89" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="M89" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="N89" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O89" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="P89" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="Q89" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10724,19 +10732,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C90" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D90" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10745,38 +10753,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="J90" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="M90" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="N90" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O90" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="P90" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S90" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T90" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10788,19 +10796,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10809,38 +10817,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="J91" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="M91" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="N91" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O91" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="P91" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="Q91" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R91" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S91" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T91" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10852,19 +10860,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D92" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10873,38 +10881,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="J92" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="M92" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="N92" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O92" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="P92" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Q92" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S92" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T92" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10916,19 +10924,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D93" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10937,38 +10945,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="J93" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="M93" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="N93" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O93" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="P93" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="Q93" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S93" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T93" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10980,19 +10988,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11001,40 +11009,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="J94" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K94" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="L94" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="M94" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="N94" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O94" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="P94" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="S94" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="T94" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11046,19 +11054,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11067,28 +11075,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="J95" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="K95" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="L95" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="M95" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="N95" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O95" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="P95" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11112,19 +11120,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11133,40 +11141,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="J96" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="K96" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="L96" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="M96" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="N96" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O96" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="P96" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="S96" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="T96" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11178,19 +11186,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E97" t="s">
         <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11199,40 +11207,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="J97" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="K97" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="L97" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="M97" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="N97" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O97" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="P97" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="Q97" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R97" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="S97" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="T97" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11244,57 +11252,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C98" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D98" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I98" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="J98" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="K98" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="L98" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="M98" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="P98" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="S98" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="T98" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11306,19 +11314,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11327,40 +11335,40 @@
         <v>101</v>
       </c>
       <c r="I99" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="J99" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="K99" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="L99" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="M99" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="N99" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O99" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="P99" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="Q99" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R99" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="S99" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="T99" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11372,19 +11380,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E100" t="s">
         <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11393,40 +11401,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="J100" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="K100" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="L100" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="M100" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="N100" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O100" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="P100" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="Q100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R100" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="S100" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="T100" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11438,19 +11446,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11459,40 +11467,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="J101" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="K101" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L101" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="M101" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="N101" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O101" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="P101" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="Q101" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R101" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="S101" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="T101" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11504,19 +11512,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11525,40 +11533,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="J102" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="K102" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="L102" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="M102" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="N102" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O102" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="P102" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="Q102" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R102" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="S102" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="T102" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11570,19 +11578,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11591,40 +11599,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="J103" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="K103" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="L103" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="M103" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="N103" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O103" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="P103" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="S103" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="T103" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11636,7 +11644,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11648,7 +11656,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11657,28 +11665,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="J104" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="K104" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="L104" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="M104" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="N104" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O104" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="P104" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11702,19 +11710,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E105" t="s">
         <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11723,40 +11731,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="J105" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="K105" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="L105" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="M105" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="N105" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O105" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="P105" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="Q105" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R105" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S105" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T105" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11768,19 +11776,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C106" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D106" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11789,38 +11797,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="J106" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="M106" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="N106" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O106" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="P106" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S106" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T106" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11832,19 +11840,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C107" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D107" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11853,38 +11861,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="J107" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="M107" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="N107" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O107" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="P107" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="S107" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="T107" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11896,7 +11904,7 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C108" t="s">
         <v>141</v>
@@ -11908,7 +11916,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11917,40 +11925,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J108" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="K108" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="L108" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="M108" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="N108" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O108" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="P108" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="Q108" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R108" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="S108" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="T108" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11962,51 +11970,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C109" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="J109" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="K109" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="O109" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="P109" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="S109" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="T109" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -12018,57 +12026,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C110" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D110" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="J110" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="K110" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="L110" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="M110" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="N110" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O110" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="P110" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="S110" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="T110" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12080,19 +12088,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12101,40 +12109,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="J111" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="K111" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="L111" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="M111" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="N111" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O111" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="P111" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="Q111" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R111" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="S111" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="T111" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12146,19 +12154,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12167,40 +12175,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="J112" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="K112" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="L112" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="M112" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="N112" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O112" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="P112" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="Q112" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R112" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="S112" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="T112" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12212,7 +12220,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12224,7 +12232,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12233,40 +12241,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="J113" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="K113" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="L113" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="M113" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="N113" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O113" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="P113" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="S113" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="T113" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12278,19 +12286,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C114" t="s">
         <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12299,40 +12307,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="J114" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="K114" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="L114" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="M114" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="N114" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O114" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="P114" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="Q114" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R114" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="S114" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="T114" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12344,19 +12352,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12365,40 +12373,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="J115" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="K115" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="L115" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="M115" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="N115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O115" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="P115" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="Q115" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R115" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="S115" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="T115" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12410,19 +12418,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E116" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="F116" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12431,40 +12439,40 @@
         <v>101</v>
       </c>
       <c r="I116" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="J116" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="K116" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="L116" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="M116" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="N116" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O116" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="P116" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="Q116" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R116" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="S116" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="T116" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12476,19 +12484,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12497,40 +12505,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="J117" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="K117" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="L117" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="M117" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="N117" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O117" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="P117" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="S117" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="T117" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12542,19 +12550,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12563,40 +12571,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="J118" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="K118" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="L118" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="M118" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="N118" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O118" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="P118" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="S118" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="T118" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12608,19 +12616,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12629,40 +12637,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="J119" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="K119" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="L119" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="M119" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="N119" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O119" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="P119" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="Q119" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R119" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="S119" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="T119" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12674,19 +12682,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12695,40 +12703,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="J120" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="K120" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="L120" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="M120" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="N120" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O120" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="P120" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="Q120" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R120" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="S120" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="T120" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12740,7 +12748,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
@@ -12752,7 +12760,7 @@
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12761,40 +12769,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="J121" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="K121" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="L121" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="M121" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="N121" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O121" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P121" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S121" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T121" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12806,19 +12814,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12827,40 +12835,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="J122" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="K122" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="L122" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="M122" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="N122" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O122" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="P122" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="S122" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T122" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12872,19 +12880,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C123" t="s">
         <v>141</v>
       </c>
       <c r="D123" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12893,40 +12901,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="J123" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="K123" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="L123" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="M123" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="N123" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O123" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="P123" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="S123" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="T123" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12938,19 +12946,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C124" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D124" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12959,29 +12967,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="J124" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="M124" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="N124" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O124" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="P124" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="Q124" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -13002,10 +13010,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C125" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -13014,7 +13022,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13023,26 +13031,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="J125" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="M125" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="N125" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O125" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="P125" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13066,17 +13074,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13085,40 +13093,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J126" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K126" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="L126" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="M126" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="N126" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O126" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="P126" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="Q126" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R126" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="S126" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="T126" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13130,19 +13138,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E127" t="s">
         <v>100</v>
       </c>
       <c r="F127" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13151,40 +13159,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="J127" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="K127" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="L127" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="M127" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="N127" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O127" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="P127" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="Q127" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R127" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="S127" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="T127" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13196,19 +13204,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13217,40 +13225,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="J128" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="K128" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="L128" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="M128" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="N128" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O128" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="P128" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="Q128" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R128" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="S128" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="T128" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13262,61 +13270,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I129" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J129" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K129" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="L129" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="M129" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="N129" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O129" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="P129" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="Q129" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R129" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="S129" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="T129" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13328,61 +13336,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I130" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J130" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K130" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="L130" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="M130" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="N130" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O130" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="P130" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="Q130" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R130" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="S130" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="T130" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13394,19 +13402,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E131" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F131" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13415,40 +13423,40 @@
         <v>101</v>
       </c>
       <c r="I131" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="J131" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="K131" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="L131" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="M131" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="N131" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O131" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="P131" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="Q131" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R131" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S131" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T131" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13460,7 +13468,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13472,7 +13480,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13481,40 +13489,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="J132" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="K132" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="L132" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="M132" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="N132" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O132" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="P132" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="S132" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="T132" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13526,19 +13534,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13547,40 +13555,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="J133" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="K133" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="L133" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="M133" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="N133" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O133" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="P133" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="S133" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="T133" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13592,19 +13600,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C134" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D134" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E134" t="s">
         <v>100</v>
       </c>
       <c r="F134" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13613,38 +13621,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="J134" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="M134" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="N134" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O134" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="P134" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="Q134" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R134" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="S134" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="T134" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13656,19 +13664,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C135" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D135" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E135" t="s">
         <v>100</v>
       </c>
       <c r="F135" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13677,38 +13685,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="J135" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="M135" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N135" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O135" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="P135" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="Q135" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R135" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="S135" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="T135" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13720,19 +13728,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D136" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="E136" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F136" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13741,38 +13749,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="J136" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="M136" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="N136" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O136" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="P136" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="Q136" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R136" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S136" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T136" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13784,19 +13792,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="C137" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D137" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13805,38 +13813,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="J137" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="M137" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="N137" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O137" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="P137" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="Q137" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R137" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="S137" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="T137" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13848,57 +13856,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="C138" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D138" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>101</v>
       </c>
       <c r="I138" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="J138" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="K138" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="L138" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="M138" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="N138" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O138" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="P138" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="S138" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="T138" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1535">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -321,6 +321,15 @@
   </si>
   <si>
     <t xml:space="preserve">Hochschulfinanzierung mit alternativen Finanzierungsmodellen sichern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quels modèles de financement pour les hautes écoles ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantire il finanziamento delle scuole universitarie attraverso modelli alternativi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Parmi les propositions formulées ci-dessous, lesquelles considère-t-il comme réalisables du point de vue juridique, durables du point de vue de la politique financière et équilibrées du point de vue fédéral, et sur quels éléments fonde-t-il cette appréciation&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelle combinaison d’instruments lui paraît appropriée pour garantir la stabilité à long terme du financement des hautes écoles&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Voit-il un moyen de facturer, dans le cadre de la péréquation financière nationale, une proportion convenue de la partie non couverte des frais liés à un étudiant issu d’un canton sans haute école&amp;nbsp;? Si oui, quelle proportion&amp;nbsp;?&lt;/li&gt;&lt;li&gt;La création d’un fonds alimenté par les éventuels excédents résultant de la distribution des bénéfices de la Banque nationale suisse (BNS), dans le strict respect de l’indépendance de la BNS et des mécanismes de distribution en vigueur, lui paraît-il une piste digne d’intérêt&amp;nbsp;? Si non, pourquoi&amp;nbsp;?&lt;/li&gt;&lt;li&gt;La création d’un fonds de compensation et de stabilité affecté afin d’atténuer les fluctuations du financement des hautes écoles dues à des facteurs structurels et à la politique financière lui paraît-elle judicieuse&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;In diesem Zusammenhang stellen sich folgende Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche der aufgeführten Varianten erachtet der Bundesrat als rechtlich umsetzbar, finanzpolitisch nachhaltig und föderal ausgewogen und wie begründet er seine Einschätzung?&lt;/li&gt;&lt;li&gt;Welche Kombination von Instrumenten erscheint geeignet, um die langfristige Stabilität der Hochschulfinanzierung sicherzustellen?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat im Rahmen des nationalen Finanzausgleichs (NFA) die Möglichkeit, die Unterdeckung zu den Vollkosten für einen Studierenden aus einem Nichthochschulkanton zu einem vereinbarten Teil zur Verrechnung zu bringen? Und zu welchem Teil?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat in einer Fondslösung, gespiesen aus allfälligen Ausschüttungsüberschüssen der&amp;nbsp;Schweizerischen Nationalbank, unter Wahrung der Unabhängigkeit der Nationalbank und der geltenden Ausschüttungsmechanismen, einen möglichen Weg, den es sich zu prüfen lohnt?&amp;nbsp;Falls nein, wieso nicht?&lt;/li&gt;&lt;li&gt;Könnte die Schaffung eines zweckgebundenen Ausgleichs- und Stabilitätsfonds zur Abfederung finanzpolitischer und struktureller Schwankungen in der Hochschulfinanzierung ausgleichend wirken?&lt;/li&gt;&lt;/ol&gt;</t>
@@ -5388,35 +5397,37 @@
         <v>102</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7"/>
+        <v>104</v>
+      </c>
+      <c r="L7" t="s">
+        <v>105</v>
+      </c>
       <c r="M7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N7" t="s">
         <v>51</v>
       </c>
       <c r="O7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="s">
         <v>54</v>
       </c>
       <c r="R7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="T7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -5428,19 +5439,19 @@
         <v>20263120</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
@@ -5449,40 +5460,40 @@
         <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N8" t="s">
         <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q8" t="s">
         <v>54</v>
       </c>
       <c r="R8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="S8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="T8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -5494,7 +5505,7 @@
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -5506,7 +5517,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -5515,28 +5526,28 @@
         <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="P9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
@@ -5560,17 +5571,17 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
         <v>45</v>
@@ -5579,38 +5590,38 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J10" t="s">
         <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L10"/>
       <c r="M10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q10" t="s">
         <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="S10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="T10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5622,10 +5633,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5634,7 +5645,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5643,40 +5654,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5688,19 +5699,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5709,38 +5720,38 @@
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="S12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="T12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5752,19 +5763,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5773,28 +5784,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5818,19 +5829,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5839,38 +5850,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P14" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="S14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="T14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5882,51 +5893,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="P15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5938,19 +5949,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E16" t="s">
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5959,38 +5970,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M16" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N16" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="S16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="T16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -6002,17 +6013,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6021,40 +6032,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L17" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="S17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="T17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6066,16 +6077,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E18" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6087,40 +6098,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K18" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M18" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N18" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O18" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="P18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q18" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R18" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T18" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6132,13 +6143,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6153,40 +6164,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K19" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N19" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R19" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="T19" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6198,7 +6209,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6210,49 +6221,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="T20" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6264,10 +6275,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6276,7 +6287,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6285,40 +6296,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L21" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M21" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N21" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O21" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P21" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="S21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="T21" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6330,19 +6341,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6351,40 +6362,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q22" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="S22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="T22" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6396,19 +6407,19 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6417,40 +6428,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K23" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M23" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N23" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O23" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q23" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R23" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="S23" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="T23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6462,19 +6473,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6483,40 +6494,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N24" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O24" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="P24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="S24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="T24" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6528,59 +6539,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I25" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M25" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N25" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="P25" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="S25" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="T25" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6592,19 +6603,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6613,38 +6624,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J26" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M26" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N26" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O26" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="P26" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="S26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="T26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6656,17 +6667,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6675,40 +6686,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J27" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K27" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L27" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M27" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N27" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P27" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="S27" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="T27" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6720,19 +6731,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6741,40 +6752,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J28" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K28" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L28" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M28" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P28" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="S28" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="T28" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6786,19 +6797,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6807,40 +6818,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J29" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K29" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L29" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M29" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N29" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O29" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P29" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S29" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T29" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6852,7 +6863,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6864,7 +6875,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6873,31 +6884,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J30" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K30" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L30" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M30" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N30" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O30" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P30" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q30" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6918,7 +6929,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6930,7 +6941,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6939,40 +6950,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J31" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K31" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L31" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M31" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O31" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="P31" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="S31" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="T31" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6984,19 +6995,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -7005,40 +7016,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K32" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L32" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M32" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N32" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O32" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="P32" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q32" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R32" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S32" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T32" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7050,7 +7061,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7062,7 +7073,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7071,40 +7082,40 @@
         <v>101</v>
       </c>
       <c r="I33" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J33" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L33" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M33" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N33" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="P33" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q33" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R33" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="S33" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="T33" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7116,61 +7127,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I34" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K34" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L34" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M34" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N34" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="P34" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R34" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="S34" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T34" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7182,19 +7193,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7203,40 +7214,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="J35" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K35" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L35" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M35" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N35" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P35" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Q35" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R35" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="S35" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="T35" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7248,10 +7259,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C36" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7260,7 +7271,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7269,40 +7280,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J36" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K36" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L36" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M36" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N36" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O36" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P36" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="S36" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="T36" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7314,19 +7325,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7335,40 +7346,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J37" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K37" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L37" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M37" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N37" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O37" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="P37" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S37" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="T37" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7380,19 +7391,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E38" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F38" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7401,38 +7412,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J38" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M38" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N38" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O38" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="P38" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Q38" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S38" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7444,19 +7455,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7465,38 +7476,38 @@
         <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J39" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M39" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N39" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O39" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="P39" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="Q39" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R39" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="S39" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="T39" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7508,19 +7519,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7529,38 +7540,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J40" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M40" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N40" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O40" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P40" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="Q40" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R40" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="S40" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="T40" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7572,61 +7583,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I41" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J41" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K41" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L41" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M41" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N41" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O41" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="P41" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="S41" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="T41" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7638,59 +7649,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I42" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J42" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M42" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N42" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O42" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P42" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="S42" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="T42" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7702,45 +7713,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C43" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D43" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I43" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J43" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K43" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L43" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M43" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N43" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O43" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="P43" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7758,19 +7769,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7779,40 +7790,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J44" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K44" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L44" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M44" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N44" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O44" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="P44" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="Q44" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R44" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="S44" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="T44" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7824,19 +7835,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7845,40 +7856,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J45" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K45" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L45" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M45" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N45" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O45" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="P45" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="S45" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="T45" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7890,19 +7901,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7911,40 +7922,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="J46" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K46" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L46" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M46" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N46" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O46" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P46" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="S46" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="T46" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7956,7 +7967,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7966,7 +7977,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7975,40 +7986,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J47" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K47" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L47" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M47" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N47" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O47" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P47" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="Q47" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R47" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="S47" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="T47" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -8020,19 +8031,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8041,40 +8052,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J48" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K48" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L48" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M48" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O48" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="P48" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="Q48" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R48" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="S48" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="T48" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8086,19 +8097,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8107,31 +8118,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J49" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K49" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L49" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M49" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N49" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O49" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="P49" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="Q49" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8152,17 +8163,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8171,40 +8182,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J50" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K50" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L50" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M50" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N50" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O50" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P50" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="S50" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="T50" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8216,19 +8227,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E51" t="s">
         <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8237,40 +8248,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J51" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K51" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L51" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M51" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="N51" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O51" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="P51" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="Q51" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R51" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="S51" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="T51" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8282,19 +8293,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E52" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8303,40 +8314,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="J52" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K52" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L52" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M52" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="N52" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O52" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P52" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="S52" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="T52" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8348,19 +8359,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8369,28 +8380,28 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J53" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K53" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L53" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M53" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="N53" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O53" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="P53" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
@@ -8414,19 +8425,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E54" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F54" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8435,40 +8446,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="J54" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="K54" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="L54" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M54" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N54" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O54" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="P54" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="Q54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R54" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="S54" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="T54" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8480,19 +8491,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8501,40 +8512,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="J55" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="K55" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="L55" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M55" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="N55" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O55" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="P55" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="Q55" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R55" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S55" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="T55" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8546,17 +8557,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8565,40 +8576,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
+        <v>672</v>
+      </c>
+      <c r="J56" t="s">
+        <v>673</v>
+      </c>
+      <c r="K56" t="s">
+        <v>674</v>
+      </c>
+      <c r="L56" t="s">
+        <v>675</v>
+      </c>
+      <c r="M56" t="s">
+        <v>676</v>
+      </c>
+      <c r="N56" t="s">
+        <v>562</v>
+      </c>
+      <c r="O56" t="s">
+        <v>677</v>
+      </c>
+      <c r="P56" t="s">
+        <v>678</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>241</v>
+      </c>
+      <c r="R56" t="s">
+        <v>667</v>
+      </c>
+      <c r="S56" t="s">
+        <v>668</v>
+      </c>
+      <c r="T56" t="s">
         <v>669</v>
-      </c>
-      <c r="J56" t="s">
-        <v>670</v>
-      </c>
-      <c r="K56" t="s">
-        <v>671</v>
-      </c>
-      <c r="L56" t="s">
-        <v>672</v>
-      </c>
-      <c r="M56" t="s">
-        <v>673</v>
-      </c>
-      <c r="N56" t="s">
-        <v>559</v>
-      </c>
-      <c r="O56" t="s">
-        <v>674</v>
-      </c>
-      <c r="P56" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>238</v>
-      </c>
-      <c r="R56" t="s">
-        <v>664</v>
-      </c>
-      <c r="S56" t="s">
-        <v>665</v>
-      </c>
-      <c r="T56" t="s">
-        <v>666</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8610,61 +8621,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C57" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D57" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="I57" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="J57" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K57" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="L57" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M57" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="N57" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O57" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="P57" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="S57" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="T57" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8676,19 +8687,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8697,40 +8708,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="J58" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K58" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L58" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="M58" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="N58" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="P58" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="S58" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="T58" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8742,19 +8753,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E59" t="s">
         <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8763,40 +8774,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J59" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K59" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="L59" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="M59" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="N59" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O59" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="P59" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="Q59" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R59" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S59" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="T59" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8808,19 +8819,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8829,40 +8840,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="J60" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K60" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="L60" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="M60" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="N60" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O60" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="P60" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="Q60" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R60" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="S60" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="T60" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8874,7 +8885,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8886,7 +8897,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8895,40 +8906,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J61" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K61" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L61" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="M61" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="N61" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O61" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="P61" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="Q61" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R61" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S61" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="T61" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8940,19 +8951,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8961,40 +8972,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="J62" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="K62" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="L62" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="M62" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N62" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O62" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="P62" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="Q62" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R62" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="S62" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="T62" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -9006,19 +9017,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9027,40 +9038,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J63" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="K63" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="L63" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="M63" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="N63" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O63" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="P63" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="S63" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="T63" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9072,45 +9083,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C64" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D64" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="J64" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K64" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="L64" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M64" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="P64" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9128,45 +9139,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C65" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D65" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J65" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K65" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L65" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="M65" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="N65" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="O65" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="P65" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9184,17 +9195,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C66" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D66" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9203,40 +9214,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="J66" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="K66" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="L66" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="M66" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="P66" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="S66" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="T66" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9248,19 +9259,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C67" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D67" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9269,40 +9280,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="J67" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="K67" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="L67" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="M67" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="N67" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O67" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="P67" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="S67" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="T67" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9314,19 +9325,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E68" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F68" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9335,40 +9346,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="J68" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="K68" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="L68" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="M68" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="N68" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O68" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="P68" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="Q68" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R68" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="S68" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="T68" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9380,61 +9391,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="I69" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="J69" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="K69" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="L69" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="M69" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="N69" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O69" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="P69" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="Q69" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R69" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="S69" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="T69" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9446,19 +9457,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E70" t="s">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9467,40 +9478,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="J70" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="K70" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="L70" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="M70" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="N70" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O70" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="P70" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="Q70" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R70" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="S70" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="T70" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9512,19 +9523,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9533,40 +9544,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="J71" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="K71" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="L71" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="M71" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="N71" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O71" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="P71" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="Q71" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R71" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="S71" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="T71" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9578,19 +9589,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9599,40 +9610,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="J72" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="K72" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="L72" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="M72" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="N72" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O72" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="P72" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="Q72" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R72" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="S72" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="T72" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9644,19 +9655,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D73" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9665,40 +9676,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="J73" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="K73" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="L73" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="M73" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="N73" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O73" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="P73" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="S73" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="T73" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9710,19 +9721,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9731,40 +9742,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="J74" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="K74" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="L74" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="M74" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="N74" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O74" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="P74" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="Q74" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R74" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="S74" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="T74" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9776,45 +9787,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C75" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D75" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="J75" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="K75" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="L75" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="M75" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="N75" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="O75" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="P75" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9832,7 +9843,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9844,7 +9855,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9853,40 +9864,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J76" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="K76" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="L76" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="M76" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="N76" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O76" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="P76" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="S76" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="T76" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9898,19 +9909,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C77" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D77" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9919,38 +9930,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="J77" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="M77" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="N77" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O77" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="P77" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="S77" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="T77" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9962,19 +9973,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C78" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9983,38 +9994,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="J78" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="M78" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="N78" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O78" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="P78" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="S78" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="T78" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -10026,51 +10037,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="J79" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="K79" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O79" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="P79" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="S79" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="T79" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10082,57 +10093,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C80" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D80" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="J80" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="K80" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="L80" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="M80" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="P80" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="S80" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="T80" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10144,57 +10155,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C81" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D81" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="J81" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="K81" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="L81" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="M81" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="N81" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="O81" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="P81" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="S81" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="T81" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10206,19 +10217,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E82" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F82" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10227,40 +10238,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="J82" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="K82" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="L82" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="M82" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="N82" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O82" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="P82" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="Q82" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R82" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="S82" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="T82" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10272,19 +10283,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10293,40 +10304,40 @@
         <v>101</v>
       </c>
       <c r="I83" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="J83" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="K83" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="L83" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="M83" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="N83" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O83" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="P83" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="Q83" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R83" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="S83" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="T83" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10338,19 +10349,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10359,40 +10370,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="J84" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="K84" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="L84" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="M84" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="N84" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P84" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="S84" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="T84" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10404,19 +10415,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10425,40 +10436,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="J85" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="K85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="L85" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="M85" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="N85" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O85" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P85" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="Q85" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R85" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="S85" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="T85" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10470,19 +10481,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10491,40 +10502,40 @@
         <v>101</v>
       </c>
       <c r="I86" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="J86" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="K86" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L86" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="M86" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="N86" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O86" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="P86" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="Q86" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R86" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="S86" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="T86" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10536,19 +10547,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E87" t="s">
         <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10557,40 +10568,40 @@
         <v>101</v>
       </c>
       <c r="I87" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="J87" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="K87" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="L87" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="M87" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="N87" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O87" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="P87" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="Q87" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R87" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="S87" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="T87" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10602,19 +10613,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D88" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10623,38 +10634,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="J88" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="M88" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="N88" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O88" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="P88" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="Q88" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R88" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S88" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T88" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10666,7 +10677,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
@@ -10678,7 +10689,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10687,31 +10698,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="J89" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="K89" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="L89" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="M89" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="N89" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O89" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="P89" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="Q89" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10732,19 +10743,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C90" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D90" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10753,38 +10764,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="J90" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="M90" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="N90" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O90" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="P90" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S90" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="T90" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10796,19 +10807,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D91" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10817,38 +10828,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="J91" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="M91" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="N91" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O91" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="P91" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="Q91" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R91" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S91" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T91" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10860,19 +10871,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C92" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10881,38 +10892,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="J92" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="M92" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="N92" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O92" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="P92" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="Q92" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R92" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S92" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T92" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10924,19 +10935,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10945,38 +10956,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="J93" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="M93" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="N93" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O93" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="P93" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="Q93" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R93" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S93" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T93" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10988,19 +10999,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11009,40 +11020,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="J94" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="K94" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="L94" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="M94" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="N94" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O94" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="P94" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="S94" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="T94" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11054,19 +11065,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11075,28 +11086,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="J95" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="K95" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="L95" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="M95" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="N95" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O95" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="P95" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11120,19 +11131,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11141,40 +11152,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="J96" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="K96" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="L96" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="M96" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="N96" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O96" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="P96" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="S96" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="T96" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11186,19 +11197,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="E97" t="s">
         <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11207,40 +11218,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="J97" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="K97" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="L97" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="M97" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="N97" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O97" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="P97" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="Q97" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R97" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="S97" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="T97" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11252,57 +11263,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="C98" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D98" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I98" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="J98" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="K98" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="L98" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="M98" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="P98" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="S98" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="T98" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11314,19 +11325,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11335,40 +11346,40 @@
         <v>101</v>
       </c>
       <c r="I99" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="J99" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="K99" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="L99" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="M99" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="N99" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O99" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="P99" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="Q99" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R99" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="S99" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="T99" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11380,19 +11391,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="E100" t="s">
         <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11401,40 +11412,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="J100" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="K100" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="L100" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="M100" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="N100" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O100" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="P100" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="Q100" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R100" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="S100" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="T100" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11446,19 +11457,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11467,40 +11478,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="J101" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="K101" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="L101" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="M101" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="N101" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O101" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="P101" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="Q101" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R101" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="S101" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="T101" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11512,19 +11523,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11533,40 +11544,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="J102" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="K102" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="L102" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="M102" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="N102" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O102" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="P102" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="Q102" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R102" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="S102" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="T102" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11578,19 +11589,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11599,40 +11610,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="J103" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="K103" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="L103" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="M103" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="N103" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O103" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="P103" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="S103" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="T103" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11644,7 +11655,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11656,7 +11667,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11665,28 +11676,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="J104" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="K104" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="L104" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="M104" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="N104" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O104" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="P104" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11710,19 +11721,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E105" t="s">
         <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11731,40 +11742,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="J105" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="K105" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="L105" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="M105" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="N105" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O105" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="P105" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="Q105" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R105" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S105" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="T105" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11776,19 +11787,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="C106" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D106" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11797,38 +11808,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="J106" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="M106" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="N106" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O106" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="P106" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S106" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="T106" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11840,19 +11851,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="C107" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11861,38 +11872,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="J107" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="M107" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="N107" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O107" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="P107" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="S107" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="T107" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11904,10 +11915,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="C108" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D108" t="s">
         <v>87</v>
@@ -11916,7 +11927,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11925,40 +11936,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="J108" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="K108" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="L108" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="M108" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="N108" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O108" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="P108" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="Q108" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R108" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="S108" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="T108" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11970,51 +11981,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="C109" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="J109" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="K109" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="O109" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="P109" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="S109" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="T109" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -12026,57 +12037,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="C110" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D110" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="J110" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="K110" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="L110" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="M110" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="N110" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O110" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="P110" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="S110" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="T110" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12088,19 +12099,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12109,40 +12120,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J111" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="K111" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="L111" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="M111" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="N111" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O111" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="P111" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="Q111" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R111" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="S111" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="T111" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12154,19 +12165,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12175,40 +12186,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="J112" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="K112" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="L112" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="M112" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="N112" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O112" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="P112" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="Q112" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R112" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="S112" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="T112" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12220,7 +12231,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12232,7 +12243,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12241,40 +12252,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="J113" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="K113" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="L113" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="M113" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="N113" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O113" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="P113" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="S113" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="T113" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12286,19 +12297,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12307,40 +12318,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="J114" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="K114" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="L114" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="M114" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="N114" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O114" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="P114" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="Q114" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R114" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="S114" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="T114" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12352,19 +12363,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12373,40 +12384,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="J115" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="K115" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="L115" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="M115" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="N115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O115" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="P115" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="Q115" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R115" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="S115" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="T115" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12418,19 +12429,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E116" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="F116" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12439,40 +12450,40 @@
         <v>101</v>
       </c>
       <c r="I116" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="J116" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="K116" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="L116" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="M116" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="N116" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O116" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="P116" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="Q116" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R116" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="S116" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="T116" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12484,19 +12495,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12505,40 +12516,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="J117" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="K117" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="L117" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="M117" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="N117" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O117" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="P117" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="S117" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="T117" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12550,19 +12561,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12571,40 +12582,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="J118" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="K118" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="L118" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="M118" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="N118" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O118" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="P118" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="S118" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="T118" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12616,19 +12627,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12637,40 +12648,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="J119" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="K119" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="L119" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="M119" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="N119" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O119" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="P119" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="Q119" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R119" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="S119" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="T119" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12682,19 +12693,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12703,40 +12714,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="J120" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="K120" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="L120" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="M120" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="N120" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O120" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="P120" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="Q120" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R120" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S120" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="T120" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12748,19 +12759,19 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
       </c>
       <c r="D121" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E121" t="s">
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12769,40 +12780,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="J121" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="K121" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="L121" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="M121" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="N121" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O121" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="P121" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S121" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T121" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12814,19 +12825,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12835,40 +12846,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="J122" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="K122" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="L122" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="M122" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="N122" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O122" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="P122" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="S122" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="T122" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12880,19 +12891,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="C123" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D123" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12901,40 +12912,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="J123" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="K123" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="L123" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="M123" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="N123" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O123" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="P123" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="S123" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="T123" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12946,19 +12957,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D124" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12967,29 +12978,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="J124" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="M124" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="N124" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O124" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="P124" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="Q124" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -13010,10 +13021,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C125" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -13022,7 +13033,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13031,26 +13042,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="J125" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="M125" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="N125" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O125" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="P125" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13074,17 +13085,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13093,40 +13104,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="J126" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="K126" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="L126" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="M126" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="N126" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O126" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="P126" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="Q126" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R126" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="S126" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="T126" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13138,19 +13149,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E127" t="s">
         <v>100</v>
       </c>
       <c r="F127" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13159,40 +13170,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="J127" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="K127" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="L127" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="M127" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="N127" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O127" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="P127" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="Q127" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R127" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="S127" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="T127" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13204,19 +13215,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13225,40 +13236,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="J128" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="K128" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="L128" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="M128" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="N128" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O128" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="P128" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="Q128" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R128" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="S128" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="T128" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13270,61 +13281,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="I129" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="J129" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="K129" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="L129" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="M129" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="N129" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O129" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="P129" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="Q129" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R129" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="S129" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="T129" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13336,61 +13347,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="I130" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="J130" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="K130" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="L130" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="M130" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="N130" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O130" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="P130" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="Q130" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R130" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="S130" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="T130" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13402,19 +13413,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="E131" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F131" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13423,40 +13434,40 @@
         <v>101</v>
       </c>
       <c r="I131" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="J131" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="K131" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="L131" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="M131" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="N131" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O131" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="P131" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="Q131" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R131" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S131" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="T131" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13468,7 +13479,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13480,7 +13491,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13489,40 +13500,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="J132" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="K132" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="L132" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="M132" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="N132" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O132" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="P132" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="S132" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="T132" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13534,19 +13545,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13555,40 +13566,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="J133" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="K133" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="L133" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="M133" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="N133" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O133" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="P133" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="S133" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="T133" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13600,19 +13611,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="C134" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D134" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="E134" t="s">
         <v>100</v>
       </c>
       <c r="F134" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13621,38 +13632,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="J134" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="M134" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="N134" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O134" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="P134" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="Q134" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R134" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="S134" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="T134" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13664,19 +13675,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="C135" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D135" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="E135" t="s">
         <v>100</v>
       </c>
       <c r="F135" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13685,38 +13696,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="J135" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="M135" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="N135" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O135" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="P135" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="Q135" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R135" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="S135" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="T135" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13728,19 +13739,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="C136" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D136" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="E136" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F136" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13749,38 +13760,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="J136" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="M136" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="N136" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O136" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="P136" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="Q136" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R136" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S136" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="T136" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13792,19 +13803,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="C137" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D137" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13813,38 +13824,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="J137" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="M137" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="N137" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O137" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="P137" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="Q137" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R137" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="S137" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="T137" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13856,57 +13867,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="C138" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D138" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>101</v>
       </c>
       <c r="I138" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="J138" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="K138" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="L138" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="M138" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="N138" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O138" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="P138" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="S138" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="T138" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -359,13 +359,13 @@
     <t xml:space="preserve">2026-03-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Streichung von Art. 22 des Epidemiengesetzes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abrogation de l’art. 22 de la loi sur les épidémies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stralcio dell’articolo 22 della legge sulle epidemie</t>
+    <t xml:space="preserve">Streichung von Artikel 22 des Epidemiengesetzes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrogation de l'article 22 de la loi sur les épidémies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stralcio dell'articolo 22 della legge sulle epidemie</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l’Assemblée fédérale un projet d’acte législatif prévoyant l’abrogation de l’art.&amp;nbsp;22 de la loi du 28&amp;nbsp;septembre&amp;nbsp;2012 sur les épidémies (LEp).&amp;nbsp;&lt;/p&gt;</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">Rechtliche Abklärungen und Potenzial von künstlicher Intelligenz in den Bereichen Polizei und innere Sicherheit</t>
   </si>
   <si>
-    <t xml:space="preserve">Clarifications juridiques et potentiel de l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police et de la sécurité intérieure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiarimenti giuridici e potenzialità dell’impiego dell’intelligenza artificiale (IA) nei settori della polizia e della sicurezza interna</t>
+    <t xml:space="preserve">Clarifications juridiques et potentiel de l'utilisation de l'intelligence artificielle (IA) dans les domaines de la police et de la sécurité intérieure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiarimenti giuridici e potenzialità dell'impiego dell'intelligenza artificiale (IA) nei settori della polizia e della sicurezza interna</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un rapport concernant l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale exposant le potentiel, les bases légales et les limites constitutionnelles, notamment pour la protection de la vie privée. Sur la base de ces conclusions, il devra soumettre au Parlement des lignes directrices pour une utilisation cohérente et conforme aux droits fondamentaux de l’IA dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale, tout en respectant la souveraineté numérique de la Suisse. Le rapport devra notamment :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Démontrer le potentiel et les domaines d’application des technologies d’IA pour rendre la lutte contre la criminalité plus efficace et contribuer à la sauvegarde de la sécurité intérieure.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Analyser le cadre juridique existant pour l’utilisation des technologies d’IA dans le domaine de la sécurité et identifier les éventuelles lacunes du cadre juridique.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Expliquer les limites constitutionnelles à l’utilisation des technologies d’IA dans les domaines de la police et de la sécurité et définir des conditions cadre et les lignes directrices pour l’utilisation de ces technologies.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Démontrer comment les exigences en matière de protection de la vie privée peuvent être satisfaites lors de l'utilisation des technologies d'IA dans les domaines de la police et de la sécurité.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Expliquer comment la souveraineté numérique de la Suisse peut être préservée et la dépendance vis-à-vis des prestataires externes évitée lors de l'acquisition et de l'exploitation des technologies d'IA dans le secteur de la sécurité.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="1541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -629,2914 +629,2917 @@
     <t xml:space="preserve">Costituzioni rivedute dei Cantoni di Berna, Glarona, Neuchâtel, Ginevra e Giura. Conferimento</t>
   </si>
   <si>
+    <t xml:space="preserve">Beratung in Kommission des Ständerates abgeschlossen / Fin des discussions en commission du Conseil des Etats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20260030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20260030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berli Rudi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbot der Sömmerung in den grenzüberschreitenden Regionen. Welche Begleitmassnahmen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interdiction de l'estivage dans les régions transfrontalières. Quelles mesures d'accompagnement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le 17 février l'OSAV a décidé une interdiction des estivages dans les régions transfrontalières. Cette mesure préventive contre la dermatose nodulaire contagieuse touche 250 fermes, notamment à Genève, Vaud et Jura et 6000 bovins.&amp;nbsp;&lt;br&gt;Quelles mesures d'accompagnement la Confédération peut-elle garantir rapidement, car la mesure prend effet immédiatement, pour éviter des conséquences économiques dramatiques pour les éleveurs concernés ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 17.&amp;nbsp;Februar 2026 hat das Bundesamt für Lebensmittelsicherheit und Veterinärwesen entschieden, die Sömmerung in den Grenzregionen zu verbieten. Diese Präventionsmassnahme gegen die Lumpy-Skin-Disease betrifft 250&amp;nbsp;Betriebe, hauptsächlich in den Kantonen Genf, Waadt und Jura, sowie 6000&amp;nbsp;Rinder.&amp;nbsp;&lt;br&gt;Angesichts der sofortigen Umsetzung der Massnahme: Welche kurzfristigen Begleitmassnahmen kann der Bund zusichern, um erhebliche wirtschaftliche Folgen für die betroffenen Tierhalterinnen und Tierhalter zu vermeiden?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Agricoltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission des finances Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausrichtung der nächsten Revision des Finanzausgleichsgesetzes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientation de la prochaine révision de la loi sur la péréquation financière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientamento della prossima revisione della legge federale concernente la perequazione finanziaria e la compensazione degli oneri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de soumettre au Parlement, dans le cadre de la prochaine révision de la loi fédérale sur la péréquation financière et la compensation des charges (PFCC), un projet qui :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;prévoie une réduction de la compensation des charges excessives dues à des facteurs socio-démographiques, étant donné que les hypothèses liées à la réforme de la péréquation financière de 2020, qui justifiaient alors l’augmentation de la compensation en question, ne se sont pas vérifiées ;&lt;/li&gt;&lt;li&gt;prévoie une nouvelle répartition des parts de financement entre la Confédération et les cantons à fort potentiel de ressources, en exploitant la marge de manœuvre prévue dans la Constitution fédérale (art. 135 Cst.), selon laquelle les contributions des cantons peuvent se situer dans une fourchette allant de deux tiers à 80&amp;nbsp;% de la contribution fédérale.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Rahmen der nächsten Revision des Bundesgesetzes über den Finanz- und Lastenausgleich (FiLaG) dem Parlament eine Vorlage zu unterbreiten, welche:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;eine Reduktion des soziodemografischen Lastenausgleichs (SLA) vorsieht, da sich die mit der Reform des Finanzausgleichs 2020 verbundenen Annahmen, welche die damalige Aufstockung des SLA rechtfertigten, nicht bestätigt haben;&lt;/li&gt;&lt;li&gt;eine Neuverteilung der Finanzierungsanteile zwischen der Eidgenossenschaft und den finanzstarken Kantonen vorsieht, unter Ausschöpfung des in der Bundesverfassung (Art. 135 BV) vorgesehenen Spielraums, wonach die Beiträge der Kantone zwischen zwei Dritteln und 80 Prozent des Bundesbeitrags betragen können;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bertschy Kathrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pvl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA-Optimierungen durch die Kantone?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les facturations provisoires de l’impôt manquantes permettent-elles aux cantons d'optimiser la RPT ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’assenza di fatture fiscali provvisorie permette ai Cantoni di effettuare ottimizzazioni nella perequazione finanziaria nazionale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le canton de Genève n'a pas encore établi certaines factures fiscales provisoires des années précédentes et doit désormais corriger cette situation. Il en découle, pour la Confédération, des recettes supplémentaires d’environ 600 à 800&amp;nbsp;millions de francs au total (source&amp;nbsp;: https://www.news.admin.ch/fr/newnsb/Y973XYMqlzrucihcHqlyi).&lt;/p&gt;&lt;p&gt;Le canton de Genève n'a pas établi, pour les années 2019 à 2024, de facturation provisoire de l’impôt fédéral direct pour un nombre d’entreprises plus élevé que prévu jusqu’à présent. Or cela va à l’encontre de la législation en la matière, selon laquelle au moins une facturation provisoire doit être établie. L'absence de factures fiscales provisoires peut également avoir une incidence sur le calcul du potentiel de ressources dans le cadre de la péréquation financière entre la Confédération et les cantons, car en l'absence de taxation définitive, ce sont les éléments imposables facturés qui sont pris en compte.&lt;/p&gt;&lt;p&gt;Le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quelles sont les conséquences de ces factures fiscales provisoires que le canton de Genève n’a pas établies sur le potentiel de ressources et sur les paiements compensatoires calculés sur cette base&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les bases de calcul de l'impôt qui ont entraîné des paiements ultérieurs élevés en matière d’impôt fédéral ont-elles été intégrées dans l’assiette fiscale agrégée servant à déterminer le potentiel de ressources et l'indice des ressources, ou le seront-elles encore&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si tel n'est pas le cas, le potentiel de ressources manquant peut-il être ajouté au canton de Genève afin qu'il soit pris en compte dans le calcul des paiements compensatoires pour les périodes suivantes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sont les bases légales et les directives régissant la saisie des bases d'imposition pour la péréquation financière ainsi que le traitement des données erronées et les corrections a posteriori&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Qui vérifie que les cantons respectent les règles relatives à la saisie correcte des bases de calcul du potentiel de ressources&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les cantons disposent-ils d'une marge de manœuvre leur permettant d'optimiser le potentiel de ressources à leur avantage en retardant la facturation ou par d'autres moyens&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Existe-t-il des indications provenant d'autres cantons concernant des possibilités d'optimisation lors du calcul du potentiel de ressources&amp;nbsp;? Si oui, quelles optimisations sont effectuées&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sanctions la Confédération peut-elle prendre à l'encontre des cantons qui ne se conforment pas aux règles lors de la transmission des données nécessaires au calcul du potentiel de ressources&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Kanton Genf hat provisorische Steuerrechnungen der vergangenen Jahre teilweise noch nicht ausgestellt und muss dies nun korrigieren. Für den Bund führt dies zu einmaligen Mehreinnahmen von insgesamt rund 600-800 Millionen Franken (Quelle: https://www.news.admin.ch/de/newnsb/Y973XYMqlzrucihcHqlyi)&lt;/p&gt;&lt;p&gt;Der Kanton Genf hat für die Jahre 2019 bis 2024 in einem grösseren Umfang als angenommen keine provisorischen Steuerrechnungen ausgestellt. Dies widerspricht dem Bundesgesetz über die direkte Bundessteuer, wonach mindestens eine provisorische Steuerrechnung ausgestellt werden muss. Das Fehlen von provisorischen Steuerrechnungen hat womöglich auch Einfluss auf die Berechnung des Ressourcenpotenzials im Ressourcenausgleich zwischen Bund und Kantonen, da bei fehlenden definitiven Veranlagungen die in Rechnung gestellten Steuerfaktoren berücksichtigt werden.&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche Auswirkungen haben diese nicht erfassten provisorischen Steuerrechnungen im Kanton Genf auf das Ressourcenpotenzial und die damit berechneten Ausgleichszahlungen?&lt;/li&gt;&lt;li&gt;Sind die Steuerbemessungsgrundlagen, welche die hohen Nachzahlungen bei der Bundessteuer bewirkt haben, in die aggregierte Steuerbemessungsgrundlage für die Ermittlung des Ressourcenpotenzials und des Ressourcenindexes mit eingeflossen oder werden sie noch einfliessen?&lt;/li&gt;&lt;li&gt;Falls das nicht der Fall ist - kann das fehlende Ressourcenpotenzial dem Kanton Genf nachgetragen werden, so dass es in den Folgeperioden noch für die Berechnung der Ausgleichszahlungen mitberücksichtigt wird?&lt;/li&gt;&lt;li&gt;Welches sind die gesetzlichen Grundlagen und Weisungen für die Erfassung der Steuerbemessungsgrundlagen für den Ressourcenausgleich sowie für die Handhabung von fehlerhaften Datenlieferungen und nachträglichen Korrekturen?&lt;/li&gt;&lt;li&gt;Wer prüft die Einhaltung der Regeln für die korrekte Erfassung der Bemessungsgrundlagen des Ressourcenpotenzials durch die Kantone?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Haben die Kantone einen Spielraum, mit verzögerter Rechnungsstellung oder anderen Aktivitäten das Ressourcenpotenzial zu ihren Gunsten zu optimieren?&lt;/li&gt;&lt;li&gt;Gibt es aus anderen Kantonen Hinweise , über Optimierungsmöglichkeiten bei der Bemessung des Ressourcenpotenzials? Wenn ja, welche Optimierungen werden getätigt?&lt;/li&gt;&lt;li&gt;Welche Sanktionsmöglichkeiten hat der Bund gegenüber Kantonen, die sich bei der Datenlieferung für die Berechnung des Ressourcenpotenzials nicht regelkonform verhalten?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freymond Sylvain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie steht es um die Umsetzung des Gewässerraums?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etat de la mise en oeuvre de l'espace réservé aux eaux ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stato di attuazione dello spazio riservato alle acque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Etat de la mise en œuvre de l’espace réservé aux eaux ?&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quel est l’état d’avancement, canton par canton, de la mise en œuvre de l’espace réservé aux eaux ? Combien de cantons ont finalisé cette planification&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelle est l’estimation actuelle des surfaces agricoles incluses dans l’espace réservé aux eaux à l’échelle nationale&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces surfaces sont-elles déclarées et utilisées&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Wie steht es um die Umsetzung des Gewässerraums?&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie weit ist die Umsetzung des Gewässerraums in den einzelnen Kantonen fortgeschritten? Wie viele Kantone haben die Planung abgeschlossen?&lt;/li&gt;&lt;li&gt;Wie gross ist die geschätzte Landwirtschaftsfläche, die schweizweit im Gewässerraum liegt?&lt;/li&gt;&lt;li&gt;Wie wird diese Fläche deklariert und genutzt?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umwelt|Landwirtschaft|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environnement|Agriculture|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente|Agricoltura|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lagerung von CO2 und nuklearen Abfällen. Gewährleistung der Nachhaltigkeit und Neutralität des Betriebs des Mont-Terri-Felslabors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stockage du CO2 et des déchets nucléaires. Assurer la pérennité et la neutralité de l'exploitation du laboratoire souterrain du Mont Terri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stoccaggio di CO2 e di scorie nucleari. Garantire la continuità e la neutralità nell'esercizio del laboratorio sotterraneo di Mont Terri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les dispositions nécessaires afin que l’exploitation du laboratoire souterrain du Mont Terri demeure assurée par la Confédération.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Il examinera notamment les possibilités suivantes&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Assurer à swisstopo les moyens nécessaires pour assurer l’exploitation du laboratoire souterrain tel qu’il le fait aujourd’hui&lt;/li&gt;&lt;li&gt;Attribuer la gestion du laboratoire à l'Institut fédéral pour la sureté nucléaire (IFSN), à l'Office fédéral de l'environnement (OFEV) ou à l'Office fédéral de l'énergie (OFEN).&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die notwendigen Vorkehrungen zu treffen, damit der Betrieb des Felslabors Mont Terri weiterhin durch den Bund gewährleistet wird.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat soll dabei insbesondere folgende Möglichkeiten prüfen:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Sicherstellung der notwendigen Mittel für Swisstopo, um den Betrieb des Felslabors wie bisher fortzusetzen;&lt;/li&gt;&lt;li&gt;Übertragung der Verwaltung des Labors an das Eidgenössische Institut für Nukleare Sicherheit (ENSI), das Bundesamt für Umwelt (BAFU) oder das Bundesamt für Energie (BFE).&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zugewiesen an die behandelnde Kommission / Attribué à la commission compétente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Umwelt|Energie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Environnement|Énergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Ambiente|Energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prüfung eines spezifischen Straftatbestands zur Bekämpfung mafiaähnlicher Organisationen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examen d'une infraction pénale indépendante visant à combattre des organisations de type mafieux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esame di una fattispecie penale indipendente volta a contrastare le organizzazioni di tipo mafioso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'examiner et d'expliquer dans un rapport que :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;si les dispositions actuelles du droit pénal, en particulier l'article 260ter du Code pénal (organisation criminelle), sont suffisantes pour combattre efficacement les structures mafieuses et similaires à la mafia ;&lt;/li&gt;&lt;li&gt;dans quelle mesure le crime organisé utilisant des méthodes similaires à celles de la mafia (par exemple, intimidation, isolement, infiltration économique, blanchiment d'argent) est insuffisamment couvert par la législation existante ;&lt;/li&gt;&lt;li&gt;si et sous quelle forme l'introduction d'une infraction pénale indépendante (« article mafieux » selon l'Italie, par exemple)– tout en respectant les garanties de l'État de droit – pourrait contribuer à améliorer les forces de l'ordre ;&lt;/li&gt;&lt;li&gt;quelle expérience des autres États (notamment les États européens) existe dans ce domaine et quels éléments pourraient être transférés en Suisse ;&lt;/li&gt;&lt;li&gt;quels effets seraient attendus sur la sécurité intérieure, la situation financière et économique ainsi que la coopération entre la Confédération et les cantons.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, zu prüfen und in einem Bericht zu erläutern:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;ob die geltenden strafrechtlichen Bestimmungen, insbesondere Artikel 260ter des Strafgesetzbuches (kriminelle Organisationen), ausreichen, um mafiöse und mafiähnliche Strukturen wirksam zu bekämpfen;&lt;/li&gt;&lt;li&gt;inwieweit die organisierte Kriminalität, die ähnliche Methoden wie die Mafia anwendet (z. B. Einschüchterung, Isolierung, wirtschaftliche Unterwanderung, Geldwäscherei), durch die bestehenden Rechtsvorschriften nicht ausreichend erfasst ist;&lt;/li&gt;&lt;li&gt;ob und in welcher Form die Einführung eines spezifischen Straftatbestands («Antimafiaparagraf» nach italienischem Vorbild beispielsweise) unter Wahrung der rechtsstaatlichen Garantien zu einer Verbesserung der Strafverfolgung beitragen könnte;&lt;/li&gt;&lt;li&gt;welche Erfahrungen andere Staaten (insbesondere europäische Staaten) in diesem Bereich gemacht haben und welche Elemente auf die Schweiz übertragen werden könnten;&lt;/li&gt;&lt;li&gt;welche Auswirkungen auf die innere Sicherheit, die finanzielle und wirtschaftliche Lage sowie die Zusammenarbeit zwischen Bund und Kantonen zu erwarten wären.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überwiesen an den Bundesrat / Transmis au Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Strafrecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Droit pénal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Diritto penale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z'graggen Heidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzielle Leistungen und Abgeltungen des Bundes an die Kantone für internationale Aufgaben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestations financières et indemnités versées aux cantons pour l’accomplissement de tâches internationales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestazioni finanziarie e indennità della Confederazione ai Cantoni per i compiti internazionali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La Confédération soutient les cantons dans l’accomplissement de tâches ayant un caractère international. Elle leur verse notamment des contributions pour les prestations cantonales fournies en faveur d’organisations et de conférences internationales, de représentations diplomatiques, d’étudiants internationaux et de prestations de transport transfrontalières, ainsi que des contributions d’encouragement dans le cadre de programmes internationaux de coopération (tels qu’Interreg).&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Vue d’ensemble&amp;nbsp;:&lt;br&gt;Quelles ressources financières la Confédération met-elle à la disposition des cantons pour des prestations ayant un caractère international (ventilées par canton)&amp;nbsp;? Je songe en particulier aux prestations suivantes&amp;nbsp;: prestations en faveur d’organisations et de conférences internationales, soutien apporté aux étudiants internationaux, surveillance et protection des ambassades et des représentations diplomatiques internationales, projets d’infrastructures internationaux, prestations de transport transfrontalières, contributions issues de programmes internationaux de coopération (tels qu’Interreg), indemnités versées pour des tâches de protection des ambassades et de protection diplomatique.&lt;/li&gt;&lt;li&gt;Prestations de transport transfrontalières&amp;nbsp;:&lt;br&gt;Des contributions sont-elles versées aux cantons pour le transport international de voyageurs ou de marchandises ou pour d’autres prestations de transport ayant un caractère international&amp;nbsp;? Si oui, quel est le montant de ces contributions&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Autres prestations&amp;nbsp;:&lt;br&gt;Y a-t-il encore d’autres prestations financières que la Confédération verse aux cantons pour l’accomplissement de tâches internationales&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bund unterstützt die Kantone bei der Wahrnehmung von Aufgaben mit internationalem Bezug. Dazu zählen unter anderem Beiträge für kantonale Leistungen zugunsten internationaler Organisationen und Konferenzen, diplomatischer Vertretungen, internationaler Studierender, grenzüberschreitender Verkehrsleistungen sowie Förderbeiträge im Rahmen internationaler Kooperationsprogramme wie Interreg.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten dazu die folgenden Fragen zu beantworten:&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Gesamtübersicht:&lt;br&gt;Welche finanziellen Mittel stellt der Bund den Kantonen für Leistungen mit internationalem Bezug zur Verfügung (nach Kantonen aufgeschlüsselt)? Es geht insbesondere um Leistungen zugunsten internationaler Organisationen und Konferenzen; Unterstützung internationaler Studierender; Bewachung und Schutz internationaler Botschaften und diplomatischer Vertretungen; Internationale Infrastrukturprojekte; Grenzüberschreitende Verkehrsleistungen; Beiträge aus internationalen Kooperationsprogrammen (z. B. Interreg); Abgeltungen oder Entschädigungen für Botschafts- und diplomatische Schutzaufgaben, usw.&lt;/li&gt;&lt;li&gt;Internationale Verkehrsleistungen:&lt;br&gt;Werden Kantonen Beiträge für den grenzüberschreitenden Personen- oder Güterverkehr oder andere international relevante Verkehrsdienstleistungen ausbezahlt? Falls ja, wie hoch sind die Beiträge.&lt;/li&gt;&lt;li&gt;Weitere Leistungen:&lt;br&gt;Gibt es weitere finanziellen Leistungen für internationale Aufgaben die der Bund an die Kantone ausrichtet?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Finanzwesen|Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Finances|Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Finanze|Trasporti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzreferendum auch auf Bundesebene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instaurer un référendum financier à l’échelon fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istituire un referendum finanziario anche a livello federale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l'Assemblée fédérale un projet d'acte législatif prévoyant un référendum financier facultatif et (en option) un référendum financer obligatoire portant sur les nouvelles dépenses uniques – et, en option, sur les dépenses annuelles récurrentes – d'un montant approprié, qui reste à déterminer.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, der ein fakultatives und (optional) ein obligatorisches Finanzreferendum für neue einmalige - und optional für jährlich wiederkehrende - Ausgaben in angemessener, noch zu bestimmender Höhe vorsieht.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inwieweit wird das Thema Salz in der Strategie zur Gesundheitsförderung und Prävention in der Schweiz berücksichtigt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle prise en compte de la question du sel dans la stratégie de promotion de la santé en Suisse ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In che misura la questione del sale viene presa in considerazione nella strategia di promozione della salute in Svizzera?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le lien entre la consommation régulière excessive de sel et le risque augmenté de développer une attaque cérébrale, une maladie coronarienne ou encore une insuffisance cardiaque n'est plus à démontrer.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La quantité excessive de sel consommée quotidiennement se traduit par l'apparition d'une hypertension artérielle, une affection sournoise qui ne fait pas mal et qui est très souvent inconnue du patient. Et chez les patients traités, la compliance thérapeutique est régulièrement insuffisante. Par le nombre de personnes touchées et les complications sérieuses que cette affection peut causer au long cours, il s'agit d'un problème majeur de santé publique. Mais un problème encore largement négligé. On connait les effets néfastes de trop de sucre, encore trop peu les conséquences de l'ingestion de trop de sel.&lt;/p&gt;&lt;p&gt;L'apport excessif de sel peut s'expliquer par un apport volontaire lors des repas, mais souvent il s'agit plutôt de "sel caché", lié à une consommation abusive de sel retrouvé dans des aliments transformés et conditionnés industriellement (plats précuisinés) ou dans la restauration rapide. L'ajout volontaire de sel par l'industrie alimentaire vise une amélioration du goût et implicitement une augmentation des ventes de ces produits industriels.&lt;/p&gt;&lt;p&gt;Cette situation avait déjà été dénoncée dans notre Parlement voilà près de dix ans par une motion du conseiller national Manuel Tornare (16.3601), une motion restée sans suite car classée sans vote après un délai de deux ans.&lt;/p&gt;&lt;p&gt;Une émission télévisée récente (ABE sur la SSR) a une nouvelle fois soulevé la question et tend à démontrer que rien ou peu de choses ont changé face à cette problématique.&lt;/p&gt;&lt;p&gt;Mes questions:&lt;/p&gt;&lt;p&gt;- Quelle est l'appréciation du Conseil fédéral sur la problématique de la consommation abusive de sel par la population en particulier en lien avec les problèmes de santé publique?&lt;/p&gt;&lt;p&gt;- Peut-il nous indiquer quelles mesures ont été prises sur ce sujet durant les dernières années?&lt;/p&gt;&lt;p&gt;- Quelles pressions sont exercées sur l'industrie alimentaire pour réduire "efficacement" la quantité de sel dans les plats précuisinés industriels?&lt;/p&gt;&lt;p&gt;- Le Conseil fédéral est-il prêt à intervenir encore davantage pour répondre efficacement à ce problème?&lt;/p&gt;&lt;p&gt;- Envisage-t-il une campagne nationale d'information et de sensibilisation?&lt;/p&gt;&lt;p&gt;Nous remercions le Conseil fédéral pour ses réponses.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Zusammenhang zwischen regelmässigem übermässigem Salzkonsum und einem erhöhten Risiko für Schlaganfall, koronare Herzkrankheiten oder Herzinsuffizienz ist inzwischen klar belegt.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine zu hohe tägliche Salzaufnahme führt zu Bluthochdruck, einer heimtückischen Erkrankung, die keine Schmerzen verursacht und von den Betroffenen häufig unbemerkt bleibt. Zudem zeigen die Patientinnen und Patienten oft nur eine geringe Bereitschaft, in der Therapie mitzuwirken. Angesichts der hohen Zahl der Betroffenen und der schwerwiegenden, langfristigen Komplikationen stellt dieses Verhalten ein erhebliches Problem für die öffentliche Gesundheit dar&amp;nbsp;– ein Problem, das jedoch nach wie vor weitgehend vernachlässigt wird. Während die gesundheitlichen Risiken von übermässigem Zuckerkonsum allgemein bekannt sind, sind die problematischen Folgen von übermässigem Salzkonsum bisher noch kaum im öffentlichen Fokus.&lt;/p&gt;&lt;p&gt;Übermässiger Salzkonsum kann teilweise durch freiwilliges Nachsalzen bei Mahlzeiten erklärt werden, häufig handelt es sich jedoch um sogenanntes «verstecktes Salz», das in industriell verarbeiteten und abgepackten Lebensmitteln&amp;nbsp;(z.&amp;nbsp;B. Fertiggerichten) oder in Fastfood enthalten ist. Die gezielte Salzbeigabe durch die Lebensmittelindustrie dient vor allem der Geschmacksverbesserung und damit implizit der Steigerung des Absatzes der Produkte.&lt;/p&gt;&lt;p&gt;Diese Sachlage wurde bereits vor fast zehn Jahren im Parlament durch die Motion&amp;nbsp;16.3601 von Nationalrat Manuel&amp;nbsp;Tornare aufgegriffen. Die Motion blieb jedoch ohne Folgen, da sie nach zwei Jahren ohne abschliessende Behandlung im Rat abgeschrieben wurde.&lt;/p&gt;&lt;p&gt;Eine kürzlich ausgestrahlte Fernsehsendung&amp;nbsp;(«A bon entendeur», SRG) hat das Thema erneut beleuchtet und gezeigt, dass sich zu dieser Sachlage bisher wenig bis gar nichts geändert hat.&lt;/p&gt;&lt;p&gt;Ich stelle dem Bundesrat folgende Fragen:&lt;/p&gt;&lt;p&gt;– Wie beurteilt der Bundesrat die Problematik des übermässigen Salzkonsums der Bevölkerung, insbesondere im Zusammenhang mit den Auswirkungen auf die öffentliche Gesundheit?&lt;/p&gt;&lt;p&gt;– Welche Massnahmen wurden in den letzten Jahren in diesem Bereich ergriffen?&lt;/p&gt;&lt;p&gt;– Welcher Druck wird auf die Lebensmittelindustrie ausgeübt, um den Salzgehalt in industriell hergestellten Fertiggerichten wirksam zu reduzieren?&lt;/p&gt;&lt;p&gt;– Ist der Bundesrat bereit, noch stärker zu intervenieren, um das Problem wirksam anzugehen?&lt;/p&gt;&lt;p&gt;– Plant der Bundesrat eine nationale Informations- und Sensibilisierungskampagne?&lt;/p&gt;&lt;p&gt;Besten Dank dem Bundesrat für seine Antworten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Medien und Kommunikation|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Médias et communication|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Media e comunicazione|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alijaj Islam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nationalen Finanzausgleich (NFA) im Bezug auf Sportschulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Péréquation financière nationale et écoles de sport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Que pense le Conseil fédéral des effets de la péréquation financière nationale sur le financement et le développement des écoles de sport cantonales et régionales ? Estime-t-il nécessaire de prendre des mesures pour garantir que les jeunes talents sportifs bénéficient d’un encouragement équivalent quel que soit leur canton de domicile ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Wie beurteilt der Bundesrat die Auswirkungen des Nationalen Finanzausgleichs auf die Finanzierung und Entwicklungsfähigkeit kantonaler und regionaler Sportschulen, und sieht er Handlungsbedarf, um sicherzustellen, dass sportlich talentierte Jugendliche unabhängig vom Wohnkanton gleichwertige Förderbedingungen erhalten?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Soziale Fragen|Bildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Questions sociales|Éducation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Questioni sociali|Formazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeschi Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausschaffungs-Schlendrian: Ausschaffungs-Initiative von 2010 noch immer nicht umgesetzt!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laxisme des autorités : l’initiative sur le renvoi de 2010 n’est toujours pas mise en œuvre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;À en croire le Conseil fédéral (réponse à la question 25.8110) ainsi que les médias (NZZ am Sonntag «Die Deutschschweiz vollzieht Landesverweise konsequenter als die Westschweiz» et Blick «Ausschaffungs-Schlendrian: Romandie zeigt Herz für kriminelle Ausländer»), l’initiative sur le renvoi (&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20090060&amp;amp;data=05%7C02%7CPhilippe.Schwab%40parl.admin.ch%7Ccdb0c7ac59b340180a8108de37cf3690%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639009560266946008%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=vVL%2BUy4Xa%2FvmG4xFHZQnTMEnDBqLzLRhOt3eY%2Bh6ZAY%3D&amp;amp;reserved=0"&gt;09.060&lt;/a&gt;) n’est toujours pas mise en œuvre.&lt;br&gt;- Que fait le Conseil fédéral pour que 100&amp;nbsp;% des expulsions soient exécutées, et ce dans tous les cantons&amp;nbsp;?&lt;br&gt;- Des retenues au niveau de la péréquation financière RPT sont-elles envisageables&amp;nbsp;?&lt;br&gt;Quand la situation devrait-elle s’améliorer&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gemäss Antwort auf die Frage 25.8110 sowie den Berichten in NZZ am Sonntag «Die Deutschschweiz vollzieht Landesverweise konsequenter als die Westschweiz» und Blick «Ausschaffungs-Schlendrian: Romandie zeigt Herz für kriminelle Ausländer» wird die Ausschaffungs-Initiative (&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20090060&amp;amp;data=05%7C02%7CPhilippe.Schwab%40parl.admin.ch%7Ccdb0c7ac59b340180a8108de37cf3690%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639009560266946008%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=vVL%2BUy4Xa%2FvmG4xFHZQnTMEnDBqLzLRhOt3eY%2Bh6ZAY%3D&amp;amp;reserved=0"&gt;09.060&lt;/a&gt;) noch immer nicht umgesetzt.&lt;br&gt;- Was unternimmt der Bundesrat, damit die Vollzugsquoten in allen Kantonen 100 % erreichen?&lt;br&gt;- Sind Kürzungen beim Finanzausgleich (NFA) eine Option?&lt;br&gt;Bis wann sind Verbesserungen zu erwarten?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission de la science, de l'éducation et de la culture Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denkmal-, Heimat- und Ortsbildschutz. Auswirkungen neuer Aufgabenteilungen und Wirksamkeit beschlossener Massnahmen evaluieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protection des monuments, du patrimoine et des sites construits. Évaluer les conséquences d'une nouvelle répartition des tâches et l'efficacité des mesures décidées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservazione dei monumenti storici e protezione del paesaggio e degli insediamenti. Valutare le ripercussioni di una nuova ripartizione dei compiti e l'efficacia delle misure decise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter et d’évaluer le potentiel et les conséquences d’une éventuelle nouvelle répartition des tâches entre la Confédération et les cantons dans le domaine de la protection des monuments, du patrimoine et des sites construits. Il indiquera également s’il est nécessaire de mettre à jour la liste des monuments, ensembles et sites archéologiques d’importance nationale. Le Conseil fédéral prendra aussi en considération l’efficacité du train de mesures qu’il a décidées le 26 septembre 2025 afin de faciliter la construction de logements grâce à l’amélioration et à la précision de l’application de l’Inventaire fédéral des sites construits d’importance nationale à protéger en Suisse (ISOS).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Potenzial und die Auswirkungen einer möglichen neuen Aufgabeteilung zwischen Bund und Kantonen im Bereich Denkmal-, Heimat- und Ortsbildschutzes aufzuzeigen und zu evaluieren sowie den Bedarf einer Bereinigung des Verzeichnisses der Denkmäler, Ensembles und archäologischen Stätten von nationaler Bedeutung aufzuzeigen. Dabei soll der Bundesrat auch die Wirksamkeit seines Massnahmenpakets vom 26.09.2025 zur Erleichterung des Wohnungsbaus durch Verbesserungen und Präzisierungen bei der Anwendung des Bundesinventars der schützenswerten Ortsbilder (ISOS) berücksichtigen.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Kultur|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Culture|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Cultura|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germann Hannes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollumfänglicher Abzug der Krankenversicherungsprämien von der direkten Bundessteuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impôt fédéral direct. Déduction totale des primes d'assurance-maladie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deduzione integrale dei premi per l'assicurazione contro le malattie in ambito di imposta federale diretta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la loi fédérale du 14&amp;nbsp;décembre&amp;nbsp;1990 sur l’impôt fédéral direct comme suit&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art.&amp;nbsp;33 Intérêts passifs et autres réductions&lt;/p&gt;&lt;p&gt;Al&amp;nbsp;1&lt;/p&gt;&lt;p&gt;Sont déduits du revenu&amp;nbsp;:&lt;/p&gt;&lt;p&gt;let. a à f, h et i&amp;nbsp;: inchangées&amp;nbsp;;&lt;/p&gt;&lt;p&gt;let. g&amp;nbsp;: biffer «&amp;nbsp;d’assurances-maladie&amp;nbsp;»&amp;nbsp;;&lt;/p&gt;&lt;p&gt;let.&amp;nbsp;k (nouvelle)&amp;nbsp;: les primes et cotisations d’assurance-maladie privée et obligatoire.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Bundesgesetz über die direkte Bundessteuer (DBG) wie folgt zu ändern:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art. 33 Schuldzinsen und andere Abzüge&lt;/p&gt;&lt;p&gt;Abs. 1&lt;/p&gt;&lt;p&gt;Von den Einkünften werden abgezogen:&lt;/p&gt;&lt;p&gt;Bst. a bis f sowie h und i: bleiben unverändert;&lt;/p&gt;&lt;p&gt;Bst. g: Streichung von "Krankenversicherung";&lt;/p&gt;&lt;p&gt;Bst. k (neu): Prämien und Beiträge für die obligatorische und private Krankenversicherung.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuer|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscalité|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposte|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wettstein Felix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der geografisch-topografische Lastenausgleich muss besser auf tatsächliche Lasten ausgerichtet sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La péréquation financière doit mieux refléter les charges découlant réellement de la géotopographie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La perequazione dell'aggravio geotopografico deve considerare meglio gli oneri effettivi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’exposer dans le rapport sur l’efficacité de la péréquation financière et de la compensation des charges 2026-2029 comment les charges géo-topographiques pourraient être compensées d’une manière plus équitable. Le rapport devra proposer des indicateurs qui tiendront compte mieux que les critères actuels des charges effectives supérieures à la moyenne découlant de facteurs géo-topographiques. Les effets de la péréquation sur les cantons seront présentés graphiquement en fonction de l’indicateur et du coefficient choisis.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Wirksamkeitsbericht zum Finanz- und Lastenausgleich 2026-2029 darzulegen, wie der geografisch-topografische Lastenausgleich fairer berechnet und ausgestaltet werden kann. Der Bericht soll Indikatoren vorschlagen, welche besser als die bisherigen geeignet sind, die tatsächlichen überdurchschnittlichen Lasten aufgrund der Topografie auszuweisen. Je nach gewähltem Indikator und dessen Gewichtung soll tabellarisch dargestellt werden, wie sich eine künftige Verteilung der Ausgleichzahlungen auf die Kantone auswirkt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verlagerung von der Schiene auf die Strasse zwischen der Jurasüdfussachse und dem Genferseebogen nach der Einführung des Fahrplans 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report du rail vers la route entre l'axe du Pied du Jura et l'Arc lémanique à la suite de l'introduction de l'horaire 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasferimento del traffico dalla ferrovia alla strada tra l'asse del versante sud del Giura e l'arco lemanico a seguito dell'introduzione dell'orario 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Depuis plus de 6 mois, l'Alliance des Villes, les Cantons de Suisse Occidentale, les entreprises et des groupes d'habitants de la région du Pied du Jura signalent une détérioration de l’offre ferroviaire sur l’axe du Pied du Jura entre Bienne et Genève, via Yverdon-les-Bains, Morges et Nyon, à l'introduction de l'horaire 2025. La suppression des liaisons ferroviaires directes ou l'allongement des temps de parcours entraînent un transfert croissant vers la route, notamment pour les déplacements professionnels. Certains trajets en train sont passés du simple au double, notamment celui entre Yverdon et Morges, ayant des répercussions sur l'attractivité du transport public. Parallèlement, les flux autoroutiers sur l'échangeur autoroutier semblent avoir considérablement augmenté depuis plusieurs mois.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans le contexte de la politique de transfert modal pour les voyageurs, il est essentiel de pouvoir mesurer l’ampleur de ce phénomène. Je prie dès lors le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Dispose-t-il de données récentes permettant de mesurer l’évolution du nombre de voyageurs ayant délaissé le rail au profit de la route sur le tronçon Bienne–Genève, en particulier depuis la réorganisation de l’horaire 2025 ?&lt;/li&gt;&lt;li&gt;Dispose-t-il de données récentes permettant de mesurer l’augmentation du trafic routier sur cet axe autoroutier (Nord vaudois - La Côte, notamment) ?&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral évalue-t-il l’impact de ce transfert sur les objectifs climatiques, sur les coûts externes du trafic (bruit, pollution, accidents) et sur la qualité de vie des régions concernées ?&lt;/li&gt;&lt;li&gt;D’ici le rétablissement d’une liaison via le bypass avec le tunnel de Gléresse en 2031, quelles mesures le Conseil fédéral entend-il mettre en œuvre pour garantir que la desserte ferroviaire du Pied du Jura retrouve un niveau d’attractivité suffisant afin de respecter les objectifs de transfert rail-route inscrits dans la Constitution ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Seit mehr als sechs Monaten weisen die Städteallianz, die Westschweizer Kantone, Unternehmen und Bewohnergruppen der Jurasüdfuss-Region auf eine Verschlechterung des Bahnangebots auf der Jurasüdfuss-Achse zwischen Biel und Genf via Yverdon-les-Bains, Morges und Nyon nach der Einführung des Fahrplans 2025 hin. Die Abschaffung direkter Zugverbindungen oder längere Fahrtzeiten führen zu einer zunehmenden Verlagerung auf die Strasse, insbesondere beim Arbeitsverkehr. Einige Zugfahrten dauern inzwischen doppelt so lange, insbesondere die Fahrt von Yverdon nach Morges, was den öffentlichen Verkehr weniger attraktiv macht. Gleichzeitig scheint der Verkehr auf dem Autobahnkreuz seit einigen Monaten erheblich zugenommen zu haben.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im Zusammenhang mit der Verlagerungspolitik ist es entscheidend, das Ausmass der erwähnten Entwicklung zu quantifizieren. Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Verfügt der Bundesrat über aktuelle Daten, die es ermöglichen, die Entwicklung der Zahl der Reisenden zu verfolgen, die auf der Strecke Biel–Genf von der Schiene auf die Strasse umgestiegen sind, insbesondere seit der Einführung des Fahrplans 2025?&lt;/li&gt;&lt;li&gt;Verfügt er über aktuelle Daten, die es ermöglichen, die Zunahme des Strassenverkehrs auf dieser Autobahnachse (insbesondere Nordwaadt‒La Côte) zu quantifizieren?&lt;/li&gt;&lt;li&gt;Wie bewertet der Bundesrat die Auswirkungen der erwähnten Verlagerung auf die Klimaziele, die externen Kosten des Verkehrs (Lärm, Verschmutzung, Unfälle) und die Lebensqualität in den betroffenen Regionen?&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat bis zur Wiederherstellung einer Verbindung mit dem Ligerztunnel im Jahr 2031 umzusetzen, um zu gewährleisten, dass die Bahnanbindung des Jurasüdfusses wieder genug attraktiv wird, damit die verfassungsmässigen Vorgaben zur Verkehrsverlagerung erfüllt werden.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importverbot für chemisch behandeltes Geflügelfleisch ("Chlorhühner") gesetzlich verankern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscrire dans la loi l'interdiction d'importer de la viande de volaille traitée chimiquement ("poulet au chlore")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introdurre nella legge il divieto di importare carne di pollame trattata chimicamente ("pollo al cloro")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’inscrire dans la loi sur l’agriculture (LAgr) et dans la loi sur les denrées alimentaires (LDAI) une disposition explicite interdisant durablement l’importation en Suisse de viande et de produits de volaille traités chimiquement – notamment au chlore.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Landwirtschaftsgesetz und im Lebensmittelgesetz eine eindeutige Regelung zu verankern, die die Einfuhr von chemisch behandeltem Geflügelfleisch&amp;nbsp;– insbesondere mit Chlor&amp;nbsp;– in die Schweiz dauerhaft untersagt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Landwirtschaft|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Agriculture|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Agricoltura|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfister Gerhard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesetzeswidrige Umsetzung von Steuerrabatten im Kanton Waadt und mögliche Auswirkungen auf den NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en oeuvre illégale de rabais fiscaux dans le canton de Vaud et conséquences possibles sur la péréquation financière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attuazione illegale di riduzioni di imposta nel Cantone di Vaud e possibili ripercussioni sulla perequazione finanziaria nazionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Dans le cadre de la mise en œuvre non conforme à la loi de rabais fiscaux dans le canton de Vaud entre 2009 et 2021, je demande au Conseil fédéral de répondre aux questions suivantes.&lt;/p&gt;&lt;p&gt;1. A-t-il été informé des pertes injustifiées subies par la caisse de l’État du canton de Vaud&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. La Confédération a-t-elle également subi des pertes, et si oui, de quel montant&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3. La Confédération a-t-elle prévu de procéder à une enquête dans le but de déterminer si les prélèvements fiscaux systématiquement trop bas ont faussé la répartition de la perception de l’impôt dans le cadre de la péréquation financière (RPT)&amp;nbsp;?&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral est-il prêt à établir un rapport montrant quelles ont été les conséquences financières de la pratique fiscale illégale du canton de Vaud sur le calcul et le montant de la RPT et sur les éventuelles répercussions sur les contributions d’autres cantons et de la Confédération&amp;nbsp;?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In Zusammenhang mit der nicht gesetzeskonformen Umsetzung von Steuerrabatten im Kanton Waadt zwischen 2009 und 2021 bitte ich den Bundesrat um die Beantwortung folgender Fragen.&lt;/p&gt;&lt;p&gt;1. Ist der Bundesrat informiert worden über die unberechtigt erfolgten Ausfälle zulasten der Staatskasse des Kantons Waadt?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Entstanden dem Bund ebenfalls Ausfälle, wenn ja, in welcher Höhe?&lt;/p&gt;&lt;p&gt;3. Ist eine Untersuchung seitens des Bundes vorgesehen, ob die systematisch zu tiefen Steuererhebungen die Bundesmittelverteilung im NFA verzerrt haben?&lt;/p&gt;&lt;p&gt;4. Ist der Bundesrat bereit, einen Bericht zu erstellen, in dem er aufzeigt, welche finanziellen Auswirkungen die gesetzwidrige Steuerpraxis des Kantons Waadt hatte auf die Berechnung und die Höhe der Ausgleichszahlen im NFA, und ob dadurch die Beiträge anderer Kantone und des Bundes beeinflusst wurden?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrie im Jurabogen. Wie kann man dieser Region, die immer wieder von Krisen heimgesucht wird, nachhaltig helfen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrie de l'Arc jurassien. Comment venir en aide durablement à cette région régulièrement touchée par des crises successives ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settore industriale dell'arco giurassiano. Come aiutare una regione colpita da crisi ricorrenti?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;A intervalles réguliers et de plus en plus récurrents, les entreprises industrielles de l'Arc jurassien sont confrontées à des défis énormes qui pourraient à terme voir disparaître plusieurs fleurons de l'économie régionale et nationale. Nous traversons à nouveau une zone de fortes turbulences liées à un ralentissement économique marqué, accentué par la problématique des droits de douane américains. La situation est particulièrement difficile pour le secteur de la machine-outil et de l'horlogerie, mais pas seulement. Le chômage et la RHT sont au plus haut dans les cantons du Jura et de Neuchâtel. Il faut agir sans délai et, sans doute, avec des outils pas encore utilisés par&amp;nbsp;le passé.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Quelle appréciation le Conseil fédéral porte-t-il sur la situation de l'économie de l'Arc jurassien?&lt;/p&gt;&lt;p&gt;2. Est-il conscient que l'avenir de l'industrie de cette région est en grand danger?&lt;/p&gt;&lt;p&gt;3. Malgré le libre marché qui est la règle pour l'instant, a-t-il la volonté de défendre ce secteur économique important, aussi en terme de savoir faire, d'emplois et de souveraineté?&lt;/p&gt;&lt;p&gt;4. Cas échéant et au-delà de la Réduction de l'horaire de travail (RHT) comment entend il s'y prendre pour pérenniser ce secteur (garantie à l'exportation, crédits relais à fond perdu, crédits à l'innovation versés aux entreprises, aides à l'exploration de nouveaux marchés, par exemple)?&lt;/p&gt;&lt;p&gt;5. Après les difficultés rencontrées par les aciéries et maintenant l'industrie de l'économie de l'Arc jurassien, ne serait-il pas temps de réunir un groupe d'experts afin de réfléchir au bienfondé ou non de développer une véritable politique industrielle pour notre pays?&lt;/p&gt;&lt;p&gt;6. Toutes autres mesures idoines?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In regelmässigen und immer kürzeren Abständen werden die Industrieunternehmen des Jurabogens mit enormen Herausforderungen konfrontiert. Letztendlich könnten sie dazu führen, dass mehrere Flaggschiffe der regionalen und nationalen Wirtschaft von der Bildfläche verschwinden. Wir durchqueren erneut eine Zone starker Turbulenzen, die mit einem deutlichen, durch&amp;nbsp;die&amp;nbsp;Problematik&amp;nbsp;der&amp;nbsp;US-Strafzölle&amp;nbsp;verschärften Konjunkturrückgang verbunden sind. Besonders schwierig ist die Situation für die Werkzeugmaschinen- und die Uhrenindustrie, aber nicht nur für diese. Die Kantone Jura und Neuenburg sind am stärksten von Arbeitslosigkeit&amp;nbsp;und&amp;nbsp;Kurzarbeit&amp;nbsp;betroffen. Es muss unverzüglich gehandelt werden, und zwar auf jeden Fall mit Instrumenten, die in der Vergangenheit noch nicht eingesetzt wurden.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich ersuche den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Wie beurteilt der Bundesrat die Lage der Wirtschaft im Jurabogen?&lt;/p&gt;&lt;p&gt;2. Ist er sich bewusst, dass die Zukunft der Industrie in dieser Region in grosser Gefahr ist?&lt;/p&gt;&lt;p&gt;3. Ist er trotz des derzeit herrschenden freien Marktes bereit, diesen wichtigen Wirtschaftssektor zu schützen, auch im Hinblick auf Knowhow, Arbeitsplätze und Souveränität?&lt;/p&gt;&lt;p&gt;4. Wie will er gegebenenfalls und über die Kurzarbeit hinaus den Fortbestand dieses Sektors sichern (z. B. durch Exportgarantien, Überbrückungskredite, Innovationskredite für Unternehmen, Beihilfen für die Erschliessung neuer Märkte)?&lt;/p&gt;&lt;p&gt;5. Wäre es nach den Schwierigkeiten der Stahlwerke und nun der Industrie des Jurabogens nicht an der Zeit, eine Expertengruppe einzuberufen, die darüber nachdenkt, ob es nicht sinnvoll wäre, eine echte Industriepolitik für unser Land zu entwickeln?&lt;/p&gt;&lt;p&gt;6. Sonstige geeignete Massnahmen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Occupazione e lavoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bühler Manfred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macht ein Ausstieg des Bundes beim Felslabor Mont Terri zum jetzigen Zeitpunkt wirklich Sinn?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est-il vraiment opportun que la Confédération se retire maintenant du laboratoire souterrain du Mont Terri ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">È davvero sensato che la Confederazione si ritiri dal laboratorio sotterraneo del Mont Terri in questo momento?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le laboratoire souterrain du Mont Terri est une infrastructure de recherche internationalement reconnue pour le stockage géologique profond des déchets radioactifs. Il est actuellement financé par la Confédération via Swisstopo (Office fédéral de topographie) et par de nombreux autres partenaires. Pour des raisons budgétaires, la Confédération prévoit toutefois de cesser de participer à son financement. Au vu des progrès réalisés dans la procédure de sélection des sites destinés au stockage profond des déchets radioactifs et du débat actuel sur l’avenir du nucléaire en Suisse, on peut se demander s’il est judicieux que la Confédération se retire de ce financement. De plus, il est difficile de dire aujourd’hui quelles seraient les conséquences d’un tel retrait sur la poursuite des expériences et sur le respect des engagements internationaux.&lt;/p&gt;&lt;p&gt;D’où les questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;En août dernier, le Conseil fédéral a décidé de revenir sur l’interdiction de construire de nouvelles centrales nucléaires. Ne devrait-il dès lors pas accorder de l’importance à la recherche scientifique sur les déchets nucléaires, et donc au laboratoire du Mont Terri&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Un retrait unilatéral de la part de la Confédération ne serait-il pas contraire au principe selon lequel l’état doit agir de manière conforme aux règles de la bonne foi (art.&amp;nbsp;5, al. 3, Cst.)&amp;nbsp;? En effet, les partenaires et les communautés de recherche doivent pouvoir compter sur un soutien continu. Le Conseil fédéral est-il conscient des éventuelles conséquences de son retrait en termes de responsabilité civile&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Que pense-t-il de la possibilité d’assurer le financement du laboratoire via des programmes nationaux de recherche, via des ressources du Fonds national suisse destinées à la recherche fondamentale ou via Innosuisse&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Felslabor Mont Terri stellt eine international anerkannte Forschungsinfrastruktur für geologische Endlagerungen radioaktiver Abfälle dar und wird derzeit vom Bund über swisstopo (Bundesamt für Landestopografie) in Zusammenarbeit mit zahlreichen Partnern finanziert. Der Bund plant, sich wegen Spargründen aus der Finanzierung des Betriebs des Felslabors Mont Terri zurückzuziehen. Angesichts der Fortschritte im Standortwahlverfahren für ein Tiefenlager für radioaktive Abfälle und der aktuellen Debatte um die zukünftige Rolle der Kernenergie in der Schweiz stellt sich die Frage, ob ein Ausstieg des Bundes aus der Finanzierung des laufenden Betriebs sinnvoll ist. Es ist aktuell zudem unklar, welche Folgen ein solcher Rückzug für die Fortführung laufender Experimente und die Einhaltung internationaler Verpflichtungen hätte.&lt;/p&gt;&lt;p&gt;In diesem Zusammenhang bitte ich den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Im August diesen Jahres hat der Bundesrat beschlossen, das Neubauverbot für Kernkraftwerke aufheben zu wollen. Müsste er in diesem Zusammenhang nicht auch an einer konsequenten wissenschaftlichen Begleitung der nuklearen Abfälle und damit am Felslabor Mont Terri festhalten?&lt;/li&gt;&lt;li&gt;Widerspricht ein einseitiger Rückzug des Bundes aus der Finanzierung nicht den Grundsätzen von staatlichem Handeln nach Treu und Glauben (Art. 5 Abs. 3 BV), da sich Partner und Forschungsgemeinschaften auf eine kontinuierliche Unterstützung verlassen haben? Ist sich der Bundesrat allfälliger haftungsrechtlicher Konsequenzen aufgrund seines Ausstiegs bewusst?&lt;/li&gt;&lt;li&gt;Wie sieht der Bundesrat die Möglichkeit, die Finanzierung des Felslabors Mont Terri über nationale Forschungsprogramme, über die Mittel für Grundlagenforschung des Schweizerischen Nationalfonds (SNF) oder über Innosuisse zu gewährleisten?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wissenschaft und Forschung|Umwelt|Energie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science et recherche|Environnement|Énergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scienza e ricerca|Ambiente|Energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regazzi Fabio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wann wird die OECD-Mindestbesteuerung so umgesetzt, dass die Schweiz attraktiv und wettbewerbsfähig bleibt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A quand une mise en oeuvre de l'imposition minimale de l'OCDE permettant à la Suisse de rester attractive et compétitive ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando l'imposizione minima dell'OCSE sarà attuata in modo da preservare l'attrattiva e la competitività della Svizzera?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Je prie le Conseil Fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comme indiqué dans les dispositions transitoires à l’article 129a de la Constitution fédérale (imposition particulière des grands groupes d’entreprises), la Confédération «&amp;nbsp;après déduction des dépenses supplémentaires induites au titre de la péréquation financière et de la compensation des charges, affecte sa part du produit brut de l’impôt complémentaire au renforcement de la promotion de l’attrait économique de la Suisse&amp;nbsp;». Quelles mesures la Confédération a-t-elle mises sur pied jusqu’à présent&amp;nbsp;afin de renforcer l’attrait économique de la Suisse&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quel cadre ou accompagnement aux cantons la Confédération propose-t-elle, dans le respect des prérogatives des cantons en matière fiscale, afin de mettre sur pied de telles mesures de renforcement, y inclus des crédits d’impôts (non)-remboursables, comme dans les autres pays&amp;nbsp;? Quels sont les travaux en cours à ce sujet&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le secteur du transport maritime est un acteur économique important en Suisse, particulièrement dans les cantons accueillant des armateurs et des négociants en matières premières. La Confédération prévoit-elle d’exploiter, comme mentionné dans les dispositions transitoires à l’article 129a, le fait que «&amp;nbsp;les bénéfices et les pertes des activités de transport maritime international ne sont pas pris en compte&amp;nbsp;»&amp;nbsp;dans l’impôt minimal de 15% ? Alors que 21 pays de l’UE ont mis sur pied des taxations spéciales pour le transport maritime, que compte faire la Suisse pour rester compétitive ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral est-il conscient qu’en ne proposant pas de mesures de soutien à l’économie au niveau fédéral en compensation de l’imposition minimale des grandes entreprises, il existe un risque majeur qu’un substrat fiscal conséquent parte à l’étranger&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Alors que des mesures de soutien à l’économie, y inclus des crédits d’impôts (non)-remboursables, sont introduits entre autres par nos voisins européens &amp;nbsp;en mettant l’accent sur la décarbonation, la transition énergétique et le R&amp;amp;D, la Suisse reste passive. Le Conseil fédéral est-il conscient que des mesures de soutien sous forme de crédits d’impôts (non)-remboursables contribueraient à la réalisation de nos objectifs climatiques&amp;nbsp;et de transition énergétique&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;In den Übergangsbestimmungen zu Artikel&amp;nbsp;129a der Bundesverfassung&amp;nbsp;(Besondere Besteuerung grosser Unternehmensgruppen) heisst es: «Der Bund verwendet seinen Anteil am Rohertrag der Ergänzungssteuer, nach Abzug seiner durch die Ergänzungssteuer verursachten Mehrausgaben für den Finanz- und Lastenausgleich, zur zusätzlichen Förderung der Standortattraktivität der Schweiz.» Welche Massnahmen hat der Bund bisher ergriffen, um die Standortattraktivität der Schweiz zu stärken?&lt;/li&gt;&lt;li&gt;Wie unterstützt der Bund die Kantone&amp;nbsp;– unter Wahrung ihrer Steuerhoheit&amp;nbsp;– bei der Ausarbeitung entsprechender Massnahmen zur Förderung der Standortattraktivität, etwa durch (nicht)&amp;nbsp;rückzahlbare Steuergutschriften, wie sie auch in anderen Ländern vorgesehen sind? Welche Projekte sind in diesem Zusammenhang derzeit im Gange?&lt;/li&gt;&lt;li&gt;Die Seeschifffahrt ist ein bedeutender Wirtschaftsfaktor in der Schweiz, insbesondere in den Kantonen mit Reedereien und Rohstoffhändlern. Beabsichtigt der Bund die in den Übergangsbestimmungen zu Artikel&amp;nbsp;129a festgelegte Tatsache zu nutzen, dass Gewinne und Verluste aus dem internationalen Seeverkehr bei der Mindeststeuer von 15&amp;nbsp;Prozent nicht berücksichtigt werden? Bereits 21&amp;nbsp;EU-Mitgliedstaaten haben spezielle Steuern für den Seeverkehr eingeführt. Nun stellt sich die Frage, welche Massnahmen die Schweiz ergreifen will, um ihre Wettbewerbsfähigkeit zu sichern?&lt;/li&gt;&lt;li&gt;Ist sich der Bundesrat bewusst, dass ohne wirtschaftliche Ausgleichsmassnahmen auf Bundesebene zur Kompensation der Mindestbesteuerung grosser Unternehmensgruppen ein erhebliches Risiko besteht, dass wichtige Steuersubstrate ins Ausland abwandern?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Während zum Beispiel unsere europäischen Nachbarstaaten unter anderem (nicht)&amp;nbsp;rückzahlbare Steuergutschriften als wirtschaftspolitische Unterstützungsmassnahmen einführen&amp;nbsp;– mit Fokus auf die Dekarbonisierung, die Energiewende sowie Forschung und&amp;amp; Entwicklung&amp;nbsp;–, bleibt die Schweiz bislang untätig. Ist sich der Bundesrat bewusst, dass solche Unterstützungsmassnahmen in Form von (nicht)&amp;nbsp;rückzahlbaren Steuergutschriften wesentlich zur Erreichung unserer Klimaziele und zur Umsetzung der Energiewende beitragen könnten?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Verkehr|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Transports|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Trasporti|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa. Iv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mineralölsteuer-Rückerstattung längerfristig sichern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantir à long terme le remboursement de l’impôt sur les huiles minérales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantire a lungo termine la restituzione dell'imposta sugli oli minerali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Parlement supprimera la limitation dans le temps, prévue par l’art. 218, al. 3, de la loi du 20&amp;nbsp;juin 2025 définissant les tâches de l’OFDF (LOFDF&amp;nbsp;; FF 2025 2035), du remboursement de l’impôt accordé pour les transports de voyageurs au moyen de bateaux sur des lignes faisant l’objet d’une concession de la Confédération, pour l’agriculture, pour la sylviculture, pour l’extraction de pierre de taille naturelle et pour la pêche professionnelle en vertu de l’art. 18, al. 2, de la loi sur l’imposition des huiles minérales (Limpmin) tel que modifié par la LOFDF. Si la LOFDF n’entre pas en vigueur avant le 31 décembre 2030, la limitation dans le temps du remboursement de la surtaxe sur les huiles minérales, prévue par l’art. 18, al. 2, Limpmin dans sa version du 1&lt;sup&gt;er&lt;/sup&gt; janvier 2026, sera supprimée.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die gestützt auf Artikel 218 Absatz 3 des BAZG-Vollzugsaufgabengesetzes vom 20. Juni 2025 (BAZG-VG; BBl 2025 2035) erfolgte Befristung der Steuerrückerstattungen für Fahrten mit Schiffen auf dem vom Bund konzessionierten Linien zum Zweck der Personenbeförderung, Landwirtschaft, Forstwirtschaft, Naturwerkstein-Abbau und Berufsfischerei nach Artikel 18 Absatz 2 des mit dem BAZG-VG geänderten Mineralölsteuergesetzes (MinöStG) sei aufzuheben. Sollte das BAZG-VG bis zum Ende der Befristung (31. Dezember 2030) noch nicht in Kraft getreten sein, soll die Befristung der Rückerstattung des Mineralölsteuerzuschlags nach Artikel 18 Absatz 2 des MinöStG in der Fassung vom 1. Januar 2026 aufzuheben.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorprüfung - in Kommission des Nationalrates / Examen préalable - en commission du Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr|Umwelt|Energie|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports|Environnement|Énergie|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti|Ambiente|Energia|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farinelli Alex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umsetzung der verfügbaren Massnahmen zur Regulierung der Wolfspopulation in der Schweiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en oeuvre des mesures disponibles pour réguler la population de loups en Suisse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attuazione delle misure disponibili per la regolazione della popolazione di lupi in Svizzera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre toutes les mesures disponibles, et si nécessaire d’assouplir davantage les critères existants, afin de réguler la population des loups en Suisse en réduisant le nombre de loups et de meutes jusqu’à un niveau le plus proche possible du minimum défini par le Plan de gestion du loup en Suisse, soit 12&amp;nbsp;meutes réparties selon les critères géographiques définis.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, alle zur Verfügung stehenden Massnahmen zu ergreifen und gegebenenfalls die bestehenden Kriterien weiter zu lockern, um die Wolfspopulation in der Schweiz zu regulieren. Die Anzahl der Rudel und Einzeltiere soll so weit wie möglich auf die im Konzept Wolf Schweiz festgelegte Mindestanzahl reduziert werden, sprich zwölf Rudel verteilt auf die definierten Wolfsregionen der Schweiz.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umwelt|Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environnement|Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente|Agricoltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gugger Niklaus-Samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuerdebakel Waadt: Finanzausgleich betroffen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Débâcle fiscale vaudoise. Conséquences sur la péréquation financière ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Des rapports datant du printemps critiquent le calcul erroné de l’impôt sur la fortune dans le canton de Vaud qui a engendré une perte pouvant se chiffrer en millions de francs. Le canton de Vaud bénéficiant de la péréquation financière nationale, les erreurs pourraient avoir des répercussions sur les autres cantons et la Confédération.&lt;br&gt;- Est-ce que le Conseil fédéral partage cette analyse&amp;nbsp;?&lt;br&gt;- Les paiements compensatoires déjà effectués peuvent-ils être corrigés&amp;nbsp;?&lt;br&gt;- Quelles mesures entend prendre le Conseil fédéral pour éviter, à l’avenir, de telles erreurs&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Berichte aus dem Frühjahr kritisieren die fehlerhafte Vermögenssteuerberechnung im Kanton Waadt, die ihm mutmasslich mehrere Millionen Franken kostete. Da Waadt Nehmerkanton im nationalen Finanzausgleich ist, könnten die Fehler auch andere Kantone und den Bund betreffen.&lt;br&gt;- Teilt der Bundesrat diese Einschätzung?&lt;br&gt;- Können bereits geleistete Ausgleichszahlungen korrigiert werden?&lt;br&gt;- Welche Massnahmen plant er, um solche Fehler künftig zu verhindern?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth Pasquier Marie-France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welche Folgen haben die US-Zölle für die Regionen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quels sont les effets des droits de douane américains sur les régions ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les droits de douane américains ont des effets variables selon les régions et les branches. De nombreuses industries (p.ex. horlogerie, agroalimentaire, chimie, métallurgie, machines, technologie de précision) sont particulièrement touchées. Les chiffres agrégés de la Confédération ne reflètent pas les réalités régionales et la RHT n’est pas une solution durable.&lt;br&gt;- Le Conseil fédéral dispose t'il de données plus précises par régions?&lt;br&gt;- Envisage-t-il des mesures pour soutenir ces branches et régions?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Folgen der US-Zölle variieren je nach Region und Branche. Zahlreiche Industriezweige&amp;nbsp;– etwa die Uhren- und Lebensmittelindustrie, die Chemie-, Metall- und Maschinenbaubranche sowie die Präzisionstechnik&amp;nbsp;– sind besonders stark betroffen. Die aggregierten Zahlen des Bundes spiegeln nicht die regionalen Gegebenheiten wider, und Kurzarbeit ist keine nachhaltige Lösung.&lt;br&gt;- Verfügt der Bundesrat über differenziertere Daten nach Regionen?&amp;nbsp;&lt;br&gt;- Zieht der Bundesrat Massnahmen in Betracht, um die betroffenen Branchen und Regionen zu unterstützen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Wirtschaft|Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Économie|Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Economia|Finanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weigert sich der Kanton Jura, für die Seniorinnen und Senioren aus Moutier zu zahlen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Jura refuse-t-il de payer pour les aînés de Moutier ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Selon les indications de directions d'EMS bernois qui hébergent des pensionnaires de Moutier au 31.12.2025, il semble que le canton du Jura refuse de prendre en charge les montants qui doivent être financés par les cantons dès le 1.1.2026.&lt;br&gt;- Si tel est le cas, qui devra prendre en charge ces montants ?&lt;br&gt;- La Confédération est-elle impliquée dans ces discussions entre les cantons de Berne et du Jura ?&lt;br&gt;- Si oui, quel est son avis ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Nach Angaben der Heimleitungen gewisser Berner Alters- und Pflegeheime, in denen am 31. Dezember 2025 noch Personen aus Moutier untergebracht sein werden, zeichnet sich ab, dass der Kanton Jura die Übernahme der kantonal zu tragenden Kosten ablehnen wird, die er ab dem 1. Januar 2026 übernehmen müsste.&lt;br&gt;- Wenn dies der Fall ist, wer muss dann diese Kosten übernehmen?&lt;br&gt;- Ist der Bund in diese Diskussionen zwischen den Kantonen Bern und Jura involviert?&lt;br&gt;- Wenn ja, was ist die Haltung des Bundes?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Soziale Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Questions sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Questioni sociali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pahud Yvan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schliessung Hôtel du Chasseron. Was schlägt Armasuisse vor, um den Tourismus in der Region Sainte-Croix/Les Rasses zu erhalten?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Décision de fermeture de l'Hôtel du Chasseron. Quelle solution propose Armasuisse pour ne pas prétériter le tourisme dans la région de Sainte-Croix/Les Rasses ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisione di chiudere l'Hôtel du Chasseron. Quale soluzione propone armasuisse per non pregiudicare il turismo nella regione di Sainte-Croix/Les Rasses?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le 25 juin dernier, le CN Pahud et le CE Broulis ont reçus un courrier du tenancier de l’hôtel du Chasseron pour les informer de la fermeture de l’hôtel au 28 septembre.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Pour la région du Balcon du Jura, et des Communes de Sainte-Croix et Bullet, l’hôtel du Chasseron est le pilier central du développement touristique 4 saisons avec une ouverture hiver, comme été.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Cette fermeture s’ajoute à celle de l’hôtel restaurant des Rochats, également propriété de la confédération, et qui prétérite l’accueil sur un sentier prioritaire qu’est le chemin des Crêtes du Jura N°5.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;En plus de l’aspect touristique,&amp;nbsp; et vu la situation géopolitique mondiale et les défis à laquelle la Suisse est confronté en matière de sécurité,&amp;nbsp; l’hôtel du Chasseron, revêt également un aspect stratégique, comme site militaire, situé sur les contreforts de la frontière nationale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Malgré les nombreux courriels adressés à Armasuisse par votre serviteur, ces dernier ont confirmés&amp;nbsp;: «&amp;nbsp;armasuisse ne relouera donc pas l’Hôtel du Chasseron à partir de l’automne 2025, et ce jusqu’à nouvel ordre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;C’est un coup dur pour toute une région qui se bat pour maintenir et développer le tourisme.&lt;/p&gt;&lt;p&gt;Ceci sans compter, que dans l’attente d’une solution, Armasuisse se prive d’un loyer, ce qui péjore les finances de la Confédération.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le manque de considération d’Armasuisse, et la non-entrée en matière afin de garder cet établissement ouvert dans l’attente d’une solution possible avec la ou les Communes concernées est également à relever.&lt;/p&gt;&lt;p&gt;Question&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Pourquoi Armasuisse n’a-t-il pas informé et pris immédiatement contact avec les Communes concernées dès la résiliation du bail et surtout dès la décision de fermeture de l’hôtel&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles solutions urgentes Armasuisse a proposé et surtout propose afin que l’établissement soit ouvert pour la saison hivernale 2025-2026&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Un tenancier peut-il être trouvé au plus vite, avec un bail à loyer provisoire, dans l’attente d’une solution à long terme&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue financier, l’Hôtel étant fermé dès le 30 septembre prochain, et donc non loué, comment le CF juge-t-il cette perte de rentrée financière&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 25.&amp;nbsp;Juni 2025 informierte der Pächter des Hôtel du Chasseron Nationalrat Yvan Pahud und Ständrat Pascal Broulis schriftlich über die bevorstehende Schliessung des Hotels per 28.&amp;nbsp;September 2025.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Hôtel du Chasseron ist im Sommer und im Winter geöffnet und bildet somit das Herzstück des Ganzjahrestourismus für den Jurabalkon sowie die Gemeinden Sainte-Croix und Bullet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Auch das Restaurant Les Rochats ‒ ebenfalls im Besitz des Bundes ‒ wird geschlossen, womit ein gastfreundliches Haus am wichtigen Jura-Höhenweg Nr.&amp;nbsp;5 verloren geht.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Hôtel du Chasseron ist nicht nur für den Tourismus zentral. Angesichts der geopolitischen Weltlage und der Herausforderungen für die Schweiz bei der Sicherheit ist es ein strategisch wichtiger Militärstandort nahe der Landesgrenze.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Als Antwort auf meine zahlreichen E-Mails bestätigte Armasuisse, das Hôtel du Chasseron ab Herbst&amp;nbsp;2025 bis auf Weiteres nicht mehr zu verpachten.&lt;/p&gt;&lt;p&gt;Dies ist ein harter Schlag für die Region, die sich stark dafür einsetzt, den Tourismus zu erhalten und zu fördern.&lt;/p&gt;&lt;p&gt;Ganz abgesehen davon, dass Armasuisse in der Zwischenzeit keine Pachteinnahmen hat, was die Finanzen des Bundes belastet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Armasuisse zeigte sich nicht gesprächsbereit und hat es abgelehnt, das Hotel bis zu einer möglichen Lösung mit einer oder mehreren betroffenen Gemeinden weiterzubetreiben.&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Warum hat Armasuisse nach der Kündigung des Pachtvertrags und vor allem nach dem Entscheid zur Hotelschliessung die betroffenen Gemeinden nicht unverzüglich informiert und das Gespräch mit ihnen gesucht?&lt;/li&gt;&lt;li&gt;Welche Sofortmassnahmen hat Armasuisse vorgeschlagen und gedenkt Armasuisse zu ergreifen, damit das Hotel in der Wintersaison 2025–2026 wiedereröffnet werden kann?&lt;/li&gt;&lt;li&gt;Lässt sich mit einem temporären Pachtvertrag kurzfristig eine Pächterin oder ein Pächter finden, bis es eine langfristige Lösung gibt?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Einnahmeverlust aufgrund der Hotelschliessung und des auslaufenden Pachtvertrags ab dem 30.&amp;nbsp;September 2025 aus finanzieller Sicht?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Économie|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Economia|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schliessung des Hôtel du Chasseron: Was plant armasuisse, damit der Tourismus in der Region Sainte-Croix/Les Rasses trotzdem erhalten bleibt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Décision de fermeture de l’Hôtel du Chasseron, quelle solution Armasuisse propose pour ne pas prétériter le tourisme dans la région de Sainte-Croix/Les Rasses ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Pour la région du Balcon du Jura vaudois, l’hôtel du Chasseron est le pilier central du développement touristique 4 saisons.&lt;br&gt;La décision de fermeture par Armasuisse au 30 septembre est incompréhensible.&lt;br&gt;- Quelles solutions urgentes Armasuisse propose afin que l’établissement puisse être réouvert au plus vite&amp;nbsp;?&lt;br&gt;- Un tenancier peut-il être trouvé au plus vite, avec un bail à loyer provisoire, dans l’attente d’une solution à long terme avec les Communes&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Hôtel du Chasseron ist der Dreh- und Angelpunkt für die ganzjährige Tourismusentwicklung in der Region des Waadtländer Jurabalkons.&lt;br&gt;Der Beschluss von armasuisse, das Hotel per 30. September zu schliessen, ist unbegreiflich.&lt;br&gt;- Welche Sofortmassnahmen schlägt armasuisse vor, damit das Hotel so schnell wie möglich wiedereröffnet werden kann?&lt;br&gt;- Lässt sich mit einem temporären Mietvertrag kurzfristig eine Wirtin oder ein Wirt gewinnen, bis eine langfristige Lösung mit den Gemeinden gefunden wird?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Économie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Economia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kt. Iv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel-Landschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massnahmen zur Aufwertung der beiden ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (volles Ständerecht)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconnaissance de l'entier des droits politiques aux deux anciens demi-cantons de Bâle-Ville et de Bâle-Campagne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misure finalizzate a rendere i due ex Semicantoni di Basilea Città e Basilea Campagna Cantoni a pieno titolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le 28&amp;nbsp;août&amp;nbsp;2025, le parlement du canton de Bâle-Campagne a décidé à l’unanimité, conformément à l’art.&amp;nbsp;160, al.&amp;nbsp;1, de la Constitution fédérale (Cst.), de déposer une initiative pour que soient reconnus l’entier des droits politiques aux deux anciens demi-cantons de Bâle-Ville et de Bâle-Campagne.&lt;/p&gt;&lt;p&gt;L’Assemblée fédérale et le Conseil fédéral sont priés de prendre les mesures nécessaires pour que, sous l’angle du principe d’égalité des droits qui doit prévaloir entre États membres de la Confédération, les anciens demi-cantons de Bâle-Ville et de Bâle-Campagne (ainsi que, en principe, les autres anciens demi-cantons) soient mis sur un pied d’égalité avec les autres cantons en ce qui concerne le nombre de sièges et de voix au Conseil des États (faire des deux Bâle des cantons à part entière, modification des art.&amp;nbsp;150, al.&amp;nbsp;1 et al.&amp;nbsp;2, et art.&amp;nbsp;142, al.&amp;nbsp;4, Cst).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 28. August 2025 hat der Landrat des Kantons Basel-Landschaft einstimmig beschlossen, gestützt auf Artikel 160 Absatz 1 der Bundesverfassung eine Standesinitiative hinsichtlich der Ergreifung von Massnahmen zur Aufwertung der beiden ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (Volles Ständerecht) einzureichen.&lt;/p&gt;&lt;p&gt;Das Bundesparlament und der Bundesrat werden gebeten, die notwendigen Schritte zu unternehmen, damit unter dem Aspekt des Gebots der bundesstaatlichen Rechtsgleichheit die ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (und grundsätzlich auch die weiteren ehemaligen Halbkantone) den übrigen Kantonen im Hinblick auf die Vertretung im Ständerat und der Standesstimmen gleichgestellt werden (Aufwertung als Kantone mit vollem Ständerecht, Änderung von Art. 150 Abs. 1 und Abs. 2 sowie Art. 142 Abs. 4 der Bundesverfassung).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piller Carrard Valérie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sperrung der Strecke Freiburg–Bern im Sommer. Ein Rückschlag für die Verkehrsverlagerung?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fermeture estivale de la ligne Fribourg-Berne. Un coup d'arrêt au transfert modal ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiusura estiva della linea Friburgo-Berna. Una battuta d'arresto al trasferimento modale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La fermeture totale de la ligne ferroviaire Fribourg-Berne pendant plus de deux mois cet été va poser de grands problèmes dans le canton de Fribourg, premier canton pendulaire de Suisse. Fortement tributaires de leurs connexions ferroviaires, en particulier vers Berne et la Suisse alémanique, les pendulaires fribourgeois s’inquiètent de l’allongement de leur temps de trajet, des conditions de voyage dans des bus qui seront certainement bondés, et de l’interdiction de transporter son vélo. En pleine période estivale qui plus est de l’Euro de football féminin, cette fermeture totale de ligne est aussi particulièrement défavorable au tourisme, avec pour conséquence un probable manque à gagner pour l'économie locale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Enfin, cette décision comporte le risque réel de favoriser les déplacements en voiture individuelle, et que les pendulaires questionnent leur volonté d’utiliser les transports publics, également à plus long terme.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans ce contexte, le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Les CFF ont-ils envisagé des alternatives moins contraignantes que cette fermeture totale de ligne entre Fribourg et Berne, par exemple une fermeture limitée à une seule voie&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Le Conseil fédéral a-t-il conscience que cette ligne joue le rôle d’épine dorsale de la Suisse, qu’elle est donc indispensable pour connecter la Suisse romande et la Suisse alémanique, et que les CFF ne peuvent pas simplement fermer la ligne avec l’excuse que des bus sont à disposition&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3) Cette fermeture aura certainement un effet sur le report de trafic sur la route, une évaluation au niveau de ce report dans les différentes communes vaudoises, fribourgeoises et bernoises est-elle envisagée&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Après l’énorme couac de la gare de Lausanne et tous les désagréments qui en découlent pour les usagers des CFF, cette fermeture de ligne pure et simple donne une fois de plus aux habitant-e-s de la Suisse romande l’impression qu’ils sont considérés comme quantité négligeable. Que répond le Conseil fédéral&amp;nbsp;?&lt;/p&gt;&lt;p&gt;5) Dans un contexte de renchérissement des billets de transport et de trains toujours plus bondés, une fermeture totale de ligne risque d’encourager la population à utiliser des véhicules individuels. Quel est l’avis du Conseil fédéral à ce sujet&amp;nbsp;?&lt;/p&gt;&lt;p&gt;6) Au vue de la quantité de désagréments, est-ce que le Conseil fédéral envisage de dédommager financièrement les usagers de la ligne&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Totalsperre der Bahnstrecke Freiburg–Bern für mehr als zwei Monate in diesem Sommer wird im Kanton Freiburg, dem grössten Pendlerkanton der Schweiz, zu grossen Problemen führen. Die Pendlerinnen und Pendler aus dem Kanton Freiburg sind stark auf ihre Zugverbindungen angewiesen, insbesondere nach Bern und in die Deutschschweiz. Sie fürchten die längeren Reisezeiten, die Bedingungen in den mit Sicherheit überfüllten Bussen und das Verbot, ihr Velo zu transportieren. Mitten in der Sommersaison und während der Fussball-Europameisterschaft der Frauen ist die Totalsperre der erwähnten Strecke auch für den Tourismus von grossem Nachteil; sie führt wahrscheinlich zu Einnahmeausfällen für die lokale Wirtschaft.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Schliesslich birgt der Entscheid der Sperrung das grosse Risiko, dass Pendlerinnen und Pendler auf das Privatauto umsteigen und auch längerfristig die Benutzung öffentlicher Verkehrsmittel in Frage stellen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Hat die SBB weniger einschneidende Alternativen zur Totalsperre der Strecke Freiburg–Bern in Betracht gezogen, z.&amp;nbsp;B. eine auf ein Gleis beschränkte Sperre?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Ist sich der Bundesrat bewusst, dass die erwähnte Strecke quasi als Rückgrat der Schweiz für die Verbindung zwischen West- und Deutschschweiz unentbehrlich ist und die SBB diese nicht einfach mit dem Verweis auf Ersatzbusse sperren kann?&lt;/p&gt;&lt;p&gt;3) Die Sperrung wird sicherlich eine Verkehrsverlagerung auf die Strasse zur Folge haben. Wird in den verschiedenen Gemeinden der Kantone Waadt, Freiburg und Bern eine Bewertung dieser Verlagerung in Betracht gezogen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Nach dem Debakel rund um den Umbau des Bahnhofs Lausanne und allen damit verbundenen Unannehmlichkeiten für die SBB-Reisenden fühlen sich die Westschweizerinnen und Westschweizer durch diese kompromisslose Sperrung einmal mehr als vernachlässigte Minderheit. Was sagt der Bundesrat dazu?&lt;/p&gt;&lt;p&gt;5) Vor dem Hintergrund steigender Tarife und zunehmend überfüllter Züge könnte eine vollständige Streckensperrung die Bevölkerung zur Nutzung von Privatautos verleiten. Wie schätzt der Bundesrat die Lage ein?&lt;/p&gt;&lt;p&gt;6) Zieht der Bundesrat angesichts der vielen Unannehmlichkeiten eine finanzielle Entschädigung für die Nutzerinnen und Nutzer der erwähnten Strecke in Betracht?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Trasporti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konzessionsentscheid zugunsten von Canal B. Fragen zur Unabhängigkeit, Transparenz und medienpolitischen Zielsetzung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concession accordée à Canal B. Questions sur l'indépendance, la transparence et les objectifs de politique médiatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisione relativa alla concessione in favore di Canal B. Domande concernenti indipendenza, trasparenza e obiettivi in materia di politica dei media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le 27 mai 2025, le DETEC a attribué la concession TV régionale pour la région Bienne-Seeland-Jura bernois non pas à l'ancien prestataire TeleBielingue, mais à Canal B, nouvelle chaîne régionale. Cette décision a provoqué un tollé politico-médiatique dans la région et au-delà.&lt;/p&gt;&lt;p&gt;TeleBielingue est une chaîne bilingue qui s'est développée au fil des décennies et dont les qualités journalistiques sont largement reconnues, tant en Suisse alémanique qu'en Suisse romande. Canal B, quant à elle, est une chaîne d’obédience évangélique qui n’a pas fait preuve, à ce jour, de compétences équivalentes. Elle est étroitement liée au réseau de médias chrétiens ERF Medien, dont l’orientation semble contraire au principe d'une information ouverte, indépendante de l'État et neutre sur le plan idéologique.&lt;/p&gt;&lt;p&gt;Les médias ont par ailleurs révélé que le secrétaire général du DETEC avait des liens étroits avec les milieux évangéliques et qu’il était membre d'une église libre, ce qui soulève des questions sur l'indépendance institutionnelle et la transparence politique de la procédure de concession.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quels sont les critères concrets relatifs aux contenus et aux aspects techniques et structurels qui ont conduit à l’attribution de la concession à la chaîne Canal B ? Comment ont-ils été évalués au regard des prestations fournies par TeleBielingue ?&lt;/li&gt;&lt;li&gt;Que pense le Conseil fédéral de la compatibilité d'un projet médiatique d'inspiration évangélique avec les exigences légales en matière de diversité, de séparation de l'Église et de l'État et d’indépendance des médias ?&lt;/li&gt;&lt;li&gt;Quelles dispositions le DETEC a-t-il prises pour exclure tout conflit d'intérêts lié aux convictions religieuses personnelles des décideurs ?&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral s'assure-t-il que les décisions en matière de politique des médias ne sont pas prises en fonction de la proximité idéologique ou religieuse, mais sur la base de critères objectifs de qualité et de performance ?&lt;/li&gt;&lt;li&gt;Comment évalue-t-il le risque que de telles décisions sapent la confiance placée dans le système de concession des télévisions régionales ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 27. Mai 2025 hat das UVEK die regionale TV-Konzession für die Region Biel-Seeland-Jura bernois nicht an den bisherigen Anbieter TeleBielingue, sondern an das neue Projekt Canal B vergeben. Diese Entscheidung hat in der Region und darüber hinaus für grosse medienpolitische Irritation gesorgt.&lt;/p&gt;&lt;p&gt;TeleBielingue ist ein über Jahrzehnte gewachsener, zweisprachiger Sender mit einem etablierten publizistischen Leistungsausweis, der sowohl in der Deutschschweiz als auch in der Romandie breite Anerkennung geniesst. Der Zuschlag an Canal B geht hingegen an ein Projekt mit klar evangelikaler Prägung, das bisher keinerlei vergleichbare publizistische Leistungen nachgewiesen hat. Canal B ist eng mit dem christlichen Mediennetzwerk ERF Medien verbunden, dessen inhaltliche Ausrichtung dem Prinzip einer offenen, staatsunabhängigen und weltanschaulich neutralen Berichterstattung zuwiderzulaufen scheint.&lt;/p&gt;&lt;p&gt;Zudem wurde öffentlich bekannt, dass der Generalsekretär des UVEK über enge Verbindungen zu evangelikalen Kreisen verfügt und Mitglied einer Freikirche ist, was Fragen zur institutionellen Unabhängigkeit und zur politischen Transparenz des Konzessionsverfahrens aufwirft.&lt;/p&gt;&lt;p&gt;In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche konkreten inhaltlichen, technischen und strukturellen Kriterien haben zum Entscheid für Canal B geführt und wie wurden diese gegenüber dem Leistungsnachweis von TeleBielingue gewichtet?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat die Vereinbarkeit eines evangelikal geprägten Medienprojekts mit den gesetzlichen Anforderungen an publizistische Vielfalt, Trennung von Kirche und Staat sowie an staatsunabhängige Medien?&lt;/li&gt;&lt;li&gt;Welche Vorkehrungen hat das UVEK getroffen, um Interessenkonflikte im Zusammenhang mit persönlichen religiösen Überzeugungen von Entscheidungsträgern auszuschliessen?&lt;/li&gt;&lt;li&gt;Wie stellt der Bundesrat sicher, dass medienpolitische Entscheide nicht aufgrund ideologischer oder religiöser Nähe, sondern aufgrund objektiver Qualitäts- und Leistungskriterien erfolgen?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat die Gefahr, dass mit solchen Entscheiden das Vertrauen in das konzessionsgestützte System für Regionalfernsehen untergraben wird?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation|Kultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Médias et communication|Culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Media e comunicazione|Cultura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bally Maya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prüfung einer einheitlichen Referenzgrösse für Vermögenssteuerwerte bei Eigenheimen für den NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Référence uniforme pour le calcul de la valeur fiscale des logements en propriété dans le cadre de la RPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esame di un parametro uniforme di riferimento per definire il valore delle proprietà abitative ai fini dell’imposta sulla sostanza nell’ambito della NPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’examiner, en vue du prochain rapport sur l’efficacité de la RPT, l’adoption d’une valeur de référence uniforme pour le calcul de la valeur fiscale des logements en propriété (par ex. valeur de répartition), de proposer des mesures et de présenter un rapport. Il s’agit d’analyser la situation actuelle et de proposer des solutions pour éliminer les effets négatifs dus aujourd’hui aux méthodes d’estimation très différentes que les cantons appliquent. &amp;nbsp;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt anlässlich des nächsten Wirkungsberichts NFA die Einführung einer einheitlichen Referenzgrösse für Vermögenssteuerwerte bei Eigenheimen (z.B.Repartitionswert) zu prüfen, entsprechenden Massnahmen vorzuschlagen und Bericht zu erstatten. Die aktuelle Situation soll analysiert und mögliche Lösungen zur Beseitigung der heutigen negativen Auswirkungen aufgrund der sehr unterschiedlichen Schätzungsmethoden in den Kantonen aufgezeigt werden. &amp;nbsp;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Nationalrat geplant / Planifié au Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Steuer|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Fiscalité|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Imposte|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auftauende Alpentäler und sich erhitzende Städte: Der Finanzausgleich muss die Folgen der Klimaerhitzung berücksichtigen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallées alpines en dégel et villes en surchauffe. La péréquation financière doit prendre en considération les conséquences du réchauffement climatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valli alpine in scioglimento e città sempre più roventi: la perequazione finanziaria deve tenere conto delle conseguenze del riscaldamento climatico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que la compensation des charges dues à des facteurs géo-topographiques tienne désormais également compte de la gestion des conséquences du réchauffement climatique. Il garantira que les ressources supplémentaires nécessaires ne seront pas déduites des autres paiements compensatoires prévus dans le cadre de la péréquation financière nationale (notamment des paiements de la Confédération au titre de la péréquation des ressources ou des montants versés pour compenser les charges dues à des facteurs socio-démographiques ou géo-topographiques), mais seront inscrites en sus au budget.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt die gesetzlichen Grundlagen anzupassen, damit der geographisch-topographische Lastenausgleich zukünftig explizit auch auf die Bewältigung der Folgen der Klimaerhitzung ausgerichtet wird. Der Bundesrat stellt sicher, dass die zusätzlich notwendigen Mittel nicht zulasten der übrigen Ausgleichszahlungen im Rahmen des Nationalen Finanzausgleichs (insbesondere der existierenden Beiträge des Bundes an den Ressourcenausgleich sowie den sozio-demographischen und den geographisch-topographischen Lastenausgleich) gehen, sondern zusätzlich eingestellt werden.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crottaz Brigitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missbrauch von codeinhaltigen Sirupen (Purple Drank). Handeln, bevor das Phänomen um sich greift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usage détourné de sirops à base de codéine (Purple Drank). Agir avant que le phénomène ne s'amplifie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso improprio di sciroppi a base di codeina ("purple drank"). Agire prima che il fenomeno si intensifichi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;En réponse à ma question 25.7511, le CF répond qu’il n’a pas connaissance du mésusage de certains médicaments contenant des substances addictives.&lt;br&gt;Pourtant, depuis plus de 10 ans, professionnels de santé et autorités de certains cantons observent &amp;nbsp;la consommation détournée de sirops antitussifs à base de codéine. Le phénomène du &lt;i&gt;Purple Drank &lt;/i&gt;— mélange de sirop, soda, antihistaminiques et parfois alcool ou cannabis — n’est plus marginal et touche des adolescents de plus en plus jeunes avec des risques avérés de dépendance, de déscolarisation, de troubles cognitifs, voire d’overdose.&lt;br&gt;La situation devient préoccupante : à Genève, les autorités sanitaires ont lancé un programme de sevrage dédié car l’utilisation massive de sirops codéinés dans un but non thérapeutique constitue un véritable problème de santé publique.&lt;br&gt;Si la révision de la Loi sur les produits thérapeutiques en 2019 a permis un meilleur encadrement, son application reste inégale. Même si le devoir d’annonce prévu dans la LStup est généralement respecté, le canton ne peut s’opposer au traitement off label prescrit, même s’il estime qu’il est abusif ou pourrait alimenter un marché noir.&amp;nbsp;&lt;br&gt;Concernant les traitements de substitution de la dépendance à l’héroïne, le régime d’autorisation cantonal est bien établi et harmonisé. Ce n’est pas le cas pour la prescription de la codéine dans le cas d’une dépendance, où les critères ne sont pas définis et les pratiques cantonales hétérogènes. Ces prescriptions sont donc difficilement contrôlables et des patients encourent le risque d’être exposés à des traitements inadaptés.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In seiner Antwort auf meine Frage 25.7511 erklärte der Bundesrat, er habe keine Kenntnis von missbräuchlicher Verwendung gewisser Medikamente, die süchtig machende Substanzen enthalten.&lt;br&gt;Dabei beobachten Gesundheitsfachleute wie auch Behörden in gewissen Kantonen seit mehr als zehn Jahren, dass codeinhaltige Hustensirupe missbräuchlich eingenommen werden. Das Phänomen &lt;i&gt;Purple Drank&lt;/i&gt; – eine Mischung aus Sirup, Limonade, Antihistaminika und zuweilen auch Alkohol oder Cannabis – ist keine Randerscheinung mehr, sondern betrifft immer jüngere Jugendliche. Die Risiken des Konsums solcher Getränke sind erwiesen und reichen von Abhängigkeit über Schulabbruch und kognitive Beeinträchtigungen bis hin zur Überdosis.&lt;br&gt;Das Phänomen nimmt besorgniserregende Ausmasse an: In Genf haben die Gesundheitsbehörden ein spezifisches Entzugsprogramm eingerichtet, denn die Einnahme grosser Mengen codeinhaltiger Sirupe ist ein ernsthaftes Problem für die öffentliche Gesundheit.&lt;br&gt;Mit der Revision des Heilmittelgesetzes im Jahr&amp;nbsp;2019 wurden griffigere Bestimmungen eingeführt, aber der Gesetzesvollzug ist uneinheitlich. Zwar wird die Meldepflicht gemäss Betäubungsmittelgesetz in der Regel eingehalten, aber der Kanton kann nicht gegen eine verordnete Off-Label-Behandlung vorgehen, selbst wenn er zur Einschätzung gelangt, dass diese missbräuchlich ist oder den Schwarzmarkt versorgen könnte.&amp;nbsp;&lt;br&gt;Bei Substitutionsbehandlungen von Heroinabhängigen ist die kantonale Bewilligungspraxis gut verankert und harmonisiert. Anders sieht es bei der Verschreibung von Codein aus, wenn eine Abhängigkeit vorliegt, denn die Kriterien dafür wurden nicht definiert und die kantonalen Praktiken sind uneinheitlich. Solche Verschreibungen lassen sich nur schwer kontrollieren, und für die Patientinnen und Patienten besteht die Gefahr von Fehlbehandlungen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaillard Benoît</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fahrplan 2025 Westschweiz. Zwischenbilanz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouvel horaire CFF 2025. Bilan intermédiaire pour la Suisse romande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilancio intermedio dell'orario 2025 della Svizzera occidentale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;ol&gt;&lt;li&gt;Il semblerait que le nouvel horaire&amp;nbsp;2025 pour la Suisse romande donne lieu à des coûts d’exploitation plus élevés que l’horaire précédent, notamment en raison du personnel et du matériel roulant. Le Conseil fédéral peut-il communiquer un chiffre à ce sujet&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelle augmentation du nombre de voyageurs-kilomètres le nouvel horaire a-t-il permis d’enregistrer jusqu’à présent sur l’ensemble du réseau de la Suisse romande par rapport à l’horaire précédent&amp;nbsp;? Quelle est l’évolution, à la hausse ou à la baisse, notamment pour les différentes liaisons grandes lignes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Dans quelle mesure la part de passagers arrivant à l’heure a-t-elle été augmentée grâce à l’horaire&amp;nbsp;2025&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sont les conséquences financières de cet horaire sur le compte de résultats des CFF&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les correspondances avec changement de quai à Renens posent particulièrement problème pour les liaisons entre Genève et la ligne du pied du Jura. N’est-il pas possible de garantir que les changements se fassent systématiquement sur le même quai avant la date de 2030 annoncée par les CFF&amp;nbsp;? Cette situation est-elle acceptable pour le Conseil fédéral&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Sous la pression des cantons romands ainsi que des régions et des villes concernées, six liaisons directes quotidiennes ont été introduites sur la ligne&amp;nbsp;IC5. Sont-elles garanties pour les prochaines années&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;ol&gt;&lt;li&gt;Es heisst, der Fahrplan 2025 Westschweiz sei teurer zu betreiben als der frühere Fahrplan, beispielsweise aufgrund höherer Kosten für Personal und Rollmaterial. Kann der Bundesrat eine Zahl kommunizieren?&lt;/li&gt;&lt;li&gt;Welche Zunahme an Personenkilometern wurde bis jetzt auf dem Gesamtnetz Westschweiz erzielt im Vergleich mit dem vorigen Fahrplan? Wie ist die allfällige Zu- oder Abnahme insbesondere bei den einzelnen Fernverkehrsverbindungen?&lt;/li&gt;&lt;li&gt;Wie stark wurde dank dem Fahrplan 2025 der Anteil der pünktlich ankommenden Fahrgäste verbessert?&lt;/li&gt;&lt;li&gt;Was sind die finanziellen Auswirkungen des Fahrplans 2025 auf die Ertragsrechnung der SBB?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Besonders problematisch sind die Anschlüss mit Perronwechsel in Renens für Verbindungen zwischen Genf und der Jurafusslinie. Ist ein systematisches Umsteigen auf dem gleichen Perron nicht vor dem von der SBB angekündigten Datum 2030 möglich? Ist diese Situation für den Bundesrat hinnehmbar?&lt;/li&gt;&lt;li&gt;Auf Druck der Westschweizer Kantone und der betroffenen Regionen und Städte wurden 6 direkte tägliche Verbindungen auf der IC5 Linie eingeführt. Sind sie für die nächsten Jahre auch definitiv abgesichert?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDP-Liberale Fraktion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überprüfung und allfällige Ergänzung der gesetzlichen Grundlagen für eine rasche Katastrophenhilfe des Bundes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aide rapide de la Confédération en cas de catastrophe. Examiner les bases légales en la matière et les compléter en cas de besoin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificare ed eventualmente completare le basi legali per un rapido aiuto in caso di catastrofe da parte della Confederazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter dans un rapport non seulement les dispositions légales qui régissent la fourniture d’une aide nationale rapide en cas de catastrophe, mais aussi, si nécessaire, celles qui doivent venir les compléter. Le rapport exposera les conditions, les compétences et les procédures existantes ou à mettre en place pour garantir la fourniture de prestations de soutien de nature financière et organisationnelle par la Confédération si une catastrophe naturelle ou un autre événement dommageable de grande ampleur survenait.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ce rapport devra en particulier :&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;préciser les conditions à remplir pour qu’une aide d’urgence soit fournie ;&lt;/li&gt;&lt;li&gt;clarifier le rôle de la Confédération vis-à-vis des cantons et des communes concernés ;&lt;/li&gt;&lt;li&gt;analyser la collaboration avec les systèmes existants (par ex. assurances, protection civile, armée et cantons), et&lt;/li&gt;&lt;li&gt;procéder à une évaluation juridique des réglementations actuelles (par ex. la loi fédérale sur la protection de la population et sur la protection civile [RS 520.1], la loi sur l’armée [RS 510.10], la loi sur les finances [RS 611.0] ainsi que les art. 5a et 57 Cst.).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Le rapport indiquera en outre si une base légale est nécessaire pour apporter un soutien standardisé et garanti par l’État de droit en cas de catastrophe, par exemple sous la forme d’une législation fédérale spécialisée.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in einem Bericht aufzuzeigen, welche gesetzlichen Regelungen für die zeitnahe Unterstützung einer inländischen Katastrophenhilfe vorhanden sind bzw. fehlen. Der Bericht soll darlegen, welche Voraussetzungen, Zuständigkeiten und Verfahren für finanzielle und organisatorische Unterstützungsleistungen des Bundes im Falle von Naturkatastrophen oder anderen Schadensereignissen grosser Tragweite bestehen oder geschaffen werden müssten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Insbesondere soll der Bericht:&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;die Bedingungen für die Soforthilfe präzisieren,&lt;/li&gt;&lt;li&gt;die Rolle des Bundes gegenüber betroffenen Kantonen und Gemeinden klären,&lt;/li&gt;&lt;li&gt;die Zusammenarbeit mit bestehenden Systemen (z.B. Versicherungen, Zivilschutz, Armee, Kantone) untersuchen,&lt;/li&gt;&lt;li&gt;und eine rechtliche Bewertung der aktuellen Regelungen (z.B. Bevölkerungsschutzgesetz [SR 520.1], Militärgesetz [SR 510.10], Finanzhaushaltsgesetz [SR 611.0], Art. 57 und 5a BV) vornehmen.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Der Bericht soll zudem aufzeigen, ob eine gesetzliche Grundlage für eine standardisierte und rechtsstaatlich abgesicherte Unterstützung in Katastrophenfällen nötig ist, beispielsweise in Form einer spezialisierten Bundesgesetzgebung.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Politique de sécurité|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funktionale Wasserregionen als Basis für künftiges Wassermanagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Délimitation des régions aquifères selon la fonction pour une gestion de l’eau tournée vers l’avenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regioni idriche funzionali quale base per la futura gestione dell’acqua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’eau relève de la souveraineté des cantons, qui sont responsables des installations et des projets relatifs à l'utilisation de l'eau, à la protection de l'eau et à la protection contre l'excès d'eau ou à la gestion des conséquences d'une sécheresse persistante.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La mesure 127 «Adoption de la stratégie Gestion de l'eau - périodes de sécheresse, fortes précipitations, qualité de l'approvisionnement en eau, protection des habitats aquatiques» a été intégrée au programme de la législature 2023 à 2027 (&lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20230082"&gt;objet 23.082&lt;/a&gt;). La Confédération se voit ainsi attribuer une fonction de supervision et de coordination.&lt;/p&gt;&lt;p&gt;Il suffit de jeter un œil sur une carte de Suisse pour se rendre compte que très souvent, les frontières des cantons sont délimitées par un cours d’eau ou le milieu d’un lac. En d’autres termes, il n’est pas rare que des mesures isolées de gestion de l’eau concernent deux cantons, voire plus rarement trois ou quatre cantons. Cela s’applique aussi aux eaux souterraines (cf. par exemple le thème des zones de captage, motion Zanetti &lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20203625"&gt;20.3625&lt;/a&gt;). À l’échelon de la Confédération, la loi fédérale sur l’aménagement des cours d’eau et la loi fédérale sur la protection des eaux prévoient une collaboration intercantonale. Il existe de bons exemples d’application. On peut citer par exemple le cours inférieur de la Thur, la commission de la Linth ou le Plan régional d’évacuation des eaux de la Birse. Cependant, le potentiel de ce genre de collaborations reste inexploité dans de nombreuses régions qui sont en outre confrontées à des défis inédits.&lt;/p&gt;&lt;p&gt;Il n’existe encore aucune cartographie nationale des «&amp;nbsp;régions aquifères selon la fonction&amp;nbsp;», c’est-à-dire des unités territoriales qui présentent une certaine homogénéité du point de vue hydrologique. Dans les Préalpes, le Plateau et le Jura, en particulier, les bassins versants d’un cours d’eau sont rarement situés dans un même canton.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes.&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Peut-il envisager d’établir une carte de Suisse des régions aquifères délimitées selon la fonction dans le cadre de sa stratégie de gestion de l’eau&amp;nbsp;?&lt;/li&gt;&lt;li&gt;La Confédération pourrait-elle assumer un rôle de coordination dans des projets de gestion de l’eau qui concernent des régions aquifères ayant une même fonction et situées à cheval sur au moins deux cantons&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les cantons pourraient ainsi être incités à réaliser des projets supracantonaux au sein d’une région aquifère présentant une même fonction. Le Conseil fédéral pourrait-il envisager de créer un instrument d’encouragement à cet effet&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Un projet de révision de la loi fédérale sur la protection des eaux est en préparation. Le Conseil fédéral serait-il d’accord pour y intégrer des règles allant dans le sens des questions 2 et 3&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Kantone sind Inhaber der Wasserhoheit. Sie sind zuständig für Anlagen und Projekte der Wassernutzung, des Wasserschutzes und des Schutzes vor zu viel Wasser bzw. der Bewältigung von Folgen anhaltender Trockenheit.&amp;nbsp;&lt;/p&gt;&lt;p&gt;In die Legislaturplanung 2023-2027 (&lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20230082"&gt;Geschäft 23.082&lt;/a&gt;) wurde die Massnahme 127 aufgenommen: «Verabschiedung der Strategie «Wassermanagement – Trockenperioden, Starkniederschläge, Qualität der Wasserversorgung, Schutz der Wasserlebensräume.» Damit ist dem Bund eine konzeptionelle und koordinierende Funktion zugewiesen.&lt;/p&gt;&lt;p&gt;Ein Blick auf die Schweizerkarte verdeutlicht, dass Kantonsgrenzen sehr oft mitten durch Gewässer führen: Flussläufe oder Mittelachsen von Seen bilden eine Kantonsgrenze. Mit anderen Worten: Einzelmassnahmen des Wassermanagements tangieren sehr oft zwei Kantone, in selteneren Fällen drei oder mehr Kantone. Das gilt auch bezüglich Grundwasser (z.B. Thematik der Zuströmbereiche, Motion Zanetti &lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20203625"&gt;20.3625&lt;/a&gt;). Auf Bundesebene sehen das Wasserbaugesetz und das Gewässerschutzgesetz die interkantonale Zusammenarbeit vor. Es gibt gute Anwendungsbeispiele, etwa im Unterlauf der Thur, die Linthkommission oder der Regionale Entwässerungsplan Birs. Es gibt auch viele Regionen mit unausgeschöpftem Potenzial und neuen Herausforderungen.&lt;/p&gt;&lt;p&gt;Bisher existiert keine landesweite Kartierung von «funktionalen Wasserregionen», das heisst von Gebietseinheiten, die wassertechnisch eine gewisse Homogenität darstellen. Vor allem im voralpinen Raum, im Mittelland und im Jura liegen die Einzugsgebiete desselben Abflusses selten nur in einem Kanton.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Daher bitte ich den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Kann sich der Bundesrat vorstellen, im Rahmen der Strategie Wassermanagement eine Karte der Schweiz mit funktionalen Wasserregionen zu erstellen?&lt;/li&gt;&lt;li&gt;Könnte der Bund in Projekten des Wassermanagements, die innerhalb einer funktionalen Wasserregion, aber auf Gebiet von mindestens zwei Kantonen liegen, eine koordinierende Rolle übernehmen?&lt;/li&gt;&lt;li&gt;Für Kantone könnte ein Anreiz geschaffen werden, Projekte kantonsübergreifend innerhalb einer funktionalen Wasserregionen zu realisieren. Kann sich der Bundesrat vorstellen, dafür ein Fördergefäss zu schaffen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Aktuell wird eine Revision des Gewässerschutzgesetzes vorbereitet. Ist der Bundesrat bereit, Regelungen im Sinne der Fragen 2 und 3 in den Entwurf zu integrieren?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broulis Pascal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stranden Reisende nach Paris im Jahr 2026 auf dem Perron in Lausanne?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les voyageurs pour Paris resteront-ils sur le quai à Lausanne en 2026 ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I viaggiatori diretti a Parigi rimarranno bloccati a Losanna nel 2026?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Comment le Conseil fédéral se détermine-t-il sur la suppression de la moitié des TGV entre Lausanne et Paris pour l’année 2026&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Est-ce que des liaisons supplémentaires depuis Lausanne via Vallorbe seront ajoutées pour compenser la baisse de fréquences via Genève&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;En fonction des informations disponibles, est-ce que les CFF prévoient de limiter cette baisse de l’offre TGV Paris–Genève–Lausanne à l’année 2026 ou cette diminution concernera plusieurs années&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles mesures le Conseil fédéral entend prendre pour maintenir une améliorer l’offre entre Paris et Lausanne, via le Jura, et respecter la Convention internationale relative au raccordement de la Suisse au réseau ferré français, notamment aux liaisons à grande vitesse entrée en vigueur le 23 mars 2003 ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie steht der Bundesrat dazu, dass im Jahr&amp;nbsp;2026 die Hälfte der TGV-Verbindungen zwischen Lausanne und Paris gestrichen wird?&lt;/li&gt;&lt;li&gt;Wird es zusätzliche Verbindungen ab Lausanne über Vallorbe geben, um zu kompensieren, dass die Verbindung über Genf weniger häufig angeboten wird?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Plant die SBB, die TGV-Verbindung Paris–Genf–Lausanne nur im Jahr&amp;nbsp;2026 oder gar für mehrere Jahre zu reduzieren?&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat zu treffen, um das Angebot zwischen Paris und Lausanne über den Jura fortzuführen und zu verbessern, und um die Vereinbarung mit Frankreich zum Anschluss der Schweiz an das französische Eisenbahnnetz, insbesondere an die Hochgeschwindigkeitslinien, die am 28.&amp;nbsp;März 2003 in Kraft trat, einzuhalten?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calame Didier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Den A5-Westast in Biel mit einem Tunnel mit Gegenverkehr fertigstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achèvement de la branche ouest de l'A5 à Bienne par un tunnel bidirectionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completare il ramo ovest della A5 a Bienne con una galleria bidirezionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil Fédéral est prié de reprendre dans les meilleurs délai le dossier de la traversé ouest de Bienne(A5)&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Projekt Westumfahrung Biel (A5) so rasch wie möglich wieder aufzunehmen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadri Lorenzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errichtung eines Schweizer Staatsfonds zur Unterstützung der Infrastruktur und der Volkswirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création d’un fonds souverain suisse pour soutenir les infrastructures et l’économie nationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istituire un fondo sovrano svizzero a sostegno delle infrastrutture e dell’economia nazionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un projet de loi visant à créer un fonds souverain suisse avec les caractéristiques suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;mode de financement&amp;nbsp;: alimenté par une partie des réserves monétaires de la Banque nationale suisse (BNS) sans incidence sur le budget ordinaire de la Confédération;&lt;/li&gt;&lt;li&gt;objectifs&amp;nbsp;: investissements dans des projets d’infrastructures stratégiques au niveau national et cantonal, notamment dans des régions périphériques comme le canton du Tessin;&lt;/li&gt;&lt;li&gt;instruments de cohésion: le fonds vise à renforcer l’intégration des régions suisses en soutenant la mobilité&amp;nbsp;durable et accessible, comme les tunnels, les lignes ferroviaires souterraines, les contournements et les projets du réseau train-tram;&lt;/li&gt;&lt;li&gt;participation interne&amp;nbsp;: possibilité pour les collectivités et les ressortissants suisses de souscrire à des obligations émises par le fonds;&lt;/li&gt;&lt;li&gt;diversification et stabilité économique&amp;nbsp;: promouvoir une utilisation productive et à long terme des réserves de la BNS pour renforcer l’économie nationale et réduire l’impact du renchérissement du franc suisse.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Gesetzesentwurf zur Errichtung eines Schweizer Staatsfonds vorzulegen, der die nachfolgenden Merkmale aufweist:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Finanzierung: Der Fonds wird aus einem Teil der Währungsreserven der Schweizerischen Nationalbank (SNB) gespiesen, ohne sich auf den ordentlichen Bundeshaushalt auszuwirken;&lt;/li&gt;&lt;li&gt;Zweck: Investitionen in strategische Infrastrukturprojekte auf nationaler und kantonaler Ebene zu tätigen, insbesondere in Randregionen wie dem Kanton Tessin;&lt;/li&gt;&lt;li&gt;Instrument für den Zusammenhalt: Der Fonds soll die Integration der Regionen der Schweiz stärken, indem eine nachhaltige und zugängliche Mobilität gefördert wird, zum Beispiel durch Tunnel, unterirdische Bahnlinien, Umfahrungen und Tram- bzw. Zugprojekte;&lt;/li&gt;&lt;li&gt;Interne Beteiligung: Schweizer Gemeinwesen und Bürgerinnen und Bürger sollen Fondsanleihen zeichnen können;&lt;/li&gt;&lt;li&gt;Diversifizierung und Stabilität der Wirtschaft: Der Fonds soll eine produktive und langfristige Nutzung der Währungsreserven der SNB fördern und so die Volkswirtschaft stärken und die Auswirkungen der Aufwertung des Schweizer Frankens abschwächen.&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Finanzwesen|Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Finances|Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Finanze|Trasporti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleichbehandlung im interkantonalen Finanzausgleich beim Kantonswechsel von Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egalité de traitement dans la péréquation intercantonale lors du transfert de Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parità di trattamento nel quadro della perequazione finanziaria intercantonale applicata in seguito al trasferimento del Comune di Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de déposer un projet de modification législative qui compense intégralement en faveur du canton de Berne le montant que ce dernier s'est engagé à payer au du canton du Jura dans le cadre du Concordat intercantonal au titre de compromis concernant les effets différés du changement de territoire dans le cadre de la péréquation financière fédérale (env. 75 millions de francs)&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf für eine Gesetzesänderung vorzulegen, damit dem Kanton Bern der Betrag vollständig ausgeglichen wird, den er im interkantonalen Konkordat dem Kanton Jura als Kompromiss zugesichert hat (ca. 75 Millionen Franken), weil sich der Gebietswechsel auf den eidgenössischen Finanz- und Lastenausgleich erst verzögert auswirkt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temporäre Ausgleichszahlungen im Zusammenhang mit dem Kantonswechsel der Gemeinde Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiements compensatoires temporaires dans le contexte du changement de canton de la commune de Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versamenti di compensazione temporanei in relazione al cambiamento di Cantone di Moutier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un projet d'acte garantissant que le canton du Jura reçoive 13 millions de francs par an de 2027 à 2031, en lien avec le changement de canton de la commune de Moutier et en complément du Concordat entre le canton de Berne et la République et Canton du Jura. À cet effet, il examinera toutes les options qui permettent de trouver une solution en temps utile, y compris un ajout à la modification de la loi fédérale sur la péréquation financière et la compensation des charges (PFCC ; RS 613.2) prévue dans le cadre de l’avant-projet sur le programme d’allégement budgétaire 2027.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Schilliger, Bürgi Roman, Farinelli, Gafner, Giacometti, Götte, Guggisberg, Nause, Sollberger, Theiler, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Erlassentwurf vorzulegen, der dafür sorgt, dass der Kanton Jura in den Jahren 2027 bis 2031 im Zusammenhang mit dem Kantonswechsel der Gemeinde Moutier und in Ergänzung zum bilateralen Abkommen zwischen den Kantonen Bern und Jura jährlich 13 Millionen Franken erhält.&amp;nbsp;Dazu prüft er alle Optionen, die eine zeitgerechte Lösung erlauben, insbesondere auch eine Ergänzung der im Vorentwurf zum Entlastungspaket 2027 vorgesehenen Änderung des Bundesgesetzes über den Finanz- und Lastenausgleich (FiLaG; SR 613.2).&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit der Kommission (Schilliger, Bürgi Roman, Farinelli, Gafner, Giacometti, Götte, Guggisberg, Nause, Sollberger, Theiler, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maitre Vincent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welche Bedeutung haben die internationalen Organisationen für Bund und Kantone? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évaluer l'importance des organisations internationales pour la Confédération et les cantons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valutare l'importanza delle organizzazioni internazionali per la Confederazione e i Cantoni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de rendre un rapport sur l’importance des Organisations internationales, d'un point de vue économique, pour la Suisse et l’ensemble des cantons.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le rapport devra notamment développer les points suivants&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Présenter un état des lieux complet et actuel de l’impact des Organisations internationales ayant leur siège en Suisse en matière d’emplois, directs et indirects, et de dynamisme économique pour la Confédération et l'ensemble des cantons&amp;nbsp;;&lt;/li&gt;&lt;li&gt;Établir les recettes fiscales, directes et indirectes, issues des organisations internationales pour les finances fédérales&amp;nbsp;(IFD, TVA, et autres taxes et impôts) ;&lt;/li&gt;&lt;li&gt;Évaluer l’apport des Organisations internationale dans la part du canton de Genève à la péréquation financière fédérale&amp;nbsp;;&lt;/li&gt;&lt;li&gt;Analyser les risques encourus pour la Suisse par les récentes décisions de désengagement de la nouvelle administration américaine.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Bericht über die wirtschaftliche Bedeutung der internationalen Organisationen für die Schweiz und die Gesamtheit der Kantone zu erstellen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bericht soll namentlich Folgendes enthalten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;eine umfassende und aktuelle Bestandsaufnahme der Auswirkungen der internationalen Organisationen mit Sitz in der Schweiz auf die direkte und indirekte Beschäftigung und die wirtschaftliche Dynamik für den Bund und alle Kantone;&lt;/li&gt;&lt;li&gt;die Angabe der Bundeseinnahmen aus direkten und indirekten Steuern (direkte Bundessteuer, MwSt und andere Steuern und Abgaben) von internationalen Organisationen;&lt;/li&gt;&lt;li&gt;eine Schätzung des Beitrags, den die internationalen Organisationen zum Anteil des Kantons Genf am eidgenössischen Finanzausgleich leisten;&lt;/li&gt;&lt;li&gt;eine Analyse der Risiken, die sich für die Schweiz aus den jüngsten Rückzugsentscheidungen der neuen US-Regierung ergeben.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Wirtschaft|Finanzwesen|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Économie|Finances|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Economia|Finanze|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candinas Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diskriminierende Regelung bei Pensionsverträgen in Behinderten-, Alters- und Pflegeheimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Règle discriminatoire dans les contrats d'accueil en EMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciplinamento discriminatorio per i contratti di pensione negli istituti per persone con disabilità e nelle case per anziani e di cura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les contrats d’accueil dans les établissements médico-sociaux (EMS) sont des contrats mixtes, avec une composante locative et une composante liée à un mandat. Dans la jurisprudence, l’accent est mis sur le droit des mandats en raison des prestations de soins fournies par les EMS. En vertu de l’art. 404, al. 1, CO, le mandat peut être révoqué ou répudié en tout temps, même sans motif particulier. Dans de telles circonstances, les résidents d’un EMS doivent se contenter de faire valoir leur droit à une indemnisation pour le dommage causé ; ils ne peuvent pas s’opposer à une résiliation du contrat concernant les prestations de soins. Or, ces personnes ont besoin aussi bien d’un contrat de logement en cours de validité que de soins ininterrompus. En perdant les prestations de soins, elles perdent aussi, de facto, la possibilité de faire valoir une éventuelle protection relevant du droit du bail.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Qui plus est, si le cas est porté devant le tribunal, la nature mixte du contrat pose le problème de la compétence des tribunaux. Il en résulte une procédure longue et coûteuse avant même qu’un tribunal ne puisse entrer en matière. Il est évident que très peu de résidents d’EMS peuvent se le permettre sur les plans à la fois temporel et financier.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Conscient de ce problème, le canton de Vaud a élaboré un contrat-type qui prévoit que l’établissement ne peut résilier le contrat que lorsqu’une solution a été trouvée au sujet du nouveau lieu de séjour du résident. Il serait utile de trouver une solution à l’échelle de la Suisse afin d’éviter que les résidents d’un EMS ne perdent leur domicile du jour au lendemain sans pouvoir, par cet argument, empêcher une résiliation qui serait par ailleurs justifiée. La Confédération dispose déjà, avec la LIPPI, d’une réglementation concernant les établissements pour personnes handicapées qui permet de poser certaines conditions au niveau des cantons, malgré la RPT, en imposant à ces derniers de prévoir des plans de mesures, notamment des procédures de conciliation entre les résidents et les institutions.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le Conseil fédéral est chargé de répondre aux questions suivantes.&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Est-il au courant de la problématique du contrat d’accueil en EMS dans sa forme actuelle ?&lt;/li&gt;&lt;li&gt;La possibilité de régler les contrats d’accueil dans la loi et de prévoir des mécanismes de protection contre les résiliations a-t-elle déjà été évoquée ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral pourrait-il envisager de fixer, dans des lois telles que la LIPPI, une protection adéquate contre les résiliations sous la forme de conditions ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Pensionsverträge von Behinderten-, Alters- oder Pflegeheimen sind gemischte Verträge, mit mietrechtlichen und auftragsrechtlichen Anteilen. Aufgrund der Betreuungsleistungen in einem Heim, wird in der Rechtsprechung der Schwerpunkt auf das Auftragsrecht gelegt. Nach&amp;nbsp;Art. 404 Abs. 1 OR kann der Auftrag von jeder Partei jederzeit widerrufen oder gekündigt werden,&amp;nbsp;ohne dass dafür besondere Gründe vorliegen müssen. Bewohner eines Heimes müssen sich in solchen Fällen auf die Geltendmachung von Schadenersatzansprüchen beschränken und können die Kündigung betreffend Betreuungsleistungen nicht erfolgreich anfechten. Die Betroffenen sind vom laufenden Mietverhältnis und andauernder Betreuung gleichermassen abhängig. Der Verlust von Betreuungsleistungen verunmöglicht es den Betroffenen zudem, den allfälligen mietrechtlichen Schutz tatsächlich in Anspruch nehmen zu können.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Wird der Fall vor Gericht gezogen, besteht aufgrund des gemischten Vertrags überdies ein Problem mit der Zuständigkeit der Gerichte. Es resultiert ein langwieriger und kostspieliger Rechtsstreit, bis überhaupt ein Gericht auf die Klage eintritt. Es ist offensichtlich, dass dieses Vorgehen nur den wenigsten Bewohnern eines Heimes zeitlich und finanziell zugemutet werden kann.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im Kanton Waadt wurde dieses Problem erkannt und ein Mustervertrag erarbeitet, welcher vorsieht, dass die Kündigung durch das Heim erst dann erfolgen kann, wenn eine Lösung bezüglich des neuen Aufenthaltsortes der betroffenen Person gefunden wurde. Eine gesamtschweizerische Lösung ist demzufolge erstrebenswert, um zu verhindern, dass Bewohner eines Heimes von einem Tag auf den anderen ihren Wohnsitz verlieren, ohne eine berechtigte Kündigung damit zu verunmöglichen. Mit dem IFEG regelt der Bund bereits heute für Behindertenheime in Kantonen trotz NFA gewisse Voraussetzungen und verlangt von den Kantonen Konzepte, die etwa Schlichtungsverfahren zwischen Bewohnern und Institutionen vorsehen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Ist die Problematik des Pensionsvertrages in der heutigen Form dem Bundesrat bekannt?&lt;/li&gt;&lt;li&gt;Wurde die Möglichkeit, den Pensionsvertrag im Gesetz zu regeln und ebenfalls Kündigungsschutzbestimmungen einzuführen je in Erwägung gezogen?&lt;/li&gt;&lt;li&gt;Kann sich der Bundesrat vorstellen, einen angemessenen Kündigungsschutz als Voraussetzung in Gesetzen wie dem IFEG aufzunehmen?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soziale Fragen|Gerichtswesen|Sozialer Schutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questions sociales|Justice|Protection sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questioni sociali|Giustizia|Protezione sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trede Aline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie soll der Zustand der Schweizer Bäche konkret verbessert werden? Genügt dafür das bestehende Instrumentarium?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment améliorer l'état des ruisseaux suisses? Les instruments existants suffisent-ils ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come migliorare concretamente le condizioni dei torrenti svizzeri? Gli strumenti oggi disponibili sono sufficienti?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;1.&amp;nbsp;Est-il d’avis que l’état décrit des ruisseaux suisses, dans lequel les pesticides jouent manifestement un rôle important, représente un effet acceptable sur les organismes non-cibles&amp;nbsp;? Si oui, comment le justifie-t-il&amp;nbsp;?&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Les rapports de l’EAWAG et du VSL sont-ils un indice, voire une preuve, que les risques liés aux pesticides toxiques sont aujourd’hui systématiquement mal évalués lors de l’homologation&amp;nbsp;? Si non, pourquoi&amp;nbsp;? Si oui, que faut-il faire pour remédier à cette situation&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Ces rapports sont-ils un indice, voire une preuve, que les risques liés à certains pesticides sont mal évalués&amp;nbsp;? Si non, comment le Conseil fédéral évalue-t-il les conclusions de ces rapports, dans la perspective de l’homologation&amp;nbsp;? Si oui, quelles sont les conséquences&amp;nbsp;?&lt;/p&gt;&lt;p&gt;4.&amp;nbsp;Quels effets indésirables directs et indirects les produits phytosanitaires peuvent-ils avoir sur les poissons, à leurs différents stades de développement&amp;nbsp;? Que disent les études précitées et d’autres sur l’état des poissons dans les ruisseaux suisses&amp;nbsp;? Le Conseil fédéral y voit-il des causes à effets&amp;nbsp;?&lt;/p&gt;&lt;p&gt;5.&amp;nbsp;Qu’entend-il faire pour améliorer la situation dans les cours d’eau suisses&amp;nbsp;? Quels sont les objectifs qu’il souhaite atteindre et à quelle échéance&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Ist der Bundesrat der Meinung, dass der beschriebene Zustand der Schweizer Bäche - bei dem Pestizide offenbar eine wichtige Rolle spielen - einen annehmbaren Effekt auf Nichtziel-Organismen darstellt? Wenn ja, wie begründet er dies?&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Sind die Berichte von EAWAG und VSL ein Indiz, allenfalls gar ein Beleg dafür, dass die Risiken von toxischen Pestiziden bei der Zulassung heute systematisch falsch eingeschätzt werden? Wenn nein, warum nicht? Wenn ja, was ist zu tun?&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Sind sie ein Indiz oder gar ein Beleg dafür, dass die Risiken bei einzelnen Pestiziden falsch eingeschätzt werden? Wenn nein, wie beurteilt der Bundesrat die Ergebnisse dann, mit Blick auf die Zulassung? Wenn ja, was sind die Konsequenzen?&lt;/p&gt;&lt;p&gt;4.&amp;nbsp;Welche direkten und indirekten unerwünschten Effekte können Pflanzenschutzmittel auf Fische haben, in ihren verschiedenen Entwicklungsstadien? Was sagen die erwähnten und andere Studien zum Zustand der Fische in Schweizer Bächen und sieht der Bundesrat Parallelen?&lt;/p&gt;&lt;p&gt;5.&amp;nbsp;Was will der Bundesrat konkret tun, um die Situation in den Schweizer Bächen zu verbessern? Welche Ziele will er dabei erreichen und bis wann?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Würth Benedikt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufgabenteilung im Bereich Denkmal-, Heimat- und Ortsbildschutz wieder auf den Kerngehalt der NFA I und der Verfassung zurückführen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protection des monuments, du patrimoine et des sites construits. Répartir à nouveau les tâches conformément à la RPT I et à la Constitution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservazione dei monumenti storici e protezione del paesaggio e degli insediamenti. Tornare alla ripartizione dei compiti prevista dalla NPC I e dalla Costituzione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le projet «&amp;nbsp;Désenchevêtrement&amp;nbsp;27&amp;nbsp;» de la Confédération et des cantons entraînera probablement aussi des adaptations légales. Dans ce cadre, voire dans un projet séparé, le Conseil fédéral est chargé de répartir à nouveau les tâches dans le domaine de la protection des monuments, du patrimoine et des sites construits selon l’essence même du message concernant la réforme de la péréquation financière et de la répartition des tâches entre la Confédération et les cantons (RPT; objet 01.074). Celui-ci prévoit que la Confédération sera seule responsable des &lt;i&gt;objets&lt;/i&gt; d'importance nationale (ch. 6.2.6 du message RPT). Cette tâche continuera d'être mise en œuvre dans le cadre de la liste des monuments, ensembles et sites archéologiques d'importance nationale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La &lt;i&gt;protection des sites construits&lt;/i&gt; ainsi que la responsabilité des objets d'importance cantonale et communale sont l’affaire exclusive des cantons.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Projekt Entflechtung 27 von Bund und Kantonen wird mutmasslich auch gesetzliche Anpassungen nach sich ziehen. In diesem Rahmen (oder gegebenenfalls mit einer separaten Vorlage) wird der Bundesrat beauftragt, die Aufgabenteilung im Bereich Denkmal-, Heimat und Ortsbildschutz wieder auf den Kerngehalt der Botschaft zur Neugestaltung des Finanzausgleichs und der Aufgaben zwischen Bund und Kantonen (NFA) zurückzuführen (Geschäft 01.074). Demgemäss soll der Bund die Verantwortung für &lt;i&gt;Objekte&lt;/i&gt; von nationaler Bedeutung übernehmen (Kap. 6.2.6 der NFA Botschaft). Diese Aufgabe soll auch weiterhin mit dem Verzeichnis der Denkmäler, Ensembles und archäologischen Stätten von nationaler Bedeutung umgesetzt werden.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der gesamte &lt;i&gt;Ortsbildschutz&lt;/i&gt; sowie die Verantwortung für Objekte von kantonaler und kommunaler Bedeutung ist ausschliesslich Sache der Kantone. &amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Kultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Cultura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für eine gerechte Berücksichtigung des Wechsels von Moutier zum Kanton Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une prise en compte équitable du transfert de Moutier dans le canton du Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per una considerazione equa delle ripercussioni finanziarie del trasferimento del Comune di Moutier nel Cantone del Giura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est invité à régler de manière appropriée les effets financiers du transfert de Moutier dans le canton du Jura pour la Répartition des tâches et des charges entre la Confédération et les cantons (RPT).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird aufgefordert, die finanziellen Auswirkungen des Wechsels von Moutier zum Kanton Jura im Hinblick auf die Aufgaben- und Lastenverteilung zwischen Bund und Kantonen&amp;nbsp;(NFA) angemessen zu regeln.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Förderung der Biodiversität entlang von SBB-Infrastrukturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favoriser la biodiversité attenante aux infrastructures des CFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promozione della biodiversità lungo le infrastrutture FFS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Garantir la biodiversité en Suisse est un défi de taille, car les surfaces appropriées sont limitées. Néanmoins, la faune et la flore pourraient certainement bénéficier d’habitats de grande valeur écologique le long des voies ferrées et sur les aires ferroviaires. Les CFF s’engagent activement en faveur de la protection et de l’entretien de ces surfaces et ont déjà, en collaboration avec l’OFEV, lancé plusieurs projets pilotes et pris des mesures visant à favoriser la biodiversité. Il reste à savoir si ces mesures sont efficaces et comment la Confédération continuera de soutenir les CFF.&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment la Confédération soutient-elle les efforts des CFF visant à favoriser la biodiversité le long des chemins de fer et sur les aires ferroviaires&amp;nbsp;?&lt;/li&gt;&lt;li&gt;L’objectif des CFF qui consiste d’ici 2030 à entretenir 20&amp;nbsp;% des talus en les maintenant proches de l’état naturel semble modérément ambitieux. Est-il possible de pousser l’objectif plus loin, voire d’augmenter ce pourcentage&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quels progrès concrets ont été réalisés en vue de cet objectif et de la lutte contre les plantes néophytes envahissantes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les projets de l’OFEV et des CFF qui visent à favoriser la biodiversité en recourant à d’autres surfaces, notamment le long des chemins de fer ou les aires ferroviaires inutilisées, sont bienvenus, mais quelles mesures sont prévues concrètement&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Dans quelle mesure les CFF travaillent-ils avec des partenaires pour accélérer la mise en œuvre de ces mesures&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral évalue-t-il l’efficacité des mesures prises pour améliorer la biodiversité, et quelles mesures supplémentaires sont nécessaires, selon lui, pour continuer à favoriser la biodiversité attenante aux infrastructures des CFF&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Sicherstellung der Biodiversität in der Schweiz stellt eine große Herausforderung dar, da geeignete Flächen begrenzt sind. Entlang der SBB-Infrastruktur oder auf Bahnarealen bestehen jedoch grosse Chancen, ökologisch wertvolle Lebensräume zu schaffen. Die SBB hat denn auch in Zusammenarbeit mit dem BAFU bereits verschiedene Pilotprojekte und Massnahmen zur Förderung der Biodiversität initiiert und setzt sich aktiv für den Schutz und die Pflege dieser Flächen ein. Es stellt sich jedoch die Frage, wie effektiv diese Massnahmen sind und wie die SBB weiterhin vom Bund unterstützt wird.&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie unterstützt der Bund die SBB in ihren Bemühungen zur Förderung der Biodiversität entlang der Bahnstrecken und auf Bahnarealen?&lt;/li&gt;&lt;li&gt;Das Ziel der SBB, bis 2030 ein Fünftel der Böschungen naturnah zu pflegen, scheint bedingt ambitioniert. Besteht die Möglichkeit, dieses Ziel zu forcieren und gegebenenfalls einen höheren Anteil der Flächen naturnah zu gestalten?&lt;/li&gt;&lt;li&gt;Welche konkreten Fortschritte wurden bisher bei der naturnahen Pflege von Böschungen und der Bekämpfung invasiver Neophyten erzielt?&lt;/li&gt;&lt;li&gt;Die Pläne von BAFU und SBB, weitere Flächen der SBB, wie zum Beispiel Gleisfelder oder ungenutzte Bahngrundstücke, für die Förderung der Biodiversität zu nutzen sind erfreulich, welche konkreten Schritte sind geplant?&lt;/li&gt;&lt;li&gt;Inwiefern arbeitet die SBB mit externen Dienstleistern zusammen, um diese Massnahmen schneller umzusetzen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie bewertet der Bundesrat die Wirksamkeit der bisherigen Maßnahmen der SBB zur Verbesserung der Biodiversität, und welche zusätzlichen Schritte sind aus seiner Sicht erforderlich, um die Biodiversität entlang der SBB-Infrastruktur weiter zu fördern?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mangel an Ärztinnen und Ärzten. Bilanz der Verpflichtung für ausländische Ärztinnen und Ärzte, während drei Jahren in einem Schweizer Spital zu arbeiten, und Bilanz der Ausnahmen nach Artikel 37 Absatz 1bis KVG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pénurie de médecins. Bilan de l'obligation pour les médecins étrangers d'effectuer trois ans de formation dans un hôpital suisse et bilan des exceptions prévues à l'article 37 alinéa 1bis LAMal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penuria di medici. Bilancio dell'obbligo per i medici stranieri di svolgere tre anni di perfezionamento in un ospedale svizzero e bilancio delle deroghe previste all'articolo 37 capoverso 1bis LAMal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Depuis janvier 2022, il a été décidé que les médecins au bénéfice d’un diplôme étranger souhaitant s’installer en Suisse doivent effectuer 3 ans de formation au sein d’un hôpital suisse,&amp;nbsp;dans le domaine de spécialité faisant l’objet de leur demande d’admission, ceci afin de se familiariser avec le système de santé suisse.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans le but d’éviter la pénurie de médecins qui a été rapidement constatée dans le domaine des soins de premier recours à la suite de l’introduction de cette règle,&amp;nbsp;une exception a été adoptée en mars 2023 (art. 37, al. 1&lt;sup&gt;bis&lt;/sup&gt;, LAMal), qui concerne uniquement les médecins praticiens, les médecins généralistes, les pédiatres, les psychiatres et les psychothérapeutes d’enfants et d’adolescents.&lt;/p&gt;&lt;p&gt;Lors des débats au parlement sur cette obligation de 3 ans de formation pour les autres spécialités, il y avait eu des réflexions sur la pénurie de certaines spécialités dans certains cantons (surtout Jura et Valais), ainsi que sur les difficultés pour les médecins généralistes de travailler efficacement s’ils ne disposent pas d’un réseau de médecins spécialistes sur lesquels s’appuyer. Afin que ces pénuries très spécifiques puissent être comblées, il est important de connaitre le devenir&amp;nbsp; des médecins étrangers au terme de leur formation de 3 ans dans un hôpital suisse, en particulier de savoir s’ils vont s’installer dans des cantons à pénurie de leur spécialité ou au contraire dans les centres urbains déjà bien fournis en spécialistes.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le CF de répondre à ces questions&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Depuis mars 2023, date de l’entrée en vigueur de l’exception d’avoir effectué ces 3 ans dans un hôpital, combien de médecins se sont-ils installés, dans quelles spécialités (pédiatre, généraliste, psychiatrie) et dans quels cantons&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Y a-t-il en particulier eu plus d’installation dans les cantons qui faisaient état d’une pénurie, en particulier le Jura et le Valais&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Depuis 2022, combien de médecins spécialistes étrangers ont-ils commencé à une formation de 3 ans dans un hôpital reconnu pour la formation postgrade&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans quels cantons ces médecins ont-ils effectué leurs 3 ans de formation&amp;nbsp;? et dans quelles spécialités&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Y en a-t-il qui ont terminé leur formation de 3 ans et qui se sont installés&amp;nbsp;? Si oui, où&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Seit Januar&amp;nbsp;2022 gilt, dass Ärztinnen und Ärzte mit einem ausländischen Diplom, die sich in der Schweiz niederlassen wollen, während drei Jahren in einem Schweizer Spital im beantragten Fachgebiet gearbeitet haben müssen. Dies wird damit begründet, dass sie sich mit dem Schweizer Gesundheitswesen familiarisieren sollen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Da es in der Grundversorgung schon bald nach der Einführung dieser Regelung zu einem Ärztemangel kam, wurde im März&amp;nbsp;2023 für bestimmte Fachgebiete, nämlich die Fachgebiete Praktischer Arzt oder Praktische Ärztin, Allgemeine Innere Medizin, Kinder- und Jugendmedizin sowie Kinder- und Jugendpsychiatrie und -psychotherapie, eine Ausnahmeregelung angenommen (Art.&amp;nbsp;37 Abs.&amp;nbsp;1&lt;sup&gt;bis&lt;/sup&gt; des Bundesgesetzes über die Krankenversicherung), um in diesen Fachbereichen einen Ärztemangel zu vermeiden.&lt;/p&gt;&lt;p&gt;Bei den Beratungen im Parlament über die Verpflichtung für die anderen Fachgebiete, drei Jahre Berufserfahrung in einem Schweizer Spital vorzuweisen, gab es Überlegungen zum Mangel an Ärztinnen und Ärzten mit bestimmten Fachgebieten in gewissen Kantonen (vor allem in den Kantonen Jura und Wallis) und zur Schwierigkeit, effizient arbeiten zu können, mit der Ärztinnen und Ärzte der Allgemeinen Inneren Medizin konfrontiert sind, wenn sie nicht über ein Netzwerk von Fachärztinnen und Fachärzten verfügen, auf die sie sich stützen können. Damit diese ganz spezifischen Mängel behoben werden können, ist es wichtig zu wissen, was die Ärztinnen und Ärzte nach den drei Jahren in einem Schweizer Spital machen, insbesondere, ob sie sich in einem Kanton niederlassen, in dem es an Personen in ihrem Fachgebiet mangelt, oder in einer Stadt, die bereits bestens mit Fachärztinnen und -ärzten versorgt ist.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie viele Ärztinnen und Ärzte haben sich seit März&amp;nbsp;2023, als die Ausnahme zur Regelung, während drei Jahren in einem Spital gearbeitet zu haben, in Kraft getreten ist, in der Schweiz niedergelassen und in welchen Fachgebieten (Kinder- und Jugendmedizin, Allgemeine Innere Medizin und Psychiatrie) und in welchen Kantonen sind sie tätig?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Haben sich in den Kantonen, in denen ein Ärztemangel herrscht, insbesondere im Jura und im Wallis, mehr Personen niedergelassen?&lt;/li&gt;&lt;li&gt;Wie viele ausländische Fachärztinnen und -ärzte haben seit 2022 eine dreijährige Stelle in einem für die Weiterbildung anerkannten Spital angetreten?&amp;nbsp;&lt;/li&gt;&lt;li&gt;In welchen Kantonen haben diese Ärztinnen und Ärzte während den drei Jahren gearbeitet? Und in welchen Fachgebieten?&lt;/li&gt;&lt;li&gt;Gibt es Ärztinnen und Ärzte, die sich nach den drei Jahren Berufserfahrung in einem Schweizer Spital in der Schweiz niedergelassen haben? Wenn ja, wo?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bildung|Beschäftigung und Arbeit|Migration|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Éducation|Emploi et travail|Politique migratoire|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formazione|Occupazione e lavoro|Migrazione|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schienennetz. Lasst uns die Anbindung Genfs verbessern!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseau ferroviaire. Désenclavons Genève !</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rete ferroviaria. Facciamo uscire Ginevra dall'isolamento!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Grand Conseil de la République et canton de Genève&lt;/p&gt;&lt;p&gt;vu I' article 160, alinéa 1, de la Constitution fédérale, du 18 avril 1999 ;&lt;/p&gt;&lt;p&gt;vu l'article 115 de la loi fédérale sur l'Assemblée fédérale, du 13 décembre 2002 ;&lt;/p&gt;&lt;p&gt;vu l'article 156 de la loi portant règlement du Grand Conseil de la République et canton de Genève, du 13 décembre 1985,&lt;/p&gt;&lt;p&gt;considérant&lt;/p&gt;&lt;p&gt;- les motions 2929 et 2930 adoptées par notre Grand Conseil le 22 juin 2023 ;&lt;/p&gt;&lt;p&gt;- l'entrée en vigueur du nouvel horaire CFF le 15 décembre 2024 ;&lt;/p&gt;&lt;p&gt;- les haltes systématiques des trains IR et IC à Renens et l'allongement important des temps de transport pour les voyageurs en provenance ou à destination de Genève ;&lt;/p&gt;&lt;p&gt;- la nécessité de changer en gare de Renens pour rejoindre l'axe ferroviaire du pied du Jura, et même de changer de quai, quel que soit le sens du trajet, contrairement à l'option proposée par les CFF à la commission des transports ;&lt;/p&gt;&lt;p&gt;- le maintien d'une liaison entre Genève et le pied du Jura aux heures de pointe (IR 57), mais impliquant un allongement du temps de parcours par rapport à l'option avec changement ;&lt;/p&gt;&lt;p&gt;- les documents mis à disposition par l'OFT en vue du message 2026 sur l'aménagement ferroviaire du Conseil fédéral ;&lt;/p&gt;&lt;p&gt;- au-delà de l'acceptation de la motion nationale 23.3668 et de l'intégration du tunnel Morges-Perroy, l'absence d'une proposition concrète de deuxième ligne entre Genève et Lausanne et de tout autre aménagement permettant d'améliorer la desserte de notre canton ;&lt;/p&gt;&lt;p&gt;-&amp;nbsp;l'invitation faite aux cantons de participer aux travaux de planification continue, comme prévu dans le cadre de l'adoption par le peuple du fonds FIF,&lt;/p&gt;&lt;p&gt;demande à l'Assemblée fédérale&lt;/p&gt;&lt;p&gt;- de demander au Conseil fédéral de mentionner les études d'aménagement d'une nouvelle ligne Genève-Lausanne dans son message 2026 sur l'aménagement ferroviaire ;&lt;/p&gt;&lt;p&gt;- de veiller à assurer d'ici à l'entrée en fonction de cette ligne, une desserte du canton de Genève d'une qualité au moins équivalente ( en termes de nombre de trains, de places et de vitesse commerciale ) à la situation qui prévalait en 2018 ;&lt;/p&gt;&lt;p&gt;- de rétablir le plus rapidement possible des liaisons directes et rapides avec Neuchâtel, Bienne et Bâle par la ligne du pied du Jura ;&lt;/p&gt;&lt;p&gt;- de poursuivre et d'intensifier les pourparlers avec la France pour améliorer la desserte internationale de Genève, en direction de Lyon et du sud de la France, mais également de Paris, Nantes, Lille, Bruxelles et Londres.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel 160 Absatz 1 der Bundesverfassung vom 18. April 1999,&lt;/p&gt;&lt;p&gt;Artikel 115 des Bundesgesetzes vom 13. Dezember 2002 über die Bundesversammlung und&lt;/p&gt;&lt;p&gt;Artikel 156 des Geschäftsreglements vom 13. September 1985 des Grossen Rates des Kantons Genf (Loi portant règlement du Grand Conseil de la République et canton de Genève);&lt;/p&gt;&lt;p&gt;und in Anbetracht dessen, dass&lt;/p&gt;&lt;p&gt;- der Grosse Rat des Kantons Genf am 11. Juni 2023 die Motionen 2929 und 2930 angenommen hat;&lt;/p&gt;&lt;p&gt;- der neue Fahrplan der Schweizerischen Bundesbahnen (SBB) am 15. Dezember 2024 in Kraft getreten ist;&lt;/p&gt;&lt;p&gt;- die Interregio-Züge (IR) und die Intercity-Züge (IC) systematisch in Renens halten und die Reisezeit für Reisende von oder nach Genf erheblich verlängert wurde;&lt;/p&gt;&lt;p&gt;- am Bahnhof von Renens umgestiegen werden muss, um auf die Eisenbahnachse des Jurasüdfusses zu gelangen, und - anders als die SBB der Verkehrskommission des Kantons Genf vorgeschlagen haben - der Bahnsteig unabhängig von der Richtung der Weiterreise gewechselt werden muss;&lt;/p&gt;&lt;p&gt;- zu Stosszeiten zwar eine Direktverbindung zwischen Genf und dem Jurasüdfuss (IR 57) beibehalten wurde, diese aber länger dauert als die Verbindung mit Umsteigen;&lt;/p&gt;&lt;p&gt;- abgesehen von der angenommenen Motion 23.3668 und der Aufnahme des Tunnels Morges-Perroy in den Ausbauschritt 2035 (AS 2035) für die Eisenbahninfrastruktur auf Bundesebene keinerlei konkrete Vorschläge für eine zweite Strecke zwischen Genf und Lausanne sowie für eine bessere Anbindung des Kantons Genf vorliegen;&lt;/p&gt;&lt;p&gt;- die Kantone - wie im Rahmen der vom Volk angenommenen Vorlage zum Bahninfrastrukturfonds (BIF) vorgesehen - eingeladen sind, sich an den Planungsarbeiten zu beteiligen;&lt;/p&gt;&lt;p&gt;- sowie in Anbetracht der vom Bundesamt für Verkehr (BAV) im Hinblick auf die Botschaft 2026 des Bundesrates zum Bahnausbau bereitgestellten Dokumente;&lt;/p&gt;&lt;p&gt;fordert der Grosse Rat des Kantons Genf die Bundesversammlung auf,&lt;/p&gt;&lt;p&gt;- vom Bundesrat zu verlangen, die Studien über eine Neubaustrecke zwischen Genf und Lausanne in seine Botschaft 2026 zur Bahninfrastruktur aufzunehmen;&lt;/p&gt;&lt;p&gt;- bis zur Inbetriebnahme dieser Verbindung eine mindestens gleichwertige Anbindung des Kantons Genf wie im Jahr 2018 (hinsichtlich der Anzahl Züge und Plätze sowie der Reisegeschwindigkeit) zu gewährleisten;&lt;/p&gt;&lt;p&gt;- direkte und schnelle Verbindungen nach Neuenburg, Biel und Basel über die Jurasüdfusslinie möglichst rasch wiederherzustellen;&lt;/p&gt;&lt;p&gt;- die Verhandlungen mit Frankreich über die bessere internationale Anbindung Genfs an Lyon und Südfrankreich sowie an Paris, Nantes, Lille, Brüssel und London fortzuführen und zu intensivieren.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel-Stadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale et le Conseil fédéral sont priés de prendre les mesures nécessaires pour que, sous l’angle du principe d’égalité des droits qui doit prévaloir entre États membres de la Confédération, les anciens demi-cantons de Bâle-Ville et de Bâle-Campagne soient mis sur un pied d’égalité avec les autres cantons en ce qui concerne le nombre de sièges au Conseil des États (faire des deux Bâle des cantons à part entière, modification des art.&amp;nbsp;142, al.&amp;nbsp;4, et 150, al.&amp;nbsp;1 et 2, de la Constitution fédérale).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Bundesparlament und der Bundesrat werden gebeten, die notwendigen Schritte zu unternehmen, damit unter dem Aspekt des Gebots der bundesstaatlichen und föderalen Rechtsgleichheit die ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft den übrigen Kantonen im Hinblick auf die Vertretung im Ständerat gleichgestellt werden (Aufwertung als Kantone mit Vollem Ständerecht, Änderung von Art. 142 Abs. 4 und Art. 150 Abs. 1 und 2 der Bundesverfassung).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beratung in Kommission des Nationalrates abgeschlossen / Fin des discussions en commission du Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission de gestion Conseil des États</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunaux fédéraux. Introduire un système disciplinaire pour renforcer la confiance à leur égard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunali della Confederazione. Introdurre un sistema disciplinare per rafforzare la fiducia in queste istituzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Il y a lieu d’élaborer les bases légales permettant d’introduire une surveillance disciplinaire des juges des tribunaux fédéraux. Les principes de l’indépendance des juges, de l’autonomie des tribunaux en matière d’organisation et de la séparation des pouvoirs devront être respectés.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Es seien die gesetzlichen Grundlagen zu erarbeiten, um eine Disziplinaraufsicht über die Richterinnen und Richter an den eidgenössischen Gerichten einzuführen. Dabei ist den Grundsätzen der richterlichen Unabhängigkeit, der Organisationsautonomie und der Gewaltentrennung Rechnung zu tragen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Gerichtswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Giustizia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrierter Ansatz für Service-Center des Service public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une approche intégrée des centres de services dans le service public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per un approccio integrato per i centri di servizio del servizio pubblico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale est chargée de créer les bases légales permettant de développer et de mettre en œuvre une approche intégrée des centres de services dans le service public. Ce faisant, elle intégrera l’infrastructure existante du réseau postal. L’objectif est de créer une infrastructure moderne et efficace pour la population et de garantir un réseau physique qui assure l’accès des personnes aux produits numériques et aux produits physiques.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung wird beauftragt, die gesetzlichen Grundlagen zu schaffen, um einen integrierten Ansatz für ServiceCenter des Service Public zu entwickeln und umzusetzen. Die bestehende Infrastruktur von PostNetz ist dabei einzubeziehen. Ziel ist es, eine moderne und effiziente Infrastruktur für die Bevölkerung zu schaffen, ein physisches Netz zu sichern, das den Zugang der Menschen zu digitalen und physischen Produkten sichert.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vieillissement de la population. Créer un mécanisme de compensation pour les primes de l’assurance-maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introdurre un meccanismo di compensazione intercantonale per i premi di cassa malati dovuti all’invecchiamento dalla popolazione </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Dans son avis sur la motion Quadri 24.4209, qui le charge «&amp;nbsp;de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population&amp;nbsp;», le Conseil fédéral affirme: «&amp;nbsp;Le Conseil fédéral reste d’avis que la péréquation financière nationale assure un équilibre entre les cantons&amp;nbsp;» et souligne notamment que «&amp;nbsp;... la compensation des charges dans le cadre de la péréquation financière nationale comprend une composante sociodémographique, qui tient compte des coûts liés à la structure de la population, notamment à la pyramide des âges. Le Canton du Tessin reçoit déjà des contributions fédérales dans ce cadre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;Malheureusement, ce n’est pas ce que disent les montants définitifs des paiements compensatoires pour 2025 récemment publiés. Au contraire, le canton du Tessin ne reçoit rien au titre de la compensation sociodémographique, bien qu’il compte le plus grand nombre de personnes de 80 ans ou plus (7,6 % de la population résidante permanente, contre 5,7&amp;nbsp;% pour la moyenne nationale). Le moment est donc venu de reconnaître la situation particulière du Tessin, qui compte une proportion non négligeable de retraités âgés originaires de la Suisse alémanique.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Confirme-t-il que le Tessin ne reçoit aucune contribution au titre de la compensation sociodémographique, contrairement à ce qu’il affirme dans son avis sur la motion 24.4209?&lt;/li&gt;&lt;li&gt;Au vu de ce qui précède, convient-il que la péréquation financière nationale n’atteint pas son but?&lt;/li&gt;&lt;li&gt;Par conséquent, ne pense-t-il pas que la création d’un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population, demandée par la motion 24.4209, soit à la fois opportune et nécessaire?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In der Stellungnahme zur Motion Quadri 24.4209, die den Bundesrat beauftragte, einen Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien einzuführen, hat der Bundesrat festgehalten: «Der Bundesrat ist weiterhin der Meinung, dass der nationale Finanzausgleich für ein Gleichgewicht zwischen den Kantonen sorgt. [...], insbesondere hat er ausgeführt, dass der nationale Finanzausgleich eine soziodemographische Komponente innerhalb des Lastenausgleichs enthält, der die Kosten aufgrund der Bevölkerungsstruktur, u. a. des Alters, berücksichtigt. Der Kanton [...] erhält bereits Beiträge vom Bund im Rahmen des Lastenausgleichs».&lt;/p&gt;&lt;p&gt;Leider decken sich aber die kürzlich veröffentlichten Berechnungen zu den Ausgleichszahlungen 2025 nicht mit diesen Aussagen. So erhält der Kanton Tessin keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich, obwohl er einen besonders hohen Anteil an Personen im Alter von 80 Jahren und mehr im Verhältnis zur ständigen Wohnbevölkerung aufweist (7,6 % gegenüber dem schweizerischen Durchschnitt von 5,7 %). Es ist daher an der Zeit, die besondere Situation des Kantons Tessin anzuerkennen, wo ein nicht unerheblicher Teil der älteren Menschen Rentnerinnen und Rentner aus der Deutschschweiz sind.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte deshalb den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bestätigt der Bundesrat, dass der Kanton Tessin – anders als in der Stellungnahme zur Motion 24.4209 behauptet – keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich erhält?&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat in Anbetracht der obigen Ausführungen die Ansicht, dass der nationale Finanzausgleich seinen Zweck nicht erfüllt?&lt;/li&gt;&lt;li&gt;Hält der Bundesrat die Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien, wie sie mit der Motion 24.4209 verlangt wird, nicht auch für sinnvoll und notwendig?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rechsteiner Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentlichkeitsarbeit des Bundes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relations publiques de la Confédération</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attività di pubbliche relazioni della Confederazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le chancelier de la Confédération a répondu le 16&amp;nbsp;décembre 2024 de manière relativement détaillée à ma question 24.7932 «&amp;nbsp;400 fonctionnaires médias. Y a-t-il un potentiel d’économies&amp;nbsp;?&amp;nbsp;». Certains points restent toutefois flous, et les réponses fournies soulèvent d’autres questions.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Meine Frage 24.7932 «400 Medienbeamte – Sparpotential erkannt?» wurde vom Bundeskanzler am 16. Dezember 2024 relativ ausführlich beantwortet. Trotzdem bleibt einiges im Unklaren und die Antworten werfen weiteren Fragen auf.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufhebung des Zentrumslastenausgleichs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppression de la compensation des charges des centres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliminare la compensazione degli oneri dei centri urbani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la législation relative à la péréquation financière et à la compensation des charges de sorte que la compensation des charges dues à des facteurs socio-démographiques (CCS) ne s’applique désormais plus qu’aux charges excessives liées à la structure de la population et que les charges des centres ne soient plus compensées.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Gesetzgebung zum Finanz- und Lastenausgleich dahingehend anzupassen, dass der soziodemografische Lastenausgleich künftig nur mehr Sonderlasten aufgrund der Bevölkerungsstruktur ausgleicht und keinen Zentrumslastenausgleich mehr vorsieht.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übernahme der EU-Richtlinie 2019/1158 zur Vereinbarkeit von Beruf und Privatleben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reprise de la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepimento della direttiva UE 2019/1158 relativa all’equilibrio tra attività professionale e vita familiare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de reprendre dans le droit suisse la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die EU-Richtlinie 2019/118 zur Vereinbarkeit von Beruf und Privatleben ins Schweizer Recht zu übernehmen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europapolitik|Soziale Fragen|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique européenne|Questions sociales|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica europea|Questioni sociali|Occupazione e lavoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widmer Céline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systemwechsel bei der Wohneigentumsbesteuerung. Steuerliche Folgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changement de système d’imposition du logement. Conséquences fiscales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambio di sistema nell'ambito dell'imposizione della proprietà abitativa. Conseguenze fiscali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les chambres fédérales ont adopté une réforme de l’imposition du logement le 20.12.2024, qui bouleverse les équilibres dans ce domaine tout en amenant de grandes pertes fiscales.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes, au sujet de la réforme telle qu’elle a été adoptée par le parlement et de l’introduction d’un impôt réel sur les résidences secondaires :&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;La BNS a annoncé une baisse des taux directeurs à 0.5%. Un scénario avec des taux hypothécaires moyens durablement en dessous de 1.5% devient de plus en plus crédibles. Quelles seraient les pertes fiscales liées à la réforme en cas de taux moyen à 1%&amp;nbsp; et à 1.25%?&amp;nbsp;&amp;nbsp;&lt;/li&gt;&lt;li&gt;Etant donné que la réforme entraine de grandes pertes fiscales, cela veut dire que certains contribuables vont être avantagés par rapport au reste de la population. Est-il correct de dire que les personnes qui toucheront la plus grande somme par rapport à la situation actuelle sont celles et ceux qui disposent de très grandes propriétés avec une énorme valeur et qui n’ont pas de dette liée à cette propriété ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Combien de baisse d’impôt peut attendre un propriétaire d’une maison de maître d’une valeur de CHF 10'000'000.- et qui finance aujourd’hui son bien entièrement en fonds propres ? Quelle serait le changement de la situation fiscale d’un propriétaire qui dispose d’un bien d’une valeur de CHF 500'000, hypothéqué à hauteur de CHF 400'000.- avec un taux hypothécaire de 3%, et devant faire des frais d’entretiens pour CHF 10'000.-, s’il dispose d’un revenu imposable de 100'000.- ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral peut-il expliquer quelle est la relation entre d’une part la valeur d’une bien immobilier utilisé comme résidence principale et d’autre part l’allègement fiscal obtenu suite à l’introduction du changement de système d’imposition du logement?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont les effets de la réforme de l’imposition du logement sur la péréquation financière? En particulier, quel est l’effet sur l’équilibre de cette péréquation à long terme?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung hat am 20. Dezember 2024 eine Reform der Wohneigentumsbesteuerung verabschiedet, die das Gleichgewicht in diesem Bereich erheblich stört und gleichzeitig grosse Steuerausfälle mit sich bringt.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, die folgenden Fragen zur Reform in der vom Parlament verabschiedeten Form und zur Einführung einer Objektsteuer auf Zweitwohnungen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Die Schweizerische Nationalbank (SNB) hat eine Senkung des Leitzinses auf 0,5&amp;nbsp;Prozent angekündigt. Es ist immer wahrscheinlicher, dass die durchschnittlichen Hypothekarzinsen dauerhaft unter 1,5&amp;nbsp;Prozent liegen. Wie hoch wären die Steuerausfälle aufgrund der Reform bei einem durchschnittlichen Zinssatz von 1 Prozent oder 1,25 Prozent?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Die Reform führt zu grossen Steuerausfällen. Das bedeutet, dass einige Steuerzahler und Steuerzahlerinnen gegenüber dem Rest der Bevölkerung begünstigt werden. Kann man sagen, dass die Personen, die über sehr grosse Immobilien mit einem enormen Wert verfügen und keine Schulden im Zusammenhang mit diesen Immobilien haben, im Vergleich zur aktuellen Situation am stärksten profitieren?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Mit welcher Steuersenkung kann ein Eigentümer einer herrschaftlichen Villa im Wert von 10&amp;nbsp;000&amp;nbsp;000 Franken rechnen, der seine Immobilie heute vollständig mit Eigenmitteln finanziert? Wie würde sich die steuerliche Situation einer Eigentümerin mit einem steuerpflichtigen Einkommen von 100 000 Franken ändern, wenn sie über eine Immobilie im Wert von 500&amp;nbsp;000 Franken verfügt, die mit einer Hypothek in Höhe von 400&amp;nbsp;000 Franken zu einem Hypothekarzins von 3&amp;nbsp;Prozent belastet ist, und sie Unterhaltskosten in Höhe von 10&amp;nbsp;000 Franken tragen muss?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. &amp;nbsp;Kann der Bundesrat erklären, in welchem Verhältnis der Wert einer Immobilie, die als Erstwohnung genutzt wird, zur Steuererleichterung steht, die durch den Systemwechsel bei der Wohneigentumsbesteuerung erreicht wird?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Wie wirkt sich die Reform der Wohneigentumsbesteuerung auf den Finanzausgleich aus?&lt;/p&gt;&lt;p&gt;Welches sind insbesondere die langfristigen Auswirkungen auf das Gleichgewicht des Finanzausgleichs?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuer|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscalité|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposte|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was ist die Umweltpolitik des ASTRA im Rahmen seiner Ausschreibungen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle est la politique environnementale de l'OFROU dans le cadre de ses appels d'offres?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual è la politica ambientale dell’USTRA in ambito appaltistico?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’OFROU réalise des travaux importants à la sortie de l'autoroute à Matran. Pour une question de prix uniquement, du gravier (grave de route principalement) est acheminé depuis un site du Jura français situé à environ 100km de Matran. Pour ne pas circuler à vide sur le retour, les poids-lourds transportent des éléments de chaussée rabotés et les amènent dans les décharges en France voisine. La distance aller-retour est de 200km environ alors que les mêmes matériaux sont disponibles dans un rayon de moins de 30km dans le canton de Fribourg ou 50km hors canton. Il s’ensuit des trajets et des engorgements supplémentaires, plus de CO2, plus de bruit, plus d’usure des infrastructures, de bruit et de poussières. De surcroit, des chauffeurs dont les conditions de travail sont très précaires remplacent des conducteurs domiciliés en Suisse qui bénéficient de bonnes conditions sociales. En utilisant des graviers locaux, on s'assure qu'ils sont exploités selon les normes locales avec du personnel local. Je remercie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Les soumissions provenant de l'OFROU prévoient-elles des filières d’approvisionnement et d’évacuation de graviers et autres matériaux minéraux&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si non, est-il prévu de prendre en compte rapidement les éléments précités?&lt;/li&gt;&lt;li&gt;Si oui, sachant que l’empreinte CO2 du transport de ces matériaux lourds est importante, comment cet élément est-il mis en valeur&amp;nbsp;dans la soumission&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces aspects sont-ils contrôlés en pratique, sur le terrain&amp;nbsp;?&lt;/li&gt;&lt;li&gt;En cas de faute, quelles sont les conséquences&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Bundesamt für Strassen (ASTRA) führt bei der Autobahnausfahrt Matran wichtige Bauarbeiten durch. Dabei wird einzig aus Kostengründen Kies (hauptsächlich als Strassenschotter) aus dem französischen Jura angeliefert, von einem Ort, der rund 100 Kilometer von Matran entfernt liegt. Um auf dem Rückweg Leerfahrten zu vermeiden, transportiert der Schwerverkehr von der Fahrbahn abgeschliffene Elemente ab und entsorgt diese im benachbarten Frankreich. Insgesamt werden rund 200 Kilometer zurückgelegt, obwohl dieselben Materialien in einem Umkreis von weniger als 30 Kilometern im Kanton Freiburg oder 50 Kilometern ausserhalb des Kantons verfügbar wären. Dies führt zu zusätzlichen Fahrten, mehr Stau, CO2, Lärm und Staub sowie zu einer verstärkten Abnutzung der Infrastrukturen. Zudem werden in der Schweiz wohnhafte Chauffeurinnen und Chauffeure, die von guten sozialen Bedingungen profitieren, durch solche mit sehr prekären Arbeitsbedingungen ersetzt. Die Verwendung von lokalem Kies stellt sicher, dass dieser nach lokalen Normen und mit lokalem Personal abgebaut wird. Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Sehen die Ausschreibungen des ASTRA Liefer- und Entsorgungswege für Kies und andere mineralische Materialien vor?&lt;/li&gt;&lt;li&gt;Wenn nein: Ist geplant, die obgenannten Punkte rasch zu berücksichtigen?&lt;/li&gt;&lt;li&gt;Wenn ja: Wie wird dieser Aspekt in der Ausschreibung hervorgehoben, zumal bekannt ist, dass der Transport von Schwergut einen grossen CO2-Fussabdruck hat?&lt;/li&gt;&lt;li&gt;Wie werden diese Aspekte in der Praxis vor Ort kontrolliert?&lt;/li&gt;&lt;li&gt;Was wären die Folgen, wenn sie nicht kontrolliert werden?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschäftigung und Arbeit|Verkehr|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emploi et travail|Transports|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupazione e lavoro|Trasporti|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marti Min Li</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kann die Post einen Beitrag zur digitalen Inklusion leisten? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Poste peut-elle contribuer à l'inclusion numérique? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Posta può contribuire all'inclusione digitale? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Diverses études comme le Baromètre numérique&amp;nbsp;2024 de la Mobilière ont constaté que des compétences numériques de base font défaut à près d’un tiers de la population. Elles relèvent des disparités notables selon l’âge, le revenu et la formation. Même si l’âge joue un rôle en matière de compétences numériques, les personnes âgées ne sont en réalité pas les seules à connaître des difficultés dans l’utilisation des outils numériques comme les services bancaires et les billetteries en ligne ou les guichets virtuels des autorités. Ces lacunes vont souvent de pair avec un sentiment de gêne. &amp;nbsp;Certains, en particulier les jeunes, surestiment leurs propres compétences. De fait, le quotidien bascule toujours plus dans le numérique et exacerbe les lacunes en matière de compétences numériques. C’est pourquoi je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Que pense-t-il du problème des compétences numériques lacunaires&amp;nbsp;? Comment pourrait-on y remédier&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les pouvoirs publics et les entreprises proches de la Confédération, par exemple, numérisent de plus en plus leurs services, et ne les proposent parfois plus que sous cette forme. Comment garantir leur accessibilité à tout le monde&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans le cadre d’un projet pilote mené dans trois filiales, la Poste a proposé une assistance sur toutes sortes de problèmes relevant du numérique. Que pense le Conseil fédéral de ce projet&amp;nbsp;? La poste pourrait-elle contribuer à faire progresser l’inclusion numérique grâce à cette offre&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Est-ce qu’une telle offre de la Poste ou d’autres entreprises pourraient aussi alléger le travail des autorités&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Verschiedene Studien wie beispielsweise der Digitalbarometer 2024 der Mobiliar haben festgestellt, dass fast ein Drittel der Bevölkerung nicht über grundlegende digitale Kompetenzen verfügt. Dabei gibt es signifikante Unterschiede nach Alter, Einkommen und Bildung. Auch wenn das Alter bei den digitalen Kompetenzen eine Rolle spielt, sind es beileibe nicht nur ältere Menschen, die Mühe haben, digitale Anwendungen wie beispielsweise E-Banking, Billetkäufe oder digitale Behördengänge zu nutzen. Dies ist oft auch mit Scham verbunden. &amp;nbsp;Teilweise werden auch die eigenen Fähigkeiten überschätzt, gerade bei jüngeren Menschen. Da immer mehr Dinge des täglichen Lebens digitalisiert werden, stellt die mangelnde digitale Kompetenz ein zunehmendes Problem dar. In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie schätzt der Bundesrat das Problem der fehlenden digitalen Kompetenzen ein und wie könnten diese verbessert werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Auch Leistungen der öffentlichen Hand oder beispielsweise von bundesnahen Betrieben werden immer häufiger digitalisiert und teilweise nur noch digital angeboten. Wie kann sichergestellt werden, dass alle Personen Zugang zu diesen Leistungen haben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Im Rahmen eines Pilotprojekts hat die Post in drei Filialen ein Angebot geschaffen, um Menschen bei digitalen Problemen aller Art zu unterstützen. Wie beurteilt der Bundesrat dieses Projekt? Könnte die Post mit diesem Angebot einen Beitrag leisten, die digitale Inklusion voranzutreiben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Könnte eine entsprechende Dienstleistung der Post oder von anderen Betreibern auch dazu beitragen, Behörden zu entlasten?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Soziale Fragen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Questions sociales|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Questioni sociali|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzielle Unterstützung für Imkerinnen und Imker bei geoklimatischen Ausnahmebedingungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soutien financier direct aux apiculteurs et apicultrices lors de situations géoclimatiques exceptionnelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sostegno finanziario diretto agli apicoltori in situazioni geoclimatiche eccezionali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale et à l'article 84, lettre o, de la Constitution cantonale, le Canton demande aux Chambres fédérales d'accorder un soutien financier direct, comme des subsides, aux apiculteurs et apicultrices pour l'achat de sucre nécessaire au nourrissement des abeilles mellifères, ceci lorsque les situations géoclimatiques rendent ce nourrissement indispensable à la survie des colonies d'abeilles.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o seiner Kantonsverfassung fordert der Kanton Jura die Bundesversammlung auf, den Imkerinnen und Imkern finanzielle Unterstützung, beispielsweise in Form von Subventionen, zu gewähren für den Kauf von Zucker, wenn dieser aufgrund der geoklimatischen Bedingungen an Honigbienen verfüttert werden muss, um deren Überleben sicherzustellen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impôt fédéral direct. Déduction totale des primes d’assurance-maladie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deduzione integrale dei premi per l’assicurazione contro le malattie in ambito di imposta federale diretta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la loi fédérale sur l'impôt fédéral direct comme suit&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art.&amp;nbsp;33 Intérêts passifs et autres réductions&lt;/p&gt;&lt;p&gt;Al.&amp;nbsp;1&lt;/p&gt;&lt;p&gt;Sont déduits du revenu&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let. a à f, h et i&amp;nbsp;: aucune modification&amp;nbsp;;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let. g&amp;nbsp;: biffer «&amp;nbsp;d’assurance-maladie&amp;nbsp;»&amp;nbsp;;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let.&amp;nbsp;k (nouvelle)&amp;nbsp;: les primes et cotisations d’assurance-maladie privée et obligatoire.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Bundesgesetz über die direkte Bundessteuer wie folgt zu ändern:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art. 33 Schuldzinsen und andere Abzüge&lt;/p&gt;&lt;p&gt;Abs. 1&lt;/p&gt;&lt;p&gt;Von den Einkünften werden abgezogen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. a bis f sowie h und i: bleiben unverändert;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. g: Streichung von "Krankenversicherung";&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. k (neu): Prämien und Beiträge für die obligatorische und private Krankenversicherung.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addor Jean-Luc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenzüberschreitende Kriminalität: Bessere Kontrolle der Landesgrenze und ein Aktionsplan, aber schnell!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminalité transfrontalière : mieux contrôler nos frontières et un plan d'action, et vite !</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Après la énième attaque d'un distributeur de billets en zone frontalière le 7 décembre à Montagny-près-Yverdon VD, pour éviter que notre pays soit considéré comme une sorte de libre-service par les bandes organisées étrangères, le Conseil fédéral va-t-il décider rapidement d'un plan d'action et dans l'immédiat, ne doit-il pas décider d'un renforcement immédiat des contrôles de nos frontières dans les secteurs exposés (à commencer par le secteur Jura-Nord vaudois) ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 7. Dezember wurde in Montagny-près-Yverdon VD zum x-ten Mal ein Geldautomat im Grenzgebiet angegriffen.&lt;br&gt;Wird der Bundesrat schnell über einen Aktionsplan sowie umgehend über eine Verstärkung der Grenzkontrollen in den exponierten Sektoren entscheiden (angefangen mit dem Sektor Waadtländer Nordjura), um zu verhindern, dass unser Land von organisierten Banden aus dem Ausland als eine Art Selbstbedienungsladen betrachtet wird?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Finanzwesen|Strafrecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Finances|Droit pénal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Finanze|Diritto penale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaccoud Jessica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grundversorgung mit Postdiensten: Werden die Randregionen aufgegeben?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service universel en matière de services postaux, un abandon des régions périphériques?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les points d’accès aux services postaux doivent être accessibles en 20 min par les transports publics. Avec la fermeture des offices de Bière, Apples et L'Isle, les habitant.e.s du Pied du Jura devront se rendre à Morges. Depuis le village de Berolle, cela représente un trajet de minimum 50 minutes. Et il n'existe aucun transport public durant le week-end.&lt;br&gt;- Comment le CF estime-t-il que le service universel peut être maintenu dans ces conditions?&lt;br&gt;- N'abandonne-t-il pas les régions périphériques?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Zugang zu den Postdiensten muss innerhalb von 20 Minuten mit öffentlichen Verkehrsmitteln gewährleistet sein. Aufgrund der Schliessung der Poststellen von Bière, Apples und L'Isle müssen die Einwohnerinnen und Einwohner am Jurasüdfuss nach Morges fahren. Vom Dorf Berolle aus bedeutet dies eine Fahrzeit von mindestens 50 Minuten. Ausserdem fahren am Wochenende keine öffentlichen Verkehrsmittel.&lt;br&gt;- Wie kann die Grundversorgung nach Auffassung des Bundesrats unter diesen Bedingungen aufrechterhalten werden?&lt;br&gt;- Lässt er die Randregionen so nicht im Stich?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gebietsveränderung zwischen den Kantonen Bern und Jura (Kantonswechsel der bernischen Gemeinde Moutier). Genehmigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification du territoire des cantons de Berne et du Jura (Transfert de la commune bernoise de Moutier). Approbation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifica territoriale tra i Cantoni di Berna e del Giura (trasferimento del Comune bernese di Moutier). Approvazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für klare Regeln bei Lebensmittelimporten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour des règles claires en matière d'importation de denrées alimentaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per un disciplinamento in materia di importazione di derrate alimentari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement demande dès lors aux Chambres fédérales de modifier la législation fédérale de manière à interdire l'importation de denrées alimentaires ne répondant pas aux réglementations qui seraient requises pour leur production en Suisse.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o der Kantonsverfassung fordert das Parlament des Kantons Jura die Bundesversammlung auf, den Import von Lebensmitteln, deren Herstellung nicht den Schweizer Vorschriften entspricht, zu verbieten.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft|Finanzwesen|Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Économie|Finances|Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Economia|Finanze|Agricoltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für eine "entwaldungsfreie" Schweizer Politik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une politique fédérale "Zéro déforestation"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una politica federale "a deforestazione zero"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement demande aux Chambres fédérales d'adapter la législation fédérale afin de garantir que les matières premières et leurs sous-produits mis sur le marché helvétique ou destinés à l'exportation ne soient pas associés à la déforestation.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o der Kantonsverfassung fordert das Parlament des Kantons Jura die Bundesversammlung auf, mit einer Anpassung des Bundesrechts sicherzustellen, dass Rohstoffe und ihre Nebenprodukte, die auf den Schweizer Markt gebracht werden oder für den Export bestimmt sind, nicht in Verbindung mit Entwaldung stehen.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Umwelt|Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Environnement|Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Ambiente|Agricoltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interkantonaler Ausgleich für den alterungsbedingten Anstieg der Krankenkassenprämien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augmentation des primes de l'assurance-maladie due au vieillissement de la population. Compensation intercantonale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compensazione intercantonale per gli aumenti dei premi di cassa malati dovuti all'invecchiamento della popolazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Mechanismus zum interkantonalen Ausgleich des altersbedingten Anstiegs der Krankenkassenprämien einzuführen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Beschäftigung und Arbeit|Migration|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Emploi et travail|Politique migratoire|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Occupazione e lavoro|Migrazione|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durrer-Knobel Regina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausbildungsdarlehen und Stipendien für Erwachsene im sekundären Bildungsbereich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourses et prêts destinés aux adultes suivant une formation du degré secondaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestiti e borse per gli adulti che seguono una formazione del livello secondario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer une loi réglant les contributions aux cantons pour l’octroi de bourses et de prêts de formation aux adultes suivant une formation du degré secondaire, sur le modèle de la loi sur les aides à la formation qui s’applique au degré tertiaire.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, analog dem&amp;nbsp;Bundesgesetz über Beiträge an die Aufwendungen der Kantone für Stipendien und Studiendarlehen im tertiären Bildungsbereich ein Gesetz zu erarbeiten, welches Beiträge an die Aufwendungen der Kantone für Stipendien und Ausbildungsdarlehen im sekundären Bildungsbereich für Erwachsene regelt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Bildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Éducation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Formazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolet Jacques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abschuss des Rudels auf dem Mont Tendre. Der Kanton muss über echte Handlungsmöglichkeiten verfügen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elimination de la meute du Mont Tendre. Il est nécessaire de donner de vrais moyens d'action au canton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbattimento del branco di lupi del Mont Tendre. Fornire ai Cantoni strumenti d'azione reali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;En date du 13 août 2024, le Département de la Jeunesse, de l’environnement et de la sécurité (DJES) du Canton de Vaud formulait auprès de l’OFEV une nouvelle demande relative au tir du loup. Elle portait sur l’élimination complète de la meute du Mont tendre, identifiée comme responsable d’une vingtaine d’attaques de loups sur des troupeaux dans le Jura vaudois. Région dans laquelle, outre les quelques loups isolés, cinq meutes sont présentes, dont la meute en question.&lt;/p&gt;&lt;p&gt;Dans sa décision du 3 septembre 2024 (soit 3 semaines après la demande), et selon son évaluation, l’OFEV reconnait&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Qu’en raison du comportement indésirable de la meute du Mont Tendre, notamment de nombreuses attaques sur des bovins en situation protégée, il y a lieu d’intervenir sur cette meute.&lt;/li&gt;&lt;li&gt;Que les mesures de régulations de l’année passée visant les louveteaux, n’ont pas donnés les effets escomptés.&lt;/li&gt;&lt;li&gt;Que des mesures plus strictes doivent être mises en place, soit &amp;nbsp;l’élimination complète de la meute du Mont Tendre.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;L’OFEV estime donc que la demande cantonale est justifiée par la prévention de futurs dommages aux animaux de rente. En prélevant la meute du Mont Tendre, la région se retrouvera avec un nombre de meute au-dessus du seuil minimal.&lt;/p&gt;&lt;p&gt;Mais l’OFEV mentionne que pour des raisons de protection des jeunes et de la mère, les louveteaux doivent être tirés en premier (art. 7, al. 4, LChP)&amp;nbsp;».&lt;/p&gt;&lt;p&gt;Aujourd’hui au 25 septembre, près de quarante attaques avec issue mortelle ont été perpétrées par cette meute dans la région. Avec les attaques des autres meutes dans le Jura vaudois, nous arrivons à presque une attaque par nuit.&lt;/p&gt;&lt;p&gt;Depuis le 3 septembre, les gardes-chasses sont à l’affut chaque nuit afin de pouvoir procéder au tir de la meute, principalement sur les lieux des attaques ou le loup reviennent plusieurs fois par nuit.&lt;/p&gt;&lt;p&gt;Malheureusement, en raison de l’exigence de l’OFEV de tirer en premier lieu les jeunes louveteaux, les gardes-chasses voient plusieurs fois par nuit des loups adultes dans leur viseur, mais n’ont pas le droit de tirer.&lt;/p&gt;&lt;p&gt;Tenant compte de l’urgence et du manque d’efficacité des mesures précédentes, le Conseil fédéral&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Estime-il normal le délai de 3 semaines entre la demande du Canton et l’autorisation délivrée par l’OFEV&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Ne devrait-il pas autoriser le tir de la Meute, sans la restriction sur les priorités de tirer les jeunes louveteaux&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 13. August 2024 reichte das Département de la Jeunesse, de l'environnement et de la sécurité (DJES) des Kantons Waadt beim BAFU ein neues Gesuch zum Abschuss von Wölfen ein. Es betraf die vollständige Eliminierung des Rudels auf dem Mont Tendre, das für rund 20 Wolfsangriffe auf Herden im Waadtländer Jura verantwortlich gemacht wird. In dieser Region gibt es neben einigen einzelnen Wölfen fünf Rudel, darunter auch das hier angesprochene Rudel.&lt;/p&gt;&lt;p&gt;In seinem Entscheid vom 3. September 2024 (also 3 Wochen nach Einreichung des Gesuchs) befand das BAFU :&lt;/p&gt;&lt;ul&gt;&lt;li&gt;- Dass aufgrund des unerwünschten Verhaltens des Rudels auf dem Mont Tendre, insbesondere wegen der zahlreichen Angriffe auf Rinder in geschützter Lage, gegen dieses Rudel vorgegangen werden muss.&lt;/li&gt;&lt;li&gt;- Dass die im vergangenen Jahr getroffenen Regulierungsmassnahmen, die auf Wolfswelpen abzielten, nicht die erhofften Auswirkungen hatten.&lt;/li&gt;&lt;li&gt;- Dass strengere Massnahmen umgesetzt werden müssen, das heisst die vollständige Eliminierung des Rudels auf dem Mont Tendre.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Das BAFU gelangt daher zur Ansicht, dass das Gesuch des Kantons gerechtfertigt ist, weil durch den Abschuss zukünftige Schäden an Nutztieren verhindert werden. Auch wenn das Rudel auf dem Mont Tendre eliminiert wird, läge die Zahl der Rudel in der Region immer noch über der Mindestschwelle.&lt;/p&gt;&lt;p&gt;Aber das BAFU erwähnt, dass aus Gründen des Schutzes der Jungtiere und der Mutter die Wolfswelpen zuerst geschossen werden müssen (Art. 7, Abs. 4, JSG).&lt;/p&gt;&lt;p&gt;Bis zum 25. September gingen in der Region fast vierzig Angriffe mit tödlichem Ausgang auf das Konto dieses Rudels. Zusammen mit den Angriffen der anderen Rudel im Waadtländer Jura ergibt das beinahe einen Angriff pro Nacht.&lt;/p&gt;&lt;p&gt;Seit dem 3. September liegen die Wildhüter jede Nacht auf der Lauer, um das Rudel abschiessen zu können, dies vor allem an Orten, an denen es zu Angriffen gekommen ist oder an denen die Wölfe mehrmals pro Nacht zurückkehren.&lt;/p&gt;&lt;p&gt;Mehrmals pro Nacht sehen die Wildhüter durch ihr Visier erwachsene Wölfe, dürfen diese aber aufgrund der Forderung des BAFU, in erster Linie junge Wölfe zu schiessen, nicht erlegen.&lt;/p&gt;&lt;p&gt;Eingedenk der Dringlichkeit und der mangelnden Wirksamkeit der bisherigen Massnahmen stelle ich dem Bundesrat die folgenden Fragen:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;- Hält er die Frist von drei Wochen zwischen dem Antrag des Kantons und der vom BAFU erteilten Bewilligung für normal?&lt;/li&gt;&lt;li&gt;- Sollte er nicht den Abschuss des Rudels erlauben, ohne einschränkend die Erlegung von Jungwölfen zu priorisieren?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badran Jacqueline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesetzliche Grundlage für den Verteilmechanismus für die Ergänzungssteuer-Erträge aus der OECD-Mindestbesteuerung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bases légales pour un mécanisme de répartition des recettes fiscales complémentaires provenant de l'imposition minimale prévue par l'OCDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creare la base legale per il meccanismo di ripartizione del gettito lordo dell'imposta integrativa in seguito all'imposizione minima dell'OCSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'exposer avec des chiffres les conséquences d'une meilleure répartition entre la Confédération et les cantons du produit brut de l'impôt complémentaire et de présenter un projet de loi spéciale s'y rapportant. Il étudiera et présentera les diverses variantes avec une clé de répartition en parts égales entre la Confédération (50&amp;nbsp;%) et les cantons (50&amp;nbsp;%), avec une redistribution limitée à 200 et à de 400&amp;nbsp;francs par personne. &amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Folgen einer verbesserten Aufteilung des Rohertrags der Ergänzungssteuer zwischen Bund und Kantonen mit Zahlen aufzuzeigen &amp;nbsp;und ein entsprechendes Spezialgesetz vorzulegen. Dabei untersucht der Bundesrat und legt Varianten vor, die einen Rückverteilsschlüssel von 50 Prozent je Bund und Kantonen beinhalten kombiniert mit einer limitierten Rückverteilung mit Obergrenze pro Einwohnerin und Einwohner von 200 Franken pro Person respektive 400 Franken pro Person. &amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Wirtschaft|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Économie|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Economia|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müller-Altermatt Stefan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logistiklasten erfassen und ausgleichen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prendre en compte et compenser les charges logistiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rilevare e compensare gli oneri logistici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les entreprises de logistique sont judicieusement regroupées et implantées à proximité des grands axes de transport et d’installations ferroviaires. C’est le cas par exemple dans le Gäu soleurois, le long de l’A1. En tant que «&amp;nbsp;Logistic&amp;nbsp;Valley&amp;nbsp;», la région joue aujourd’hui un rôle central pour l’approvisionnement du pays.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Même si cette implantation en clusters est judicieuse du point de vue de l’intérêt général, les défis auxquels les régions concernées doivent alors faire face sont importants. L’implantation des entreprises de logistique nécessite de nombreux projets de construction de routes et autres, avec les coûts et les investissements élevés qui en découlent, ainsi que des coûts supplémentaires pour les communes et le canton dans le domaine de la formation et de l’intégration.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;En revanche, la valeur ajoutée directe du secteur logistique n’est pas particulièrement élevée et, par conséquent, les impôts sur les bénéfices ne le sont pas non plus. Dans ce secteur, la plupart des emplois se situent dans le segment des salaires plutôt bas, ce qui crée peu de croissance pour ce qui est des impôts des personnes physiques. En résumé, les coûts augmentent alors que les bénéfices restent stables ou n’augmentent que légèrement. Cet état de fait se reflète également dans la faiblesse des ressources du canton de Soleure dans la péréquation financière nationale.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le compte est donc de moins en moins bon, et de plus en plus de communes s’opposent à des développements judicieux pour l’intérêt général.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;La question se pose de savoir si, par analogie avec d’autres charges (dues à des facteurs géo-topographiques ou socio-démographiques), cette charge du secteur logistique pourrait être compensée de manière pertinente. Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Partage-t-il l’avis que la région de Gäu (avec les régions limitrophes) joue un rôle important pour l’approvisionnement du pays et que, ce faisant, elle est grevée de charges non compensées&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Partage-t-il l’inquiétude selon laquelle il devient de plus en plus difficile, en raison des charges, de pouvoir satisfaire les besoins de la logistique sur des sites appropriés et que, par conséquent, la branche risque de se tourner vers des sites ayant un impact plus important sur l’homme, la nature et les infrastructures&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3) Dispose-t-il d’indicateurs ou d’études permettant de mesurer l’ampleur des charges logistiques&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Est-il prêt à intégrer les charges logistiques dans la péréquation financière nationale en tant que partie de la compensation des charges&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Logistikbetriebe werden sinnvollerweise geclustert und in der Nähe der Hauptverkehrsachsen und zu Bahnanlagen angesiedelt. Dies ist entlang der A1, beispielsweise im Solothurner Gäu, geschehen. Die Region erfüllt heute als «Logistic-Valley» eine für die Landesversorgung zentrale Aufgabe.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;So sinnvoll diese geclusterte Ansiedlung aus übergeordneter Sicht ist, so gross sind die Herausforderungen, mit denen die betroffenen Regionen dann zu kämpfen haben. Mit den Ansiedlungen der Logistikbetriebe werden zahlreiche Strassen- und sonstige Bauprojekte mit entsprechenden Kosten und hohem Investitionsbedarf nötig und auch im Bildungs- und Integrationsbereich fallen Mehrkosten für die Gemeinden sowie den Kanton an.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die direkte Wertschöpfung der Logistikbranche hingegen ist nicht sonderlich hoch und entsprechend fallen auch keine hohen Gewinnsteuern ab. Die Arbeitsplätze der Branche liegen mehrheitlich im eher tieferen Lohnsegment und führen ergo auch im Bereich der Steuern von natürlichen Personen zu wenig Wachstum. Zusammenfassend wachsen also die Kosten bei gleichbleibenden oder nur leicht steigenden Erträgen. Dieses Bild zeigt sich auch in der Ressourcenschwäche des Kantons Solothurn im NFA.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die Rechnung geht folgerichtig immer weniger auf und es regt sich in immer mehr Gemeinden Widerstand gegen übergeordnet sinnvolle Entwicklungen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Es stellt sich also die Frage, ob analog anderer Lasten (geografisch-topografisch; sozio-demografisch) diese dargelegte Last der Logistikbranche sinnvoll ausgeglichen werden kann. Diesbezüglich erbitte ich den Bundesrat um Antwort auf die folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Teilt der Bundesrat die Ansicht, dass die Region Gäu (zusammen mit den angrenzenden Regionen) eine wichtige Aufgabe für die Landesversorgung erfüllt und in Erfüllung dieser Aufgabe mit nicht ausgeglichenen Lasten belastet wird?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Teilt der Bundesrat die Bedenken, dass es aufgrund der Lasten immer schwieriger wird, die Bedürfnisse der Logistik an geeigneten Standorten befriedigen zu können und deshalb die Gefahr droht, dass die Branche ausweicht auf Standorte mit höheren Auswirkungen auf Mensch, Natur und Infrastruktur?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3) Verfügt der Bundesrat über Messgrössen oder Studien, welche eine Aussage über das Ausmass der Logistiklasten zulassen?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Ist der Bundesrat bereit, die Logistiklasten als Teil des Lastenausgleichs in den NFA zu integrieren?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prelicz-Huber Katharina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stipendien, die zum Leben reichen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des bourses couvrant les frais de subsistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borse di studio sufficienti al sostentamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de créer les bases légales permettant à la Confédération de soutenir, au moyen de financements incitatifs, les cantons et les communes qui allouent des aides à la formation couvrant les frais de subsistance durant toute la durée d'une formation ou d'une formation continue.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen zu schaffen, die es dem Bund ermöglichen, Gemeinden und Kantone in Form einer Anschubfinanzierung zu unterstützen, welche Aus- und Weiterbildungsbeiträge existenzsichernd und über die ganzen Erwerbsjahre gewähren.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belprahon, endgültig eine Berner Gemeinde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belprahon, commune définitivement bernoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral (CF) a écrit (question 24.7640) que le transfert de Moutier "permettra de mettre un point final à la Question jurassienne". Le 16.09.2024, le comité "Belprahon dit oui" a publié que voter oui au Concordat le 22.09.2024 est "le meilleur moyen d'entretenir l'espoir d'un rattachement futur de Belprahon au canton du Jura".&lt;br&gt;Le CF peut-il&lt;br&gt;1. confirmer que Belprahon a voté le 17.09.2017 par 121 contre 114 pour rester bernoise?&lt;br&gt;2. et que ce vote est régulier, incontestable et définitif?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat schrieb in seiner Antwort auf die Frage 24.7640, dass mit dem Kantonswechsel von Moutier die Jurafrage endgültig gelöst werden kann. Das Komitee "Belprahon sagt Ja» schrieb am 16. September 2024, eine Ja-Stimme zum Konkordat vom 22. September 2024 sei das beste Mittel, um die Hoffnung auf einen zukünftigen Anschluss von Belprahon an den Kanton Jura am Leben zu halten.&lt;br&gt;Kann der Bundesrat bestätigen, dass;&lt;br&gt;1. Belprahon am 17. September 2017 mit 121 zu 114 Stimmen für den Verbleib im Kanton Bern gestimmt hat?&lt;br&gt;2. diese Abstimmung ordnungsgemäss erfolgt ist und das Ergebnis unanfechtbar und endgültig ist?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studie zu einem dritten Juradurchstich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planification concernant la troisième traversée du Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio sul terzo traforo del Giura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l’art.&amp;nbsp;1, al. 3, let. g, de l’arrêté fédéral sur l’aménagement&amp;nbsp;2025 de l’infrastructure ferroviaire, des travaux de planification et des études préparatoires doivent être réalisés pour le tronçon entre Bâle et le Mittelland (3e traversée). Les cantons du nord-ouest de la Suisse et les CFF ont procédé à diverses clarifications jusqu’à l’établissement de l’arrêté fédéral précité. Depuis, le dossier est en suspens. Seul le plan en cinq points du nœud de Bâle contient la nouvelle traversée du Jura («&amp;nbsp;tunnel de Wisenberg&amp;nbsp;») comme une étape. L’état d’avancement du projet et les conséquences qui en découlent ne sont toujours pas connus.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Il serait important de disposer d’informations solides et fiables sur une nouvelle traversée du Jura, notamment dans la perspective des nouvelles offres qui seront examinées dans le cadre de l’étape d’aménagement du message&amp;nbsp;2030. Ainsi (outre les nouvelles offres de transport de voyageurs sur grandes lignes et de marchandises), les concepts d’offre régionaux importants ne peuvent être élaborés de manière judicieuse sans savoir si la nouvelle traversée sera réalisée ou non et dans quel délai. Cette sécurité de planification est nécessaire pour traiter de manière ciblée les dépendances du côté de l’offre d’une nouvelle percée dans le Jura avec l’extension nécessaire des capacités du nœud de Bâle, y compris la gare souterraine de Bâle CFF (prévue par le message&amp;nbsp;2026 sur l’aménagement ferroviaire) pour tous les types de trafic.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les études devraient être lancées rapidement dans le but d’obtenir à temps les résultats et que ceux-ci soient encore traités par les régions de planification. Du point de vue de l’aménagement du territoire, il serait également important d’obtenir rapidement des informations&amp;nbsp;: le développement de l’urbanisation dans les régions concernées de Liestal et d’Olten doit être coordonné suffisamment tôt avec l’extension du réseau ferroviaire.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Une étude préliminaire pour une nouvelle traversée du Jura est-elle prévue dans la perspective du message&amp;nbsp;2030&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quand les résultats des études correspondantes, avec examen des variantes et des étapes de réalisation, seront-ils disponibles&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral convient-il qu’une offre doit être immédiatement obtenue dans le but de garantir une coordination et, par conséquent, une sécurité globale de la planification pour les grandes extensions&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gemäss Art. 1. Abs. 3 lit. g Bundesbeschluss über den Ausbauschritt 2025 der Eisenbahninfrastruktur sind vorbereitende Planungsarbeiten und Studien für den Korridor Basel – Mittelland (3. Juradurchstich) zu erstellen. Nachdem bis zum genannten Bundesbeschluss die Nordwestschweizer Kantone und die SBB verschiedene Abklärungen getroffen hatten, ist es seitdem ruhig geworden. Einzig im Fünf-Punkte-Plan des Knotens Basel ist der neue Juradurchstich («Wisenbergtunnel») als ein Element enthalten. Es bleibt dabei allerdings offen, wie der Zielzustand und dessen mögliche Realisierungsabfolgen aussehen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Nicht zuletzt im Hinblick auf neue Angebote, die im Rahmen des Ausbauschrittes in der Botschaft 2030 zur Prüfung gelangen werden, wären fundierte und belastbare Erkenntnisse zu einem neuen Juradurchstich wichtig. So können (neben neuen Personenfern- und Güterverkehrsangeboten) vor allem wichtige regionale Angebotskonzepte nur sinnvoll erstellt werden, wenn klar ist, ob bzw. in welchem Zeithorizont mit einem neuen Juradurchstich gerechnet werden kann und wie dieser konfiguriert ist. Diese Planungssicherheit ist elementar, um die angebotsseitigen Abhängigkeiten eines neuen Juradurchstichs mit dem notwendigen Kapazitätsausbau im Knoten Basel inkl. Tiefbahnhof Basel SBB (Forderung Botschaft 2026) für alle Verkehrsarten zielorientiert zu bearbeiten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Damit die Studienergebnisse rechtzeitig vorliegen und von den Planungsregionen noch verarbeitet werden können, müssten entsprechende Arbeiten rasch gestartet werden. Auch aus raumplanerischer Sicht wären baldige Erkenntnisse wichtig, da die Siedlungsentwicklung in den betroffenen Räumen Liestal und Olten frühzeitig mit dem Bahnausbau abgestimmt werden muss.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird deshalb gebeten, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wird im Hinblick auf die Botschaft 2030 eine Vorstudie für einen neuen Juradurchstich erstellt?&lt;/li&gt;&lt;li&gt;Wann werden entsprechende Studienergebnisse mit Variantenüberprüfung und Realisierungsabfolgen vorliegen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat die Auffassung, dass eine planerische Koordination und damit umfassende Planungssicherheit bei grossen Bahnausbauten, die sich bzgl. Angebot unmittelbar bedingen, zu gewährleisten ist?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schweizer Bäche in schlechtem Zustand – was unternimmt der Bundesrat?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petits cours d’eau suisses en mauvais état. Qu’entreprend le Conseil fédéral ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’&lt;a href="https://www.eawag.ch/de/info/portal/aktuelles/news/defizite-im-oekologischen-zustand-schweizer-baeche/"&gt;&lt;u&gt;étude du 6&amp;nbsp;mai&amp;nbsp;2024 menée par l’Institut fédéral pour l’aménagement, l’épuration et la protection des eaux&lt;/u&gt;&lt;/a&gt; a analysé 99&amp;nbsp;ruisseaux suisses situés dans le Plateau, certaines parties du Jura et zones de plaines des grandes vallées. Les résultats montrent que la majorité des cours d’eau analysés ne peut remplir sa fonction d’habitat pour les animaux que de façon restreinte. De nombreux cours d’eau sont enterrés et, dans les bassins versants caractérisés par une forte utilisation agricole, souvent pollués par des pesticides.&lt;br&gt;- Quel regard le Conseil fédéral porte-t-il sur ces conclusions&amp;nbsp;?&lt;br&gt;- Quelles mesures prend-il pour y remédier&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Eine &lt;a href="https://www.eawag.ch/de/info/portal/aktuelles/news/defizite-im-oekologischen-zustand-schweizer-baeche/"&gt;&lt;u&gt;Studie der EAWAG vom 6. Mai 2024&lt;/u&gt;&lt;/a&gt; hat 99 Schweizer Bäche untersucht und kommt zum Schluss, dass die Mehrheit dieser Bäche im Mittelland, in Teilen des Juras und der Talebenen grösserer Täler ihre Rolle als Lebensraum für Tiere nur eingeschränkt wahrnehmen können. Viele Gewässer sind eingedolt und in stark landwirtschaftlich genutzten Einzugsgebieten oft durch Pestizide belastet.&lt;br&gt;-&amp;nbsp;Wie beurteilt der Bundesrat diese Erkenntnisse?&lt;br&gt;-&amp;nbsp;Welche Massnahmen ergreift er?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurassischer Separatismus und Respekt vor den Institutionen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le séparatisme jurassien dans le respect des institutions ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;La destruction du "Fritz" des Rangiers par les séparatistes jurassiens du Groupe Bélier le 10.08.1989 et les tags "DMF tue" et une croix gammée sur le socle constituent-ils des actes les plus propres qui soient et des marques de respect des institutions au yeux du Conseil fédéral ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden. Am 10. August 1989 zerstörten jurassische Separatisten der Béliers die Statue Le Fritz, die «Wache von Les Rangiers», und verschmierten den Sockel mit dem Slogan "DMF tue" und einem Hakenkreuz.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;L'irruption de militants sépatistes du Bélier qui se sont menottés le 11.12.1968 dans la salle du Conseil national lors de l'élection du CF von Moos à la Présidence constitue-elle un acte des plus propre qui soit et une marque de respect des institutions au yeux du Conseil fédéral?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden.&lt;br&gt;Am 11. Dezember 1968 drangen anlässlich der Wahl von Bundesrat von Moos zum Bundespräsidenten militante Separatisten der Béliers in den Nationalratssaal ein.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;L'incendie du pont en bois de Büren an der Aare le 5/6 avril 1989 par des activistes jurassiens constituent-ils un acte les plus propres qui soit et une marque de respect des institutions au yeux du Conseil fédéral ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden. Am 5./6. April 1989 verübten jurassische Aktivisten einen Brandanschlag auf die Holzbrücke in Büren an der Aare.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachlässigkeit, Sparen oder Grenzen aufheben?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laxisme, économies ou volonté de supprimer la frontière?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lassismo, misure di risparmio o volontà di sopprimere le frontiere?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le mur en pierres sèche, les bornes, et la laie frontière ne sont quasiment plus entretenus. Si rien n'est entrepris rapidement, ce riche patrimoine historique et culturel va disparaître.&lt;/p&gt;&lt;p&gt;Aussi, j’ai l’honneur de poser les questions suivantes au CF&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel office est compétent, et responsable de l’entretien de la laie frontière, du mur, des bornes et des frontières territoriales de notre pays&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Pourquoi l’entretiens de la frontière, soit le mur frontière, les bornes et la laie frontière n’est plus exécuté&amp;nbsp;afin de maintenir ce patrimoine ?&lt;/li&gt;&lt;li&gt;Quelle mesure le CF entent-il prendre pour garantir et maintenir par un entretien, ce riche patrimoine historique et culturel fédéral&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Trockenmauern, Grenzsteine und Grenzschneisen werden kaum noch gepflegt. Wenn nicht bald etwas unternommen wird, wird dieses reiche historische und kulturelle Erbe verschwinden.&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Welches Amt ist zuständig für den Unterhalt von Grenzschneisen, Grenzmauern, Grenzsteinen und unserer Landesgrenze?&lt;/li&gt;&lt;li&gt;Warum wird nicht mehr für den Grenzunterhalt gesorgt? Mit dem Unterhalt von Grenzmauern, Grenzsteinen und Grenzschneisen könnte das erwähnte Erbe aufrecht erhalten werden.&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat zu ergreifen, um dieses reiche historische und kulturelle Erbe des Bundes zu unterhalten, damit es gesichert bleibt?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Sicherheitspolitik|Kultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Politique de sécurité|Culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Cultura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nichtverwendung des Repartitionswerts beim NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPT. Prendre en compte la valeur de répartition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mancato impiego del valore di ripartizione nel quadro della NPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le calcul du potentiel de ressources dans le cadre de la RPT repose sur des valeurs de référence qui s'appliquent à l'impôt fédéral direct. Or pour les logements en propriété, ce sont les valeurs déterminantes pour l’impôt sur la fortune qui prévalent, ce qui ne manquer pas d’irriter.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Pour quelle raison le calcul du potentiel de ressources repose-t-il pour les logements en propriété sur les valeurs de l'impôt cantonal sur la fortune, alors que pour le revenu ou le bénéfice, notamment, ce sont celles de l'impôt fédéral direct qui sont prises en compte&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Pourquoi la valeur de réparation n'est-elle pas prise en compte pour déterminer le potentiel de ressources pour les valeurs patrimoniales relatives aux logements en propriété&amp;nbsp;? En quoi consistent les coûts supplémentaires dont il a été question dans la phase de projet et à combien se chiffreraient-ils&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Quelles conséquences financières aurait la prise en compte des valeurs de répartition&lt;/p&gt;&lt;p&gt;sur le potentiel de ressources et, partant, sur la répartition des paiements RPT&amp;nbsp;?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Berechnung des Ressourcenpotentials beim NFA beruht grundsätzlich auf Referenzwerten, welche für die direkte Bundessteuer gelten. Eine Ausnahme bilden die Vermögenssteuerwerte bei Eigenheimen, was irritierend ist.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte, den Bundesrat um Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Aus welchem Grund werden für die Berechnung des&amp;nbsp;Ressourcenpotentials die kantonalen Vermögenssteuerwerte bei&amp;nbsp;den Eigenheimen herangezogen, obwohl für die anderen Grössen wie dem&amp;nbsp;Einkommen oder dem Gewinn die Werte für die direkten Bundessteuern&lt;/p&gt;&lt;p&gt;berücksichtigt werden?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Warum wird zur Bestimmung des Ressourcenpotentials für die Vermögenswerte der Eigenheime nicht der Repartitionswert berücksichtigt? Worin besteht der Mehraufwand, mit dem in der Projektphase argumentiert wurde und wie hoch wäre dieser zu beziffern?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Welche finanziellen Auswirkungen hätte die Berücksichtigung der Repartitionswerte auf das Ressourcenpotential und damit auf die Verteilung der NFA-Zahlungen?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glarner Andreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Post geht eine strategische Partnerschaft mit Western Union ein. Was soll das?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Poste signe un partenariat stratégique avec Western Union. Qu’est-ce que ça signifie?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Posta stringe un partenariato strategico con Western Union. Che senso ha?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Depuis la fin avril 2024, la Poste propose une offre supplémentaire à sa clientèle&amp;nbsp;: le prestataire de paiement Western Union est désormais présent dans les filiales de la Poste en exploitation propre. Il est ainsi possible de transférer de l’argent dans plus de 200 pays, comme le précise un &lt;a href="https://www.post.ch/fr/notre-profil/medias/communiques-de-presse/2024/la-poste-signe-un-partenariat-strategique-avec-western-union"&gt;communiqué de presse&lt;/a&gt; de la Poste daté du 3&amp;nbsp;avril 2024.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Déjà présents dans les filiales de la Poste, les prestataires de services financiers que sont PostFinance, la Banque Migros, la Bernerland Bank et la Cornèr Bank se voient compléter par Western Union, alors que les prestataires de services que sont Assura, Axa, le Groupe Mutuel, le Canton du Jura, SwissCaution et Sympany font déjà partie de l’«&amp;nbsp;équipement standard&amp;nbsp;» d’une filiale postale. L’objectif déclaré de la Poste est de transformer ses filiales en centres de services régionaux. La Poste outrepasse ainsi largement son mandat de service universel et désavantage les prestataires du marché libre. Qui plus est, l’intégration de Western Union dans toutes les filiales de la Poste facilitera grandement la tâche des demandeurs d’asile et des personnes admises à titre provisoire pour transférer de l’argent de l’aide sociale vers leur pays d’origine.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Face à cette situation, je prie le Conseil fédéral de bien vouloir répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;- Dans quelle mesure la transformation des filiales de la Poste en centres de services régionaux est-elle compatible avec le mandat de service universel&amp;nbsp;?&lt;/p&gt;&lt;p&gt;- Quels sont, en matière de droit de la concurrence, les effets de l’augmentation permanente de la taille des centres de services régionaux de la Poste&amp;nbsp;?&lt;/p&gt;&lt;p&gt;- Que pense le Conseil fédéral de la violation de l’art.&amp;nbsp;121a de la Constitution fédérale (gestion de l’immigration), étant donné qu’il vante la possibilité pour les demandeurs d’asile ou les personnes admises à titre provisoire de transférer plus facilement de l’argent de l’aide sociale vers leur pays d’origine en raison de la présence accrue de Western Union dans une entreprise de la Confédération&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ab Ende April 2024 öffnet die Post ihr Filialnetz für ein weiteres Kundenangebot: Die Zahlungsdienstleisterin Western Union wird in den eigenbetriebenen Filialen der Post präsent sein. Neu kann somit in den Postfilialen Geld in mehr als 200 Länder überwiesen werden, wie sie in einem &lt;a href="https://www.post.ch/de/ueber-uns/medien/medienmitteilungen/2024/post-geht-strategische-partnerschaft-mit-western-union-ein"&gt;Mediencommuniqué&lt;/a&gt;&amp;nbsp;vom 3. April 2024 festhält.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Neben Western Union sind bereits die PostFinance, die Migros Bank, die Bernerland Bank und die Cornèr Bank als Finanzdienstleister in den Postfilialen präsent. Weiter gehören bereits Dienstleister wie Assura, Axa, Groupe Mutuel, Kanton Jura, Swisscaution und Sympany zur “Standardausrüstung” einer Postfiliale. Es ist das erklärte Ziel der Post, die Postfilialen in regionale Dienstleistungszentren umzubauen. Die Post überschreitet damit ihren Grundversorgungsauftrag bei weitem und benachteiligt Anbieter des freien Marktes. Zudem wird durch die Aufnahme von Western Union in alle Postfilialen die Überweisung von Sozialhilfegeldern durch Asylbewerber und vorläufig Aufgenommene in deren Herkunftsländer stark erleichtert.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten zu folgenden Fragen Stellung zu beziehen:&lt;/p&gt;&lt;p&gt;- Inwiefern lässt sich der Ausbau der Postfilialen in regionale Dienstleistungszentren mit dem Grundversorgungsauftrag vereinbaren?&lt;/p&gt;&lt;p&gt;- Welche wettbewerbsrechtlichen Auswirkungen entstehen durch die immer grösseren regionalen Dienstleistungszentren der Post?&lt;/p&gt;&lt;p&gt;- Wie gewichtet der Bundesrat den Verstoss gegen Artikel 121a der Bundesverfassung (Steuerung der Zuwanderung), da er mit der vermehrten Präsenz von Western Union in einem Bundesbetrieb, die Möglichkeit für Asylbewerber oder vorläufig Aufgenomme anpreist, Sozialhilfegelder einfacher in die Herkunftsländer zu überweisen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kälin Irène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufwand der Kantone für Veranlagung und Einzug der Bundessteuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépenses cantonales pour la taxation et la perception de l’impôt fédéral direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onere dei Cantoni per l’imposizione e l’esazione dell’imposta federale diretta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;En vertu de l’art.&amp;nbsp;128, al.&amp;nbsp;4, de la Constitution, la part des cantons au produit de l’impôt fédéral direct doit être d’au moins 17&amp;nbsp;%. L’art.&amp;nbsp;196, al.&amp;nbsp;1, de la loi fédérale sur l’impôt fédéral direct fixe quant à lui à 21,2&amp;nbsp;% la part qui revient aux cantons pour les personnes physiques et morales.&amp;nbsp;La taxation et la perception sont effectuées par les cantons. Que les cantons puissent garder une part de l’impôt fédéral direct s’explique notamment par le fait qu’ils se chargent de la taxation et de la perception de l’impôt pour la Confédération. En raison de la transformation numérique et des gains d’efficacité qui en découlent, la charge administrative liée à la taxation et à la perception de l’impôt a dû continuellement diminuer pour les cantons au cours des dernières années. Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;À combien s’élèvent, à l’heure actuelle, les dépenses des cantons pour la taxation et la perception de l’impôt fédéral direct&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces dépenses ont-elles évolué au cours des dix dernières années&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles autres prestations fournies par les cantons en exécution de lois fédérales sont-elles indemnisées par la part de 21,2&amp;nbsp;% qui leur revient aujourd’hui&amp;nbsp;? Lesquelles d’entre elles sont-elles fournies sur la base d’une convention de prestations ou d’autres dispositions contractuelles&amp;nbsp;?&lt;/li&gt;&lt;li&gt;À combien s’élevaient les montants par prestation convenue et par canton en 2023 ou pour le dernier exercice bouclé&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Nach Artikel 128 Absatz 4 Bundesverfassung beträgt der Anteil der Kantone an der direkten Bundessteuer mindestens 17 Prozent. In Artikel 196 Absatz 1 des Bundesgesetzes über die direkte Bundessteuer ist der Kantonsanteil für natürliche und juristische Personen aktuell bei 21,2 Prozent festgelegt.&amp;nbsp;Die Bundessteuer wird von den Kantonen veranlagt und eingezogen. Der Anteil der Bundessteuern, der bei den Kantonen verbleibt wird u.a. auch damit begründet, dass die Kantone das für den Bund die Veranlagung und den Einzug der Bundesstern machen. Dank Digitalisierung und der damit einhergehenden Effizienzsteigerung dürfte der administrative Aufwand, der bei den Kantonen anfällt für die Veranlagung und den Einzug der Bundessteuern, in den letzten Jahren kontinuierlich gesunken sein. Vor diesem Hintergrund bitte ich um die Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie hoch beziffert sich aktuell der Aufwand der Kantone für das Veranlagen und den Einzug der Bundessteuer?&lt;/li&gt;&lt;li&gt;Wie hat sich dieser Aufwand in den letzten zehn Jahren verändert?&lt;/li&gt;&lt;li&gt;Welche weiteren Leistungen, die die Kantone in Erfüllung von Bundesgesetzen erbringen, sind mit dem heutigen Kantonsanteil von 21,2 abgegolten? Welche davon beruhen auf Leistungsvereinbarungen oder anderen vertraglichen Regelungen?&lt;/li&gt;&lt;li&gt;Wie hoch waren die Beträge pro vereinbarter Leistung und pro Kanton im Jahr 2023 bzw. im jüngsten abgerechneten Rechnungsjahr?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Médias et communication|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Media e comunicazione|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einfacher Zugang zu Ergänzungsleistungen für Anspruchsberechtigte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendre les prestations complémentaires aisément accessibles aux personnes qui y ont droit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facilitare l'accesso alle prestazioni complementari per chi ne ha diritto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement fait usage du droit d'initiative du Canton en matière fédérale et demande aux Chambres fédérales de modifier urgemment la loi fédérale sur les prestations complémentaires (LPC, 831.30) afin de garantir un accès aisé, voire automatique, à ces prestations pour les personnes qui y ont droit.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel 160 Absatz 1 der Bundesverfassung und Artikel 84 Buchstabe o der Verfassung des Kantons Jura fordert das Parlament des Kantons Jura die Bundesversammlung dazu auf, schnellstmöglich das Gesetz über Ergänzungsleistungen zur Alters-, Hinterlassenen- und Invalidenversicherung (ELG, 831.30) dahingehend anzupassen, dass jene, die Anspruch auf Ergänzungsleistungen haben, leichter oder sogar automatisch Zugang zu diesen haben.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soziale Fragen|Sozialer Schutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questions sociales|Protection sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questioni sociali|Protezione sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiederherstellung des Wettbewerbs- und Konsumentenschutzes im Autohandel. Beseitigung eines Handelshemmnisses bei Elektrofahrzeugen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantie constructeur pour les véhicules électriques importés. Rétablir une concurrence équitable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ripristinare la protezione della concorrenza e dei consumatori nel commercio di autoveicoli. Eliminare un ostacolo al commercio di veicoli elettrici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier l’ordonnance automobile (OAVAuto) afin d’assurer que la garantie constructeur (GC) sera valable dans tous les cas, que le véhicule ait fait l’objet d’une importation directe ou parallèle.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, durch Änderung der KFZ-Verordnung (KFZV) sicherzustellen, dass bei Parallel- oder Direktimporten von Kraftfahrzeugen die Herstellergarantie unabhängig vom Vertriebskanal gewährleistet bleibt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Verkehr|Energie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Transports|Énergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Trasporti|Energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weichelt Manuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schaffung von Anlauf- und Meldestellen für Gewaltopfer in Institutionen für Menschen mit Behinderungen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création de centres de consultation et services de signalement pour les personnes handicapées victimes de violence institutionnelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istituire servizi di assistenza e segnalazione per le persone con disabilità istituzionalizzate vittime di violenza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est prié de proposer une révision de la LIPPI rendant obligatoire l’existence de centres de consultation et services de signalement destinés aux victimes de violence dans les institutions pour personnes handicapées.&lt;/p&gt;&lt;p&gt;Ces centres de consultation et services de signalement devront être indépendants des institutions, garantir la confidentialité et être accessibles à toutes les personnes handicapées et à leurs proches. Ils seront mis en place en étroite collaboration avec les personnes handicapées et les organisations qui les représentent. Dans la mesure du possible, ils seront rattachés à des structures existantes afin de créer des synergies.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt mit einer Revision des IFEG dafür zu sorgen, dass Anlauf- und Meldestellen für Gewaltopfer in Institutionen für Menschen mit Behinderungen obligatorisch werden.&lt;/p&gt;&lt;p&gt;Diese Anlauf- und Meldestellen müssen unabhängig von Institutionen arbeiten, vertraulich sein und für alle Menschen mit Behinderungen und ihre Angehörigen zugänglich sein. Sie sind in enger Zusammenarbeit mit Menschen mit Behinderungen und den Organisationen von Menschen mit einer Behinderung zu entwickeln. Wo immer möglich, sollten Synergien geschaffen werden, indem sie an bestehende Strukturen angegliedert werden.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soziale Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questions sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questioni sociali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storni Bruno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung der Gesundheitskosten in den Kantonen je nach demografischer Entwicklung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolution des coûts de la santé dans les cantons en fonction de l'évolution de la structure d'âge de leur population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evoluzione dei costi della salute nei cantoni in funzione della crescente diversa evoluzione demografica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La différence de la structure d’âge de la population résidente s’accentue de plus en plus entre les cantons ruraux périphériques à faible développement économique et les cantons urbains à fort développement économique.&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si les plus de 65 ans représentent 19&amp;nbsp;% de la population suisse, leur proportion se monte à 24 % dans le canton le plus âgé et à 17&amp;nbsp;% dans le canton le plus jeune.&lt;/strong&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ces différences sont importantes et s’accentuent, notamment parce que les jeunes quittent les cantons périphériques pour les grandes villes et les agglomérations des cantons qui offrent de meilleures perspectives de travail.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les coûts de la santé, on le sait, augmentent avec l’âge et pèseront de plus en plus sur les primes de l'assurance-maladie dans les cantons périphériques par rapport aux cantons urbains dont la structure démographique est plus favorable, et l’écart se creusera encore en raison de l’évolution démographique mentionnée.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;L’impact des risques liés au vieillissement sur les coûts de la santé est bien visible dans les chiffres des centres de coûts du domaine des soins (EMS, physiothérapie, spitex; cf. Mokke). &amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;L’évolution de la structure d’âge dans les cantons du Tessin et du Jura, par exemple, entraînera une augmentation des coûts de la santé supérieure à la moyenne, qui se reportera sur les primes de l’assurance-maladie.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une étude de santésuisse (septembre 2021) montre que si le Tessin avait la structure d’âge moyenne de la Suisse, les coûts de la santé dans le canton correspondraient à la moyenne suisse.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;La péréquation des charges sociodémographiques, loin d’aider les cantons à faible développement économique, favorise nettement les cantons urbains (GE, ZH, VD, BS).&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Questions:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Le Conseil fédéral est-il au courant que les différences importantes des coûts de la santé s’accentuent en fonction de la structure d’âge de la population des cantons?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont ses scénarios d’évolution démographique (par canton)?&lt;/li&gt;&lt;li&gt;Quelle est l’incidence du vieillissement de la population sur l’évolution générale des coûts de la santé?&lt;/li&gt;&lt;li&gt;Comment la différence des coûts de la santé entre les cantons évoluera-t-elle?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Quel sera l'impact de cette évolution sur la viabilité financière, l'offre et la qualité des soins dans les cantons à faible développement économique, dans lesquels le nombre des plus de 65 ans augmente plus qu’ailleurs?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Alterszusammensetzung der Wohnbevölkerung in den Kantonen zeigt zunehmende Unterschiede zwischen peripheren ländlichen Kantonen mit geringer Wirtschaftsentwicklung und städtischen Kantonen mit hohem Wirtschaftswachstum.&lt;strong&gt; &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Im schweizerischen Durchschnitt machen die Über-65-Jährigen 19 Prozent aus, im Kanton mit dem höchsten Altersdurchschnitt liegt dieser Anteil bei 24 Prozent, im "jüngsten" Kanton bei 17 Prozent.&lt;/strong&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Diese grossen und grösser werdenden Unterschiede sind insbesondere auf die Abwanderung der jungen Leute aus den Randregionen in die grossen Städte und Agglomerationen, die sich in Kantonen mit einem interessanten Arbeitsmarkt befinden, zurückzuführen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die Gesundheitskosten steigen bekanntlich mit dem Alter. Mit der oben erwähnten demografischen Entwicklung werden diese Kosten die Krankenkassenprämien (KK) in den Randkantonen im Vergleich zu den städtischen Kantonen, die dank ihrer günstigeren demografischen Struktur einen moderateren Wachstumstrend aufweisen, immer stärker belasten; die Kluft der Ungleichheiten zwischen den Kantonen wird grösser.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Einfluss der Altersrisiken auf die Gesundheitskosten lässt sich an den Beträgen pro Kostenstelle im Gesundheitswesen ablesen: Altersheime, Physiotherapie, Spitex (siehe Mokke). &amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Kantone wie das Tessin und der Jura weisen eine Entwicklung in der Altersstruktur der Bevölkerung auf, die zu einem überdurchschnittlichen Anstieg der Gesundheitskosten und damit auch der Prämien für die Krankenversicherung führen wird.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Studie von Santésuisse (September 2021) hat gezeigt, dass die Gesundheitskosten im Kanton Tessin auf den Schweizer Durchschnittswert sänke, wenn dieser die durchschnittliche demografische Struktur der Schweiz aufwiese.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Der Ausgleich der soziodemografischen Lasten hilft den Kantonen mit geringer wirtschaftlicher Entwicklung sicher nicht, begünstigt aber eindeutig die städtischen Kantone (GE, ZH, VD, BS).&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Darum frage ich den Bundesrat:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Ist sich der Bundesrat bewusst, dass die Unterschiede bei den Gesundheitskosten in den Kantonen je nach demografischer Struktur der Wohnbevölkerung immer grösser werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie werden sich seiner Ansicht nach die altersbezogenen demografischen Szenarien je Kanton entwickeln?&lt;/li&gt;&lt;li&gt;Wie stark wirkt sich der Anteil der alternden Bevölkerung auf die Entwicklung der allgemeinen Gesundheitskosten aus?&lt;/li&gt;&lt;li&gt;Wie wird sich der Unterschied bei den Gesundheitskosten zwischen den Kantonen entwickeln?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie wird sich diese Entwicklung auf die finanzielle Nachhaltigkeit, das Angebot und die Qualität der Pflege in Kantonen mit geringer wirtschaftlicher Entwicklung und dem höchsten Wachstum der über 65-jährigen Bevölkerung auswirken?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zusammenarbeit statt Diktat der Post. Stärkung der Mitsprache der Gemeinden im Postgesetz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La collaboration au lieu du diktat de la Poste. Pour un renforcement du droit de regard des communes dans la loi sur la poste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooperazione anziché subire i dettami della Posta. Rafforzare la voce dei Comuni nella legge sulle poste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La loi sur la poste doit être modifiée de telle sorte que les communes et les cantons ne disposent plus uniquement du droit d’être consultés lors de la fermeture d’offices de poste, mais aussi d’un droit de participation élargi, et qu’ils doivent approuver toute fermeture.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Postgesetz ist so zu ändern, dass die Gemeinden und Kantone bei der Schliessung von Poststellen nicht mehr nur ein Anhörungsrecht, sondern ein erweitertes Mitwirkungsrecht erhalten und einer Schliessung zustimmen müssen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Wirtschaft|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Économie|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Economia|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einen dauerhaften Grenzschutz gewährleisten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantir une protection permanente des frontières</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantire una protezione permanente dei confini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La législation est adaptée de manière à garantir une protection permanente des frontières nationales. A cet effet, la disponibilité ininterrompue de patrouilles mobiles de l'OFDF en suffisance ainsi que le contrôle des principaux points de passage par des moyens électroniques sont assurés.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Gesetzgebung ist so anzupassen, dass ein dauerhafter Schutz der Landesgrenzen sichergestellt ist. Zu diesem Zweck muss eine ausreichende Anzahl mobiler Patrouillen des Bundesamts für Zoll und Grenzsicherheit (BAZG) ununterbrochen verfügbar sein und die Kontrolle der wichtigsten Grenzübergänge gewährleistet sein.&lt;/p&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Kommission des Ständerats / En commission du Conseil des Etats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20260030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20260030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berli Rudi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbot der Sömmerung in den grenzüberschreitenden Regionen. Welche Begleitmassnahmen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interdiction de l'estivage dans les régions transfrontalières. Quelles mesures d'accompagnement ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le 17 février l'OSAV a décidé une interdiction des estivages dans les régions transfrontalières. Cette mesure préventive contre la dermatose nodulaire contagieuse touche 250 fermes, notamment à Genève, Vaud et Jura et 6000 bovins.&amp;nbsp;&lt;br&gt;Quelles mesures d'accompagnement la Confédération peut-elle garantir rapidement, car la mesure prend effet immédiatement, pour éviter des conséquences économiques dramatiques pour les éleveurs concernés ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 17.&amp;nbsp;Februar 2026 hat das Bundesamt für Lebensmittelsicherheit und Veterinärwesen entschieden, die Sömmerung in den Grenzregionen zu verbieten. Diese Präventionsmassnahme gegen die Lumpy-Skin-Disease betrifft 250&amp;nbsp;Betriebe, hauptsächlich in den Kantonen Genf, Waadt und Jura, sowie 6000&amp;nbsp;Rinder.&amp;nbsp;&lt;br&gt;Angesichts der sofortigen Umsetzung der Massnahme: Welche kurzfristigen Begleitmassnahmen kann der Bund zusichern, um erhebliche wirtschaftliche Folgen für die betroffenen Tierhalterinnen und Tierhalter zu vermeiden?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Agricoltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commission des finances Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ausrichtung der nächsten Revision des Finanzausgleichsgesetzes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientation de la prochaine révision de la loi sur la péréquation financière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientamento della prossima revisione della legge federale concernente la perequazione finanziaria e la compensazione degli oneri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de soumettre au Parlement, dans le cadre de la prochaine révision de la loi fédérale sur la péréquation financière et la compensation des charges (PFCC), un projet qui :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;prévoie une réduction de la compensation des charges excessives dues à des facteurs socio-démographiques, étant donné que les hypothèses liées à la réforme de la péréquation financière de 2020, qui justifiaient alors l’augmentation de la compensation en question, ne se sont pas vérifiées ;&lt;/li&gt;&lt;li&gt;prévoie une nouvelle répartition des parts de financement entre la Confédération et les cantons à fort potentiel de ressources, en exploitant la marge de manœuvre prévue dans la Constitution fédérale (art. 135 Cst.), selon laquelle les contributions des cantons peuvent se situer dans une fourchette allant de deux tiers à 80&amp;nbsp;% de la contribution fédérale.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Rahmen der nächsten Revision des Bundesgesetzes über den Finanz- und Lastenausgleich (FiLaG) dem Parlament eine Vorlage zu unterbreiten, welche:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;eine Reduktion des soziodemografischen Lastenausgleichs (SLA) vorsieht, da sich die mit der Reform des Finanzausgleichs 2020 verbundenen Annahmen, welche die damalige Aufstockung des SLA rechtfertigten, nicht bestätigt haben;&lt;/li&gt;&lt;li&gt;eine Neuverteilung der Finanzierungsanteile zwischen der Eidgenossenschaft und den finanzstarken Kantonen vorsieht, unter Ausschöpfung des in der Bundesverfassung (Art. 135 BV) vorgesehenen Spielraums, wonach die Beiträge der Kantone zwischen zwei Dritteln und 80 Prozent des Bundesbeitrags betragen können;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bertschy Kathrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pvl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA-Optimierungen durch die Kantone?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les facturations provisoires de l’impôt manquantes permettent-elles aux cantons d'optimiser la RPT ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’assenza di fatture fiscali provvisorie permette ai Cantoni di effettuare ottimizzazioni nella perequazione finanziaria nazionale?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le canton de Genève n'a pas encore établi certaines factures fiscales provisoires des années précédentes et doit désormais corriger cette situation. Il en découle, pour la Confédération, des recettes supplémentaires d’environ 600 à 800&amp;nbsp;millions de francs au total (source&amp;nbsp;: https://www.news.admin.ch/fr/newnsb/Y973XYMqlzrucihcHqlyi).&lt;/p&gt;&lt;p&gt;Le canton de Genève n'a pas établi, pour les années 2019 à 2024, de facturation provisoire de l’impôt fédéral direct pour un nombre d’entreprises plus élevé que prévu jusqu’à présent. Or cela va à l’encontre de la législation en la matière, selon laquelle au moins une facturation provisoire doit être établie. L'absence de factures fiscales provisoires peut également avoir une incidence sur le calcul du potentiel de ressources dans le cadre de la péréquation financière entre la Confédération et les cantons, car en l'absence de taxation définitive, ce sont les éléments imposables facturés qui sont pris en compte.&lt;/p&gt;&lt;p&gt;Le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quelles sont les conséquences de ces factures fiscales provisoires que le canton de Genève n’a pas établies sur le potentiel de ressources et sur les paiements compensatoires calculés sur cette base&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les bases de calcul de l'impôt qui ont entraîné des paiements ultérieurs élevés en matière d’impôt fédéral ont-elles été intégrées dans l’assiette fiscale agrégée servant à déterminer le potentiel de ressources et l'indice des ressources, ou le seront-elles encore&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si tel n'est pas le cas, le potentiel de ressources manquant peut-il être ajouté au canton de Genève afin qu'il soit pris en compte dans le calcul des paiements compensatoires pour les périodes suivantes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sont les bases légales et les directives régissant la saisie des bases d'imposition pour la péréquation financière ainsi que le traitement des données erronées et les corrections a posteriori&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Qui vérifie que les cantons respectent les règles relatives à la saisie correcte des bases de calcul du potentiel de ressources&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les cantons disposent-ils d'une marge de manœuvre leur permettant d'optimiser le potentiel de ressources à leur avantage en retardant la facturation ou par d'autres moyens&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Existe-t-il des indications provenant d'autres cantons concernant des possibilités d'optimisation lors du calcul du potentiel de ressources&amp;nbsp;? Si oui, quelles optimisations sont effectuées&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sanctions la Confédération peut-elle prendre à l'encontre des cantons qui ne se conforment pas aux règles lors de la transmission des données nécessaires au calcul du potentiel de ressources&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Kanton Genf hat provisorische Steuerrechnungen der vergangenen Jahre teilweise noch nicht ausgestellt und muss dies nun korrigieren. Für den Bund führt dies zu einmaligen Mehreinnahmen von insgesamt rund 600-800 Millionen Franken (Quelle: https://www.news.admin.ch/de/newnsb/Y973XYMqlzrucihcHqlyi)&lt;/p&gt;&lt;p&gt;Der Kanton Genf hat für die Jahre 2019 bis 2024 in einem grösseren Umfang als angenommen keine provisorischen Steuerrechnungen ausgestellt. Dies widerspricht dem Bundesgesetz über die direkte Bundessteuer, wonach mindestens eine provisorische Steuerrechnung ausgestellt werden muss. Das Fehlen von provisorischen Steuerrechnungen hat womöglich auch Einfluss auf die Berechnung des Ressourcenpotenzials im Ressourcenausgleich zwischen Bund und Kantonen, da bei fehlenden definitiven Veranlagungen die in Rechnung gestellten Steuerfaktoren berücksichtigt werden.&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche Auswirkungen haben diese nicht erfassten provisorischen Steuerrechnungen im Kanton Genf auf das Ressourcenpotenzial und die damit berechneten Ausgleichszahlungen?&lt;/li&gt;&lt;li&gt;Sind die Steuerbemessungsgrundlagen, welche die hohen Nachzahlungen bei der Bundessteuer bewirkt haben, in die aggregierte Steuerbemessungsgrundlage für die Ermittlung des Ressourcenpotenzials und des Ressourcenindexes mit eingeflossen oder werden sie noch einfliessen?&lt;/li&gt;&lt;li&gt;Falls das nicht der Fall ist - kann das fehlende Ressourcenpotenzial dem Kanton Genf nachgetragen werden, so dass es in den Folgeperioden noch für die Berechnung der Ausgleichszahlungen mitberücksichtigt wird?&lt;/li&gt;&lt;li&gt;Welches sind die gesetzlichen Grundlagen und Weisungen für die Erfassung der Steuerbemessungsgrundlagen für den Ressourcenausgleich sowie für die Handhabung von fehlerhaften Datenlieferungen und nachträglichen Korrekturen?&lt;/li&gt;&lt;li&gt;Wer prüft die Einhaltung der Regeln für die korrekte Erfassung der Bemessungsgrundlagen des Ressourcenpotenzials durch die Kantone?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Haben die Kantone einen Spielraum, mit verzögerter Rechnungsstellung oder anderen Aktivitäten das Ressourcenpotenzial zu ihren Gunsten zu optimieren?&lt;/li&gt;&lt;li&gt;Gibt es aus anderen Kantonen Hinweise , über Optimierungsmöglichkeiten bei der Bemessung des Ressourcenpotenzials? Wenn ja, welche Optimierungen werden getätigt?&lt;/li&gt;&lt;li&gt;Welche Sanktionsmöglichkeiten hat der Bund gegenüber Kantonen, die sich bei der Datenlieferung für die Berechnung des Ressourcenpotenzials nicht regelkonform verhalten?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freymond Sylvain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wie steht es um die Umsetzung des Gewässerraums?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etat de la mise en oeuvre de l'espace réservé aux eaux ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stato di attuazione dello spazio riservato alle acque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Etat de la mise en œuvre de l’espace réservé aux eaux ?&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quel est l’état d’avancement, canton par canton, de la mise en œuvre de l’espace réservé aux eaux ? Combien de cantons ont finalisé cette planification&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelle est l’estimation actuelle des surfaces agricoles incluses dans l’espace réservé aux eaux à l’échelle nationale&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces surfaces sont-elles déclarées et utilisées&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Wie steht es um die Umsetzung des Gewässerraums?&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie weit ist die Umsetzung des Gewässerraums in den einzelnen Kantonen fortgeschritten? Wie viele Kantone haben die Planung abgeschlossen?&lt;/li&gt;&lt;li&gt;Wie gross ist die geschätzte Landwirtschaftsfläche, die schweizweit im Gewässerraum liegt?&lt;/li&gt;&lt;li&gt;Wie wird diese Fläche deklariert und genutzt?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umwelt|Landwirtschaft|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environnement|Agriculture|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambiente|Agricoltura|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lagerung von CO2 und nuklearen Abfällen. Gewährleistung der Nachhaltigkeit und Neutralität des Betriebs des Mont-Terri-Felslabors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stockage du CO2 et des déchets nucléaires. Assurer la pérennité et la neutralité de l'exploitation du laboratoire souterrain du Mont Terri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stoccaggio di CO2 e di scorie nucleari. Garantire la continuità e la neutralità nell'esercizio del laboratorio sotterraneo di Mont Terri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les dispositions nécessaires afin que l’exploitation du laboratoire souterrain du Mont Terri demeure assurée par la Confédération.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Il examinera notamment les possibilités suivantes&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Assurer à swisstopo les moyens nécessaires pour assurer l’exploitation du laboratoire souterrain tel qu’il le fait aujourd’hui&lt;/li&gt;&lt;li&gt;Attribuer la gestion du laboratoire à l'Institut fédéral pour la sureté nucléaire (IFSN), à l'Office fédéral de l'environnement (OFEV) ou à l'Office fédéral de l'énergie (OFEN).&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die notwendigen Vorkehrungen zu treffen, damit der Betrieb des Felslabors Mont Terri weiterhin durch den Bund gewährleistet wird.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat soll dabei insbesondere folgende Möglichkeiten prüfen:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Sicherstellung der notwendigen Mittel für Swisstopo, um den Betrieb des Felslabors wie bisher fortzusetzen;&lt;/li&gt;&lt;li&gt;Übertragung der Verwaltung des Labors an das Eidgenössische Institut für Nukleare Sicherheit (ENSI), das Bundesamt für Umwelt (BAFU) oder das Bundesamt für Energie (BFE).&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zugewiesen an die behandelnde Kommission / Attribué à la commission compétente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Umwelt|Energie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Environnement|Énergie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Ambiente|Energia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prüfung eines spezifischen Straftatbestands zur Bekämpfung mafiaähnlicher Organisationen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examen d'une infraction pénale indépendante visant à combattre des organisations de type mafieux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esame di una fattispecie penale indipendente volta a contrastare le organizzazioni di tipo mafioso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'examiner et d'expliquer dans un rapport que :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;si les dispositions actuelles du droit pénal, en particulier l'article 260ter du Code pénal (organisation criminelle), sont suffisantes pour combattre efficacement les structures mafieuses et similaires à la mafia ;&lt;/li&gt;&lt;li&gt;dans quelle mesure le crime organisé utilisant des méthodes similaires à celles de la mafia (par exemple, intimidation, isolement, infiltration économique, blanchiment d'argent) est insuffisamment couvert par la législation existante ;&lt;/li&gt;&lt;li&gt;si et sous quelle forme l'introduction d'une infraction pénale indépendante (« article mafieux » selon l'Italie, par exemple)– tout en respectant les garanties de l'État de droit – pourrait contribuer à améliorer les forces de l'ordre ;&lt;/li&gt;&lt;li&gt;quelle expérience des autres États (notamment les États européens) existe dans ce domaine et quels éléments pourraient être transférés en Suisse ;&lt;/li&gt;&lt;li&gt;quels effets seraient attendus sur la sécurité intérieure, la situation financière et économique ainsi que la coopération entre la Confédération et les cantons.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, zu prüfen und in einem Bericht zu erläutern:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;ob die geltenden strafrechtlichen Bestimmungen, insbesondere Artikel 260ter des Strafgesetzbuches (kriminelle Organisationen), ausreichen, um mafiöse und mafiähnliche Strukturen wirksam zu bekämpfen;&lt;/li&gt;&lt;li&gt;inwieweit die organisierte Kriminalität, die ähnliche Methoden wie die Mafia anwendet (z. B. Einschüchterung, Isolierung, wirtschaftliche Unterwanderung, Geldwäscherei), durch die bestehenden Rechtsvorschriften nicht ausreichend erfasst ist;&lt;/li&gt;&lt;li&gt;ob und in welcher Form die Einführung eines spezifischen Straftatbestands («Antimafiaparagraf» nach italienischem Vorbild beispielsweise) unter Wahrung der rechtsstaatlichen Garantien zu einer Verbesserung der Strafverfolgung beitragen könnte;&lt;/li&gt;&lt;li&gt;welche Erfahrungen andere Staaten (insbesondere europäische Staaten) in diesem Bereich gemacht haben und welche Elemente auf die Schweiz übertragen werden könnten;&lt;/li&gt;&lt;li&gt;welche Auswirkungen auf die innere Sicherheit, die finanzielle und wirtschaftliche Lage sowie die Zusammenarbeit zwischen Bund und Kantonen zu erwarten wären.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überwiesen an den Bundesrat / Transmis au Conseil fédéral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Strafrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Droit pénal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Diritto penale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z'graggen Heidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzielle Leistungen und Abgeltungen des Bundes an die Kantone für internationale Aufgaben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prestations financières et indemnités versées aux cantons pour l’accomplissement de tâches internationales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prestazioni finanziarie e indennità della Confederazione ai Cantoni per i compiti internazionali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La Confédération soutient les cantons dans l’accomplissement de tâches ayant un caractère international. Elle leur verse notamment des contributions pour les prestations cantonales fournies en faveur d’organisations et de conférences internationales, de représentations diplomatiques, d’étudiants internationaux et de prestations de transport transfrontalières, ainsi que des contributions d’encouragement dans le cadre de programmes internationaux de coopération (tels qu’Interreg).&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Vue d’ensemble&amp;nbsp;:&lt;br&gt;Quelles ressources financières la Confédération met-elle à la disposition des cantons pour des prestations ayant un caractère international (ventilées par canton)&amp;nbsp;? Je songe en particulier aux prestations suivantes&amp;nbsp;: prestations en faveur d’organisations et de conférences internationales, soutien apporté aux étudiants internationaux, surveillance et protection des ambassades et des représentations diplomatiques internationales, projets d’infrastructures internationaux, prestations de transport transfrontalières, contributions issues de programmes internationaux de coopération (tels qu’Interreg), indemnités versées pour des tâches de protection des ambassades et de protection diplomatique.&lt;/li&gt;&lt;li&gt;Prestations de transport transfrontalières&amp;nbsp;:&lt;br&gt;Des contributions sont-elles versées aux cantons pour le transport international de voyageurs ou de marchandises ou pour d’autres prestations de transport ayant un caractère international&amp;nbsp;? Si oui, quel est le montant de ces contributions&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Autres prestations&amp;nbsp;:&lt;br&gt;Y a-t-il encore d’autres prestations financières que la Confédération verse aux cantons pour l’accomplissement de tâches internationales&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bund unterstützt die Kantone bei der Wahrnehmung von Aufgaben mit internationalem Bezug. Dazu zählen unter anderem Beiträge für kantonale Leistungen zugunsten internationaler Organisationen und Konferenzen, diplomatischer Vertretungen, internationaler Studierender, grenzüberschreitender Verkehrsleistungen sowie Förderbeiträge im Rahmen internationaler Kooperationsprogramme wie Interreg.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten dazu die folgenden Fragen zu beantworten:&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Gesamtübersicht:&lt;br&gt;Welche finanziellen Mittel stellt der Bund den Kantonen für Leistungen mit internationalem Bezug zur Verfügung (nach Kantonen aufgeschlüsselt)? Es geht insbesondere um Leistungen zugunsten internationaler Organisationen und Konferenzen; Unterstützung internationaler Studierender; Bewachung und Schutz internationaler Botschaften und diplomatischer Vertretungen; Internationale Infrastrukturprojekte; Grenzüberschreitende Verkehrsleistungen; Beiträge aus internationalen Kooperationsprogrammen (z. B. Interreg); Abgeltungen oder Entschädigungen für Botschafts- und diplomatische Schutzaufgaben, usw.&lt;/li&gt;&lt;li&gt;Internationale Verkehrsleistungen:&lt;br&gt;Werden Kantonen Beiträge für den grenzüberschreitenden Personen- oder Güterverkehr oder andere international relevante Verkehrsdienstleistungen ausbezahlt? Falls ja, wie hoch sind die Beiträge.&lt;/li&gt;&lt;li&gt;Weitere Leistungen:&lt;br&gt;Gibt es weitere finanziellen Leistungen für internationale Aufgaben die der Bund an die Kantone ausrichtet?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;&lt;br&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Finanzwesen|Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Finances|Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Finanze|Trasporti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzreferendum auch auf Bundesebene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instaurer un référendum financier à l’échelon fédéral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Istituire un referendum finanziario anche a livello federale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l'Assemblée fédérale un projet d'acte législatif prévoyant un référendum financier facultatif et (en option) un référendum financer obligatoire portant sur les nouvelles dépenses uniques – et, en option, sur les dépenses annuelles récurrentes – d'un montant approprié, qui reste à déterminer.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, der ein fakultatives und (optional) ein obligatorisches Finanzreferendum für neue einmalige - und optional für jährlich wiederkehrende - Ausgaben in angemessener, noch zu bestimmender Höhe vorsieht.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inwieweit wird das Thema Salz in der Strategie zur Gesundheitsförderung und Prävention in der Schweiz berücksichtigt?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quelle prise en compte de la question du sel dans la stratégie de promotion de la santé en Suisse ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In che misura la questione del sale viene presa in considerazione nella strategia di promozione della salute in Svizzera?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le lien entre la consommation régulière excessive de sel et le risque augmenté de développer une attaque cérébrale, une maladie coronarienne ou encore une insuffisance cardiaque n'est plus à démontrer.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La quantité excessive de sel consommée quotidiennement se traduit par l'apparition d'une hypertension artérielle, une affection sournoise qui ne fait pas mal et qui est très souvent inconnue du patient. Et chez les patients traités, la compliance thérapeutique est régulièrement insuffisante. Par le nombre de personnes touchées et les complications sérieuses que cette affection peut causer au long cours, il s'agit d'un problème majeur de santé publique. Mais un problème encore largement négligé. On connait les effets néfastes de trop de sucre, encore trop peu les conséquences de l'ingestion de trop de sel.&lt;/p&gt;&lt;p&gt;L'apport excessif de sel peut s'expliquer par un apport volontaire lors des repas, mais souvent il s'agit plutôt de "sel caché", lié à une consommation abusive de sel retrouvé dans des aliments transformés et conditionnés industriellement (plats précuisinés) ou dans la restauration rapide. L'ajout volontaire de sel par l'industrie alimentaire vise une amélioration du goût et implicitement une augmentation des ventes de ces produits industriels.&lt;/p&gt;&lt;p&gt;Cette situation avait déjà été dénoncée dans notre Parlement voilà près de dix ans par une motion du conseiller national Manuel Tornare (16.3601), une motion restée sans suite car classée sans vote après un délai de deux ans.&lt;/p&gt;&lt;p&gt;Une émission télévisée récente (ABE sur la SSR) a une nouvelle fois soulevé la question et tend à démontrer que rien ou peu de choses ont changé face à cette problématique.&lt;/p&gt;&lt;p&gt;Mes questions:&lt;/p&gt;&lt;p&gt;- Quelle est l'appréciation du Conseil fédéral sur la problématique de la consommation abusive de sel par la population en particulier en lien avec les problèmes de santé publique?&lt;/p&gt;&lt;p&gt;- Peut-il nous indiquer quelles mesures ont été prises sur ce sujet durant les dernières années?&lt;/p&gt;&lt;p&gt;- Quelles pressions sont exercées sur l'industrie alimentaire pour réduire "efficacement" la quantité de sel dans les plats précuisinés industriels?&lt;/p&gt;&lt;p&gt;- Le Conseil fédéral est-il prêt à intervenir encore davantage pour répondre efficacement à ce problème?&lt;/p&gt;&lt;p&gt;- Envisage-t-il une campagne nationale d'information et de sensibilisation?&lt;/p&gt;&lt;p&gt;Nous remercions le Conseil fédéral pour ses réponses.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Zusammenhang zwischen regelmässigem übermässigem Salzkonsum und einem erhöhten Risiko für Schlaganfall, koronare Herzkrankheiten oder Herzinsuffizienz ist inzwischen klar belegt.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine zu hohe tägliche Salzaufnahme führt zu Bluthochdruck, einer heimtückischen Erkrankung, die keine Schmerzen verursacht und von den Betroffenen häufig unbemerkt bleibt. Zudem zeigen die Patientinnen und Patienten oft nur eine geringe Bereitschaft, in der Therapie mitzuwirken. Angesichts der hohen Zahl der Betroffenen und der schwerwiegenden, langfristigen Komplikationen stellt dieses Verhalten ein erhebliches Problem für die öffentliche Gesundheit dar&amp;nbsp;– ein Problem, das jedoch nach wie vor weitgehend vernachlässigt wird. Während die gesundheitlichen Risiken von übermässigem Zuckerkonsum allgemein bekannt sind, sind die problematischen Folgen von übermässigem Salzkonsum bisher noch kaum im öffentlichen Fokus.&lt;/p&gt;&lt;p&gt;Übermässiger Salzkonsum kann teilweise durch freiwilliges Nachsalzen bei Mahlzeiten erklärt werden, häufig handelt es sich jedoch um sogenanntes «verstecktes Salz», das in industriell verarbeiteten und abgepackten Lebensmitteln&amp;nbsp;(z.&amp;nbsp;B. Fertiggerichten) oder in Fastfood enthalten ist. Die gezielte Salzbeigabe durch die Lebensmittelindustrie dient vor allem der Geschmacksverbesserung und damit implizit der Steigerung des Absatzes der Produkte.&lt;/p&gt;&lt;p&gt;Diese Sachlage wurde bereits vor fast zehn Jahren im Parlament durch die Motion&amp;nbsp;16.3601 von Nationalrat Manuel&amp;nbsp;Tornare aufgegriffen. Die Motion blieb jedoch ohne Folgen, da sie nach zwei Jahren ohne abschliessende Behandlung im Rat abgeschrieben wurde.&lt;/p&gt;&lt;p&gt;Eine kürzlich ausgestrahlte Fernsehsendung&amp;nbsp;(«A bon entendeur», SRG) hat das Thema erneut beleuchtet und gezeigt, dass sich zu dieser Sachlage bisher wenig bis gar nichts geändert hat.&lt;/p&gt;&lt;p&gt;Ich stelle dem Bundesrat folgende Fragen:&lt;/p&gt;&lt;p&gt;– Wie beurteilt der Bundesrat die Problematik des übermässigen Salzkonsums der Bevölkerung, insbesondere im Zusammenhang mit den Auswirkungen auf die öffentliche Gesundheit?&lt;/p&gt;&lt;p&gt;– Welche Massnahmen wurden in den letzten Jahren in diesem Bereich ergriffen?&lt;/p&gt;&lt;p&gt;– Welcher Druck wird auf die Lebensmittelindustrie ausgeübt, um den Salzgehalt in industriell hergestellten Fertiggerichten wirksam zu reduzieren?&lt;/p&gt;&lt;p&gt;– Ist der Bundesrat bereit, noch stärker zu intervenieren, um das Problem wirksam anzugehen?&lt;/p&gt;&lt;p&gt;– Plant der Bundesrat eine nationale Informations- und Sensibilisierungskampagne?&lt;/p&gt;&lt;p&gt;Besten Dank dem Bundesrat für seine Antworten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Medien und Kommunikation|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Médias et communication|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Media e comunicazione|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alijaj Islam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nationalen Finanzausgleich (NFA) im Bezug auf Sportschulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Péréquation financière nationale et écoles de sport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Que pense le Conseil fédéral des effets de la péréquation financière nationale sur le financement et le développement des écoles de sport cantonales et régionales ? Estime-t-il nécessaire de prendre des mesures pour garantir que les jeunes talents sportifs bénéficient d’un encouragement équivalent quel que soit leur canton de domicile ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Wie beurteilt der Bundesrat die Auswirkungen des Nationalen Finanzausgleichs auf die Finanzierung und Entwicklungsfähigkeit kantonaler und regionaler Sportschulen, und sieht er Handlungsbedarf, um sicherzustellen, dass sportlich talentierte Jugendliche unabhängig vom Wohnkanton gleichwertige Förderbedingungen erhalten?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Soziale Fragen|Bildung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Questions sociales|Éducation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Questioni sociali|Formazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeschi Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ausschaffungs-Schlendrian: Ausschaffungs-Initiative von 2010 noch immer nicht umgesetzt!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laxisme des autorités : l’initiative sur le renvoi de 2010 n’est toujours pas mise en œuvre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;À en croire le Conseil fédéral (réponse à la question 25.8110) ainsi que les médias (NZZ am Sonntag «Die Deutschschweiz vollzieht Landesverweise konsequenter als die Westschweiz» et Blick «Ausschaffungs-Schlendrian: Romandie zeigt Herz für kriminelle Ausländer»), l’initiative sur le renvoi (&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20090060&amp;amp;data=05%7C02%7CPhilippe.Schwab%40parl.admin.ch%7Ccdb0c7ac59b340180a8108de37cf3690%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639009560266946008%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=vVL%2BUy4Xa%2FvmG4xFHZQnTMEnDBqLzLRhOt3eY%2Bh6ZAY%3D&amp;amp;reserved=0"&gt;09.060&lt;/a&gt;) n’est toujours pas mise en œuvre.&lt;br&gt;- Que fait le Conseil fédéral pour que 100&amp;nbsp;% des expulsions soient exécutées, et ce dans tous les cantons&amp;nbsp;?&lt;br&gt;- Des retenues au niveau de la péréquation financière RPT sont-elles envisageables&amp;nbsp;?&lt;br&gt;Quand la situation devrait-elle s’améliorer&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gemäss Antwort auf die Frage 25.8110 sowie den Berichten in NZZ am Sonntag «Die Deutschschweiz vollzieht Landesverweise konsequenter als die Westschweiz» und Blick «Ausschaffungs-Schlendrian: Romandie zeigt Herz für kriminelle Ausländer» wird die Ausschaffungs-Initiative (&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20090060&amp;amp;data=05%7C02%7CPhilippe.Schwab%40parl.admin.ch%7Ccdb0c7ac59b340180a8108de37cf3690%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639009560266946008%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=vVL%2BUy4Xa%2FvmG4xFHZQnTMEnDBqLzLRhOt3eY%2Bh6ZAY%3D&amp;amp;reserved=0"&gt;09.060&lt;/a&gt;) noch immer nicht umgesetzt.&lt;br&gt;- Was unternimmt der Bundesrat, damit die Vollzugsquoten in allen Kantonen 100 % erreichen?&lt;br&gt;- Sind Kürzungen beim Finanzausgleich (NFA) eine Option?&lt;br&gt;Bis wann sind Verbesserungen zu erwarten?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20258286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commission de la science, de l'éducation et de la culture Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denkmal-, Heimat- und Ortsbildschutz. Auswirkungen neuer Aufgabenteilungen und Wirksamkeit beschlossener Massnahmen evaluieren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protection des monuments, du patrimoine et des sites construits. Évaluer les conséquences d'une nouvelle répartition des tâches et l'efficacité des mesures décidées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conservazione dei monumenti storici e protezione del paesaggio e degli insediamenti. Valutare le ripercussioni di una nuova ripartizione dei compiti e l'efficacia delle misure decise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter et d’évaluer le potentiel et les conséquences d’une éventuelle nouvelle répartition des tâches entre la Confédération et les cantons dans le domaine de la protection des monuments, du patrimoine et des sites construits. Il indiquera également s’il est nécessaire de mettre à jour la liste des monuments, ensembles et sites archéologiques d’importance nationale. Le Conseil fédéral prendra aussi en considération l’efficacité du train de mesures qu’il a décidées le 26 septembre 2025 afin de faciliter la construction de logements grâce à l’amélioration et à la précision de l’application de l’Inventaire fédéral des sites construits d’importance nationale à protéger en Suisse (ISOS).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Potenzial und die Auswirkungen einer möglichen neuen Aufgabeteilung zwischen Bund und Kantonen im Bereich Denkmal-, Heimat- und Ortsbildschutzes aufzuzeigen und zu evaluieren sowie den Bedarf einer Bereinigung des Verzeichnisses der Denkmäler, Ensembles und archäologischen Stätten von nationaler Bedeutung aufzuzeigen. Dabei soll der Bundesrat auch die Wirksamkeit seines Massnahmenpakets vom 26.09.2025 zur Erleichterung des Wohnungsbaus durch Verbesserungen und Präzisierungen bei der Anwendung des Bundesinventars der schützenswerten Ortsbilder (ISOS) berücksichtigen.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Kultur|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Culture|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Cultura|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germann Hannes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vollumfänglicher Abzug der Krankenversicherungsprämien von der direkten Bundessteuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impôt fédéral direct. Déduction totale des primes d'assurance-maladie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deduzione integrale dei premi per l'assicurazione contro le malattie in ambito di imposta federale diretta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la loi fédérale du 14&amp;nbsp;décembre&amp;nbsp;1990 sur l’impôt fédéral direct comme suit&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art.&amp;nbsp;33 Intérêts passifs et autres réductions&lt;/p&gt;&lt;p&gt;Al&amp;nbsp;1&lt;/p&gt;&lt;p&gt;Sont déduits du revenu&amp;nbsp;:&lt;/p&gt;&lt;p&gt;let. a à f, h et i&amp;nbsp;: inchangées&amp;nbsp;;&lt;/p&gt;&lt;p&gt;let. g&amp;nbsp;: biffer «&amp;nbsp;d’assurances-maladie&amp;nbsp;»&amp;nbsp;;&lt;/p&gt;&lt;p&gt;let.&amp;nbsp;k (nouvelle)&amp;nbsp;: les primes et cotisations d’assurance-maladie privée et obligatoire.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Bundesgesetz über die direkte Bundessteuer (DBG) wie folgt zu ändern:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art. 33 Schuldzinsen und andere Abzüge&lt;/p&gt;&lt;p&gt;Abs. 1&lt;/p&gt;&lt;p&gt;Von den Einkünften werden abgezogen:&lt;/p&gt;&lt;p&gt;Bst. a bis f sowie h und i: bleiben unverändert;&lt;/p&gt;&lt;p&gt;Bst. g: Streichung von "Krankenversicherung";&lt;/p&gt;&lt;p&gt;Bst. k (neu): Prämien und Beiträge für die obligatorische und private Krankenversicherung.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuer|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscalité|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imposte|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wettstein Felix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Der geografisch-topografische Lastenausgleich muss besser auf tatsächliche Lasten ausgerichtet sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La péréquation financière doit mieux refléter les charges découlant réellement de la géotopographie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La perequazione dell'aggravio geotopografico deve considerare meglio gli oneri effettivi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’exposer dans le rapport sur l’efficacité de la péréquation financière et de la compensation des charges 2026-2029 comment les charges géo-topographiques pourraient être compensées d’une manière plus équitable. Le rapport devra proposer des indicateurs qui tiendront compte mieux que les critères actuels des charges effectives supérieures à la moyenne découlant de facteurs géo-topographiques. Les effets de la péréquation sur les cantons seront présentés graphiquement en fonction de l’indicateur et du coefficient choisis.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Wirksamkeitsbericht zum Finanz- und Lastenausgleich 2026-2029 darzulegen, wie der geografisch-topografische Lastenausgleich fairer berechnet und ausgestaltet werden kann. Der Bericht soll Indikatoren vorschlagen, welche besser als die bisherigen geeignet sind, die tatsächlichen überdurchschnittlichen Lasten aufgrund der Topografie auszuweisen. Je nach gewähltem Indikator und dessen Gewichtung soll tabellarisch dargestellt werden, wie sich eine künftige Verteilung der Ausgleichzahlungen auf die Kantone auswirkt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verlagerung von der Schiene auf die Strasse zwischen der Jurasüdfussachse und dem Genferseebogen nach der Einführung des Fahrplans 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report du rail vers la route entre l'axe du Pied du Jura et l'Arc lémanique à la suite de l'introduction de l'horaire 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasferimento del traffico dalla ferrovia alla strada tra l'asse del versante sud del Giura e l'arco lemanico a seguito dell'introduzione dell'orario 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Depuis plus de 6 mois, l'Alliance des Villes, les Cantons de Suisse Occidentale, les entreprises et des groupes d'habitants de la région du Pied du Jura signalent une détérioration de l’offre ferroviaire sur l’axe du Pied du Jura entre Bienne et Genève, via Yverdon-les-Bains, Morges et Nyon, à l'introduction de l'horaire 2025. La suppression des liaisons ferroviaires directes ou l'allongement des temps de parcours entraînent un transfert croissant vers la route, notamment pour les déplacements professionnels. Certains trajets en train sont passés du simple au double, notamment celui entre Yverdon et Morges, ayant des répercussions sur l'attractivité du transport public. Parallèlement, les flux autoroutiers sur l'échangeur autoroutier semblent avoir considérablement augmenté depuis plusieurs mois.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans le contexte de la politique de transfert modal pour les voyageurs, il est essentiel de pouvoir mesurer l’ampleur de ce phénomène. Je prie dès lors le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Dispose-t-il de données récentes permettant de mesurer l’évolution du nombre de voyageurs ayant délaissé le rail au profit de la route sur le tronçon Bienne–Genève, en particulier depuis la réorganisation de l’horaire 2025 ?&lt;/li&gt;&lt;li&gt;Dispose-t-il de données récentes permettant de mesurer l’augmentation du trafic routier sur cet axe autoroutier (Nord vaudois - La Côte, notamment) ?&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral évalue-t-il l’impact de ce transfert sur les objectifs climatiques, sur les coûts externes du trafic (bruit, pollution, accidents) et sur la qualité de vie des régions concernées ?&lt;/li&gt;&lt;li&gt;D’ici le rétablissement d’une liaison via le bypass avec le tunnel de Gléresse en 2031, quelles mesures le Conseil fédéral entend-il mettre en œuvre pour garantir que la desserte ferroviaire du Pied du Jura retrouve un niveau d’attractivité suffisant afin de respecter les objectifs de transfert rail-route inscrits dans la Constitution ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Seit mehr als sechs Monaten weisen die Städteallianz, die Westschweizer Kantone, Unternehmen und Bewohnergruppen der Jurasüdfuss-Region auf eine Verschlechterung des Bahnangebots auf der Jurasüdfuss-Achse zwischen Biel und Genf via Yverdon-les-Bains, Morges und Nyon nach der Einführung des Fahrplans 2025 hin. Die Abschaffung direkter Zugverbindungen oder längere Fahrtzeiten führen zu einer zunehmenden Verlagerung auf die Strasse, insbesondere beim Arbeitsverkehr. Einige Zugfahrten dauern inzwischen doppelt so lange, insbesondere die Fahrt von Yverdon nach Morges, was den öffentlichen Verkehr weniger attraktiv macht. Gleichzeitig scheint der Verkehr auf dem Autobahnkreuz seit einigen Monaten erheblich zugenommen zu haben.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im Zusammenhang mit der Verlagerungspolitik ist es entscheidend, das Ausmass der erwähnten Entwicklung zu quantifizieren. Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Verfügt der Bundesrat über aktuelle Daten, die es ermöglichen, die Entwicklung der Zahl der Reisenden zu verfolgen, die auf der Strecke Biel–Genf von der Schiene auf die Strasse umgestiegen sind, insbesondere seit der Einführung des Fahrplans 2025?&lt;/li&gt;&lt;li&gt;Verfügt er über aktuelle Daten, die es ermöglichen, die Zunahme des Strassenverkehrs auf dieser Autobahnachse (insbesondere Nordwaadt‒La Côte) zu quantifizieren?&lt;/li&gt;&lt;li&gt;Wie bewertet der Bundesrat die Auswirkungen der erwähnten Verlagerung auf die Klimaziele, die externen Kosten des Verkehrs (Lärm, Verschmutzung, Unfälle) und die Lebensqualität in den betroffenen Regionen?&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat bis zur Wiederherstellung einer Verbindung mit dem Ligerztunnel im Jahr 2031 umzusetzen, um zu gewährleisten, dass die Bahnanbindung des Jurasüdfusses wieder genug attraktiv wird, damit die verfassungsmässigen Vorgaben zur Verkehrsverlagerung erfüllt werden.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Importverbot für chemisch behandeltes Geflügelfleisch ("Chlorhühner") gesetzlich verankern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inscrire dans la loi l'interdiction d'importer de la viande de volaille traitée chimiquement ("poulet au chlore")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introdurre nella legge il divieto di importare carne di pollame trattata chimicamente ("pollo al cloro")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’inscrire dans la loi sur l’agriculture (LAgr) et dans la loi sur les denrées alimentaires (LDAI) une disposition explicite interdisant durablement l’importation en Suisse de viande et de produits de volaille traités chimiquement – notamment au chlore.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, im Landwirtschaftsgesetz und im Lebensmittelgesetz eine eindeutige Regelung zu verankern, die die Einfuhr von chemisch behandeltem Geflügelfleisch&amp;nbsp;– insbesondere mit Chlor&amp;nbsp;– in die Schweiz dauerhaft untersagt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Landwirtschaft|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Agriculture|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Agricoltura|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pfister Gerhard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesetzeswidrige Umsetzung von Steuerrabatten im Kanton Waadt und mögliche Auswirkungen auf den NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise en oeuvre illégale de rabais fiscaux dans le canton de Vaud et conséquences possibles sur la péréquation financière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attuazione illegale di riduzioni di imposta nel Cantone di Vaud e possibili ripercussioni sulla perequazione finanziaria nazionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Dans le cadre de la mise en œuvre non conforme à la loi de rabais fiscaux dans le canton de Vaud entre 2009 et 2021, je demande au Conseil fédéral de répondre aux questions suivantes.&lt;/p&gt;&lt;p&gt;1. A-t-il été informé des pertes injustifiées subies par la caisse de l’État du canton de Vaud&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. La Confédération a-t-elle également subi des pertes, et si oui, de quel montant&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3. La Confédération a-t-elle prévu de procéder à une enquête dans le but de déterminer si les prélèvements fiscaux systématiquement trop bas ont faussé la répartition de la perception de l’impôt dans le cadre de la péréquation financière (RPT)&amp;nbsp;?&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral est-il prêt à établir un rapport montrant quelles ont été les conséquences financières de la pratique fiscale illégale du canton de Vaud sur le calcul et le montant de la RPT et sur les éventuelles répercussions sur les contributions d’autres cantons et de la Confédération&amp;nbsp;?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In Zusammenhang mit der nicht gesetzeskonformen Umsetzung von Steuerrabatten im Kanton Waadt zwischen 2009 und 2021 bitte ich den Bundesrat um die Beantwortung folgender Fragen.&lt;/p&gt;&lt;p&gt;1. Ist der Bundesrat informiert worden über die unberechtigt erfolgten Ausfälle zulasten der Staatskasse des Kantons Waadt?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Entstanden dem Bund ebenfalls Ausfälle, wenn ja, in welcher Höhe?&lt;/p&gt;&lt;p&gt;3. Ist eine Untersuchung seitens des Bundes vorgesehen, ob die systematisch zu tiefen Steuererhebungen die Bundesmittelverteilung im NFA verzerrt haben?&lt;/p&gt;&lt;p&gt;4. Ist der Bundesrat bereit, einen Bericht zu erstellen, in dem er aufzeigt, welche finanziellen Auswirkungen die gesetzwidrige Steuerpraxis des Kantons Waadt hatte auf die Berechnung und die Höhe der Ausgleichszahlen im NFA, und ob dadurch die Beiträge anderer Kantone und des Bundes beeinflusst wurden?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrie im Jurabogen. Wie kann man dieser Region, die immer wieder von Krisen heimgesucht wird, nachhaltig helfen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrie de l'Arc jurassien. Comment venir en aide durablement à cette région régulièrement touchée par des crises successives ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settore industriale dell'arco giurassiano. Come aiutare una regione colpita da crisi ricorrenti?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;A intervalles réguliers et de plus en plus récurrents, les entreprises industrielles de l'Arc jurassien sont confrontées à des défis énormes qui pourraient à terme voir disparaître plusieurs fleurons de l'économie régionale et nationale. Nous traversons à nouveau une zone de fortes turbulences liées à un ralentissement économique marqué, accentué par la problématique des droits de douane américains. La situation est particulièrement difficile pour le secteur de la machine-outil et de l'horlogerie, mais pas seulement. Le chômage et la RHT sont au plus haut dans les cantons du Jura et de Neuchâtel. Il faut agir sans délai et, sans doute, avec des outils pas encore utilisés par&amp;nbsp;le passé.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Quelle appréciation le Conseil fédéral porte-t-il sur la situation de l'économie de l'Arc jurassien?&lt;/p&gt;&lt;p&gt;2. Est-il conscient que l'avenir de l'industrie de cette région est en grand danger?&lt;/p&gt;&lt;p&gt;3. Malgré le libre marché qui est la règle pour l'instant, a-t-il la volonté de défendre ce secteur économique important, aussi en terme de savoir faire, d'emplois et de souveraineté?&lt;/p&gt;&lt;p&gt;4. Cas échéant et au-delà de la Réduction de l'horaire de travail (RHT) comment entend il s'y prendre pour pérenniser ce secteur (garantie à l'exportation, crédits relais à fond perdu, crédits à l'innovation versés aux entreprises, aides à l'exploration de nouveaux marchés, par exemple)?&lt;/p&gt;&lt;p&gt;5. Après les difficultés rencontrées par les aciéries et maintenant l'industrie de l'économie de l'Arc jurassien, ne serait-il pas temps de réunir un groupe d'experts afin de réfléchir au bienfondé ou non de développer une véritable politique industrielle pour notre pays?&lt;/p&gt;&lt;p&gt;6. Toutes autres mesures idoines?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In regelmässigen und immer kürzeren Abständen werden die Industrieunternehmen des Jurabogens mit enormen Herausforderungen konfrontiert. Letztendlich könnten sie dazu führen, dass mehrere Flaggschiffe der regionalen und nationalen Wirtschaft von der Bildfläche verschwinden. Wir durchqueren erneut eine Zone starker Turbulenzen, die mit einem deutlichen, durch&amp;nbsp;die&amp;nbsp;Problematik&amp;nbsp;der&amp;nbsp;US-Strafzölle&amp;nbsp;verschärften Konjunkturrückgang verbunden sind. Besonders schwierig ist die Situation für die Werkzeugmaschinen- und die Uhrenindustrie, aber nicht nur für diese. Die Kantone Jura und Neuenburg sind am stärksten von Arbeitslosigkeit&amp;nbsp;und&amp;nbsp;Kurzarbeit&amp;nbsp;betroffen. Es muss unverzüglich gehandelt werden, und zwar auf jeden Fall mit Instrumenten, die in der Vergangenheit noch nicht eingesetzt wurden.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich ersuche den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Wie beurteilt der Bundesrat die Lage der Wirtschaft im Jurabogen?&lt;/p&gt;&lt;p&gt;2. Ist er sich bewusst, dass die Zukunft der Industrie in dieser Region in grosser Gefahr ist?&lt;/p&gt;&lt;p&gt;3. Ist er trotz des derzeit herrschenden freien Marktes bereit, diesen wichtigen Wirtschaftssektor zu schützen, auch im Hinblick auf Knowhow, Arbeitsplätze und Souveränität?&lt;/p&gt;&lt;p&gt;4. Wie will er gegebenenfalls und über die Kurzarbeit hinaus den Fortbestand dieses Sektors sichern (z. B. durch Exportgarantien, Überbrückungskredite, Innovationskredite für Unternehmen, Beihilfen für die Erschliessung neuer Märkte)?&lt;/p&gt;&lt;p&gt;5. Wäre es nach den Schwierigkeiten der Stahlwerke und nun der Industrie des Jurabogens nicht an der Zeit, eine Expertengruppe einzuberufen, die darüber nachdenkt, ob es nicht sinnvoll wäre, eine echte Industriepolitik für unser Land zu entwickeln?&lt;/p&gt;&lt;p&gt;6. Sonstige geeignete Massnahmen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Occupazione e lavoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bühler Manfred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macht ein Ausstieg des Bundes beim Felslabor Mont Terri zum jetzigen Zeitpunkt wirklich Sinn?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est-il vraiment opportun que la Confédération se retire maintenant du laboratoire souterrain du Mont Terri ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">È davvero sensato che la Confederazione si ritiri dal laboratorio sotterraneo del Mont Terri in questo momento?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le laboratoire souterrain du Mont Terri est une infrastructure de recherche internationalement reconnue pour le stockage géologique profond des déchets radioactifs. Il est actuellement financé par la Confédération via Swisstopo (Office fédéral de topographie) et par de nombreux autres partenaires. Pour des raisons budgétaires, la Confédération prévoit toutefois de cesser de participer à son financement. Au vu des progrès réalisés dans la procédure de sélection des sites destinés au stockage profond des déchets radioactifs et du débat actuel sur l’avenir du nucléaire en Suisse, on peut se demander s’il est judicieux que la Confédération se retire de ce financement. De plus, il est difficile de dire aujourd’hui quelles seraient les conséquences d’un tel retrait sur la poursuite des expériences et sur le respect des engagements internationaux.&lt;/p&gt;&lt;p&gt;D’où les questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;En août dernier, le Conseil fédéral a décidé de revenir sur l’interdiction de construire de nouvelles centrales nucléaires. Ne devrait-il dès lors pas accorder de l’importance à la recherche scientifique sur les déchets nucléaires, et donc au laboratoire du Mont Terri&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Un retrait unilatéral de la part de la Confédération ne serait-il pas contraire au principe selon lequel l’état doit agir de manière conforme aux règles de la bonne foi (art.&amp;nbsp;5, al. 3, Cst.)&amp;nbsp;? En effet, les partenaires et les communautés de recherche doivent pouvoir compter sur un soutien continu. Le Conseil fédéral est-il conscient des éventuelles conséquences de son retrait en termes de responsabilité civile&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Que pense-t-il de la possibilité d’assurer le financement du laboratoire via des programmes nationaux de recherche, via des ressources du Fonds national suisse destinées à la recherche fondamentale ou via Innosuisse&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Felslabor Mont Terri stellt eine international anerkannte Forschungsinfrastruktur für geologische Endlagerungen radioaktiver Abfälle dar und wird derzeit vom Bund über swisstopo (Bundesamt für Landestopografie) in Zusammenarbeit mit zahlreichen Partnern finanziert. Der Bund plant, sich wegen Spargründen aus der Finanzierung des Betriebs des Felslabors Mont Terri zurückzuziehen. Angesichts der Fortschritte im Standortwahlverfahren für ein Tiefenlager für radioaktive Abfälle und der aktuellen Debatte um die zukünftige Rolle der Kernenergie in der Schweiz stellt sich die Frage, ob ein Ausstieg des Bundes aus der Finanzierung des laufenden Betriebs sinnvoll ist. Es ist aktuell zudem unklar, welche Folgen ein solcher Rückzug für die Fortführung laufender Experimente und die Einhaltung internationaler Verpflichtungen hätte.&lt;/p&gt;&lt;p&gt;In diesem Zusammenhang bitte ich den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Im August diesen Jahres hat der Bundesrat beschlossen, das Neubauverbot für Kernkraftwerke aufheben zu wollen. Müsste er in diesem Zusammenhang nicht auch an einer konsequenten wissenschaftlichen Begleitung der nuklearen Abfälle und damit am Felslabor Mont Terri festhalten?&lt;/li&gt;&lt;li&gt;Widerspricht ein einseitiger Rückzug des Bundes aus der Finanzierung nicht den Grundsätzen von staatlichem Handeln nach Treu und Glauben (Art. 5 Abs. 3 BV), da sich Partner und Forschungsgemeinschaften auf eine kontinuierliche Unterstützung verlassen haben? Ist sich der Bundesrat allfälliger haftungsrechtlicher Konsequenzen aufgrund seines Ausstiegs bewusst?&lt;/li&gt;&lt;li&gt;Wie sieht der Bundesrat die Möglichkeit, die Finanzierung des Felslabors Mont Terri über nationale Forschungsprogramme, über die Mittel für Grundlagenforschung des Schweizerischen Nationalfonds (SNF) oder über Innosuisse zu gewährleisten?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wissenschaft und Forschung|Umwelt|Energie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Science et recherche|Environnement|Énergie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scienza e ricerca|Ambiente|Energia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regazzi Fabio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wann wird die OECD-Mindestbesteuerung so umgesetzt, dass die Schweiz attraktiv und wettbewerbsfähig bleibt?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A quand une mise en oeuvre de l'imposition minimale de l'OCDE permettant à la Suisse de rester attractive et compétitive ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando l'imposizione minima dell'OCSE sarà attuata in modo da preservare l'attrattiva e la competitività della Svizzera?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Je prie le Conseil Fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comme indiqué dans les dispositions transitoires à l’article 129a de la Constitution fédérale (imposition particulière des grands groupes d’entreprises), la Confédération «&amp;nbsp;après déduction des dépenses supplémentaires induites au titre de la péréquation financière et de la compensation des charges, affecte sa part du produit brut de l’impôt complémentaire au renforcement de la promotion de l’attrait économique de la Suisse&amp;nbsp;». Quelles mesures la Confédération a-t-elle mises sur pied jusqu’à présent&amp;nbsp;afin de renforcer l’attrait économique de la Suisse&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quel cadre ou accompagnement aux cantons la Confédération propose-t-elle, dans le respect des prérogatives des cantons en matière fiscale, afin de mettre sur pied de telles mesures de renforcement, y inclus des crédits d’impôts (non)-remboursables, comme dans les autres pays&amp;nbsp;? Quels sont les travaux en cours à ce sujet&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le secteur du transport maritime est un acteur économique important en Suisse, particulièrement dans les cantons accueillant des armateurs et des négociants en matières premières. La Confédération prévoit-elle d’exploiter, comme mentionné dans les dispositions transitoires à l’article 129a, le fait que «&amp;nbsp;les bénéfices et les pertes des activités de transport maritime international ne sont pas pris en compte&amp;nbsp;»&amp;nbsp;dans l’impôt minimal de 15% ? Alors que 21 pays de l’UE ont mis sur pied des taxations spéciales pour le transport maritime, que compte faire la Suisse pour rester compétitive ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral est-il conscient qu’en ne proposant pas de mesures de soutien à l’économie au niveau fédéral en compensation de l’imposition minimale des grandes entreprises, il existe un risque majeur qu’un substrat fiscal conséquent parte à l’étranger&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Alors que des mesures de soutien à l’économie, y inclus des crédits d’impôts (non)-remboursables, sont introduits entre autres par nos voisins européens &amp;nbsp;en mettant l’accent sur la décarbonation, la transition énergétique et le R&amp;amp;D, la Suisse reste passive. Le Conseil fédéral est-il conscient que des mesures de soutien sous forme de crédits d’impôts (non)-remboursables contribueraient à la réalisation de nos objectifs climatiques&amp;nbsp;et de transition énergétique&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;In den Übergangsbestimmungen zu Artikel&amp;nbsp;129a der Bundesverfassung&amp;nbsp;(Besondere Besteuerung grosser Unternehmensgruppen) heisst es: «Der Bund verwendet seinen Anteil am Rohertrag der Ergänzungssteuer, nach Abzug seiner durch die Ergänzungssteuer verursachten Mehrausgaben für den Finanz- und Lastenausgleich, zur zusätzlichen Förderung der Standortattraktivität der Schweiz.» Welche Massnahmen hat der Bund bisher ergriffen, um die Standortattraktivität der Schweiz zu stärken?&lt;/li&gt;&lt;li&gt;Wie unterstützt der Bund die Kantone&amp;nbsp;– unter Wahrung ihrer Steuerhoheit&amp;nbsp;– bei der Ausarbeitung entsprechender Massnahmen zur Förderung der Standortattraktivität, etwa durch (nicht)&amp;nbsp;rückzahlbare Steuergutschriften, wie sie auch in anderen Ländern vorgesehen sind? Welche Projekte sind in diesem Zusammenhang derzeit im Gange?&lt;/li&gt;&lt;li&gt;Die Seeschifffahrt ist ein bedeutender Wirtschaftsfaktor in der Schweiz, insbesondere in den Kantonen mit Reedereien und Rohstoffhändlern. Beabsichtigt der Bund die in den Übergangsbestimmungen zu Artikel&amp;nbsp;129a festgelegte Tatsache zu nutzen, dass Gewinne und Verluste aus dem internationalen Seeverkehr bei der Mindeststeuer von 15&amp;nbsp;Prozent nicht berücksichtigt werden? Bereits 21&amp;nbsp;EU-Mitgliedstaaten haben spezielle Steuern für den Seeverkehr eingeführt. Nun stellt sich die Frage, welche Massnahmen die Schweiz ergreifen will, um ihre Wettbewerbsfähigkeit zu sichern?&lt;/li&gt;&lt;li&gt;Ist sich der Bundesrat bewusst, dass ohne wirtschaftliche Ausgleichsmassnahmen auf Bundesebene zur Kompensation der Mindestbesteuerung grosser Unternehmensgruppen ein erhebliches Risiko besteht, dass wichtige Steuersubstrate ins Ausland abwandern?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Während zum Beispiel unsere europäischen Nachbarstaaten unter anderem (nicht)&amp;nbsp;rückzahlbare Steuergutschriften als wirtschaftspolitische Unterstützungsmassnahmen einführen&amp;nbsp;– mit Fokus auf die Dekarbonisierung, die Energiewende sowie Forschung und&amp;amp; Entwicklung&amp;nbsp;–, bleibt die Schweiz bislang untätig. Ist sich der Bundesrat bewusst, dass solche Unterstützungsmassnahmen in Form von (nicht)&amp;nbsp;rückzahlbaren Steuergutschriften wesentlich zur Erreichung unserer Klimaziele und zur Umsetzung der Energiewende beitragen könnten?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Verkehr|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Transports|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Trasporti|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pa. Iv.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineralölsteuer-Rückerstattung längerfristig sichern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantir à long terme le remboursement de l’impôt sur les huiles minérales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantire a lungo termine la restituzione dell'imposta sugli oli minerali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Parlement supprimera la limitation dans le temps, prévue par l’art. 218, al. 3, de la loi du 20&amp;nbsp;juin 2025 définissant les tâches de l’OFDF (LOFDF&amp;nbsp;; FF 2025 2035), du remboursement de l’impôt accordé pour les transports de voyageurs au moyen de bateaux sur des lignes faisant l’objet d’une concession de la Confédération, pour l’agriculture, pour la sylviculture, pour l’extraction de pierre de taille naturelle et pour la pêche professionnelle en vertu de l’art. 18, al. 2, de la loi sur l’imposition des huiles minérales (Limpmin) tel que modifié par la LOFDF. Si la LOFDF n’entre pas en vigueur avant le 31 décembre 2030, la limitation dans le temps du remboursement de la surtaxe sur les huiles minérales, prévue par l’art. 18, al. 2, Limpmin dans sa version du 1&lt;sup&gt;er&lt;/sup&gt; janvier 2026, sera supprimée.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die gestützt auf Artikel 218 Absatz 3 des BAZG-Vollzugsaufgabengesetzes vom 20. Juni 2025 (BAZG-VG; BBl 2025 2035) erfolgte Befristung der Steuerrückerstattungen für Fahrten mit Schiffen auf dem vom Bund konzessionierten Linien zum Zweck der Personenbeförderung, Landwirtschaft, Forstwirtschaft, Naturwerkstein-Abbau und Berufsfischerei nach Artikel 18 Absatz 2 des mit dem BAZG-VG geänderten Mineralölsteuergesetzes (MinöStG) sei aufzuheben. Sollte das BAZG-VG bis zum Ende der Befristung (31. Dezember 2030) noch nicht in Kraft getreten sein, soll die Befristung der Rückerstattung des Mineralölsteuerzuschlags nach Artikel 18 Absatz 2 des MinöStG in der Fassung vom 1. Januar 2026 aufzuheben.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorprüfung - in Kommission des Nationalrates / Examen préalable - en commission du Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehr|Umwelt|Energie|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports|Environnement|Énergie|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti|Ambiente|Energia|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farinelli Alex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umsetzung der verfügbaren Massnahmen zur Regulierung der Wolfspopulation in der Schweiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise en oeuvre des mesures disponibles pour réguler la population de loups en Suisse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attuazione delle misure disponibili per la regolazione della popolazione di lupi in Svizzera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre toutes les mesures disponibles, et si nécessaire d’assouplir davantage les critères existants, afin de réguler la population des loups en Suisse en réduisant le nombre de loups et de meutes jusqu’à un niveau le plus proche possible du minimum défini par le Plan de gestion du loup en Suisse, soit 12&amp;nbsp;meutes réparties selon les critères géographiques définis.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, alle zur Verfügung stehenden Massnahmen zu ergreifen und gegebenenfalls die bestehenden Kriterien weiter zu lockern, um die Wolfspopulation in der Schweiz zu regulieren. Die Anzahl der Rudel und Einzeltiere soll so weit wie möglich auf die im Konzept Wolf Schweiz festgelegte Mindestanzahl reduziert werden, sprich zwölf Rudel verteilt auf die definierten Wolfsregionen der Schweiz.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umwelt|Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environnement|Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambiente|Agricoltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gugger Niklaus-Samuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuerdebakel Waadt: Finanzausgleich betroffen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Débâcle fiscale vaudoise. Conséquences sur la péréquation financière ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Des rapports datant du printemps critiquent le calcul erroné de l’impôt sur la fortune dans le canton de Vaud qui a engendré une perte pouvant se chiffrer en millions de francs. Le canton de Vaud bénéficiant de la péréquation financière nationale, les erreurs pourraient avoir des répercussions sur les autres cantons et la Confédération.&lt;br&gt;- Est-ce que le Conseil fédéral partage cette analyse&amp;nbsp;?&lt;br&gt;- Les paiements compensatoires déjà effectués peuvent-ils être corrigés&amp;nbsp;?&lt;br&gt;- Quelles mesures entend prendre le Conseil fédéral pour éviter, à l’avenir, de telles erreurs&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Berichte aus dem Frühjahr kritisieren die fehlerhafte Vermögenssteuerberechnung im Kanton Waadt, die ihm mutmasslich mehrere Millionen Franken kostete. Da Waadt Nehmerkanton im nationalen Finanzausgleich ist, könnten die Fehler auch andere Kantone und den Bund betreffen.&lt;br&gt;- Teilt der Bundesrat diese Einschätzung?&lt;br&gt;- Können bereits geleistete Ausgleichszahlungen korrigiert werden?&lt;br&gt;- Welche Massnahmen plant er, um solche Fehler künftig zu verhindern?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roth Pasquier Marie-France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welche Folgen haben die US-Zölle für die Regionen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quels sont les effets des droits de douane américains sur les régions ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les droits de douane américains ont des effets variables selon les régions et les branches. De nombreuses industries (p.ex. horlogerie, agroalimentaire, chimie, métallurgie, machines, technologie de précision) sont particulièrement touchées. Les chiffres agrégés de la Confédération ne reflètent pas les réalités régionales et la RHT n’est pas une solution durable.&lt;br&gt;- Le Conseil fédéral dispose t'il de données plus précises par régions?&lt;br&gt;- Envisage-t-il des mesures pour soutenir ces branches et régions?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Folgen der US-Zölle variieren je nach Region und Branche. Zahlreiche Industriezweige&amp;nbsp;– etwa die Uhren- und Lebensmittelindustrie, die Chemie-, Metall- und Maschinenbaubranche sowie die Präzisionstechnik&amp;nbsp;– sind besonders stark betroffen. Die aggregierten Zahlen des Bundes spiegeln nicht die regionalen Gegebenheiten wider, und Kurzarbeit ist keine nachhaltige Lösung.&lt;br&gt;- Verfügt der Bundesrat über differenziertere Daten nach Regionen?&amp;nbsp;&lt;br&gt;- Zieht der Bundesrat Massnahmen in Betracht, um die betroffenen Branchen und Regionen zu unterstützen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Wirtschaft|Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Économie|Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Economia|Finanze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weigert sich der Kanton Jura, für die Seniorinnen und Senioren aus Moutier zu zahlen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Jura refuse-t-il de payer pour les aînés de Moutier ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Selon les indications de directions d'EMS bernois qui hébergent des pensionnaires de Moutier au 31.12.2025, il semble que le canton du Jura refuse de prendre en charge les montants qui doivent être financés par les cantons dès le 1.1.2026.&lt;br&gt;- Si tel est le cas, qui devra prendre en charge ces montants ?&lt;br&gt;- La Confédération est-elle impliquée dans ces discussions entre les cantons de Berne et du Jura ?&lt;br&gt;- Si oui, quel est son avis ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Nach Angaben der Heimleitungen gewisser Berner Alters- und Pflegeheime, in denen am 31. Dezember 2025 noch Personen aus Moutier untergebracht sein werden, zeichnet sich ab, dass der Kanton Jura die Übernahme der kantonal zu tragenden Kosten ablehnen wird, die er ab dem 1. Januar 2026 übernehmen müsste.&lt;br&gt;- Wenn dies der Fall ist, wer muss dann diese Kosten übernehmen?&lt;br&gt;- Ist der Bund in diese Diskussionen zwischen den Kantonen Bern und Jura involviert?&lt;br&gt;- Wenn ja, was ist die Haltung des Bundes?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Soziale Fragen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Questions sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pahud Yvan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schliessung Hôtel du Chasseron. Was schlägt Armasuisse vor, um den Tourismus in der Region Sainte-Croix/Les Rasses zu erhalten?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Décision de fermeture de l'Hôtel du Chasseron. Quelle solution propose Armasuisse pour ne pas prétériter le tourisme dans la région de Sainte-Croix/Les Rasses ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisione di chiudere l'Hôtel du Chasseron. Quale soluzione propone armasuisse per non pregiudicare il turismo nella regione di Sainte-Croix/Les Rasses?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le 25 juin dernier, le CN Pahud et le CE Broulis ont reçus un courrier du tenancier de l’hôtel du Chasseron pour les informer de la fermeture de l’hôtel au 28 septembre.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Pour la région du Balcon du Jura, et des Communes de Sainte-Croix et Bullet, l’hôtel du Chasseron est le pilier central du développement touristique 4 saisons avec une ouverture hiver, comme été.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Cette fermeture s’ajoute à celle de l’hôtel restaurant des Rochats, également propriété de la confédération, et qui prétérite l’accueil sur un sentier prioritaire qu’est le chemin des Crêtes du Jura N°5.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;En plus de l’aspect touristique,&amp;nbsp; et vu la situation géopolitique mondiale et les défis à laquelle la Suisse est confronté en matière de sécurité,&amp;nbsp; l’hôtel du Chasseron, revêt également un aspect stratégique, comme site militaire, situé sur les contreforts de la frontière nationale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Malgré les nombreux courriels adressés à Armasuisse par votre serviteur, ces dernier ont confirmés&amp;nbsp;: «&amp;nbsp;armasuisse ne relouera donc pas l’Hôtel du Chasseron à partir de l’automne 2025, et ce jusqu’à nouvel ordre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;C’est un coup dur pour toute une région qui se bat pour maintenir et développer le tourisme.&lt;/p&gt;&lt;p&gt;Ceci sans compter, que dans l’attente d’une solution, Armasuisse se prive d’un loyer, ce qui péjore les finances de la Confédération.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le manque de considération d’Armasuisse, et la non-entrée en matière afin de garder cet établissement ouvert dans l’attente d’une solution possible avec la ou les Communes concernées est également à relever.&lt;/p&gt;&lt;p&gt;Question&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Pourquoi Armasuisse n’a-t-il pas informé et pris immédiatement contact avec les Communes concernées dès la résiliation du bail et surtout dès la décision de fermeture de l’hôtel&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles solutions urgentes Armasuisse a proposé et surtout propose afin que l’établissement soit ouvert pour la saison hivernale 2025-2026&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Un tenancier peut-il être trouvé au plus vite, avec un bail à loyer provisoire, dans l’attente d’une solution à long terme&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue financier, l’Hôtel étant fermé dès le 30 septembre prochain, et donc non loué, comment le CF juge-t-il cette perte de rentrée financière&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 25.&amp;nbsp;Juni 2025 informierte der Pächter des Hôtel du Chasseron Nationalrat Yvan Pahud und Ständrat Pascal Broulis schriftlich über die bevorstehende Schliessung des Hotels per 28.&amp;nbsp;September 2025.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Hôtel du Chasseron ist im Sommer und im Winter geöffnet und bildet somit das Herzstück des Ganzjahrestourismus für den Jurabalkon sowie die Gemeinden Sainte-Croix und Bullet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Auch das Restaurant Les Rochats ‒ ebenfalls im Besitz des Bundes ‒ wird geschlossen, womit ein gastfreundliches Haus am wichtigen Jura-Höhenweg Nr.&amp;nbsp;5 verloren geht.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Hôtel du Chasseron ist nicht nur für den Tourismus zentral. Angesichts der geopolitischen Weltlage und der Herausforderungen für die Schweiz bei der Sicherheit ist es ein strategisch wichtiger Militärstandort nahe der Landesgrenze.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Als Antwort auf meine zahlreichen E-Mails bestätigte Armasuisse, das Hôtel du Chasseron ab Herbst&amp;nbsp;2025 bis auf Weiteres nicht mehr zu verpachten.&lt;/p&gt;&lt;p&gt;Dies ist ein harter Schlag für die Region, die sich stark dafür einsetzt, den Tourismus zu erhalten und zu fördern.&lt;/p&gt;&lt;p&gt;Ganz abgesehen davon, dass Armasuisse in der Zwischenzeit keine Pachteinnahmen hat, was die Finanzen des Bundes belastet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Armasuisse zeigte sich nicht gesprächsbereit und hat es abgelehnt, das Hotel bis zu einer möglichen Lösung mit einer oder mehreren betroffenen Gemeinden weiterzubetreiben.&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Warum hat Armasuisse nach der Kündigung des Pachtvertrags und vor allem nach dem Entscheid zur Hotelschliessung die betroffenen Gemeinden nicht unverzüglich informiert und das Gespräch mit ihnen gesucht?&lt;/li&gt;&lt;li&gt;Welche Sofortmassnahmen hat Armasuisse vorgeschlagen und gedenkt Armasuisse zu ergreifen, damit das Hotel in der Wintersaison 2025–2026 wiedereröffnet werden kann?&lt;/li&gt;&lt;li&gt;Lässt sich mit einem temporären Pachtvertrag kurzfristig eine Pächterin oder ein Pächter finden, bis es eine langfristige Lösung gibt?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Einnahmeverlust aufgrund der Hotelschliessung und des auslaufenden Pachtvertrags ab dem 30.&amp;nbsp;September 2025 aus finanzieller Sicht?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Économie|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Economia|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schliessung des Hôtel du Chasseron: Was plant armasuisse, damit der Tourismus in der Region Sainte-Croix/Les Rasses trotzdem erhalten bleibt?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Décision de fermeture de l’Hôtel du Chasseron, quelle solution Armasuisse propose pour ne pas prétériter le tourisme dans la région de Sainte-Croix/Les Rasses ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Pour la région du Balcon du Jura vaudois, l’hôtel du Chasseron est le pilier central du développement touristique 4 saisons.&lt;br&gt;La décision de fermeture par Armasuisse au 30 septembre est incompréhensible.&lt;br&gt;- Quelles solutions urgentes Armasuisse propose afin que l’établissement puisse être réouvert au plus vite&amp;nbsp;?&lt;br&gt;- Un tenancier peut-il être trouvé au plus vite, avec un bail à loyer provisoire, dans l’attente d’une solution à long terme avec les Communes&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Hôtel du Chasseron ist der Dreh- und Angelpunkt für die ganzjährige Tourismusentwicklung in der Region des Waadtländer Jurabalkons.&lt;br&gt;Der Beschluss von armasuisse, das Hotel per 30. September zu schliessen, ist unbegreiflich.&lt;br&gt;- Welche Sofortmassnahmen schlägt armasuisse vor, damit das Hotel so schnell wie möglich wiedereröffnet werden kann?&lt;br&gt;- Lässt sich mit einem temporären Mietvertrag kurzfristig eine Wirtin oder ein Wirt gewinnen, bis eine langfristige Lösung mit den Gemeinden gefunden wird?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20257581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Économie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Economia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kt. Iv.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basel-Landschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massnahmen zur Aufwertung der beiden ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (volles Ständerecht)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconnaissance de l'entier des droits politiques aux deux anciens demi-cantons de Bâle-Ville et de Bâle-Campagne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misure finalizzate a rendere i due ex Semicantoni di Basilea Città e Basilea Campagna Cantoni a pieno titolo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le 28&amp;nbsp;août&amp;nbsp;2025, le parlement du canton de Bâle-Campagne a décidé à l’unanimité, conformément à l’art.&amp;nbsp;160, al.&amp;nbsp;1, de la Constitution fédérale (Cst.), de déposer une initiative pour que soient reconnus l’entier des droits politiques aux deux anciens demi-cantons de Bâle-Ville et de Bâle-Campagne.&lt;/p&gt;&lt;p&gt;L’Assemblée fédérale et le Conseil fédéral sont priés de prendre les mesures nécessaires pour que, sous l’angle du principe d’égalité des droits qui doit prévaloir entre États membres de la Confédération, les anciens demi-cantons de Bâle-Ville et de Bâle-Campagne (ainsi que, en principe, les autres anciens demi-cantons) soient mis sur un pied d’égalité avec les autres cantons en ce qui concerne le nombre de sièges et de voix au Conseil des États (faire des deux Bâle des cantons à part entière, modification des art.&amp;nbsp;150, al.&amp;nbsp;1 et al.&amp;nbsp;2, et art.&amp;nbsp;142, al.&amp;nbsp;4, Cst).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 28. August 2025 hat der Landrat des Kantons Basel-Landschaft einstimmig beschlossen, gestützt auf Artikel 160 Absatz 1 der Bundesverfassung eine Standesinitiative hinsichtlich der Ergreifung von Massnahmen zur Aufwertung der beiden ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (Volles Ständerecht) einzureichen.&lt;/p&gt;&lt;p&gt;Das Bundesparlament und der Bundesrat werden gebeten, die notwendigen Schritte zu unternehmen, damit unter dem Aspekt des Gebots der bundesstaatlichen Rechtsgleichheit die ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft (und grundsätzlich auch die weiteren ehemaligen Halbkantone) den übrigen Kantonen im Hinblick auf die Vertretung im Ständerat und der Standesstimmen gleichgestellt werden (Aufwertung als Kantone mit vollem Ständerecht, Änderung von Art. 150 Abs. 1 und Abs. 2 sowie Art. 142 Abs. 4 der Bundesverfassung).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piller Carrard Valérie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sperrung der Strecke Freiburg–Bern im Sommer. Ein Rückschlag für die Verkehrsverlagerung?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fermeture estivale de la ligne Fribourg-Berne. Un coup d'arrêt au transfert modal ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiusura estiva della linea Friburgo-Berna. Una battuta d'arresto al trasferimento modale?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La fermeture totale de la ligne ferroviaire Fribourg-Berne pendant plus de deux mois cet été va poser de grands problèmes dans le canton de Fribourg, premier canton pendulaire de Suisse. Fortement tributaires de leurs connexions ferroviaires, en particulier vers Berne et la Suisse alémanique, les pendulaires fribourgeois s’inquiètent de l’allongement de leur temps de trajet, des conditions de voyage dans des bus qui seront certainement bondés, et de l’interdiction de transporter son vélo. En pleine période estivale qui plus est de l’Euro de football féminin, cette fermeture totale de ligne est aussi particulièrement défavorable au tourisme, avec pour conséquence un probable manque à gagner pour l'économie locale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Enfin, cette décision comporte le risque réel de favoriser les déplacements en voiture individuelle, et que les pendulaires questionnent leur volonté d’utiliser les transports publics, également à plus long terme.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans ce contexte, le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Les CFF ont-ils envisagé des alternatives moins contraignantes que cette fermeture totale de ligne entre Fribourg et Berne, par exemple une fermeture limitée à une seule voie&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Le Conseil fédéral a-t-il conscience que cette ligne joue le rôle d’épine dorsale de la Suisse, qu’elle est donc indispensable pour connecter la Suisse romande et la Suisse alémanique, et que les CFF ne peuvent pas simplement fermer la ligne avec l’excuse que des bus sont à disposition&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3) Cette fermeture aura certainement un effet sur le report de trafic sur la route, une évaluation au niveau de ce report dans les différentes communes vaudoises, fribourgeoises et bernoises est-elle envisagée&amp;nbsp;?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Après l’énorme couac de la gare de Lausanne et tous les désagréments qui en découlent pour les usagers des CFF, cette fermeture de ligne pure et simple donne une fois de plus aux habitant-e-s de la Suisse romande l’impression qu’ils sont considérés comme quantité négligeable. Que répond le Conseil fédéral&amp;nbsp;?&lt;/p&gt;&lt;p&gt;5) Dans un contexte de renchérissement des billets de transport et de trains toujours plus bondés, une fermeture totale de ligne risque d’encourager la population à utiliser des véhicules individuels. Quel est l’avis du Conseil fédéral à ce sujet&amp;nbsp;?&lt;/p&gt;&lt;p&gt;6) Au vue de la quantité de désagréments, est-ce que le Conseil fédéral envisage de dédommager financièrement les usagers de la ligne&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Totalsperre der Bahnstrecke Freiburg–Bern für mehr als zwei Monate in diesem Sommer wird im Kanton Freiburg, dem grössten Pendlerkanton der Schweiz, zu grossen Problemen führen. Die Pendlerinnen und Pendler aus dem Kanton Freiburg sind stark auf ihre Zugverbindungen angewiesen, insbesondere nach Bern und in die Deutschschweiz. Sie fürchten die längeren Reisezeiten, die Bedingungen in den mit Sicherheit überfüllten Bussen und das Verbot, ihr Velo zu transportieren. Mitten in der Sommersaison und während der Fussball-Europameisterschaft der Frauen ist die Totalsperre der erwähnten Strecke auch für den Tourismus von grossem Nachteil; sie führt wahrscheinlich zu Einnahmeausfällen für die lokale Wirtschaft.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Schliesslich birgt der Entscheid der Sperrung das grosse Risiko, dass Pendlerinnen und Pendler auf das Privatauto umsteigen und auch längerfristig die Benutzung öffentlicher Verkehrsmittel in Frage stellen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Hat die SBB weniger einschneidende Alternativen zur Totalsperre der Strecke Freiburg–Bern in Betracht gezogen, z.&amp;nbsp;B. eine auf ein Gleis beschränkte Sperre?&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Ist sich der Bundesrat bewusst, dass die erwähnte Strecke quasi als Rückgrat der Schweiz für die Verbindung zwischen West- und Deutschschweiz unentbehrlich ist und die SBB diese nicht einfach mit dem Verweis auf Ersatzbusse sperren kann?&lt;/p&gt;&lt;p&gt;3) Die Sperrung wird sicherlich eine Verkehrsverlagerung auf die Strasse zur Folge haben. Wird in den verschiedenen Gemeinden der Kantone Waadt, Freiburg und Bern eine Bewertung dieser Verlagerung in Betracht gezogen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Nach dem Debakel rund um den Umbau des Bahnhofs Lausanne und allen damit verbundenen Unannehmlichkeiten für die SBB-Reisenden fühlen sich die Westschweizerinnen und Westschweizer durch diese kompromisslose Sperrung einmal mehr als vernachlässigte Minderheit. Was sagt der Bundesrat dazu?&lt;/p&gt;&lt;p&gt;5) Vor dem Hintergrund steigender Tarife und zunehmend überfüllter Züge könnte eine vollständige Streckensperrung die Bevölkerung zur Nutzung von Privatautos verleiten. Wie schätzt der Bundesrat die Lage ein?&lt;/p&gt;&lt;p&gt;6) Zieht der Bundesrat angesichts der vielen Unannehmlichkeiten eine finanzielle Entschädigung für die Nutzerinnen und Nutzer der erwähnten Strecke in Betracht?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Trasporti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roth David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konzessionsentscheid zugunsten von Canal B. Fragen zur Unabhängigkeit, Transparenz und medienpolitischen Zielsetzung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concession accordée à Canal B. Questions sur l'indépendance, la transparence et les objectifs de politique médiatique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisione relativa alla concessione in favore di Canal B. Domande concernenti indipendenza, trasparenza e obiettivi in materia di politica dei media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le 27 mai 2025, le DETEC a attribué la concession TV régionale pour la région Bienne-Seeland-Jura bernois non pas à l'ancien prestataire TeleBielingue, mais à Canal B, nouvelle chaîne régionale. Cette décision a provoqué un tollé politico-médiatique dans la région et au-delà.&lt;/p&gt;&lt;p&gt;TeleBielingue est une chaîne bilingue qui s'est développée au fil des décennies et dont les qualités journalistiques sont largement reconnues, tant en Suisse alémanique qu'en Suisse romande. Canal B, quant à elle, est une chaîne d’obédience évangélique qui n’a pas fait preuve, à ce jour, de compétences équivalentes. Elle est étroitement liée au réseau de médias chrétiens ERF Medien, dont l’orientation semble contraire au principe d'une information ouverte, indépendante de l'État et neutre sur le plan idéologique.&lt;/p&gt;&lt;p&gt;Les médias ont par ailleurs révélé que le secrétaire général du DETEC avait des liens étroits avec les milieux évangéliques et qu’il était membre d'une église libre, ce qui soulève des questions sur l'indépendance institutionnelle et la transparence politique de la procédure de concession.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quels sont les critères concrets relatifs aux contenus et aux aspects techniques et structurels qui ont conduit à l’attribution de la concession à la chaîne Canal B ? Comment ont-ils été évalués au regard des prestations fournies par TeleBielingue ?&lt;/li&gt;&lt;li&gt;Que pense le Conseil fédéral de la compatibilité d'un projet médiatique d'inspiration évangélique avec les exigences légales en matière de diversité, de séparation de l'Église et de l'État et d’indépendance des médias ?&lt;/li&gt;&lt;li&gt;Quelles dispositions le DETEC a-t-il prises pour exclure tout conflit d'intérêts lié aux convictions religieuses personnelles des décideurs ?&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral s'assure-t-il que les décisions en matière de politique des médias ne sont pas prises en fonction de la proximité idéologique ou religieuse, mais sur la base de critères objectifs de qualité et de performance ?&lt;/li&gt;&lt;li&gt;Comment évalue-t-il le risque que de telles décisions sapent la confiance placée dans le système de concession des télévisions régionales ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 27. Mai 2025 hat das UVEK die regionale TV-Konzession für die Region Biel-Seeland-Jura bernois nicht an den bisherigen Anbieter TeleBielingue, sondern an das neue Projekt Canal B vergeben. Diese Entscheidung hat in der Region und darüber hinaus für grosse medienpolitische Irritation gesorgt.&lt;/p&gt;&lt;p&gt;TeleBielingue ist ein über Jahrzehnte gewachsener, zweisprachiger Sender mit einem etablierten publizistischen Leistungsausweis, der sowohl in der Deutschschweiz als auch in der Romandie breite Anerkennung geniesst. Der Zuschlag an Canal B geht hingegen an ein Projekt mit klar evangelikaler Prägung, das bisher keinerlei vergleichbare publizistische Leistungen nachgewiesen hat. Canal B ist eng mit dem christlichen Mediennetzwerk ERF Medien verbunden, dessen inhaltliche Ausrichtung dem Prinzip einer offenen, staatsunabhängigen und weltanschaulich neutralen Berichterstattung zuwiderzulaufen scheint.&lt;/p&gt;&lt;p&gt;Zudem wurde öffentlich bekannt, dass der Generalsekretär des UVEK über enge Verbindungen zu evangelikalen Kreisen verfügt und Mitglied einer Freikirche ist, was Fragen zur institutionellen Unabhängigkeit und zur politischen Transparenz des Konzessionsverfahrens aufwirft.&lt;/p&gt;&lt;p&gt;In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche konkreten inhaltlichen, technischen und strukturellen Kriterien haben zum Entscheid für Canal B geführt und wie wurden diese gegenüber dem Leistungsnachweis von TeleBielingue gewichtet?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat die Vereinbarkeit eines evangelikal geprägten Medienprojekts mit den gesetzlichen Anforderungen an publizistische Vielfalt, Trennung von Kirche und Staat sowie an staatsunabhängige Medien?&lt;/li&gt;&lt;li&gt;Welche Vorkehrungen hat das UVEK getroffen, um Interessenkonflikte im Zusammenhang mit persönlichen religiösen Überzeugungen von Entscheidungsträgern auszuschliessen?&lt;/li&gt;&lt;li&gt;Wie stellt der Bundesrat sicher, dass medienpolitische Entscheide nicht aufgrund ideologischer oder religiöser Nähe, sondern aufgrund objektiver Qualitäts- und Leistungskriterien erfolgen?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat die Gefahr, dass mit solchen Entscheiden das Vertrauen in das konzessionsgestützte System für Regionalfernsehen untergraben wird?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation|Kultur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Médias et communication|Culture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Media e comunicazione|Cultura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bally Maya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prüfung einer einheitlichen Referenzgrösse für Vermögenssteuerwerte bei Eigenheimen für den NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Référence uniforme pour le calcul de la valeur fiscale des logements en propriété dans le cadre de la RPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esame di un parametro uniforme di riferimento per definire il valore delle proprietà abitative ai fini dell’imposta sulla sostanza nell’ambito della NPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’examiner, en vue du prochain rapport sur l’efficacité de la RPT, l’adoption d’une valeur de référence uniforme pour le calcul de la valeur fiscale des logements en propriété (par ex. valeur de répartition), de proposer des mesures et de présenter un rapport. Il s’agit d’analyser la situation actuelle et de proposer des solutions pour éliminer les effets négatifs dus aujourd’hui aux méthodes d’estimation très différentes que les cantons appliquent. &amp;nbsp;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt anlässlich des nächsten Wirkungsberichts NFA die Einführung einer einheitlichen Referenzgrösse für Vermögenssteuerwerte bei Eigenheimen (z.B.Repartitionswert) zu prüfen, entsprechenden Massnahmen vorzuschlagen und Bericht zu erstatten. Die aktuelle Situation soll analysiert und mögliche Lösungen zur Beseitigung der heutigen negativen Auswirkungen aufgrund der sehr unterschiedlichen Schätzungsmethoden in den Kantonen aufgezeigt werden. &amp;nbsp;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Nationalrat geplant / Planifié au Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Steuer|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Fiscalité|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Imposte|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftauende Alpentäler und sich erhitzende Städte: Der Finanzausgleich muss die Folgen der Klimaerhitzung berücksichtigen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vallées alpines en dégel et villes en surchauffe. La péréquation financière doit prendre en considération les conséquences du réchauffement climatique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valli alpine in scioglimento e città sempre più roventi: la perequazione finanziaria deve tenere conto delle conseguenze del riscaldamento climatico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que la compensation des charges dues à des facteurs géo-topographiques tienne désormais également compte de la gestion des conséquences du réchauffement climatique. Il garantira que les ressources supplémentaires nécessaires ne seront pas déduites des autres paiements compensatoires prévus dans le cadre de la péréquation financière nationale (notamment des paiements de la Confédération au titre de la péréquation des ressources ou des montants versés pour compenser les charges dues à des facteurs socio-démographiques ou géo-topographiques), mais seront inscrites en sus au budget.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt die gesetzlichen Grundlagen anzupassen, damit der geographisch-topographische Lastenausgleich zukünftig explizit auch auf die Bewältigung der Folgen der Klimaerhitzung ausgerichtet wird. Der Bundesrat stellt sicher, dass die zusätzlich notwendigen Mittel nicht zulasten der übrigen Ausgleichszahlungen im Rahmen des Nationalen Finanzausgleichs (insbesondere der existierenden Beiträge des Bundes an den Ressourcenausgleich sowie den sozio-demographischen und den geographisch-topographischen Lastenausgleich) gehen, sondern zusätzlich eingestellt werden.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crottaz Brigitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missbrauch von codeinhaltigen Sirupen (Purple Drank). Handeln, bevor das Phänomen um sich greift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usage détourné de sirops à base de codéine (Purple Drank). Agir avant que le phénomène ne s'amplifie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uso improprio di sciroppi a base di codeina ("purple drank"). Agire prima che il fenomeno si intensifichi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;En réponse à ma question 25.7511, le CF répond qu’il n’a pas connaissance du mésusage de certains médicaments contenant des substances addictives.&lt;br&gt;Pourtant, depuis plus de 10 ans, professionnels de santé et autorités de certains cantons observent &amp;nbsp;la consommation détournée de sirops antitussifs à base de codéine. Le phénomène du &lt;i&gt;Purple Drank &lt;/i&gt;— mélange de sirop, soda, antihistaminiques et parfois alcool ou cannabis — n’est plus marginal et touche des adolescents de plus en plus jeunes avec des risques avérés de dépendance, de déscolarisation, de troubles cognitifs, voire d’overdose.&lt;br&gt;La situation devient préoccupante : à Genève, les autorités sanitaires ont lancé un programme de sevrage dédié car l’utilisation massive de sirops codéinés dans un but non thérapeutique constitue un véritable problème de santé publique.&lt;br&gt;Si la révision de la Loi sur les produits thérapeutiques en 2019 a permis un meilleur encadrement, son application reste inégale. Même si le devoir d’annonce prévu dans la LStup est généralement respecté, le canton ne peut s’opposer au traitement off label prescrit, même s’il estime qu’il est abusif ou pourrait alimenter un marché noir.&amp;nbsp;&lt;br&gt;Concernant les traitements de substitution de la dépendance à l’héroïne, le régime d’autorisation cantonal est bien établi et harmonisé. Ce n’est pas le cas pour la prescription de la codéine dans le cas d’une dépendance, où les critères ne sont pas définis et les pratiques cantonales hétérogènes. Ces prescriptions sont donc difficilement contrôlables et des patients encourent le risque d’être exposés à des traitements inadaptés.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In seiner Antwort auf meine Frage 25.7511 erklärte der Bundesrat, er habe keine Kenntnis von missbräuchlicher Verwendung gewisser Medikamente, die süchtig machende Substanzen enthalten.&lt;br&gt;Dabei beobachten Gesundheitsfachleute wie auch Behörden in gewissen Kantonen seit mehr als zehn Jahren, dass codeinhaltige Hustensirupe missbräuchlich eingenommen werden. Das Phänomen &lt;i&gt;Purple Drank&lt;/i&gt; – eine Mischung aus Sirup, Limonade, Antihistaminika und zuweilen auch Alkohol oder Cannabis – ist keine Randerscheinung mehr, sondern betrifft immer jüngere Jugendliche. Die Risiken des Konsums solcher Getränke sind erwiesen und reichen von Abhängigkeit über Schulabbruch und kognitive Beeinträchtigungen bis hin zur Überdosis.&lt;br&gt;Das Phänomen nimmt besorgniserregende Ausmasse an: In Genf haben die Gesundheitsbehörden ein spezifisches Entzugsprogramm eingerichtet, denn die Einnahme grosser Mengen codeinhaltiger Sirupe ist ein ernsthaftes Problem für die öffentliche Gesundheit.&lt;br&gt;Mit der Revision des Heilmittelgesetzes im Jahr&amp;nbsp;2019 wurden griffigere Bestimmungen eingeführt, aber der Gesetzesvollzug ist uneinheitlich. Zwar wird die Meldepflicht gemäss Betäubungsmittelgesetz in der Regel eingehalten, aber der Kanton kann nicht gegen eine verordnete Off-Label-Behandlung vorgehen, selbst wenn er zur Einschätzung gelangt, dass diese missbräuchlich ist oder den Schwarzmarkt versorgen könnte.&amp;nbsp;&lt;br&gt;Bei Substitutionsbehandlungen von Heroinabhängigen ist die kantonale Bewilligungspraxis gut verankert und harmonisiert. Anders sieht es bei der Verschreibung von Codein aus, wenn eine Abhängigkeit vorliegt, denn die Kriterien dafür wurden nicht definiert und die kantonalen Praktiken sind uneinheitlich. Solche Verschreibungen lassen sich nur schwer kontrollieren, und für die Patientinnen und Patienten besteht die Gefahr von Fehlbehandlungen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaillard Benoît</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fahrplan 2025 Westschweiz. Zwischenbilanz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nouvel horaire CFF 2025. Bilan intermédiaire pour la Suisse romande</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilancio intermedio dell'orario 2025 della Svizzera occidentale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;ol&gt;&lt;li&gt;Il semblerait que le nouvel horaire&amp;nbsp;2025 pour la Suisse romande donne lieu à des coûts d’exploitation plus élevés que l’horaire précédent, notamment en raison du personnel et du matériel roulant. Le Conseil fédéral peut-il communiquer un chiffre à ce sujet&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelle augmentation du nombre de voyageurs-kilomètres le nouvel horaire a-t-il permis d’enregistrer jusqu’à présent sur l’ensemble du réseau de la Suisse romande par rapport à l’horaire précédent&amp;nbsp;? Quelle est l’évolution, à la hausse ou à la baisse, notamment pour les différentes liaisons grandes lignes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Dans quelle mesure la part de passagers arrivant à l’heure a-t-elle été augmentée grâce à l’horaire&amp;nbsp;2025&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles sont les conséquences financières de cet horaire sur le compte de résultats des CFF&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les correspondances avec changement de quai à Renens posent particulièrement problème pour les liaisons entre Genève et la ligne du pied du Jura. N’est-il pas possible de garantir que les changements se fassent systématiquement sur le même quai avant la date de 2030 annoncée par les CFF&amp;nbsp;? Cette situation est-elle acceptable pour le Conseil fédéral&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Sous la pression des cantons romands ainsi que des régions et des villes concernées, six liaisons directes quotidiennes ont été introduites sur la ligne&amp;nbsp;IC5. Sont-elles garanties pour les prochaines années&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;ol&gt;&lt;li&gt;Es heisst, der Fahrplan 2025 Westschweiz sei teurer zu betreiben als der frühere Fahrplan, beispielsweise aufgrund höherer Kosten für Personal und Rollmaterial. Kann der Bundesrat eine Zahl kommunizieren?&lt;/li&gt;&lt;li&gt;Welche Zunahme an Personenkilometern wurde bis jetzt auf dem Gesamtnetz Westschweiz erzielt im Vergleich mit dem vorigen Fahrplan? Wie ist die allfällige Zu- oder Abnahme insbesondere bei den einzelnen Fernverkehrsverbindungen?&lt;/li&gt;&lt;li&gt;Wie stark wurde dank dem Fahrplan 2025 der Anteil der pünktlich ankommenden Fahrgäste verbessert?&lt;/li&gt;&lt;li&gt;Was sind die finanziellen Auswirkungen des Fahrplans 2025 auf die Ertragsrechnung der SBB?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Besonders problematisch sind die Anschlüss mit Perronwechsel in Renens für Verbindungen zwischen Genf und der Jurafusslinie. Ist ein systematisches Umsteigen auf dem gleichen Perron nicht vor dem von der SBB angekündigten Datum 2030 möglich? Ist diese Situation für den Bundesrat hinnehmbar?&lt;/li&gt;&lt;li&gt;Auf Druck der Westschweizer Kantone und der betroffenen Regionen und Städte wurden 6 direkte tägliche Verbindungen auf der IC5 Linie eingeführt. Sind sie für die nächsten Jahre auch definitiv abgesichert?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDP-Liberale Fraktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überprüfung und allfällige Ergänzung der gesetzlichen Grundlagen für eine rasche Katastrophenhilfe des Bundes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aide rapide de la Confédération en cas de catastrophe. Examiner les bases légales en la matière et les compléter en cas de besoin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificare ed eventualmente completare le basi legali per un rapido aiuto in caso di catastrofe da parte della Confederazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter dans un rapport non seulement les dispositions légales qui régissent la fourniture d’une aide nationale rapide en cas de catastrophe, mais aussi, si nécessaire, celles qui doivent venir les compléter. Le rapport exposera les conditions, les compétences et les procédures existantes ou à mettre en place pour garantir la fourniture de prestations de soutien de nature financière et organisationnelle par la Confédération si une catastrophe naturelle ou un autre événement dommageable de grande ampleur survenait.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ce rapport devra en particulier :&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;préciser les conditions à remplir pour qu’une aide d’urgence soit fournie ;&lt;/li&gt;&lt;li&gt;clarifier le rôle de la Confédération vis-à-vis des cantons et des communes concernés ;&lt;/li&gt;&lt;li&gt;analyser la collaboration avec les systèmes existants (par ex. assurances, protection civile, armée et cantons), et&lt;/li&gt;&lt;li&gt;procéder à une évaluation juridique des réglementations actuelles (par ex. la loi fédérale sur la protection de la population et sur la protection civile [RS 520.1], la loi sur l’armée [RS 510.10], la loi sur les finances [RS 611.0] ainsi que les art. 5a et 57 Cst.).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Le rapport indiquera en outre si une base légale est nécessaire pour apporter un soutien standardisé et garanti par l’État de droit en cas de catastrophe, par exemple sous la forme d’une législation fédérale spécialisée.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in einem Bericht aufzuzeigen, welche gesetzlichen Regelungen für die zeitnahe Unterstützung einer inländischen Katastrophenhilfe vorhanden sind bzw. fehlen. Der Bericht soll darlegen, welche Voraussetzungen, Zuständigkeiten und Verfahren für finanzielle und organisatorische Unterstützungsleistungen des Bundes im Falle von Naturkatastrophen oder anderen Schadensereignissen grosser Tragweite bestehen oder geschaffen werden müssten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Insbesondere soll der Bericht:&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;die Bedingungen für die Soforthilfe präzisieren,&lt;/li&gt;&lt;li&gt;die Rolle des Bundes gegenüber betroffenen Kantonen und Gemeinden klären,&lt;/li&gt;&lt;li&gt;die Zusammenarbeit mit bestehenden Systemen (z.B. Versicherungen, Zivilschutz, Armee, Kantone) untersuchen,&lt;/li&gt;&lt;li&gt;und eine rechtliche Bewertung der aktuellen Regelungen (z.B. Bevölkerungsschutzgesetz [SR 520.1], Militärgesetz [SR 510.10], Finanzhaushaltsgesetz [SR 611.0], Art. 57 und 5a BV) vornehmen.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Der Bericht soll zudem aufzeigen, ob eine gesetzliche Grundlage für eine standardisierte und rechtsstaatlich abgesicherte Unterstützung in Katastrophenfällen nötig ist, beispielsweise in Form einer spezialisierten Bundesgesetzgebung.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Politique de sécurité|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funktionale Wasserregionen als Basis für künftiges Wassermanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Délimitation des régions aquifères selon la fonction pour une gestion de l’eau tournée vers l’avenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regioni idriche funzionali quale base per la futura gestione dell’acqua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’eau relève de la souveraineté des cantons, qui sont responsables des installations et des projets relatifs à l'utilisation de l'eau, à la protection de l'eau et à la protection contre l'excès d'eau ou à la gestion des conséquences d'une sécheresse persistante.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La mesure 127 «Adoption de la stratégie Gestion de l'eau - périodes de sécheresse, fortes précipitations, qualité de l'approvisionnement en eau, protection des habitats aquatiques» a été intégrée au programme de la législature 2023 à 2027 (&lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20230082"&gt;objet 23.082&lt;/a&gt;). La Confédération se voit ainsi attribuer une fonction de supervision et de coordination.&lt;/p&gt;&lt;p&gt;Il suffit de jeter un œil sur une carte de Suisse pour se rendre compte que très souvent, les frontières des cantons sont délimitées par un cours d’eau ou le milieu d’un lac. En d’autres termes, il n’est pas rare que des mesures isolées de gestion de l’eau concernent deux cantons, voire plus rarement trois ou quatre cantons. Cela s’applique aussi aux eaux souterraines (cf. par exemple le thème des zones de captage, motion Zanetti &lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20203625"&gt;20.3625&lt;/a&gt;). À l’échelon de la Confédération, la loi fédérale sur l’aménagement des cours d’eau et la loi fédérale sur la protection des eaux prévoient une collaboration intercantonale. Il existe de bons exemples d’application. On peut citer par exemple le cours inférieur de la Thur, la commission de la Linth ou le Plan régional d’évacuation des eaux de la Birse. Cependant, le potentiel de ce genre de collaborations reste inexploité dans de nombreuses régions qui sont en outre confrontées à des défis inédits.&lt;/p&gt;&lt;p&gt;Il n’existe encore aucune cartographie nationale des «&amp;nbsp;régions aquifères selon la fonction&amp;nbsp;», c’est-à-dire des unités territoriales qui présentent une certaine homogénéité du point de vue hydrologique. Dans les Préalpes, le Plateau et le Jura, en particulier, les bassins versants d’un cours d’eau sont rarement situés dans un même canton.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes.&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Peut-il envisager d’établir une carte de Suisse des régions aquifères délimitées selon la fonction dans le cadre de sa stratégie de gestion de l’eau&amp;nbsp;?&lt;/li&gt;&lt;li&gt;La Confédération pourrait-elle assumer un rôle de coordination dans des projets de gestion de l’eau qui concernent des régions aquifères ayant une même fonction et situées à cheval sur au moins deux cantons&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les cantons pourraient ainsi être incités à réaliser des projets supracantonaux au sein d’une région aquifère présentant une même fonction. Le Conseil fédéral pourrait-il envisager de créer un instrument d’encouragement à cet effet&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Un projet de révision de la loi fédérale sur la protection des eaux est en préparation. Le Conseil fédéral serait-il d’accord pour y intégrer des règles allant dans le sens des questions 2 et 3&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Kantone sind Inhaber der Wasserhoheit. Sie sind zuständig für Anlagen und Projekte der Wassernutzung, des Wasserschutzes und des Schutzes vor zu viel Wasser bzw. der Bewältigung von Folgen anhaltender Trockenheit.&amp;nbsp;&lt;/p&gt;&lt;p&gt;In die Legislaturplanung 2023-2027 (&lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20230082"&gt;Geschäft 23.082&lt;/a&gt;) wurde die Massnahme 127 aufgenommen: «Verabschiedung der Strategie «Wassermanagement – Trockenperioden, Starkniederschläge, Qualität der Wasserversorgung, Schutz der Wasserlebensräume.» Damit ist dem Bund eine konzeptionelle und koordinierende Funktion zugewiesen.&lt;/p&gt;&lt;p&gt;Ein Blick auf die Schweizerkarte verdeutlicht, dass Kantonsgrenzen sehr oft mitten durch Gewässer führen: Flussläufe oder Mittelachsen von Seen bilden eine Kantonsgrenze. Mit anderen Worten: Einzelmassnahmen des Wassermanagements tangieren sehr oft zwei Kantone, in selteneren Fällen drei oder mehr Kantone. Das gilt auch bezüglich Grundwasser (z.B. Thematik der Zuströmbereiche, Motion Zanetti &lt;a href="https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20203625"&gt;20.3625&lt;/a&gt;). Auf Bundesebene sehen das Wasserbaugesetz und das Gewässerschutzgesetz die interkantonale Zusammenarbeit vor. Es gibt gute Anwendungsbeispiele, etwa im Unterlauf der Thur, die Linthkommission oder der Regionale Entwässerungsplan Birs. Es gibt auch viele Regionen mit unausgeschöpftem Potenzial und neuen Herausforderungen.&lt;/p&gt;&lt;p&gt;Bisher existiert keine landesweite Kartierung von «funktionalen Wasserregionen», das heisst von Gebietseinheiten, die wassertechnisch eine gewisse Homogenität darstellen. Vor allem im voralpinen Raum, im Mittelland und im Jura liegen die Einzugsgebiete desselben Abflusses selten nur in einem Kanton.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Daher bitte ich den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Kann sich der Bundesrat vorstellen, im Rahmen der Strategie Wassermanagement eine Karte der Schweiz mit funktionalen Wasserregionen zu erstellen?&lt;/li&gt;&lt;li&gt;Könnte der Bund in Projekten des Wassermanagements, die innerhalb einer funktionalen Wasserregion, aber auf Gebiet von mindestens zwei Kantonen liegen, eine koordinierende Rolle übernehmen?&lt;/li&gt;&lt;li&gt;Für Kantone könnte ein Anreiz geschaffen werden, Projekte kantonsübergreifend innerhalb einer funktionalen Wasserregionen zu realisieren. Kann sich der Bundesrat vorstellen, dafür ein Fördergefäss zu schaffen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Aktuell wird eine Revision des Gewässerschutzgesetzes vorbereitet. Ist der Bundesrat bereit, Regelungen im Sinne der Fragen 2 und 3 in den Entwurf zu integrieren?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broulis Pascal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stranden Reisende nach Paris im Jahr 2026 auf dem Perron in Lausanne?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les voyageurs pour Paris resteront-ils sur le quai à Lausanne en 2026 ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I viaggiatori diretti a Parigi rimarranno bloccati a Losanna nel 2026?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Comment le Conseil fédéral se détermine-t-il sur la suppression de la moitié des TGV entre Lausanne et Paris pour l’année 2026&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Est-ce que des liaisons supplémentaires depuis Lausanne via Vallorbe seront ajoutées pour compenser la baisse de fréquences via Genève&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;En fonction des informations disponibles, est-ce que les CFF prévoient de limiter cette baisse de l’offre TGV Paris–Genève–Lausanne à l’année 2026 ou cette diminution concernera plusieurs années&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles mesures le Conseil fédéral entend prendre pour maintenir une améliorer l’offre entre Paris et Lausanne, via le Jura, et respecter la Convention internationale relative au raccordement de la Suisse au réseau ferré français, notamment aux liaisons à grande vitesse entrée en vigueur le 23 mars 2003 ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie steht der Bundesrat dazu, dass im Jahr&amp;nbsp;2026 die Hälfte der TGV-Verbindungen zwischen Lausanne und Paris gestrichen wird?&lt;/li&gt;&lt;li&gt;Wird es zusätzliche Verbindungen ab Lausanne über Vallorbe geben, um zu kompensieren, dass die Verbindung über Genf weniger häufig angeboten wird?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Plant die SBB, die TGV-Verbindung Paris–Genf–Lausanne nur im Jahr&amp;nbsp;2026 oder gar für mehrere Jahre zu reduzieren?&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat zu treffen, um das Angebot zwischen Paris und Lausanne über den Jura fortzuführen und zu verbessern, und um die Vereinbarung mit Frankreich zum Anschluss der Schweiz an das französische Eisenbahnnetz, insbesondere an die Hochgeschwindigkeitslinien, die am 28.&amp;nbsp;März 2003 in Kraft trat, einzuhalten?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calame Didier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Den A5-Westast in Biel mit einem Tunnel mit Gegenverkehr fertigstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Achèvement de la branche ouest de l'A5 à Bienne par un tunnel bidirectionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completare il ramo ovest della A5 a Bienne con una galleria bidirezionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil Fédéral est prié de reprendre dans les meilleurs délai le dossier de la traversé ouest de Bienne(A5)&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Projekt Westumfahrung Biel (A5) so rasch wie möglich wieder aufzunehmen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quadri Lorenzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Errichtung eines Schweizer Staatsfonds zur Unterstützung der Infrastruktur und der Volkswirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création d’un fonds souverain suisse pour soutenir les infrastructures et l’économie nationale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Istituire un fondo sovrano svizzero a sostegno delle infrastrutture e dell’economia nazionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un projet de loi visant à créer un fonds souverain suisse avec les caractéristiques suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;mode de financement&amp;nbsp;: alimenté par une partie des réserves monétaires de la Banque nationale suisse (BNS) sans incidence sur le budget ordinaire de la Confédération;&lt;/li&gt;&lt;li&gt;objectifs&amp;nbsp;: investissements dans des projets d’infrastructures stratégiques au niveau national et cantonal, notamment dans des régions périphériques comme le canton du Tessin;&lt;/li&gt;&lt;li&gt;instruments de cohésion: le fonds vise à renforcer l’intégration des régions suisses en soutenant la mobilité&amp;nbsp;durable et accessible, comme les tunnels, les lignes ferroviaires souterraines, les contournements et les projets du réseau train-tram;&lt;/li&gt;&lt;li&gt;participation interne&amp;nbsp;: possibilité pour les collectivités et les ressortissants suisses de souscrire à des obligations émises par le fonds;&lt;/li&gt;&lt;li&gt;diversification et stabilité économique&amp;nbsp;: promouvoir une utilisation productive et à long terme des réserves de la BNS pour renforcer l’économie nationale et réduire l’impact du renchérissement du franc suisse.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Gesetzesentwurf zur Errichtung eines Schweizer Staatsfonds vorzulegen, der die nachfolgenden Merkmale aufweist:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Finanzierung: Der Fonds wird aus einem Teil der Währungsreserven der Schweizerischen Nationalbank (SNB) gespiesen, ohne sich auf den ordentlichen Bundeshaushalt auszuwirken;&lt;/li&gt;&lt;li&gt;Zweck: Investitionen in strategische Infrastrukturprojekte auf nationaler und kantonaler Ebene zu tätigen, insbesondere in Randregionen wie dem Kanton Tessin;&lt;/li&gt;&lt;li&gt;Instrument für den Zusammenhalt: Der Fonds soll die Integration der Regionen der Schweiz stärken, indem eine nachhaltige und zugängliche Mobilität gefördert wird, zum Beispiel durch Tunnel, unterirdische Bahnlinien, Umfahrungen und Tram- bzw. Zugprojekte;&lt;/li&gt;&lt;li&gt;Interne Beteiligung: Schweizer Gemeinwesen und Bürgerinnen und Bürger sollen Fondsanleihen zeichnen können;&lt;/li&gt;&lt;li&gt;Diversifizierung und Stabilität der Wirtschaft: Der Fonds soll eine produktive und langfristige Nutzung der Währungsreserven der SNB fördern und so die Volkswirtschaft stärken und die Auswirkungen der Aufwertung des Schweizer Frankens abschwächen.&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Finanzwesen|Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Finances|Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Finanze|Trasporti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gleichbehandlung im interkantonalen Finanzausgleich beim Kantonswechsel von Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egalité de traitement dans la péréquation intercantonale lors du transfert de Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parità di trattamento nel quadro della perequazione finanziaria intercantonale applicata in seguito al trasferimento del Comune di Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de déposer un projet de modification législative qui compense intégralement en faveur du canton de Berne le montant que ce dernier s'est engagé à payer au du canton du Jura dans le cadre du Concordat intercantonal au titre de compromis concernant les effets différés du changement de territoire dans le cadre de la péréquation financière fédérale (env. 75 millions de francs)&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf für eine Gesetzesänderung vorzulegen, damit dem Kanton Bern der Betrag vollständig ausgeglichen wird, den er im interkantonalen Konkordat dem Kanton Jura als Kompromiss zugesichert hat (ca. 75 Millionen Franken), weil sich der Gebietswechsel auf den eidgenössischen Finanz- und Lastenausgleich erst verzögert auswirkt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temporäre Ausgleichszahlungen im Zusammenhang mit dem Kantonswechsel der Gemeinde Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paiements compensatoires temporaires dans le contexte du changement de canton de la commune de Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versamenti di compensazione temporanei in relazione al cambiamento di Cantone di Moutier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un projet d'acte garantissant que le canton du Jura reçoive 13 millions de francs par an de 2027 à 2031, en lien avec le changement de canton de la commune de Moutier et en complément du Concordat entre le canton de Berne et la République et Canton du Jura. À cet effet, il examinera toutes les options qui permettent de trouver une solution en temps utile, y compris un ajout à la modification de la loi fédérale sur la péréquation financière et la compensation des charges (PFCC ; RS 613.2) prévue dans le cadre de l’avant-projet sur le programme d’allégement budgétaire 2027.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Schilliger, Bürgi Roman, Farinelli, Gafner, Giacometti, Götte, Guggisberg, Nause, Sollberger, Theiler, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Erlassentwurf vorzulegen, der dafür sorgt, dass der Kanton Jura in den Jahren 2027 bis 2031 im Zusammenhang mit dem Kantonswechsel der Gemeinde Moutier und in Ergänzung zum bilateralen Abkommen zwischen den Kantonen Bern und Jura jährlich 13 Millionen Franken erhält.&amp;nbsp;Dazu prüft er alle Optionen, die eine zeitgerechte Lösung erlauben, insbesondere auch eine Ergänzung der im Vorentwurf zum Entlastungspaket 2027 vorgesehenen Änderung des Bundesgesetzes über den Finanz- und Lastenausgleich (FiLaG; SR 613.2).&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit der Kommission (Schilliger, Bürgi Roman, Farinelli, Gafner, Giacometti, Götte, Guggisberg, Nause, Sollberger, Theiler, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maitre Vincent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welche Bedeutung haben die internationalen Organisationen für Bund und Kantone? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Évaluer l'importance des organisations internationales pour la Confédération et les cantons </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valutare l'importanza delle organizzazioni internazionali per la Confederazione e i Cantoni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de rendre un rapport sur l’importance des Organisations internationales, d'un point de vue économique, pour la Suisse et l’ensemble des cantons.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le rapport devra notamment développer les points suivants&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Présenter un état des lieux complet et actuel de l’impact des Organisations internationales ayant leur siège en Suisse en matière d’emplois, directs et indirects, et de dynamisme économique pour la Confédération et l'ensemble des cantons&amp;nbsp;;&lt;/li&gt;&lt;li&gt;Établir les recettes fiscales, directes et indirectes, issues des organisations internationales pour les finances fédérales&amp;nbsp;(IFD, TVA, et autres taxes et impôts) ;&lt;/li&gt;&lt;li&gt;Évaluer l’apport des Organisations internationale dans la part du canton de Genève à la péréquation financière fédérale&amp;nbsp;;&lt;/li&gt;&lt;li&gt;Analyser les risques encourus pour la Suisse par les récentes décisions de désengagement de la nouvelle administration américaine.&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Bericht über die wirtschaftliche Bedeutung der internationalen Organisationen für die Schweiz und die Gesamtheit der Kantone zu erstellen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bericht soll namentlich Folgendes enthalten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;eine umfassende und aktuelle Bestandsaufnahme der Auswirkungen der internationalen Organisationen mit Sitz in der Schweiz auf die direkte und indirekte Beschäftigung und die wirtschaftliche Dynamik für den Bund und alle Kantone;&lt;/li&gt;&lt;li&gt;die Angabe der Bundeseinnahmen aus direkten und indirekten Steuern (direkte Bundessteuer, MwSt und andere Steuern und Abgaben) von internationalen Organisationen;&lt;/li&gt;&lt;li&gt;eine Schätzung des Beitrags, den die internationalen Organisationen zum Anteil des Kantons Genf am eidgenössischen Finanzausgleich leisten;&lt;/li&gt;&lt;li&gt;eine Analyse der Risiken, die sich für die Schweiz aus den jüngsten Rückzugsentscheidungen der neuen US-Regierung ergeben.&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Wirtschaft|Finanzwesen|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Économie|Finances|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Economia|Finanze|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candinas Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diskriminierende Regelung bei Pensionsverträgen in Behinderten-, Alters- und Pflegeheimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Règle discriminatoire dans les contrats d'accueil en EMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disciplinamento discriminatorio per i contratti di pensione negli istituti per persone con disabilità e nelle case per anziani e di cura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les contrats d’accueil dans les établissements médico-sociaux (EMS) sont des contrats mixtes, avec une composante locative et une composante liée à un mandat. Dans la jurisprudence, l’accent est mis sur le droit des mandats en raison des prestations de soins fournies par les EMS. En vertu de l’art. 404, al. 1, CO, le mandat peut être révoqué ou répudié en tout temps, même sans motif particulier. Dans de telles circonstances, les résidents d’un EMS doivent se contenter de faire valoir leur droit à une indemnisation pour le dommage causé ; ils ne peuvent pas s’opposer à une résiliation du contrat concernant les prestations de soins. Or, ces personnes ont besoin aussi bien d’un contrat de logement en cours de validité que de soins ininterrompus. En perdant les prestations de soins, elles perdent aussi, de facto, la possibilité de faire valoir une éventuelle protection relevant du droit du bail.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Qui plus est, si le cas est porté devant le tribunal, la nature mixte du contrat pose le problème de la compétence des tribunaux. Il en résulte une procédure longue et coûteuse avant même qu’un tribunal ne puisse entrer en matière. Il est évident que très peu de résidents d’EMS peuvent se le permettre sur les plans à la fois temporel et financier.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Conscient de ce problème, le canton de Vaud a élaboré un contrat-type qui prévoit que l’établissement ne peut résilier le contrat que lorsqu’une solution a été trouvée au sujet du nouveau lieu de séjour du résident. Il serait utile de trouver une solution à l’échelle de la Suisse afin d’éviter que les résidents d’un EMS ne perdent leur domicile du jour au lendemain sans pouvoir, par cet argument, empêcher une résiliation qui serait par ailleurs justifiée. La Confédération dispose déjà, avec la LIPPI, d’une réglementation concernant les établissements pour personnes handicapées qui permet de poser certaines conditions au niveau des cantons, malgré la RPT, en imposant à ces derniers de prévoir des plans de mesures, notamment des procédures de conciliation entre les résidents et les institutions.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le Conseil fédéral est chargé de répondre aux questions suivantes.&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Est-il au courant de la problématique du contrat d’accueil en EMS dans sa forme actuelle ?&lt;/li&gt;&lt;li&gt;La possibilité de régler les contrats d’accueil dans la loi et de prévoir des mécanismes de protection contre les résiliations a-t-elle déjà été évoquée ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral pourrait-il envisager de fixer, dans des lois telles que la LIPPI, une protection adéquate contre les résiliations sous la forme de conditions ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Pensionsverträge von Behinderten-, Alters- oder Pflegeheimen sind gemischte Verträge, mit mietrechtlichen und auftragsrechtlichen Anteilen. Aufgrund der Betreuungsleistungen in einem Heim, wird in der Rechtsprechung der Schwerpunkt auf das Auftragsrecht gelegt. Nach&amp;nbsp;Art. 404 Abs. 1 OR kann der Auftrag von jeder Partei jederzeit widerrufen oder gekündigt werden,&amp;nbsp;ohne dass dafür besondere Gründe vorliegen müssen. Bewohner eines Heimes müssen sich in solchen Fällen auf die Geltendmachung von Schadenersatzansprüchen beschränken und können die Kündigung betreffend Betreuungsleistungen nicht erfolgreich anfechten. Die Betroffenen sind vom laufenden Mietverhältnis und andauernder Betreuung gleichermassen abhängig. Der Verlust von Betreuungsleistungen verunmöglicht es den Betroffenen zudem, den allfälligen mietrechtlichen Schutz tatsächlich in Anspruch nehmen zu können.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Wird der Fall vor Gericht gezogen, besteht aufgrund des gemischten Vertrags überdies ein Problem mit der Zuständigkeit der Gerichte. Es resultiert ein langwieriger und kostspieliger Rechtsstreit, bis überhaupt ein Gericht auf die Klage eintritt. Es ist offensichtlich, dass dieses Vorgehen nur den wenigsten Bewohnern eines Heimes zeitlich und finanziell zugemutet werden kann.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im Kanton Waadt wurde dieses Problem erkannt und ein Mustervertrag erarbeitet, welcher vorsieht, dass die Kündigung durch das Heim erst dann erfolgen kann, wenn eine Lösung bezüglich des neuen Aufenthaltsortes der betroffenen Person gefunden wurde. Eine gesamtschweizerische Lösung ist demzufolge erstrebenswert, um zu verhindern, dass Bewohner eines Heimes von einem Tag auf den anderen ihren Wohnsitz verlieren, ohne eine berechtigte Kündigung damit zu verunmöglichen. Mit dem IFEG regelt der Bund bereits heute für Behindertenheime in Kantonen trotz NFA gewisse Voraussetzungen und verlangt von den Kantonen Konzepte, die etwa Schlichtungsverfahren zwischen Bewohnern und Institutionen vorsehen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Ist die Problematik des Pensionsvertrages in der heutigen Form dem Bundesrat bekannt?&lt;/li&gt;&lt;li&gt;Wurde die Möglichkeit, den Pensionsvertrag im Gesetz zu regeln und ebenfalls Kündigungsschutzbestimmungen einzuführen je in Erwägung gezogen?&lt;/li&gt;&lt;li&gt;Kann sich der Bundesrat vorstellen, einen angemessenen Kündigungsschutz als Voraussetzung in Gesetzen wie dem IFEG aufzunehmen?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soziale Fragen|Gerichtswesen|Sozialer Schutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions sociales|Justice|Protection sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questioni sociali|Giustizia|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trede Aline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wie soll der Zustand der Schweizer Bäche konkret verbessert werden? Genügt dafür das bestehende Instrumentarium?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment améliorer l'état des ruisseaux suisses? Les instruments existants suffisent-ils ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Come migliorare concretamente le condizioni dei torrenti svizzeri? Gli strumenti oggi disponibili sono sufficienti?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;1.&amp;nbsp;Est-il d’avis que l’état décrit des ruisseaux suisses, dans lequel les pesticides jouent manifestement un rôle important, représente un effet acceptable sur les organismes non-cibles&amp;nbsp;? Si oui, comment le justifie-t-il&amp;nbsp;?&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Les rapports de l’EAWAG et du VSL sont-ils un indice, voire une preuve, que les risques liés aux pesticides toxiques sont aujourd’hui systématiquement mal évalués lors de l’homologation&amp;nbsp;? Si non, pourquoi&amp;nbsp;? Si oui, que faut-il faire pour remédier à cette situation&amp;nbsp;?&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Ces rapports sont-ils un indice, voire une preuve, que les risques liés à certains pesticides sont mal évalués&amp;nbsp;? Si non, comment le Conseil fédéral évalue-t-il les conclusions de ces rapports, dans la perspective de l’homologation&amp;nbsp;? Si oui, quelles sont les conséquences&amp;nbsp;?&lt;/p&gt;&lt;p&gt;4.&amp;nbsp;Quels effets indésirables directs et indirects les produits phytosanitaires peuvent-ils avoir sur les poissons, à leurs différents stades de développement&amp;nbsp;? Que disent les études précitées et d’autres sur l’état des poissons dans les ruisseaux suisses&amp;nbsp;? Le Conseil fédéral y voit-il des causes à effets&amp;nbsp;?&lt;/p&gt;&lt;p&gt;5.&amp;nbsp;Qu’entend-il faire pour améliorer la situation dans les cours d’eau suisses&amp;nbsp;? Quels sont les objectifs qu’il souhaite atteindre et à quelle échéance&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Ist der Bundesrat der Meinung, dass der beschriebene Zustand der Schweizer Bäche - bei dem Pestizide offenbar eine wichtige Rolle spielen - einen annehmbaren Effekt auf Nichtziel-Organismen darstellt? Wenn ja, wie begründet er dies?&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Sind die Berichte von EAWAG und VSL ein Indiz, allenfalls gar ein Beleg dafür, dass die Risiken von toxischen Pestiziden bei der Zulassung heute systematisch falsch eingeschätzt werden? Wenn nein, warum nicht? Wenn ja, was ist zu tun?&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Sind sie ein Indiz oder gar ein Beleg dafür, dass die Risiken bei einzelnen Pestiziden falsch eingeschätzt werden? Wenn nein, wie beurteilt der Bundesrat die Ergebnisse dann, mit Blick auf die Zulassung? Wenn ja, was sind die Konsequenzen?&lt;/p&gt;&lt;p&gt;4.&amp;nbsp;Welche direkten und indirekten unerwünschten Effekte können Pflanzenschutzmittel auf Fische haben, in ihren verschiedenen Entwicklungsstadien? Was sagen die erwähnten und andere Studien zum Zustand der Fische in Schweizer Bächen und sieht der Bundesrat Parallelen?&lt;/p&gt;&lt;p&gt;5.&amp;nbsp;Was will der Bundesrat konkret tun, um die Situation in den Schweizer Bächen zu verbessern? Welche Ziele will er dabei erreichen und bis wann?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Würth Benedikt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufgabenteilung im Bereich Denkmal-, Heimat- und Ortsbildschutz wieder auf den Kerngehalt der NFA I und der Verfassung zurückführen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protection des monuments, du patrimoine et des sites construits. Répartir à nouveau les tâches conformément à la RPT I et à la Constitution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conservazione dei monumenti storici e protezione del paesaggio e degli insediamenti. Tornare alla ripartizione dei compiti prevista dalla NPC I e dalla Costituzione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le projet «&amp;nbsp;Désenchevêtrement&amp;nbsp;27&amp;nbsp;» de la Confédération et des cantons entraînera probablement aussi des adaptations légales. Dans ce cadre, voire dans un projet séparé, le Conseil fédéral est chargé de répartir à nouveau les tâches dans le domaine de la protection des monuments, du patrimoine et des sites construits selon l’essence même du message concernant la réforme de la péréquation financière et de la répartition des tâches entre la Confédération et les cantons (RPT; objet 01.074). Celui-ci prévoit que la Confédération sera seule responsable des &lt;i&gt;objets&lt;/i&gt; d'importance nationale (ch. 6.2.6 du message RPT). Cette tâche continuera d'être mise en œuvre dans le cadre de la liste des monuments, ensembles et sites archéologiques d'importance nationale.&amp;nbsp;&lt;/p&gt;&lt;p&gt;La &lt;i&gt;protection des sites construits&lt;/i&gt; ainsi que la responsabilité des objets d'importance cantonale et communale sont l’affaire exclusive des cantons.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Projekt Entflechtung 27 von Bund und Kantonen wird mutmasslich auch gesetzliche Anpassungen nach sich ziehen. In diesem Rahmen (oder gegebenenfalls mit einer separaten Vorlage) wird der Bundesrat beauftragt, die Aufgabenteilung im Bereich Denkmal-, Heimat und Ortsbildschutz wieder auf den Kerngehalt der Botschaft zur Neugestaltung des Finanzausgleichs und der Aufgaben zwischen Bund und Kantonen (NFA) zurückzuführen (Geschäft 01.074). Demgemäss soll der Bund die Verantwortung für &lt;i&gt;Objekte&lt;/i&gt; von nationaler Bedeutung übernehmen (Kap. 6.2.6 der NFA Botschaft). Diese Aufgabe soll auch weiterhin mit dem Verzeichnis der Denkmäler, Ensembles und archäologischen Stätten von nationaler Bedeutung umgesetzt werden.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der gesamte &lt;i&gt;Ortsbildschutz&lt;/i&gt; sowie die Verantwortung für Objekte von kantonaler und kommunaler Bedeutung ist ausschliesslich Sache der Kantone. &amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Kultur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Culture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Cultura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für eine gerechte Berücksichtigung des Wechsels von Moutier zum Kanton Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une prise en compte équitable du transfert de Moutier dans le canton du Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per una considerazione equa delle ripercussioni finanziarie del trasferimento del Comune di Moutier nel Cantone del Giura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est invité à régler de manière appropriée les effets financiers du transfert de Moutier dans le canton du Jura pour la Répartition des tâches et des charges entre la Confédération et les cantons (RPT).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird aufgefordert, die finanziellen Auswirkungen des Wechsels von Moutier zum Kanton Jura im Hinblick auf die Aufgaben- und Lastenverteilung zwischen Bund und Kantonen&amp;nbsp;(NFA) angemessen zu regeln.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Förderung der Biodiversität entlang von SBB-Infrastrukturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favoriser la biodiversité attenante aux infrastructures des CFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promozione della biodiversità lungo le infrastrutture FFS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Garantir la biodiversité en Suisse est un défi de taille, car les surfaces appropriées sont limitées. Néanmoins, la faune et la flore pourraient certainement bénéficier d’habitats de grande valeur écologique le long des voies ferrées et sur les aires ferroviaires. Les CFF s’engagent activement en faveur de la protection et de l’entretien de ces surfaces et ont déjà, en collaboration avec l’OFEV, lancé plusieurs projets pilotes et pris des mesures visant à favoriser la biodiversité. Il reste à savoir si ces mesures sont efficaces et comment la Confédération continuera de soutenir les CFF.&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment la Confédération soutient-elle les efforts des CFF visant à favoriser la biodiversité le long des chemins de fer et sur les aires ferroviaires&amp;nbsp;?&lt;/li&gt;&lt;li&gt;L’objectif des CFF qui consiste d’ici 2030 à entretenir 20&amp;nbsp;% des talus en les maintenant proches de l’état naturel semble modérément ambitieux. Est-il possible de pousser l’objectif plus loin, voire d’augmenter ce pourcentage&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quels progrès concrets ont été réalisés en vue de cet objectif et de la lutte contre les plantes néophytes envahissantes&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Les projets de l’OFEV et des CFF qui visent à favoriser la biodiversité en recourant à d’autres surfaces, notamment le long des chemins de fer ou les aires ferroviaires inutilisées, sont bienvenus, mais quelles mesures sont prévues concrètement&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Dans quelle mesure les CFF travaillent-ils avec des partenaires pour accélérer la mise en œuvre de ces mesures&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Comment le Conseil fédéral évalue-t-il l’efficacité des mesures prises pour améliorer la biodiversité, et quelles mesures supplémentaires sont nécessaires, selon lui, pour continuer à favoriser la biodiversité attenante aux infrastructures des CFF&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Sicherstellung der Biodiversität in der Schweiz stellt eine große Herausforderung dar, da geeignete Flächen begrenzt sind. Entlang der SBB-Infrastruktur oder auf Bahnarealen bestehen jedoch grosse Chancen, ökologisch wertvolle Lebensräume zu schaffen. Die SBB hat denn auch in Zusammenarbeit mit dem BAFU bereits verschiedene Pilotprojekte und Massnahmen zur Förderung der Biodiversität initiiert und setzt sich aktiv für den Schutz und die Pflege dieser Flächen ein. Es stellt sich jedoch die Frage, wie effektiv diese Massnahmen sind und wie die SBB weiterhin vom Bund unterstützt wird.&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie unterstützt der Bund die SBB in ihren Bemühungen zur Förderung der Biodiversität entlang der Bahnstrecken und auf Bahnarealen?&lt;/li&gt;&lt;li&gt;Das Ziel der SBB, bis 2030 ein Fünftel der Böschungen naturnah zu pflegen, scheint bedingt ambitioniert. Besteht die Möglichkeit, dieses Ziel zu forcieren und gegebenenfalls einen höheren Anteil der Flächen naturnah zu gestalten?&lt;/li&gt;&lt;li&gt;Welche konkreten Fortschritte wurden bisher bei der naturnahen Pflege von Böschungen und der Bekämpfung invasiver Neophyten erzielt?&lt;/li&gt;&lt;li&gt;Die Pläne von BAFU und SBB, weitere Flächen der SBB, wie zum Beispiel Gleisfelder oder ungenutzte Bahngrundstücke, für die Förderung der Biodiversität zu nutzen sind erfreulich, welche konkreten Schritte sind geplant?&lt;/li&gt;&lt;li&gt;Inwiefern arbeitet die SBB mit externen Dienstleistern zusammen, um diese Massnahmen schneller umzusetzen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie bewertet der Bundesrat die Wirksamkeit der bisherigen Maßnahmen der SBB zur Verbesserung der Biodiversität, und welche zusätzlichen Schritte sind aus seiner Sicht erforderlich, um die Biodiversität entlang der SBB-Infrastruktur weiter zu fördern?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehr|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mangel an Ärztinnen und Ärzten. Bilanz der Verpflichtung für ausländische Ärztinnen und Ärzte, während drei Jahren in einem Schweizer Spital zu arbeiten, und Bilanz der Ausnahmen nach Artikel 37 Absatz 1bis KVG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pénurie de médecins. Bilan de l'obligation pour les médecins étrangers d'effectuer trois ans de formation dans un hôpital suisse et bilan des exceptions prévues à l'article 37 alinéa 1bis LAMal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penuria di medici. Bilancio dell'obbligo per i medici stranieri di svolgere tre anni di perfezionamento in un ospedale svizzero e bilancio delle deroghe previste all'articolo 37 capoverso 1bis LAMal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Depuis janvier 2022, il a été décidé que les médecins au bénéfice d’un diplôme étranger souhaitant s’installer en Suisse doivent effectuer 3 ans de formation au sein d’un hôpital suisse,&amp;nbsp;dans le domaine de spécialité faisant l’objet de leur demande d’admission, ceci afin de se familiariser avec le système de santé suisse.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans le but d’éviter la pénurie de médecins qui a été rapidement constatée dans le domaine des soins de premier recours à la suite de l’introduction de cette règle,&amp;nbsp;une exception a été adoptée en mars 2023 (art. 37, al. 1&lt;sup&gt;bis&lt;/sup&gt;, LAMal), qui concerne uniquement les médecins praticiens, les médecins généralistes, les pédiatres, les psychiatres et les psychothérapeutes d’enfants et d’adolescents.&lt;/p&gt;&lt;p&gt;Lors des débats au parlement sur cette obligation de 3 ans de formation pour les autres spécialités, il y avait eu des réflexions sur la pénurie de certaines spécialités dans certains cantons (surtout Jura et Valais), ainsi que sur les difficultés pour les médecins généralistes de travailler efficacement s’ils ne disposent pas d’un réseau de médecins spécialistes sur lesquels s’appuyer. Afin que ces pénuries très spécifiques puissent être comblées, il est important de connaitre le devenir&amp;nbsp; des médecins étrangers au terme de leur formation de 3 ans dans un hôpital suisse, en particulier de savoir s’ils vont s’installer dans des cantons à pénurie de leur spécialité ou au contraire dans les centres urbains déjà bien fournis en spécialistes.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le CF de répondre à ces questions&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Depuis mars 2023, date de l’entrée en vigueur de l’exception d’avoir effectué ces 3 ans dans un hôpital, combien de médecins se sont-ils installés, dans quelles spécialités (pédiatre, généraliste, psychiatrie) et dans quels cantons&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Y a-t-il en particulier eu plus d’installation dans les cantons qui faisaient état d’une pénurie, en particulier le Jura et le Valais&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Depuis 2022, combien de médecins spécialistes étrangers ont-ils commencé à une formation de 3 ans dans un hôpital reconnu pour la formation postgrade&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans quels cantons ces médecins ont-ils effectué leurs 3 ans de formation&amp;nbsp;? et dans quelles spécialités&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Y en a-t-il qui ont terminé leur formation de 3 ans et qui se sont installés&amp;nbsp;? Si oui, où&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Seit Januar&amp;nbsp;2022 gilt, dass Ärztinnen und Ärzte mit einem ausländischen Diplom, die sich in der Schweiz niederlassen wollen, während drei Jahren in einem Schweizer Spital im beantragten Fachgebiet gearbeitet haben müssen. Dies wird damit begründet, dass sie sich mit dem Schweizer Gesundheitswesen familiarisieren sollen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Da es in der Grundversorgung schon bald nach der Einführung dieser Regelung zu einem Ärztemangel kam, wurde im März&amp;nbsp;2023 für bestimmte Fachgebiete, nämlich die Fachgebiete Praktischer Arzt oder Praktische Ärztin, Allgemeine Innere Medizin, Kinder- und Jugendmedizin sowie Kinder- und Jugendpsychiatrie und -psychotherapie, eine Ausnahmeregelung angenommen (Art.&amp;nbsp;37 Abs.&amp;nbsp;1&lt;sup&gt;bis&lt;/sup&gt; des Bundesgesetzes über die Krankenversicherung), um in diesen Fachbereichen einen Ärztemangel zu vermeiden.&lt;/p&gt;&lt;p&gt;Bei den Beratungen im Parlament über die Verpflichtung für die anderen Fachgebiete, drei Jahre Berufserfahrung in einem Schweizer Spital vorzuweisen, gab es Überlegungen zum Mangel an Ärztinnen und Ärzten mit bestimmten Fachgebieten in gewissen Kantonen (vor allem in den Kantonen Jura und Wallis) und zur Schwierigkeit, effizient arbeiten zu können, mit der Ärztinnen und Ärzte der Allgemeinen Inneren Medizin konfrontiert sind, wenn sie nicht über ein Netzwerk von Fachärztinnen und Fachärzten verfügen, auf die sie sich stützen können. Damit diese ganz spezifischen Mängel behoben werden können, ist es wichtig zu wissen, was die Ärztinnen und Ärzte nach den drei Jahren in einem Schweizer Spital machen, insbesondere, ob sie sich in einem Kanton niederlassen, in dem es an Personen in ihrem Fachgebiet mangelt, oder in einer Stadt, die bereits bestens mit Fachärztinnen und -ärzten versorgt ist.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie viele Ärztinnen und Ärzte haben sich seit März&amp;nbsp;2023, als die Ausnahme zur Regelung, während drei Jahren in einem Spital gearbeitet zu haben, in Kraft getreten ist, in der Schweiz niedergelassen und in welchen Fachgebieten (Kinder- und Jugendmedizin, Allgemeine Innere Medizin und Psychiatrie) und in welchen Kantonen sind sie tätig?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Haben sich in den Kantonen, in denen ein Ärztemangel herrscht, insbesondere im Jura und im Wallis, mehr Personen niedergelassen?&lt;/li&gt;&lt;li&gt;Wie viele ausländische Fachärztinnen und -ärzte haben seit 2022 eine dreijährige Stelle in einem für die Weiterbildung anerkannten Spital angetreten?&amp;nbsp;&lt;/li&gt;&lt;li&gt;In welchen Kantonen haben diese Ärztinnen und Ärzte während den drei Jahren gearbeitet? Und in welchen Fachgebieten?&lt;/li&gt;&lt;li&gt;Gibt es Ärztinnen und Ärzte, die sich nach den drei Jahren Berufserfahrung in einem Schweizer Spital in der Schweiz niedergelassen haben? Wenn ja, wo?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bildung|Beschäftigung und Arbeit|Migration|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Éducation|Emploi et travail|Politique migratoire|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formazione|Occupazione e lavoro|Migrazione|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schienennetz. Lasst uns die Anbindung Genfs verbessern!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réseau ferroviaire. Désenclavons Genève !</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rete ferroviaria. Facciamo uscire Ginevra dall'isolamento!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Grand Conseil de la République et canton de Genève&lt;/p&gt;&lt;p&gt;vu I' article 160, alinéa 1, de la Constitution fédérale, du 18 avril 1999 ;&lt;/p&gt;&lt;p&gt;vu l'article 115 de la loi fédérale sur l'Assemblée fédérale, du 13 décembre 2002 ;&lt;/p&gt;&lt;p&gt;vu l'article 156 de la loi portant règlement du Grand Conseil de la République et canton de Genève, du 13 décembre 1985,&lt;/p&gt;&lt;p&gt;considérant&lt;/p&gt;&lt;p&gt;- les motions 2929 et 2930 adoptées par notre Grand Conseil le 22 juin 2023 ;&lt;/p&gt;&lt;p&gt;- l'entrée en vigueur du nouvel horaire CFF le 15 décembre 2024 ;&lt;/p&gt;&lt;p&gt;- les haltes systématiques des trains IR et IC à Renens et l'allongement important des temps de transport pour les voyageurs en provenance ou à destination de Genève ;&lt;/p&gt;&lt;p&gt;- la nécessité de changer en gare de Renens pour rejoindre l'axe ferroviaire du pied du Jura, et même de changer de quai, quel que soit le sens du trajet, contrairement à l'option proposée par les CFF à la commission des transports ;&lt;/p&gt;&lt;p&gt;- le maintien d'une liaison entre Genève et le pied du Jura aux heures de pointe (IR 57), mais impliquant un allongement du temps de parcours par rapport à l'option avec changement ;&lt;/p&gt;&lt;p&gt;- les documents mis à disposition par l'OFT en vue du message 2026 sur l'aménagement ferroviaire du Conseil fédéral ;&lt;/p&gt;&lt;p&gt;- au-delà de l'acceptation de la motion nationale 23.3668 et de l'intégration du tunnel Morges-Perroy, l'absence d'une proposition concrète de deuxième ligne entre Genève et Lausanne et de tout autre aménagement permettant d'améliorer la desserte de notre canton ;&lt;/p&gt;&lt;p&gt;-&amp;nbsp;l'invitation faite aux cantons de participer aux travaux de planification continue, comme prévu dans le cadre de l'adoption par le peuple du fonds FIF,&lt;/p&gt;&lt;p&gt;demande à l'Assemblée fédérale&lt;/p&gt;&lt;p&gt;- de demander au Conseil fédéral de mentionner les études d'aménagement d'une nouvelle ligne Genève-Lausanne dans son message 2026 sur l'aménagement ferroviaire ;&lt;/p&gt;&lt;p&gt;- de veiller à assurer d'ici à l'entrée en fonction de cette ligne, une desserte du canton de Genève d'une qualité au moins équivalente ( en termes de nombre de trains, de places et de vitesse commerciale ) à la situation qui prévalait en 2018 ;&lt;/p&gt;&lt;p&gt;- de rétablir le plus rapidement possible des liaisons directes et rapides avec Neuchâtel, Bienne et Bâle par la ligne du pied du Jura ;&lt;/p&gt;&lt;p&gt;- de poursuivre et d'intensifier les pourparlers avec la France pour améliorer la desserte internationale de Genève, en direction de Lyon et du sud de la France, mais également de Paris, Nantes, Lille, Bruxelles et Londres.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel 160 Absatz 1 der Bundesverfassung vom 18. April 1999,&lt;/p&gt;&lt;p&gt;Artikel 115 des Bundesgesetzes vom 13. Dezember 2002 über die Bundesversammlung und&lt;/p&gt;&lt;p&gt;Artikel 156 des Geschäftsreglements vom 13. September 1985 des Grossen Rates des Kantons Genf (Loi portant règlement du Grand Conseil de la République et canton de Genève);&lt;/p&gt;&lt;p&gt;und in Anbetracht dessen, dass&lt;/p&gt;&lt;p&gt;- der Grosse Rat des Kantons Genf am 11. Juni 2023 die Motionen 2929 und 2930 angenommen hat;&lt;/p&gt;&lt;p&gt;- der neue Fahrplan der Schweizerischen Bundesbahnen (SBB) am 15. Dezember 2024 in Kraft getreten ist;&lt;/p&gt;&lt;p&gt;- die Interregio-Züge (IR) und die Intercity-Züge (IC) systematisch in Renens halten und die Reisezeit für Reisende von oder nach Genf erheblich verlängert wurde;&lt;/p&gt;&lt;p&gt;- am Bahnhof von Renens umgestiegen werden muss, um auf die Eisenbahnachse des Jurasüdfusses zu gelangen, und - anders als die SBB der Verkehrskommission des Kantons Genf vorgeschlagen haben - der Bahnsteig unabhängig von der Richtung der Weiterreise gewechselt werden muss;&lt;/p&gt;&lt;p&gt;- zu Stosszeiten zwar eine Direktverbindung zwischen Genf und dem Jurasüdfuss (IR 57) beibehalten wurde, diese aber länger dauert als die Verbindung mit Umsteigen;&lt;/p&gt;&lt;p&gt;- abgesehen von der angenommenen Motion 23.3668 und der Aufnahme des Tunnels Morges-Perroy in den Ausbauschritt 2035 (AS 2035) für die Eisenbahninfrastruktur auf Bundesebene keinerlei konkrete Vorschläge für eine zweite Strecke zwischen Genf und Lausanne sowie für eine bessere Anbindung des Kantons Genf vorliegen;&lt;/p&gt;&lt;p&gt;- die Kantone - wie im Rahmen der vom Volk angenommenen Vorlage zum Bahninfrastrukturfonds (BIF) vorgesehen - eingeladen sind, sich an den Planungsarbeiten zu beteiligen;&lt;/p&gt;&lt;p&gt;- sowie in Anbetracht der vom Bundesamt für Verkehr (BAV) im Hinblick auf die Botschaft 2026 des Bundesrates zum Bahnausbau bereitgestellten Dokumente;&lt;/p&gt;&lt;p&gt;fordert der Grosse Rat des Kantons Genf die Bundesversammlung auf,&lt;/p&gt;&lt;p&gt;- vom Bundesrat zu verlangen, die Studien über eine Neubaustrecke zwischen Genf und Lausanne in seine Botschaft 2026 zur Bahninfrastruktur aufzunehmen;&lt;/p&gt;&lt;p&gt;- bis zur Inbetriebnahme dieser Verbindung eine mindestens gleichwertige Anbindung des Kantons Genf wie im Jahr 2018 (hinsichtlich der Anzahl Züge und Plätze sowie der Reisegeschwindigkeit) zu gewährleisten;&lt;/p&gt;&lt;p&gt;- direkte und schnelle Verbindungen nach Neuenburg, Biel und Basel über die Jurasüdfusslinie möglichst rasch wiederherzustellen;&lt;/p&gt;&lt;p&gt;- die Verhandlungen mit Frankreich über die bessere internationale Anbindung Genfs an Lyon und Südfrankreich sowie an Paris, Nantes, Lille, Brüssel und London fortzuführen und zu intensivieren.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basel-Stadt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale et le Conseil fédéral sont priés de prendre les mesures nécessaires pour que, sous l’angle du principe d’égalité des droits qui doit prévaloir entre États membres de la Confédération, les anciens demi-cantons de Bâle-Ville et de Bâle-Campagne soient mis sur un pied d’égalité avec les autres cantons en ce qui concerne le nombre de sièges au Conseil des États (faire des deux Bâle des cantons à part entière, modification des art.&amp;nbsp;142, al.&amp;nbsp;4, et 150, al.&amp;nbsp;1 et 2, de la Constitution fédérale).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Bundesparlament und der Bundesrat werden gebeten, die notwendigen Schritte zu unternehmen, damit unter dem Aspekt des Gebots der bundesstaatlichen und föderalen Rechtsgleichheit die ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft den übrigen Kantonen im Hinblick auf die Vertretung im Ständerat gleichgestellt werden (Aufwertung als Kantone mit Vollem Ständerecht, Änderung von Art. 142 Abs. 4 und Art. 150 Abs. 1 und 2 der Bundesverfassung).&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beratung in Kommission des Nationalrates abgeschlossen / Fin des discussions en commission du Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commission de gestion Conseil des États</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunaux fédéraux. Introduire un système disciplinaire pour renforcer la confiance à leur égard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunali della Confederazione. Introdurre un sistema disciplinare per rafforzare la fiducia in queste istituzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Il y a lieu d’élaborer les bases légales permettant d’introduire une surveillance disciplinaire des juges des tribunaux fédéraux. Les principes de l’indépendance des juges, de l’autonomie des tribunaux en matière d’organisation et de la séparation des pouvoirs devront être respectés.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Es seien die gesetzlichen Grundlagen zu erarbeiten, um eine Disziplinaraufsicht über die Richterinnen und Richter an den eidgenössischen Gerichten einzuführen. Dabei ist den Grundsätzen der richterlichen Unabhängigkeit, der Organisationsautonomie und der Gewaltentrennung Rechnung zu tragen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Gerichtswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Justice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Giustizia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrierter Ansatz für Service-Center des Service public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une approche intégrée des centres de services dans le service public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per un approccio integrato per i centri di servizio del servizio pubblico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale est chargée de créer les bases légales permettant de développer et de mettre en œuvre une approche intégrée des centres de services dans le service public. Ce faisant, elle intégrera l’infrastructure existante du réseau postal. L’objectif est de créer une infrastructure moderne et efficace pour la population et de garantir un réseau physique qui assure l’accès des personnes aux produits numériques et aux produits physiques.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung wird beauftragt, die gesetzlichen Grundlagen zu schaffen, um einen integrierten Ansatz für ServiceCenter des Service Public zu entwickeln und umzusetzen. Die bestehende Infrastruktur von PostNetz ist dabei einzubeziehen. Ziel ist es, eine moderne und effiziente Infrastruktur für die Bevölkerung zu schaffen, ein physisches Netz zu sichern, das den Zugang der Menschen zu digitalen und physischen Produkten sichert.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vieillissement de la population. Créer un mécanisme de compensation pour les primes de l’assurance-maladie </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introdurre un meccanismo di compensazione intercantonale per i premi di cassa malati dovuti all’invecchiamento dalla popolazione </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Dans son avis sur la motion Quadri 24.4209, qui le charge «&amp;nbsp;de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population&amp;nbsp;», le Conseil fédéral affirme: «&amp;nbsp;Le Conseil fédéral reste d’avis que la péréquation financière nationale assure un équilibre entre les cantons&amp;nbsp;» et souligne notamment que «&amp;nbsp;... la compensation des charges dans le cadre de la péréquation financière nationale comprend une composante sociodémographique, qui tient compte des coûts liés à la structure de la population, notamment à la pyramide des âges. Le Canton du Tessin reçoit déjà des contributions fédérales dans ce cadre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;Malheureusement, ce n’est pas ce que disent les montants définitifs des paiements compensatoires pour 2025 récemment publiés. Au contraire, le canton du Tessin ne reçoit rien au titre de la compensation sociodémographique, bien qu’il compte le plus grand nombre de personnes de 80 ans ou plus (7,6 % de la population résidante permanente, contre 5,7&amp;nbsp;% pour la moyenne nationale). Le moment est donc venu de reconnaître la situation particulière du Tessin, qui compte une proportion non négligeable de retraités âgés originaires de la Suisse alémanique.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Confirme-t-il que le Tessin ne reçoit aucune contribution au titre de la compensation sociodémographique, contrairement à ce qu’il affirme dans son avis sur la motion 24.4209?&lt;/li&gt;&lt;li&gt;Au vu de ce qui précède, convient-il que la péréquation financière nationale n’atteint pas son but?&lt;/li&gt;&lt;li&gt;Par conséquent, ne pense-t-il pas que la création d’un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population, demandée par la motion 24.4209, soit à la fois opportune et nécessaire?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In der Stellungnahme zur Motion Quadri 24.4209, die den Bundesrat beauftragte, einen Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien einzuführen, hat der Bundesrat festgehalten: «Der Bundesrat ist weiterhin der Meinung, dass der nationale Finanzausgleich für ein Gleichgewicht zwischen den Kantonen sorgt. [...], insbesondere hat er ausgeführt, dass der nationale Finanzausgleich eine soziodemographische Komponente innerhalb des Lastenausgleichs enthält, der die Kosten aufgrund der Bevölkerungsstruktur, u. a. des Alters, berücksichtigt. Der Kanton [...] erhält bereits Beiträge vom Bund im Rahmen des Lastenausgleichs».&lt;/p&gt;&lt;p&gt;Leider decken sich aber die kürzlich veröffentlichten Berechnungen zu den Ausgleichszahlungen 2025 nicht mit diesen Aussagen. So erhält der Kanton Tessin keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich, obwohl er einen besonders hohen Anteil an Personen im Alter von 80 Jahren und mehr im Verhältnis zur ständigen Wohnbevölkerung aufweist (7,6 % gegenüber dem schweizerischen Durchschnitt von 5,7 %). Es ist daher an der Zeit, die besondere Situation des Kantons Tessin anzuerkennen, wo ein nicht unerheblicher Teil der älteren Menschen Rentnerinnen und Rentner aus der Deutschschweiz sind.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte deshalb den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bestätigt der Bundesrat, dass der Kanton Tessin – anders als in der Stellungnahme zur Motion 24.4209 behauptet – keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich erhält?&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat in Anbetracht der obigen Ausführungen die Ansicht, dass der nationale Finanzausgleich seinen Zweck nicht erfüllt?&lt;/li&gt;&lt;li&gt;Hält der Bundesrat die Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien, wie sie mit der Motion 24.4209 verlangt wird, nicht auch für sinnvoll und notwendig?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechsteiner Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlichkeitsarbeit des Bundes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relations publiques de la Confédération</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attività di pubbliche relazioni della Confederazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le chancelier de la Confédération a répondu le 16&amp;nbsp;décembre 2024 de manière relativement détaillée à ma question 24.7932 «&amp;nbsp;400 fonctionnaires médias. Y a-t-il un potentiel d’économies&amp;nbsp;?&amp;nbsp;». Certains points restent toutefois flous, et les réponses fournies soulèvent d’autres questions.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Meine Frage 24.7932 «400 Medienbeamte – Sparpotential erkannt?» wurde vom Bundeskanzler am 16. Dezember 2024 relativ ausführlich beantwortet. Trotzdem bleibt einiges im Unklaren und die Antworten werfen weiteren Fragen auf.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufhebung des Zentrumslastenausgleichs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suppression de la compensation des charges des centres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eliminare la compensazione degli oneri dei centri urbani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la législation relative à la péréquation financière et à la compensation des charges de sorte que la compensation des charges dues à des facteurs socio-démographiques (CCS) ne s’applique désormais plus qu’aux charges excessives liées à la structure de la population et que les charges des centres ne soient plus compensées.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Gesetzgebung zum Finanz- und Lastenausgleich dahingehend anzupassen, dass der soziodemografische Lastenausgleich künftig nur mehr Sonderlasten aufgrund der Bevölkerungsstruktur ausgleicht und keinen Zentrumslastenausgleich mehr vorsieht.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina Fabian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übernahme der EU-Richtlinie 2019/1158 zur Vereinbarkeit von Beruf und Privatleben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reprise de la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepimento della direttiva UE 2019/1158 relativa all’equilibrio tra attività professionale e vita familiare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de reprendre dans le droit suisse la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die EU-Richtlinie 2019/118 zur Vereinbarkeit von Beruf und Privatleben ins Schweizer Recht zu übernehmen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europapolitik|Soziale Fragen|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique européenne|Questions sociales|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica europea|Questioni sociali|Occupazione e lavoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widmer Céline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systemwechsel bei der Wohneigentumsbesteuerung. Steuerliche Folgen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changement de système d’imposition du logement. Conséquences fiscales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cambio di sistema nell'ambito dell'imposizione della proprietà abitativa. Conseguenze fiscali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les chambres fédérales ont adopté une réforme de l’imposition du logement le 20.12.2024, qui bouleverse les équilibres dans ce domaine tout en amenant de grandes pertes fiscales.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes, au sujet de la réforme telle qu’elle a été adoptée par le parlement et de l’introduction d’un impôt réel sur les résidences secondaires :&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;La BNS a annoncé une baisse des taux directeurs à 0.5%. Un scénario avec des taux hypothécaires moyens durablement en dessous de 1.5% devient de plus en plus crédibles. Quelles seraient les pertes fiscales liées à la réforme en cas de taux moyen à 1%&amp;nbsp; et à 1.25%?&amp;nbsp;&amp;nbsp;&lt;/li&gt;&lt;li&gt;Etant donné que la réforme entraine de grandes pertes fiscales, cela veut dire que certains contribuables vont être avantagés par rapport au reste de la population. Est-il correct de dire que les personnes qui toucheront la plus grande somme par rapport à la situation actuelle sont celles et ceux qui disposent de très grandes propriétés avec une énorme valeur et qui n’ont pas de dette liée à cette propriété ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Combien de baisse d’impôt peut attendre un propriétaire d’une maison de maître d’une valeur de CHF 10'000'000.- et qui finance aujourd’hui son bien entièrement en fonds propres ? Quelle serait le changement de la situation fiscale d’un propriétaire qui dispose d’un bien d’une valeur de CHF 500'000, hypothéqué à hauteur de CHF 400'000.- avec un taux hypothécaire de 3%, et devant faire des frais d’entretiens pour CHF 10'000.-, s’il dispose d’un revenu imposable de 100'000.- ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral peut-il expliquer quelle est la relation entre d’une part la valeur d’une bien immobilier utilisé comme résidence principale et d’autre part l’allègement fiscal obtenu suite à l’introduction du changement de système d’imposition du logement?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont les effets de la réforme de l’imposition du logement sur la péréquation financière? En particulier, quel est l’effet sur l’équilibre de cette péréquation à long terme?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung hat am 20. Dezember 2024 eine Reform der Wohneigentumsbesteuerung verabschiedet, die das Gleichgewicht in diesem Bereich erheblich stört und gleichzeitig grosse Steuerausfälle mit sich bringt.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, die folgenden Fragen zur Reform in der vom Parlament verabschiedeten Form und zur Einführung einer Objektsteuer auf Zweitwohnungen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Die Schweizerische Nationalbank (SNB) hat eine Senkung des Leitzinses auf 0,5&amp;nbsp;Prozent angekündigt. Es ist immer wahrscheinlicher, dass die durchschnittlichen Hypothekarzinsen dauerhaft unter 1,5&amp;nbsp;Prozent liegen. Wie hoch wären die Steuerausfälle aufgrund der Reform bei einem durchschnittlichen Zinssatz von 1 Prozent oder 1,25 Prozent?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Die Reform führt zu grossen Steuerausfällen. Das bedeutet, dass einige Steuerzahler und Steuerzahlerinnen gegenüber dem Rest der Bevölkerung begünstigt werden. Kann man sagen, dass die Personen, die über sehr grosse Immobilien mit einem enormen Wert verfügen und keine Schulden im Zusammenhang mit diesen Immobilien haben, im Vergleich zur aktuellen Situation am stärksten profitieren?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Mit welcher Steuersenkung kann ein Eigentümer einer herrschaftlichen Villa im Wert von 10&amp;nbsp;000&amp;nbsp;000 Franken rechnen, der seine Immobilie heute vollständig mit Eigenmitteln finanziert? Wie würde sich die steuerliche Situation einer Eigentümerin mit einem steuerpflichtigen Einkommen von 100 000 Franken ändern, wenn sie über eine Immobilie im Wert von 500&amp;nbsp;000 Franken verfügt, die mit einer Hypothek in Höhe von 400&amp;nbsp;000 Franken zu einem Hypothekarzins von 3&amp;nbsp;Prozent belastet ist, und sie Unterhaltskosten in Höhe von 10&amp;nbsp;000 Franken tragen muss?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. &amp;nbsp;Kann der Bundesrat erklären, in welchem Verhältnis der Wert einer Immobilie, die als Erstwohnung genutzt wird, zur Steuererleichterung steht, die durch den Systemwechsel bei der Wohneigentumsbesteuerung erreicht wird?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Wie wirkt sich die Reform der Wohneigentumsbesteuerung auf den Finanzausgleich aus?&lt;/p&gt;&lt;p&gt;Welches sind insbesondere die langfristigen Auswirkungen auf das Gleichgewicht des Finanzausgleichs?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuer|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscalité|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imposte|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Was ist die Umweltpolitik des ASTRA im Rahmen seiner Ausschreibungen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quelle est la politique environnementale de l'OFROU dans le cadre de ses appels d'offres?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual è la politica ambientale dell’USTRA in ambito appaltistico?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’OFROU réalise des travaux importants à la sortie de l'autoroute à Matran. Pour une question de prix uniquement, du gravier (grave de route principalement) est acheminé depuis un site du Jura français situé à environ 100km de Matran. Pour ne pas circuler à vide sur le retour, les poids-lourds transportent des éléments de chaussée rabotés et les amènent dans les décharges en France voisine. La distance aller-retour est de 200km environ alors que les mêmes matériaux sont disponibles dans un rayon de moins de 30km dans le canton de Fribourg ou 50km hors canton. Il s’ensuit des trajets et des engorgements supplémentaires, plus de CO2, plus de bruit, plus d’usure des infrastructures, de bruit et de poussières. De surcroit, des chauffeurs dont les conditions de travail sont très précaires remplacent des conducteurs domiciliés en Suisse qui bénéficient de bonnes conditions sociales. En utilisant des graviers locaux, on s'assure qu'ils sont exploités selon les normes locales avec du personnel local. Je remercie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Les soumissions provenant de l'OFROU prévoient-elles des filières d’approvisionnement et d’évacuation de graviers et autres matériaux minéraux&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si non, est-il prévu de prendre en compte rapidement les éléments précités?&lt;/li&gt;&lt;li&gt;Si oui, sachant que l’empreinte CO2 du transport de ces matériaux lourds est importante, comment cet élément est-il mis en valeur&amp;nbsp;dans la soumission&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces aspects sont-ils contrôlés en pratique, sur le terrain&amp;nbsp;?&lt;/li&gt;&lt;li&gt;En cas de faute, quelles sont les conséquences&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Bundesamt für Strassen (ASTRA) führt bei der Autobahnausfahrt Matran wichtige Bauarbeiten durch. Dabei wird einzig aus Kostengründen Kies (hauptsächlich als Strassenschotter) aus dem französischen Jura angeliefert, von einem Ort, der rund 100 Kilometer von Matran entfernt liegt. Um auf dem Rückweg Leerfahrten zu vermeiden, transportiert der Schwerverkehr von der Fahrbahn abgeschliffene Elemente ab und entsorgt diese im benachbarten Frankreich. Insgesamt werden rund 200 Kilometer zurückgelegt, obwohl dieselben Materialien in einem Umkreis von weniger als 30 Kilometern im Kanton Freiburg oder 50 Kilometern ausserhalb des Kantons verfügbar wären. Dies führt zu zusätzlichen Fahrten, mehr Stau, CO2, Lärm und Staub sowie zu einer verstärkten Abnutzung der Infrastrukturen. Zudem werden in der Schweiz wohnhafte Chauffeurinnen und Chauffeure, die von guten sozialen Bedingungen profitieren, durch solche mit sehr prekären Arbeitsbedingungen ersetzt. Die Verwendung von lokalem Kies stellt sicher, dass dieser nach lokalen Normen und mit lokalem Personal abgebaut wird. Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Sehen die Ausschreibungen des ASTRA Liefer- und Entsorgungswege für Kies und andere mineralische Materialien vor?&lt;/li&gt;&lt;li&gt;Wenn nein: Ist geplant, die obgenannten Punkte rasch zu berücksichtigen?&lt;/li&gt;&lt;li&gt;Wenn ja: Wie wird dieser Aspekt in der Ausschreibung hervorgehoben, zumal bekannt ist, dass der Transport von Schwergut einen grossen CO2-Fussabdruck hat?&lt;/li&gt;&lt;li&gt;Wie werden diese Aspekte in der Praxis vor Ort kontrolliert?&lt;/li&gt;&lt;li&gt;Was wären die Folgen, wenn sie nicht kontrolliert werden?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschäftigung und Arbeit|Verkehr|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emploi et travail|Transports|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupazione e lavoro|Trasporti|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marti Min Li</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kann die Post einen Beitrag zur digitalen Inklusion leisten? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Poste peut-elle contribuer à l'inclusion numérique? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Posta può contribuire all'inclusione digitale? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Diverses études comme le Baromètre numérique&amp;nbsp;2024 de la Mobilière ont constaté que des compétences numériques de base font défaut à près d’un tiers de la population. Elles relèvent des disparités notables selon l’âge, le revenu et la formation. Même si l’âge joue un rôle en matière de compétences numériques, les personnes âgées ne sont en réalité pas les seules à connaître des difficultés dans l’utilisation des outils numériques comme les services bancaires et les billetteries en ligne ou les guichets virtuels des autorités. Ces lacunes vont souvent de pair avec un sentiment de gêne. &amp;nbsp;Certains, en particulier les jeunes, surestiment leurs propres compétences. De fait, le quotidien bascule toujours plus dans le numérique et exacerbe les lacunes en matière de compétences numériques. C’est pourquoi je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Que pense-t-il du problème des compétences numériques lacunaires&amp;nbsp;? Comment pourrait-on y remédier&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les pouvoirs publics et les entreprises proches de la Confédération, par exemple, numérisent de plus en plus leurs services, et ne les proposent parfois plus que sous cette forme. Comment garantir leur accessibilité à tout le monde&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans le cadre d’un projet pilote mené dans trois filiales, la Poste a proposé une assistance sur toutes sortes de problèmes relevant du numérique. Que pense le Conseil fédéral de ce projet&amp;nbsp;? La poste pourrait-elle contribuer à faire progresser l’inclusion numérique grâce à cette offre&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Est-ce qu’une telle offre de la Poste ou d’autres entreprises pourraient aussi alléger le travail des autorités&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Verschiedene Studien wie beispielsweise der Digitalbarometer 2024 der Mobiliar haben festgestellt, dass fast ein Drittel der Bevölkerung nicht über grundlegende digitale Kompetenzen verfügt. Dabei gibt es signifikante Unterschiede nach Alter, Einkommen und Bildung. Auch wenn das Alter bei den digitalen Kompetenzen eine Rolle spielt, sind es beileibe nicht nur ältere Menschen, die Mühe haben, digitale Anwendungen wie beispielsweise E-Banking, Billetkäufe oder digitale Behördengänge zu nutzen. Dies ist oft auch mit Scham verbunden. &amp;nbsp;Teilweise werden auch die eigenen Fähigkeiten überschätzt, gerade bei jüngeren Menschen. Da immer mehr Dinge des täglichen Lebens digitalisiert werden, stellt die mangelnde digitale Kompetenz ein zunehmendes Problem dar. In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie schätzt der Bundesrat das Problem der fehlenden digitalen Kompetenzen ein und wie könnten diese verbessert werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Auch Leistungen der öffentlichen Hand oder beispielsweise von bundesnahen Betrieben werden immer häufiger digitalisiert und teilweise nur noch digital angeboten. Wie kann sichergestellt werden, dass alle Personen Zugang zu diesen Leistungen haben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Im Rahmen eines Pilotprojekts hat die Post in drei Filialen ein Angebot geschaffen, um Menschen bei digitalen Problemen aller Art zu unterstützen. Wie beurteilt der Bundesrat dieses Projekt? Könnte die Post mit diesem Angebot einen Beitrag leisten, die digitale Inklusion voranzutreiben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Könnte eine entsprechende Dienstleistung der Post oder von anderen Betreibern auch dazu beitragen, Behörden zu entlasten?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Soziale Fragen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Questions sociales|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Questioni sociali|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzielle Unterstützung für Imkerinnen und Imker bei geoklimatischen Ausnahmebedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soutien financier direct aux apiculteurs et apicultrices lors de situations géoclimatiques exceptionnelles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sostegno finanziario diretto agli apicoltori in situazioni geoclimatiche eccezionali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale et à l'article 84, lettre o, de la Constitution cantonale, le Canton demande aux Chambres fédérales d'accorder un soutien financier direct, comme des subsides, aux apiculteurs et apicultrices pour l'achat de sucre nécessaire au nourrissement des abeilles mellifères, ceci lorsque les situations géoclimatiques rendent ce nourrissement indispensable à la survie des colonies d'abeilles.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o seiner Kantonsverfassung fordert der Kanton Jura die Bundesversammlung auf, den Imkerinnen und Imkern finanzielle Unterstützung, beispielsweise in Form von Subventionen, zu gewähren für den Kauf von Zucker, wenn dieser aufgrund der geoklimatischen Bedingungen an Honigbienen verfüttert werden muss, um deren Überleben sicherzustellen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impôt fédéral direct. Déduction totale des primes d’assurance-maladie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deduzione integrale dei premi per l’assicurazione contro le malattie in ambito di imposta federale diretta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la loi fédérale sur l'impôt fédéral direct comme suit&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art.&amp;nbsp;33 Intérêts passifs et autres réductions&lt;/p&gt;&lt;p&gt;Al.&amp;nbsp;1&lt;/p&gt;&lt;p&gt;Sont déduits du revenu&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let. a à f, h et i&amp;nbsp;: aucune modification&amp;nbsp;;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let. g&amp;nbsp;: biffer «&amp;nbsp;d’assurance-maladie&amp;nbsp;»&amp;nbsp;;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;let.&amp;nbsp;k (nouvelle)&amp;nbsp;: les primes et cotisations d’assurance-maladie privée et obligatoire.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, das Bundesgesetz über die direkte Bundessteuer wie folgt zu ändern:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Art. 33 Schuldzinsen und andere Abzüge&lt;/p&gt;&lt;p&gt;Abs. 1&lt;/p&gt;&lt;p&gt;Von den Einkünften werden abgezogen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. a bis f sowie h und i: bleiben unverändert;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. g: Streichung von "Krankenversicherung";&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Bst. k (neu): Prämien und Beiträge für die obligatorische und private Krankenversicherung.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addor Jean-Luc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenzüberschreitende Kriminalität: Bessere Kontrolle der Landesgrenze und ein Aktionsplan, aber schnell!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criminalité transfrontalière : mieux contrôler nos frontières et un plan d'action, et vite !</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Après la énième attaque d'un distributeur de billets en zone frontalière le 7 décembre à Montagny-près-Yverdon VD, pour éviter que notre pays soit considéré comme une sorte de libre-service par les bandes organisées étrangères, le Conseil fédéral va-t-il décider rapidement d'un plan d'action et dans l'immédiat, ne doit-il pas décider d'un renforcement immédiat des contrôles de nos frontières dans les secteurs exposés (à commencer par le secteur Jura-Nord vaudois) ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 7. Dezember wurde in Montagny-près-Yverdon VD zum x-ten Mal ein Geldautomat im Grenzgebiet angegriffen.&lt;br&gt;Wird der Bundesrat schnell über einen Aktionsplan sowie umgehend über eine Verstärkung der Grenzkontrollen in den exponierten Sektoren entscheiden (angefangen mit dem Sektor Waadtländer Nordjura), um zu verhindern, dass unser Land von organisierten Banden aus dem Ausland als eine Art Selbstbedienungsladen betrachtet wird?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Finanzwesen|Strafrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Finances|Droit pénal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Finanze|Diritto penale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaccoud Jessica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grundversorgung mit Postdiensten: Werden die Randregionen aufgegeben?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service universel en matière de services postaux, un abandon des régions périphériques?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les points d’accès aux services postaux doivent être accessibles en 20 min par les transports publics. Avec la fermeture des offices de Bière, Apples et L'Isle, les habitant.e.s du Pied du Jura devront se rendre à Morges. Depuis le village de Berolle, cela représente un trajet de minimum 50 minutes. Et il n'existe aucun transport public durant le week-end.&lt;br&gt;- Comment le CF estime-t-il que le service universel peut être maintenu dans ces conditions?&lt;br&gt;- N'abandonne-t-il pas les régions périphériques?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Zugang zu den Postdiensten muss innerhalb von 20 Minuten mit öffentlichen Verkehrsmitteln gewährleistet sein. Aufgrund der Schliessung der Poststellen von Bière, Apples und L'Isle müssen die Einwohnerinnen und Einwohner am Jurasüdfuss nach Morges fahren. Vom Dorf Berolle aus bedeutet dies eine Fahrzeit von mindestens 50 Minuten. Ausserdem fahren am Wochenende keine öffentlichen Verkehrsmittel.&lt;br&gt;- Wie kann die Grundversorgung nach Auffassung des Bundesrats unter diesen Bedingungen aufrechterhalten werden?&lt;br&gt;- Lässt er die Randregionen so nicht im Stich?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gebietsveränderung zwischen den Kantonen Bern und Jura (Kantonswechsel der bernischen Gemeinde Moutier). Genehmigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modification du territoire des cantons de Berne et du Jura (Transfert de la commune bernoise de Moutier). Approbation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modifica territoriale tra i Cantoni di Berna e del Giura (trasferimento del Comune bernese di Moutier). Approvazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für klare Regeln bei Lebensmittelimporten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour des règles claires en matière d'importation de denrées alimentaires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per un disciplinamento in materia di importazione di derrate alimentari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement demande dès lors aux Chambres fédérales de modifier la législation fédérale de manière à interdire l'importation de denrées alimentaires ne répondant pas aux réglementations qui seraient requises pour leur production en Suisse.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o der Kantonsverfassung fordert das Parlament des Kantons Jura die Bundesversammlung auf, den Import von Lebensmitteln, deren Herstellung nicht den Schweizer Vorschriften entspricht, zu verbieten.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Wirtschaft|Finanzwesen|Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Économie|Finances|Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Economia|Finanze|Agricoltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für eine "entwaldungsfreie" Schweizer Politik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une politique fédérale "Zéro déforestation"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una politica federale "a deforestazione zero"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement demande aux Chambres fédérales d'adapter la législation fédérale afin de garantir que les matières premières et leurs sous-produits mis sur le marché helvétique ou destinés à l'exportation ne soient pas associés à la déforestation.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o der Kantonsverfassung fordert das Parlament des Kantons Jura die Bundesversammlung auf, mit einer Anpassung des Bundesrechts sicherzustellen, dass Rohstoffe und ihre Nebenprodukte, die auf den Schweizer Markt gebracht werden oder für den Export bestimmt sind, nicht in Verbindung mit Entwaldung stehen.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Umwelt|Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Environnement|Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Ambiente|Agricoltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interkantonaler Ausgleich für den alterungsbedingten Anstieg der Krankenkassenprämien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augmentation des primes de l'assurance-maladie due au vieillissement de la population. Compensation intercantonale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compensazione intercantonale per gli aumenti dei premi di cassa malati dovuti all'invecchiamento della popolazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Mechanismus zum interkantonalen Ausgleich des altersbedingten Anstiegs der Krankenkassenprämien einzuführen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Beschäftigung und Arbeit|Migration|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Emploi et travail|Politique migratoire|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Occupazione e lavoro|Migrazione|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durrer-Knobel Regina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ausbildungsdarlehen und Stipendien für Erwachsene im sekundären Bildungsbereich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourses et prêts destinés aux adultes suivant une formation du degré secondaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prestiti e borse per gli adulti che seguono una formazione del livello secondario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer une loi réglant les contributions aux cantons pour l’octroi de bourses et de prêts de formation aux adultes suivant une formation du degré secondaire, sur le modèle de la loi sur les aides à la formation qui s’applique au degré tertiaire.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, analog dem&amp;nbsp;Bundesgesetz über Beiträge an die Aufwendungen der Kantone für Stipendien und Studiendarlehen im tertiären Bildungsbereich ein Gesetz zu erarbeiten, welches Beiträge an die Aufwendungen der Kantone für Stipendien und Ausbildungsdarlehen im sekundären Bildungsbereich für Erwachsene regelt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Bildung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Éducation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Formazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolet Jacques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abschuss des Rudels auf dem Mont Tendre. Der Kanton muss über echte Handlungsmöglichkeiten verfügen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elimination de la meute du Mont Tendre. Il est nécessaire de donner de vrais moyens d'action au canton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbattimento del branco di lupi del Mont Tendre. Fornire ai Cantoni strumenti d'azione reali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;En date du 13 août 2024, le Département de la Jeunesse, de l’environnement et de la sécurité (DJES) du Canton de Vaud formulait auprès de l’OFEV une nouvelle demande relative au tir du loup. Elle portait sur l’élimination complète de la meute du Mont tendre, identifiée comme responsable d’une vingtaine d’attaques de loups sur des troupeaux dans le Jura vaudois. Région dans laquelle, outre les quelques loups isolés, cinq meutes sont présentes, dont la meute en question.&lt;/p&gt;&lt;p&gt;Dans sa décision du 3 septembre 2024 (soit 3 semaines après la demande), et selon son évaluation, l’OFEV reconnait&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Qu’en raison du comportement indésirable de la meute du Mont Tendre, notamment de nombreuses attaques sur des bovins en situation protégée, il y a lieu d’intervenir sur cette meute.&lt;/li&gt;&lt;li&gt;Que les mesures de régulations de l’année passée visant les louveteaux, n’ont pas donnés les effets escomptés.&lt;/li&gt;&lt;li&gt;Que des mesures plus strictes doivent être mises en place, soit &amp;nbsp;l’élimination complète de la meute du Mont Tendre.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;L’OFEV estime donc que la demande cantonale est justifiée par la prévention de futurs dommages aux animaux de rente. En prélevant la meute du Mont Tendre, la région se retrouvera avec un nombre de meute au-dessus du seuil minimal.&lt;/p&gt;&lt;p&gt;Mais l’OFEV mentionne que pour des raisons de protection des jeunes et de la mère, les louveteaux doivent être tirés en premier (art. 7, al. 4, LChP)&amp;nbsp;».&lt;/p&gt;&lt;p&gt;Aujourd’hui au 25 septembre, près de quarante attaques avec issue mortelle ont été perpétrées par cette meute dans la région. Avec les attaques des autres meutes dans le Jura vaudois, nous arrivons à presque une attaque par nuit.&lt;/p&gt;&lt;p&gt;Depuis le 3 septembre, les gardes-chasses sont à l’affut chaque nuit afin de pouvoir procéder au tir de la meute, principalement sur les lieux des attaques ou le loup reviennent plusieurs fois par nuit.&lt;/p&gt;&lt;p&gt;Malheureusement, en raison de l’exigence de l’OFEV de tirer en premier lieu les jeunes louveteaux, les gardes-chasses voient plusieurs fois par nuit des loups adultes dans leur viseur, mais n’ont pas le droit de tirer.&lt;/p&gt;&lt;p&gt;Tenant compte de l’urgence et du manque d’efficacité des mesures précédentes, le Conseil fédéral&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Estime-il normal le délai de 3 semaines entre la demande du Canton et l’autorisation délivrée par l’OFEV&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Ne devrait-il pas autoriser le tir de la Meute, sans la restriction sur les priorités de tirer les jeunes louveteaux&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 13. August 2024 reichte das Département de la Jeunesse, de l'environnement et de la sécurité (DJES) des Kantons Waadt beim BAFU ein neues Gesuch zum Abschuss von Wölfen ein. Es betraf die vollständige Eliminierung des Rudels auf dem Mont Tendre, das für rund 20 Wolfsangriffe auf Herden im Waadtländer Jura verantwortlich gemacht wird. In dieser Region gibt es neben einigen einzelnen Wölfen fünf Rudel, darunter auch das hier angesprochene Rudel.&lt;/p&gt;&lt;p&gt;In seinem Entscheid vom 3. September 2024 (also 3 Wochen nach Einreichung des Gesuchs) befand das BAFU :&lt;/p&gt;&lt;ul&gt;&lt;li&gt;- Dass aufgrund des unerwünschten Verhaltens des Rudels auf dem Mont Tendre, insbesondere wegen der zahlreichen Angriffe auf Rinder in geschützter Lage, gegen dieses Rudel vorgegangen werden muss.&lt;/li&gt;&lt;li&gt;- Dass die im vergangenen Jahr getroffenen Regulierungsmassnahmen, die auf Wolfswelpen abzielten, nicht die erhofften Auswirkungen hatten.&lt;/li&gt;&lt;li&gt;- Dass strengere Massnahmen umgesetzt werden müssen, das heisst die vollständige Eliminierung des Rudels auf dem Mont Tendre.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Das BAFU gelangt daher zur Ansicht, dass das Gesuch des Kantons gerechtfertigt ist, weil durch den Abschuss zukünftige Schäden an Nutztieren verhindert werden. Auch wenn das Rudel auf dem Mont Tendre eliminiert wird, läge die Zahl der Rudel in der Region immer noch über der Mindestschwelle.&lt;/p&gt;&lt;p&gt;Aber das BAFU erwähnt, dass aus Gründen des Schutzes der Jungtiere und der Mutter die Wolfswelpen zuerst geschossen werden müssen (Art. 7, Abs. 4, JSG).&lt;/p&gt;&lt;p&gt;Bis zum 25. September gingen in der Region fast vierzig Angriffe mit tödlichem Ausgang auf das Konto dieses Rudels. Zusammen mit den Angriffen der anderen Rudel im Waadtländer Jura ergibt das beinahe einen Angriff pro Nacht.&lt;/p&gt;&lt;p&gt;Seit dem 3. September liegen die Wildhüter jede Nacht auf der Lauer, um das Rudel abschiessen zu können, dies vor allem an Orten, an denen es zu Angriffen gekommen ist oder an denen die Wölfe mehrmals pro Nacht zurückkehren.&lt;/p&gt;&lt;p&gt;Mehrmals pro Nacht sehen die Wildhüter durch ihr Visier erwachsene Wölfe, dürfen diese aber aufgrund der Forderung des BAFU, in erster Linie junge Wölfe zu schiessen, nicht erlegen.&lt;/p&gt;&lt;p&gt;Eingedenk der Dringlichkeit und der mangelnden Wirksamkeit der bisherigen Massnahmen stelle ich dem Bundesrat die folgenden Fragen:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;- Hält er die Frist von drei Wochen zwischen dem Antrag des Kantons und der vom BAFU erteilten Bewilligung für normal?&lt;/li&gt;&lt;li&gt;- Sollte er nicht den Abschuss des Rudels erlauben, ohne einschränkend die Erlegung von Jungwölfen zu priorisieren?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badran Jacqueline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesetzliche Grundlage für den Verteilmechanismus für die Ergänzungssteuer-Erträge aus der OECD-Mindestbesteuerung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bases légales pour un mécanisme de répartition des recettes fiscales complémentaires provenant de l'imposition minimale prévue par l'OCDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creare la base legale per il meccanismo di ripartizione del gettito lordo dell'imposta integrativa in seguito all'imposizione minima dell'OCSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'exposer avec des chiffres les conséquences d'une meilleure répartition entre la Confédération et les cantons du produit brut de l'impôt complémentaire et de présenter un projet de loi spéciale s'y rapportant. Il étudiera et présentera les diverses variantes avec une clé de répartition en parts égales entre la Confédération (50&amp;nbsp;%) et les cantons (50&amp;nbsp;%), avec une redistribution limitée à 200 et à de 400&amp;nbsp;francs par personne. &amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Folgen einer verbesserten Aufteilung des Rohertrags der Ergänzungssteuer zwischen Bund und Kantonen mit Zahlen aufzuzeigen &amp;nbsp;und ein entsprechendes Spezialgesetz vorzulegen. Dabei untersucht der Bundesrat und legt Varianten vor, die einen Rückverteilsschlüssel von 50 Prozent je Bund und Kantonen beinhalten kombiniert mit einer limitierten Rückverteilung mit Obergrenze pro Einwohnerin und Einwohner von 200 Franken pro Person respektive 400 Franken pro Person. &amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Wirtschaft|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Économie|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Economia|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Müller-Altermatt Stefan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logistiklasten erfassen und ausgleichen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prendre en compte et compenser les charges logistiques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rilevare e compensare gli oneri logistici</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les entreprises de logistique sont judicieusement regroupées et implantées à proximité des grands axes de transport et d’installations ferroviaires. C’est le cas par exemple dans le Gäu soleurois, le long de l’A1. En tant que «&amp;nbsp;Logistic&amp;nbsp;Valley&amp;nbsp;», la région joue aujourd’hui un rôle central pour l’approvisionnement du pays.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Même si cette implantation en clusters est judicieuse du point de vue de l’intérêt général, les défis auxquels les régions concernées doivent alors faire face sont importants. L’implantation des entreprises de logistique nécessite de nombreux projets de construction de routes et autres, avec les coûts et les investissements élevés qui en découlent, ainsi que des coûts supplémentaires pour les communes et le canton dans le domaine de la formation et de l’intégration.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;En revanche, la valeur ajoutée directe du secteur logistique n’est pas particulièrement élevée et, par conséquent, les impôts sur les bénéfices ne le sont pas non plus. Dans ce secteur, la plupart des emplois se situent dans le segment des salaires plutôt bas, ce qui crée peu de croissance pour ce qui est des impôts des personnes physiques. En résumé, les coûts augmentent alors que les bénéfices restent stables ou n’augmentent que légèrement. Cet état de fait se reflète également dans la faiblesse des ressources du canton de Soleure dans la péréquation financière nationale.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le compte est donc de moins en moins bon, et de plus en plus de communes s’opposent à des développements judicieux pour l’intérêt général.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;La question se pose de savoir si, par analogie avec d’autres charges (dues à des facteurs géo-topographiques ou socio-démographiques), cette charge du secteur logistique pourrait être compensée de manière pertinente. Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Partage-t-il l’avis que la région de Gäu (avec les régions limitrophes) joue un rôle important pour l’approvisionnement du pays et que, ce faisant, elle est grevée de charges non compensées&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Partage-t-il l’inquiétude selon laquelle il devient de plus en plus difficile, en raison des charges, de pouvoir satisfaire les besoins de la logistique sur des sites appropriés et que, par conséquent, la branche risque de se tourner vers des sites ayant un impact plus important sur l’homme, la nature et les infrastructures&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3) Dispose-t-il d’indicateurs ou d’études permettant de mesurer l’ampleur des charges logistiques&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Est-il prêt à intégrer les charges logistiques dans la péréquation financière nationale en tant que partie de la compensation des charges&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Logistikbetriebe werden sinnvollerweise geclustert und in der Nähe der Hauptverkehrsachsen und zu Bahnanlagen angesiedelt. Dies ist entlang der A1, beispielsweise im Solothurner Gäu, geschehen. Die Region erfüllt heute als «Logistic-Valley» eine für die Landesversorgung zentrale Aufgabe.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;So sinnvoll diese geclusterte Ansiedlung aus übergeordneter Sicht ist, so gross sind die Herausforderungen, mit denen die betroffenen Regionen dann zu kämpfen haben. Mit den Ansiedlungen der Logistikbetriebe werden zahlreiche Strassen- und sonstige Bauprojekte mit entsprechenden Kosten und hohem Investitionsbedarf nötig und auch im Bildungs- und Integrationsbereich fallen Mehrkosten für die Gemeinden sowie den Kanton an.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die direkte Wertschöpfung der Logistikbranche hingegen ist nicht sonderlich hoch und entsprechend fallen auch keine hohen Gewinnsteuern ab. Die Arbeitsplätze der Branche liegen mehrheitlich im eher tieferen Lohnsegment und führen ergo auch im Bereich der Steuern von natürlichen Personen zu wenig Wachstum. Zusammenfassend wachsen also die Kosten bei gleichbleibenden oder nur leicht steigenden Erträgen. Dieses Bild zeigt sich auch in der Ressourcenschwäche des Kantons Solothurn im NFA.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die Rechnung geht folgerichtig immer weniger auf und es regt sich in immer mehr Gemeinden Widerstand gegen übergeordnet sinnvolle Entwicklungen.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Es stellt sich also die Frage, ob analog anderer Lasten (geografisch-topografisch; sozio-demografisch) diese dargelegte Last der Logistikbranche sinnvoll ausgeglichen werden kann. Diesbezüglich erbitte ich den Bundesrat um Antwort auf die folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1) Teilt der Bundesrat die Ansicht, dass die Region Gäu (zusammen mit den angrenzenden Regionen) eine wichtige Aufgabe für die Landesversorgung erfüllt und in Erfüllung dieser Aufgabe mit nicht ausgeglichenen Lasten belastet wird?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2) Teilt der Bundesrat die Bedenken, dass es aufgrund der Lasten immer schwieriger wird, die Bedürfnisse der Logistik an geeigneten Standorten befriedigen zu können und deshalb die Gefahr droht, dass die Branche ausweicht auf Standorte mit höheren Auswirkungen auf Mensch, Natur und Infrastruktur?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3) Verfügt der Bundesrat über Messgrössen oder Studien, welche eine Aussage über das Ausmass der Logistiklasten zulassen?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4) Ist der Bundesrat bereit, die Logistiklasten als Teil des Lastenausgleichs in den NFA zu integrieren?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prelicz-Huber Katharina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stipendien, die zum Leben reichen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Des bourses couvrant les frais de subsistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borse di studio sufficienti al sostentamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de créer les bases légales permettant à la Confédération de soutenir, au moyen de financements incitatifs, les cantons et les communes qui allouent des aides à la formation couvrant les frais de subsistance durant toute la durée d'une formation ou d'une formation continue.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen zu schaffen, die es dem Bund ermöglichen, Gemeinden und Kantone in Form einer Anschubfinanzierung zu unterstützen, welche Aus- und Weiterbildungsbeiträge existenzsichernd und über die ganzen Erwerbsjahre gewähren.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belprahon, endgültig eine Berner Gemeinde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belprahon, commune définitivement bernoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral (CF) a écrit (question 24.7640) que le transfert de Moutier "permettra de mettre un point final à la Question jurassienne". Le 16.09.2024, le comité "Belprahon dit oui" a publié que voter oui au Concordat le 22.09.2024 est "le meilleur moyen d'entretenir l'espoir d'un rattachement futur de Belprahon au canton du Jura".&lt;br&gt;Le CF peut-il&lt;br&gt;1. confirmer que Belprahon a voté le 17.09.2017 par 121 contre 114 pour rester bernoise?&lt;br&gt;2. et que ce vote est régulier, incontestable et définitif?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat schrieb in seiner Antwort auf die Frage 24.7640, dass mit dem Kantonswechsel von Moutier die Jurafrage endgültig gelöst werden kann. Das Komitee "Belprahon sagt Ja» schrieb am 16. September 2024, eine Ja-Stimme zum Konkordat vom 22. September 2024 sei das beste Mittel, um die Hoffnung auf einen zukünftigen Anschluss von Belprahon an den Kanton Jura am Leben zu halten.&lt;br&gt;Kann der Bundesrat bestätigen, dass;&lt;br&gt;1. Belprahon am 17. September 2017 mit 121 zu 114 Stimmen für den Verbleib im Kanton Bern gestimmt hat?&lt;br&gt;2. diese Abstimmung ordnungsgemäss erfolgt ist und das Ergebnis unanfechtbar und endgültig ist?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studie zu einem dritten Juradurchstich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planification concernant la troisième traversée du Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studio sul terzo traforo del Giura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l’art.&amp;nbsp;1, al. 3, let. g, de l’arrêté fédéral sur l’aménagement&amp;nbsp;2025 de l’infrastructure ferroviaire, des travaux de planification et des études préparatoires doivent être réalisés pour le tronçon entre Bâle et le Mittelland (3e traversée). Les cantons du nord-ouest de la Suisse et les CFF ont procédé à diverses clarifications jusqu’à l’établissement de l’arrêté fédéral précité. Depuis, le dossier est en suspens. Seul le plan en cinq points du nœud de Bâle contient la nouvelle traversée du Jura («&amp;nbsp;tunnel de Wisenberg&amp;nbsp;») comme une étape. L’état d’avancement du projet et les conséquences qui en découlent ne sont toujours pas connus.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Il serait important de disposer d’informations solides et fiables sur une nouvelle traversée du Jura, notamment dans la perspective des nouvelles offres qui seront examinées dans le cadre de l’étape d’aménagement du message&amp;nbsp;2030. Ainsi (outre les nouvelles offres de transport de voyageurs sur grandes lignes et de marchandises), les concepts d’offre régionaux importants ne peuvent être élaborés de manière judicieuse sans savoir si la nouvelle traversée sera réalisée ou non et dans quel délai. Cette sécurité de planification est nécessaire pour traiter de manière ciblée les dépendances du côté de l’offre d’une nouvelle percée dans le Jura avec l’extension nécessaire des capacités du nœud de Bâle, y compris la gare souterraine de Bâle CFF (prévue par le message&amp;nbsp;2026 sur l’aménagement ferroviaire) pour tous les types de trafic.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les études devraient être lancées rapidement dans le but d’obtenir à temps les résultats et que ceux-ci soient encore traités par les régions de planification. Du point de vue de l’aménagement du territoire, il serait également important d’obtenir rapidement des informations&amp;nbsp;: le développement de l’urbanisation dans les régions concernées de Liestal et d’Olten doit être coordonné suffisamment tôt avec l’extension du réseau ferroviaire.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Une étude préliminaire pour une nouvelle traversée du Jura est-elle prévue dans la perspective du message&amp;nbsp;2030&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quand les résultats des études correspondantes, avec examen des variantes et des étapes de réalisation, seront-ils disponibles&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral convient-il qu’une offre doit être immédiatement obtenue dans le but de garantir une coordination et, par conséquent, une sécurité globale de la planification pour les grandes extensions&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gemäss Art. 1. Abs. 3 lit. g Bundesbeschluss über den Ausbauschritt 2025 der Eisenbahninfrastruktur sind vorbereitende Planungsarbeiten und Studien für den Korridor Basel – Mittelland (3. Juradurchstich) zu erstellen. Nachdem bis zum genannten Bundesbeschluss die Nordwestschweizer Kantone und die SBB verschiedene Abklärungen getroffen hatten, ist es seitdem ruhig geworden. Einzig im Fünf-Punkte-Plan des Knotens Basel ist der neue Juradurchstich («Wisenbergtunnel») als ein Element enthalten. Es bleibt dabei allerdings offen, wie der Zielzustand und dessen mögliche Realisierungsabfolgen aussehen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Nicht zuletzt im Hinblick auf neue Angebote, die im Rahmen des Ausbauschrittes in der Botschaft 2030 zur Prüfung gelangen werden, wären fundierte und belastbare Erkenntnisse zu einem neuen Juradurchstich wichtig. So können (neben neuen Personenfern- und Güterverkehrsangeboten) vor allem wichtige regionale Angebotskonzepte nur sinnvoll erstellt werden, wenn klar ist, ob bzw. in welchem Zeithorizont mit einem neuen Juradurchstich gerechnet werden kann und wie dieser konfiguriert ist. Diese Planungssicherheit ist elementar, um die angebotsseitigen Abhängigkeiten eines neuen Juradurchstichs mit dem notwendigen Kapazitätsausbau im Knoten Basel inkl. Tiefbahnhof Basel SBB (Forderung Botschaft 2026) für alle Verkehrsarten zielorientiert zu bearbeiten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Damit die Studienergebnisse rechtzeitig vorliegen und von den Planungsregionen noch verarbeitet werden können, müssten entsprechende Arbeiten rasch gestartet werden. Auch aus raumplanerischer Sicht wären baldige Erkenntnisse wichtig, da die Siedlungsentwicklung in den betroffenen Räumen Liestal und Olten frühzeitig mit dem Bahnausbau abgestimmt werden muss.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird deshalb gebeten, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wird im Hinblick auf die Botschaft 2030 eine Vorstudie für einen neuen Juradurchstich erstellt?&lt;/li&gt;&lt;li&gt;Wann werden entsprechende Studienergebnisse mit Variantenüberprüfung und Realisierungsabfolgen vorliegen?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat die Auffassung, dass eine planerische Koordination und damit umfassende Planungssicherheit bei grossen Bahnausbauten, die sich bzgl. Angebot unmittelbar bedingen, zu gewährleisten ist?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schweizer Bäche in schlechtem Zustand – was unternimmt der Bundesrat?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petits cours d’eau suisses en mauvais état. Qu’entreprend le Conseil fédéral ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’&lt;a href="https://www.eawag.ch/de/info/portal/aktuelles/news/defizite-im-oekologischen-zustand-schweizer-baeche/"&gt;&lt;u&gt;étude du 6&amp;nbsp;mai&amp;nbsp;2024 menée par l’Institut fédéral pour l’aménagement, l’épuration et la protection des eaux&lt;/u&gt;&lt;/a&gt; a analysé 99&amp;nbsp;ruisseaux suisses situés dans le Plateau, certaines parties du Jura et zones de plaines des grandes vallées. Les résultats montrent que la majorité des cours d’eau analysés ne peut remplir sa fonction d’habitat pour les animaux que de façon restreinte. De nombreux cours d’eau sont enterrés et, dans les bassins versants caractérisés par une forte utilisation agricole, souvent pollués par des pesticides.&lt;br&gt;- Quel regard le Conseil fédéral porte-t-il sur ces conclusions&amp;nbsp;?&lt;br&gt;- Quelles mesures prend-il pour y remédier&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Eine &lt;a href="https://www.eawag.ch/de/info/portal/aktuelles/news/defizite-im-oekologischen-zustand-schweizer-baeche/"&gt;&lt;u&gt;Studie der EAWAG vom 6. Mai 2024&lt;/u&gt;&lt;/a&gt; hat 99 Schweizer Bäche untersucht und kommt zum Schluss, dass die Mehrheit dieser Bäche im Mittelland, in Teilen des Juras und der Talebenen grösserer Täler ihre Rolle als Lebensraum für Tiere nur eingeschränkt wahrnehmen können. Viele Gewässer sind eingedolt und in stark landwirtschaftlich genutzten Einzugsgebieten oft durch Pestizide belastet.&lt;br&gt;-&amp;nbsp;Wie beurteilt der Bundesrat diese Erkenntnisse?&lt;br&gt;-&amp;nbsp;Welche Massnahmen ergreift er?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jurassischer Separatismus und Respekt vor den Institutionen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le séparatisme jurassien dans le respect des institutions ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;La destruction du "Fritz" des Rangiers par les séparatistes jurassiens du Groupe Bélier le 10.08.1989 et les tags "DMF tue" et une croix gammée sur le socle constituent-ils des actes les plus propres qui soient et des marques de respect des institutions au yeux du Conseil fédéral ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden. Am 10. August 1989 zerstörten jurassische Separatisten der Béliers die Statue Le Fritz, die «Wache von Les Rangiers», und verschmierten den Sockel mit dem Slogan "DMF tue" und einem Hakenkreuz.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;L'irruption de militants sépatistes du Bélier qui se sont menottés le 11.12.1968 dans la salle du Conseil national lors de l'élection du CF von Moos à la Présidence constitue-elle un acte des plus propre qui soit et une marque de respect des institutions au yeux du Conseil fédéral?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden.&lt;br&gt;Am 11. Dezember 1968 drangen anlässlich der Wahl von Bundesrat von Moos zum Bundespräsidenten militante Separatisten der Béliers in den Nationalratssaal ein.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La CF Elisabeth Baume-Schneider a déclaré le 23.06.2024 (19h30, RTS1) que la création du canton du Jura avait été faite "de la manière la plus propre qui soit" en "respectant les institutions du point de vue fédéral".&lt;br&gt;L'incendie du pont en bois de Büren an der Aare le 5/6 avril 1989 par des activistes jurassiens constituent-ils un acte les plus propres qui soit et une marque de respect des institutions au yeux du Conseil fédéral ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Bundesrätin Elisabeth Baume-Schneider sagte am 23. Juni 2024 (19.30 Uhr, RTS 1), die Gründung des Kantons Jura sei auf die sauberste Art und Weise erfolgt und die Institutionen seien aus Bundessicht respektiert worden. Am 5./6. April 1989 verübten jurassische Aktivisten einen Brandanschlag auf die Holzbrücke in Büren an der Aare.&lt;br&gt;Ist dies nach Ansicht des Bundesrates die sauberste Art und Weise und ein Zeichen des Respekts vor den Institutionen?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20247642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachlässigkeit, Sparen oder Grenzen aufheben?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laxisme, économies ou volonté de supprimer la frontière?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lassismo, misure di risparmio o volontà di sopprimere le frontiere?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le mur en pierres sèche, les bornes, et la laie frontière ne sont quasiment plus entretenus. Si rien n'est entrepris rapidement, ce riche patrimoine historique et culturel va disparaître.&lt;/p&gt;&lt;p&gt;Aussi, j’ai l’honneur de poser les questions suivantes au CF&amp;nbsp;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel office est compétent, et responsable de l’entretien de la laie frontière, du mur, des bornes et des frontières territoriales de notre pays&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Pourquoi l’entretiens de la frontière, soit le mur frontière, les bornes et la laie frontière n’est plus exécuté&amp;nbsp;afin de maintenir ce patrimoine ?&lt;/li&gt;&lt;li&gt;Quelle mesure le CF entent-il prendre pour garantir et maintenir par un entretien, ce riche patrimoine historique et culturel fédéral&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Trockenmauern, Grenzsteine und Grenzschneisen werden kaum noch gepflegt. Wenn nicht bald etwas unternommen wird, wird dieses reiche historische und kulturelle Erbe verschwinden.&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Welches Amt ist zuständig für den Unterhalt von Grenzschneisen, Grenzmauern, Grenzsteinen und unserer Landesgrenze?&lt;/li&gt;&lt;li&gt;Warum wird nicht mehr für den Grenzunterhalt gesorgt? Mit dem Unterhalt von Grenzmauern, Grenzsteinen und Grenzschneisen könnte das erwähnte Erbe aufrecht erhalten werden.&lt;/li&gt;&lt;li&gt;Welche Massnahmen gedenkt der Bundesrat zu ergreifen, um dieses reiche historische und kulturelle Erbe des Bundes zu unterhalten, damit es gesichert bleibt?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Sicherheitspolitik|Kultur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Politique de sécurité|Culture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Cultura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nichtverwendung des Repartitionswerts beim NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPT. Prendre en compte la valeur de répartition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mancato impiego del valore di ripartizione nel quadro della NPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le calcul du potentiel de ressources dans le cadre de la RPT repose sur des valeurs de référence qui s'appliquent à l'impôt fédéral direct. Or pour les logements en propriété, ce sont les valeurs déterminantes pour l’impôt sur la fortune qui prévalent, ce qui ne manquer pas d’irriter.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Pour quelle raison le calcul du potentiel de ressources repose-t-il pour les logements en propriété sur les valeurs de l'impôt cantonal sur la fortune, alors que pour le revenu ou le bénéfice, notamment, ce sont celles de l'impôt fédéral direct qui sont prises en compte&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Pourquoi la valeur de réparation n'est-elle pas prise en compte pour déterminer le potentiel de ressources pour les valeurs patrimoniales relatives aux logements en propriété&amp;nbsp;? En quoi consistent les coûts supplémentaires dont il a été question dans la phase de projet et à combien se chiffreraient-ils&amp;nbsp;?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Quelles conséquences financières aurait la prise en compte des valeurs de répartition&lt;/p&gt;&lt;p&gt;sur le potentiel de ressources et, partant, sur la répartition des paiements RPT&amp;nbsp;?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Berechnung des Ressourcenpotentials beim NFA beruht grundsätzlich auf Referenzwerten, welche für die direkte Bundessteuer gelten. Eine Ausnahme bilden die Vermögenssteuerwerte bei Eigenheimen, was irritierend ist.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte, den Bundesrat um Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Aus welchem Grund werden für die Berechnung des&amp;nbsp;Ressourcenpotentials die kantonalen Vermögenssteuerwerte bei&amp;nbsp;den Eigenheimen herangezogen, obwohl für die anderen Grössen wie dem&amp;nbsp;Einkommen oder dem Gewinn die Werte für die direkten Bundessteuern&lt;/p&gt;&lt;p&gt;berücksichtigt werden?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2.&amp;nbsp;Warum wird zur Bestimmung des Ressourcenpotentials für die Vermögenswerte der Eigenheime nicht der Repartitionswert berücksichtigt? Worin besteht der Mehraufwand, mit dem in der Projektphase argumentiert wurde und wie hoch wäre dieser zu beziffern?&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3.&amp;nbsp;Welche finanziellen Auswirkungen hätte die Berücksichtigung der Repartitionswerte auf das Ressourcenpotential und damit auf die Verteilung der NFA-Zahlungen?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glarner Andreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Post geht eine strategische Partnerschaft mit Western Union ein. Was soll das?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Poste signe un partenariat stratégique avec Western Union. Qu’est-ce que ça signifie?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Posta stringe un partenariato strategico con Western Union. Che senso ha?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Depuis la fin avril 2024, la Poste propose une offre supplémentaire à sa clientèle&amp;nbsp;: le prestataire de paiement Western Union est désormais présent dans les filiales de la Poste en exploitation propre. Il est ainsi possible de transférer de l’argent dans plus de 200 pays, comme le précise un &lt;a href="https://www.post.ch/fr/notre-profil/medias/communiques-de-presse/2024/la-poste-signe-un-partenariat-strategique-avec-western-union"&gt;communiqué de presse&lt;/a&gt; de la Poste daté du 3&amp;nbsp;avril 2024.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Déjà présents dans les filiales de la Poste, les prestataires de services financiers que sont PostFinance, la Banque Migros, la Bernerland Bank et la Cornèr Bank se voient compléter par Western Union, alors que les prestataires de services que sont Assura, Axa, le Groupe Mutuel, le Canton du Jura, SwissCaution et Sympany font déjà partie de l’«&amp;nbsp;équipement standard&amp;nbsp;» d’une filiale postale. L’objectif déclaré de la Poste est de transformer ses filiales en centres de services régionaux. La Poste outrepasse ainsi largement son mandat de service universel et désavantage les prestataires du marché libre. Qui plus est, l’intégration de Western Union dans toutes les filiales de la Poste facilitera grandement la tâche des demandeurs d’asile et des personnes admises à titre provisoire pour transférer de l’argent de l’aide sociale vers leur pays d’origine.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Face à cette situation, je prie le Conseil fédéral de bien vouloir répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;- Dans quelle mesure la transformation des filiales de la Poste en centres de services régionaux est-elle compatible avec le mandat de service universel&amp;nbsp;?&lt;/p&gt;&lt;p&gt;- Quels sont, en matière de droit de la concurrence, les effets de l’augmentation permanente de la taille des centres de services régionaux de la Poste&amp;nbsp;?&lt;/p&gt;&lt;p&gt;- Que pense le Conseil fédéral de la violation de l’art.&amp;nbsp;121a de la Constitution fédérale (gestion de l’immigration), étant donné qu’il vante la possibilité pour les demandeurs d’asile ou les personnes admises à titre provisoire de transférer plus facilement de l’argent de l’aide sociale vers leur pays d’origine en raison de la présence accrue de Western Union dans une entreprise de la Confédération&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ab Ende April 2024 öffnet die Post ihr Filialnetz für ein weiteres Kundenangebot: Die Zahlungsdienstleisterin Western Union wird in den eigenbetriebenen Filialen der Post präsent sein. Neu kann somit in den Postfilialen Geld in mehr als 200 Länder überwiesen werden, wie sie in einem &lt;a href="https://www.post.ch/de/ueber-uns/medien/medienmitteilungen/2024/post-geht-strategische-partnerschaft-mit-western-union-ein"&gt;Mediencommuniqué&lt;/a&gt;&amp;nbsp;vom 3. April 2024 festhält.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Neben Western Union sind bereits die PostFinance, die Migros Bank, die Bernerland Bank und die Cornèr Bank als Finanzdienstleister in den Postfilialen präsent. Weiter gehören bereits Dienstleister wie Assura, Axa, Groupe Mutuel, Kanton Jura, Swisscaution und Sympany zur “Standardausrüstung” einer Postfiliale. Es ist das erklärte Ziel der Post, die Postfilialen in regionale Dienstleistungszentren umzubauen. Die Post überschreitet damit ihren Grundversorgungsauftrag bei weitem und benachteiligt Anbieter des freien Marktes. Zudem wird durch die Aufnahme von Western Union in alle Postfilialen die Überweisung von Sozialhilfegeldern durch Asylbewerber und vorläufig Aufgenommene in deren Herkunftsländer stark erleichtert.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten zu folgenden Fragen Stellung zu beziehen:&lt;/p&gt;&lt;p&gt;- Inwiefern lässt sich der Ausbau der Postfilialen in regionale Dienstleistungszentren mit dem Grundversorgungsauftrag vereinbaren?&lt;/p&gt;&lt;p&gt;- Welche wettbewerbsrechtlichen Auswirkungen entstehen durch die immer grösseren regionalen Dienstleistungszentren der Post?&lt;/p&gt;&lt;p&gt;- Wie gewichtet der Bundesrat den Verstoss gegen Artikel 121a der Bundesverfassung (Steuerung der Zuwanderung), da er mit der vermehrten Präsenz von Western Union in einem Bundesbetrieb, die Möglichkeit für Asylbewerber oder vorläufig Aufgenomme anpreist, Sozialhilfegelder einfacher in die Herkunftsländer zu überweisen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kälin Irène</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufwand der Kantone für Veranlagung und Einzug der Bundessteuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dépenses cantonales pour la taxation et la perception de l’impôt fédéral direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onere dei Cantoni per l’imposizione e l’esazione dell’imposta federale diretta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;En vertu de l’art.&amp;nbsp;128, al.&amp;nbsp;4, de la Constitution, la part des cantons au produit de l’impôt fédéral direct doit être d’au moins 17&amp;nbsp;%. L’art.&amp;nbsp;196, al.&amp;nbsp;1, de la loi fédérale sur l’impôt fédéral direct fixe quant à lui à 21,2&amp;nbsp;% la part qui revient aux cantons pour les personnes physiques et morales.&amp;nbsp;La taxation et la perception sont effectuées par les cantons. Que les cantons puissent garder une part de l’impôt fédéral direct s’explique notamment par le fait qu’ils se chargent de la taxation et de la perception de l’impôt pour la Confédération. En raison de la transformation numérique et des gains d’efficacité qui en découlent, la charge administrative liée à la taxation et à la perception de l’impôt a dû continuellement diminuer pour les cantons au cours des dernières années. Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;À combien s’élèvent, à l’heure actuelle, les dépenses des cantons pour la taxation et la perception de l’impôt fédéral direct&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces dépenses ont-elles évolué au cours des dix dernières années&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles autres prestations fournies par les cantons en exécution de lois fédérales sont-elles indemnisées par la part de 21,2&amp;nbsp;% qui leur revient aujourd’hui&amp;nbsp;? Lesquelles d’entre elles sont-elles fournies sur la base d’une convention de prestations ou d’autres dispositions contractuelles&amp;nbsp;?&lt;/li&gt;&lt;li&gt;À combien s’élevaient les montants par prestation convenue et par canton en 2023 ou pour le dernier exercice bouclé&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Nach Artikel 128 Absatz 4 Bundesverfassung beträgt der Anteil der Kantone an der direkten Bundessteuer mindestens 17 Prozent. In Artikel 196 Absatz 1 des Bundesgesetzes über die direkte Bundessteuer ist der Kantonsanteil für natürliche und juristische Personen aktuell bei 21,2 Prozent festgelegt.&amp;nbsp;Die Bundessteuer wird von den Kantonen veranlagt und eingezogen. Der Anteil der Bundessteuern, der bei den Kantonen verbleibt wird u.a. auch damit begründet, dass die Kantone das für den Bund die Veranlagung und den Einzug der Bundesstern machen. Dank Digitalisierung und der damit einhergehenden Effizienzsteigerung dürfte der administrative Aufwand, der bei den Kantonen anfällt für die Veranlagung und den Einzug der Bundessteuern, in den letzten Jahren kontinuierlich gesunken sein. Vor diesem Hintergrund bitte ich um die Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie hoch beziffert sich aktuell der Aufwand der Kantone für das Veranlagen und den Einzug der Bundessteuer?&lt;/li&gt;&lt;li&gt;Wie hat sich dieser Aufwand in den letzten zehn Jahren verändert?&lt;/li&gt;&lt;li&gt;Welche weiteren Leistungen, die die Kantone in Erfüllung von Bundesgesetzen erbringen, sind mit dem heutigen Kantonsanteil von 21,2 abgegolten? Welche davon beruhen auf Leistungsvereinbarungen oder anderen vertraglichen Regelungen?&lt;/li&gt;&lt;li&gt;Wie hoch waren die Beträge pro vereinbarter Leistung und pro Kanton im Jahr 2023 bzw. im jüngsten abgerechneten Rechnungsjahr?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Médias et communication|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Media e comunicazione|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einfacher Zugang zu Ergänzungsleistungen für Anspruchsberechtigte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rendre les prestations complémentaires aisément accessibles aux personnes qui y ont droit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facilitare l'accesso alle prestazioni complementari per chi ne ha diritto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale, et à l'article 84, lettre o, de la Constitution cantonale, le Parlement fait usage du droit d'initiative du Canton en matière fédérale et demande aux Chambres fédérales de modifier urgemment la loi fédérale sur les prestations complémentaires (LPC, 831.30) afin de garantir un accès aisé, voire automatique, à ces prestations pour les personnes qui y ont droit.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel 160 Absatz 1 der Bundesverfassung und Artikel 84 Buchstabe o der Verfassung des Kantons Jura fordert das Parlament des Kantons Jura die Bundesversammlung dazu auf, schnellstmöglich das Gesetz über Ergänzungsleistungen zur Alters-, Hinterlassenen- und Invalidenversicherung (ELG, 831.30) dahingehend anzupassen, dass jene, die Anspruch auf Ergänzungsleistungen haben, leichter oder sogar automatisch Zugang zu diesen haben.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soziale Fragen|Sozialer Schutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions sociales|Protection sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questioni sociali|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiederherstellung des Wettbewerbs- und Konsumentenschutzes im Autohandel. Beseitigung eines Handelshemmnisses bei Elektrofahrzeugen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantie constructeur pour les véhicules électriques importés. Rétablir une concurrence équitable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ripristinare la protezione della concorrenza e dei consumatori nel commercio di autoveicoli. Eliminare un ostacolo al commercio di veicoli elettrici</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier l’ordonnance automobile (OAVAuto) afin d’assurer que la garantie constructeur (GC) sera valable dans tous les cas, que le véhicule ait fait l’objet d’une importation directe ou parallèle.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, durch Änderung der KFZ-Verordnung (KFZV) sicherzustellen, dass bei Parallel- oder Direktimporten von Kraftfahrzeugen die Herstellergarantie unabhängig vom Vertriebskanal gewährleistet bleibt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Verkehr|Energie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Transports|Énergie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Trasporti|Energia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weichelt Manuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schaffung von Anlauf- und Meldestellen für Gewaltopfer in Institutionen für Menschen mit Behinderungen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création de centres de consultation et services de signalement pour les personnes handicapées victimes de violence institutionnelle </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Istituire servizi di assistenza e segnalazione per le persone con disabilità istituzionalizzate vittime di violenza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est prié de proposer une révision de la LIPPI rendant obligatoire l’existence de centres de consultation et services de signalement destinés aux victimes de violence dans les institutions pour personnes handicapées.&lt;/p&gt;&lt;p&gt;Ces centres de consultation et services de signalement devront être indépendants des institutions, garantir la confidentialité et être accessibles à toutes les personnes handicapées et à leurs proches. Ils seront mis en place en étroite collaboration avec les personnes handicapées et les organisations qui les représentent. Dans la mesure du possible, ils seront rattachés à des structures existantes afin de créer des synergies.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt mit einer Revision des IFEG dafür zu sorgen, dass Anlauf- und Meldestellen für Gewaltopfer in Institutionen für Menschen mit Behinderungen obligatorisch werden.&lt;/p&gt;&lt;p&gt;Diese Anlauf- und Meldestellen müssen unabhängig von Institutionen arbeiten, vertraulich sein und für alle Menschen mit Behinderungen und ihre Angehörigen zugänglich sein. Sie sind in enger Zusammenarbeit mit Menschen mit Behinderungen und den Organisationen von Menschen mit einer Behinderung zu entwickeln. Wo immer möglich, sollten Synergien geschaffen werden, indem sie an bestehende Strukturen angegliedert werden.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soziale Fragen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storni Bruno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entwicklung der Gesundheitskosten in den Kantonen je nach demografischer Entwicklung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution des coûts de la santé dans les cantons en fonction de l'évolution de la structure d'âge de leur population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evoluzione dei costi della salute nei cantoni in funzione della crescente diversa evoluzione demografica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La différence de la structure d’âge de la population résidente s’accentue de plus en plus entre les cantons ruraux périphériques à faible développement économique et les cantons urbains à fort développement économique.&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si les plus de 65 ans représentent 19&amp;nbsp;% de la population suisse, leur proportion se monte à 24 % dans le canton le plus âgé et à 17&amp;nbsp;% dans le canton le plus jeune.&lt;/strong&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ces différences sont importantes et s’accentuent, notamment parce que les jeunes quittent les cantons périphériques pour les grandes villes et les agglomérations des cantons qui offrent de meilleures perspectives de travail.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les coûts de la santé, on le sait, augmentent avec l’âge et pèseront de plus en plus sur les primes de l'assurance-maladie dans les cantons périphériques par rapport aux cantons urbains dont la structure démographique est plus favorable, et l’écart se creusera encore en raison de l’évolution démographique mentionnée.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;L’impact des risques liés au vieillissement sur les coûts de la santé est bien visible dans les chiffres des centres de coûts du domaine des soins (EMS, physiothérapie, spitex; cf. Mokke). &amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;L’évolution de la structure d’âge dans les cantons du Tessin et du Jura, par exemple, entraînera une augmentation des coûts de la santé supérieure à la moyenne, qui se reportera sur les primes de l’assurance-maladie.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une étude de santésuisse (septembre 2021) montre que si le Tessin avait la structure d’âge moyenne de la Suisse, les coûts de la santé dans le canton correspondraient à la moyenne suisse.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;La péréquation des charges sociodémographiques, loin d’aider les cantons à faible développement économique, favorise nettement les cantons urbains (GE, ZH, VD, BS).&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Questions:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Le Conseil fédéral est-il au courant que les différences importantes des coûts de la santé s’accentuent en fonction de la structure d’âge de la population des cantons?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont ses scénarios d’évolution démographique (par canton)?&lt;/li&gt;&lt;li&gt;Quelle est l’incidence du vieillissement de la population sur l’évolution générale des coûts de la santé?&lt;/li&gt;&lt;li&gt;Comment la différence des coûts de la santé entre les cantons évoluera-t-elle?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Quel sera l'impact de cette évolution sur la viabilité financière, l'offre et la qualité des soins dans les cantons à faible développement économique, dans lesquels le nombre des plus de 65 ans augmente plus qu’ailleurs?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Alterszusammensetzung der Wohnbevölkerung in den Kantonen zeigt zunehmende Unterschiede zwischen peripheren ländlichen Kantonen mit geringer Wirtschaftsentwicklung und städtischen Kantonen mit hohem Wirtschaftswachstum.&lt;strong&gt; &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Im schweizerischen Durchschnitt machen die Über-65-Jährigen 19 Prozent aus, im Kanton mit dem höchsten Altersdurchschnitt liegt dieser Anteil bei 24 Prozent, im "jüngsten" Kanton bei 17 Prozent.&lt;/strong&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Diese grossen und grösser werdenden Unterschiede sind insbesondere auf die Abwanderung der jungen Leute aus den Randregionen in die grossen Städte und Agglomerationen, die sich in Kantonen mit einem interessanten Arbeitsmarkt befinden, zurückzuführen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Die Gesundheitskosten steigen bekanntlich mit dem Alter. Mit der oben erwähnten demografischen Entwicklung werden diese Kosten die Krankenkassenprämien (KK) in den Randkantonen im Vergleich zu den städtischen Kantonen, die dank ihrer günstigeren demografischen Struktur einen moderateren Wachstumstrend aufweisen, immer stärker belasten; die Kluft der Ungleichheiten zwischen den Kantonen wird grösser.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Einfluss der Altersrisiken auf die Gesundheitskosten lässt sich an den Beträgen pro Kostenstelle im Gesundheitswesen ablesen: Altersheime, Physiotherapie, Spitex (siehe Mokke). &amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Kantone wie das Tessin und der Jura weisen eine Entwicklung in der Altersstruktur der Bevölkerung auf, die zu einem überdurchschnittlichen Anstieg der Gesundheitskosten und damit auch der Prämien für die Krankenversicherung führen wird.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Studie von Santésuisse (September 2021) hat gezeigt, dass die Gesundheitskosten im Kanton Tessin auf den Schweizer Durchschnittswert sänke, wenn dieser die durchschnittliche demografische Struktur der Schweiz aufwiese.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Der Ausgleich der soziodemografischen Lasten hilft den Kantonen mit geringer wirtschaftlicher Entwicklung sicher nicht, begünstigt aber eindeutig die städtischen Kantone (GE, ZH, VD, BS).&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Darum frage ich den Bundesrat:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Ist sich der Bundesrat bewusst, dass die Unterschiede bei den Gesundheitskosten in den Kantonen je nach demografischer Struktur der Wohnbevölkerung immer grösser werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie werden sich seiner Ansicht nach die altersbezogenen demografischen Szenarien je Kanton entwickeln?&lt;/li&gt;&lt;li&gt;Wie stark wirkt sich der Anteil der alternden Bevölkerung auf die Entwicklung der allgemeinen Gesundheitskosten aus?&lt;/li&gt;&lt;li&gt;Wie wird sich der Unterschied bei den Gesundheitskosten zwischen den Kantonen entwickeln?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Wie wird sich diese Entwicklung auf die finanzielle Nachhaltigkeit, das Angebot und die Qualität der Pflege in Kantonen mit geringer wirtschaftlicher Entwicklung und dem höchsten Wachstum der über 65-jährigen Bevölkerung auswirken?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zusammenarbeit statt Diktat der Post. Stärkung der Mitsprache der Gemeinden im Postgesetz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La collaboration au lieu du diktat de la Poste. Pour un renforcement du droit de regard des communes dans la loi sur la poste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooperazione anziché subire i dettami della Posta. Rafforzare la voce dei Comuni nella legge sulle poste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La loi sur la poste doit être modifiée de telle sorte que les communes et les cantons ne disposent plus uniquement du droit d’être consultés lors de la fermeture d’offices de poste, mais aussi d’un droit de participation élargi, et qu’ils doivent approuver toute fermeture.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Postgesetz ist so zu ändern, dass die Gemeinden und Kantone bei der Schliessung von Poststellen nicht mehr nur ein Anhörungsrecht, sondern ein erweitertes Mitwirkungsrecht erhalten und einer Schliessung zustimmen müssen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Wirtschaft|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Économie|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Economia|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einen dauerhaften Grenzschutz gewährleisten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantir une protection permanente des frontières</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantire una protezione permanente dei confini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La législation est adaptée de manière à garantir une protection permanente des frontières nationales. A cet effet, la disponibilité ininterrompue de patrouilles mobiles de l'OFDF en suffisance ainsi que le contrôle des principaux points de passage par des moyens électroniques sont assurés.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Gesetzgebung ist so anzupassen, dass ein dauerhafter Schutz der Landesgrenzen sichergestellt ist. Zu diesem Zweck muss eine ausreichende Anzahl mobiler Patrouillen des Bundesamts für Zoll und Grenzsicherheit (BAZG) ununterbrochen verfügbar sein und die Kontrolle der wichtigsten Grenzübergänge gewährleistet sein.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20243701</t>
@@ -11649,25 +11652,25 @@
         <v>1174</v>
       </c>
       <c r="N103" t="s">
-        <v>205</v>
+        <v>1175</v>
       </c>
       <c r="O103" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="P103" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="Q103" t="s">
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="S103" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="T103" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="U103" t="s">
         <v>59</v>
@@ -11679,7 +11682,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C104" t="s">
         <v>75</v>
@@ -11691,7 +11694,7 @@
         <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11700,28 +11703,28 @@
         <v>78</v>
       </c>
       <c r="I104" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J104" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="K104" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="L104" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="M104" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N104" t="s">
         <v>170</v>
       </c>
       <c r="O104" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P104" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="Q104" t="s">
         <v>55</v>
@@ -11745,7 +11748,7 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -11757,7 +11760,7 @@
         <v>104</v>
       </c>
       <c r="F105" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11766,28 +11769,28 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="J105" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="K105" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="L105" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="M105" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="N105" t="s">
         <v>170</v>
       </c>
       <c r="O105" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="P105" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="Q105" t="s">
         <v>247</v>
@@ -11811,19 +11814,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C106" t="s">
         <v>163</v>
       </c>
       <c r="D106" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E106" t="s">
         <v>77</v>
       </c>
       <c r="F106" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11832,26 +11835,26 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="J106" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="M106" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="N106" t="s">
         <v>170</v>
       </c>
       <c r="O106" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="P106" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="Q106" t="s">
         <v>55</v>
@@ -11875,19 +11878,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C107" t="s">
         <v>163</v>
       </c>
       <c r="D107" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E107" t="s">
         <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11896,38 +11899,38 @@
         <v>78</v>
       </c>
       <c r="I107" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="J107" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="M107" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N107" t="s">
         <v>170</v>
       </c>
       <c r="O107" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="P107" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="Q107" t="s">
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="S107" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="T107" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="U107" t="s">
         <v>59</v>
@@ -11939,7 +11942,7 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C108" t="s">
         <v>150</v>
@@ -11951,7 +11954,7 @@
         <v>62</v>
       </c>
       <c r="F108" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11960,28 +11963,28 @@
         <v>78</v>
       </c>
       <c r="I108" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="J108" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="K108" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="L108" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="M108" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="N108" t="s">
         <v>244</v>
       </c>
       <c r="O108" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="P108" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="Q108" t="s">
         <v>247</v>
@@ -12005,7 +12008,7 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C109" t="s">
         <v>200</v>
@@ -12013,43 +12016,43 @@
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="J109" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="K109" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="O109" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="P109" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="S109" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="T109" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="U109" t="s">
         <v>59</v>
@@ -12061,7 +12064,7 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C110" t="s">
         <v>525</v>
@@ -12071,47 +12074,47 @@
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="J110" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="K110" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L110" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="M110" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N110" t="s">
-        <v>205</v>
+        <v>1175</v>
       </c>
       <c r="O110" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="P110" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="Q110" t="s">
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="S110" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="T110" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="U110" t="s">
         <v>59</v>
@@ -12123,19 +12126,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C111" t="s">
         <v>75</v>
       </c>
       <c r="D111" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E111" t="s">
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12144,40 +12147,40 @@
         <v>78</v>
       </c>
       <c r="I111" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="J111" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="K111" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="L111" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="M111" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="N111" t="s">
         <v>170</v>
       </c>
       <c r="O111" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="P111" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="Q111" t="s">
         <v>247</v>
       </c>
       <c r="R111" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="S111" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="T111" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="U111" t="s">
         <v>59</v>
@@ -12189,19 +12192,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C112" t="s">
         <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="E112" t="s">
         <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12210,40 +12213,40 @@
         <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J112" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="K112" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="L112" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="M112" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N112" t="s">
         <v>170</v>
       </c>
       <c r="O112" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="P112" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="Q112" t="s">
         <v>247</v>
       </c>
       <c r="R112" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="S112" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="T112" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="U112" t="s">
         <v>59</v>
@@ -12255,7 +12258,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C113" t="s">
         <v>75</v>
@@ -12267,7 +12270,7 @@
         <v>62</v>
       </c>
       <c r="F113" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12276,28 +12279,28 @@
         <v>78</v>
       </c>
       <c r="I113" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="J113" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="K113" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="L113" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="M113" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="N113" t="s">
         <v>170</v>
       </c>
       <c r="O113" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="P113" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="Q113" t="s">
         <v>55</v>
@@ -12321,7 +12324,7 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C114" t="s">
         <v>150</v>
@@ -12333,7 +12336,7 @@
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12342,28 +12345,28 @@
         <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="J114" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="K114" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="L114" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="M114" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N114" t="s">
         <v>283</v>
       </c>
       <c r="O114" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="P114" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="Q114" t="s">
         <v>195</v>
@@ -12387,19 +12390,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12408,40 +12411,40 @@
         <v>78</v>
       </c>
       <c r="I115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="J115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="K115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="L115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="M115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N115" t="s">
         <v>271</v>
       </c>
       <c r="O115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="P115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="Q115" t="s">
         <v>247</v>
       </c>
       <c r="R115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="S115" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="T115" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="U115" t="s">
         <v>59</v>
@@ -12453,19 +12456,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="E116" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="F116" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12474,40 +12477,40 @@
         <v>105</v>
       </c>
       <c r="I116" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="J116" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="K116" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="L116" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="M116" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="N116" t="s">
         <v>170</v>
       </c>
       <c r="O116" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="P116" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="Q116" t="s">
         <v>195</v>
       </c>
       <c r="R116" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="S116" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="T116" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="U116" t="s">
         <v>59</v>
@@ -12519,7 +12522,7 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C117" t="s">
         <v>75</v>
@@ -12531,7 +12534,7 @@
         <v>77</v>
       </c>
       <c r="F117" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12540,40 +12543,40 @@
         <v>78</v>
       </c>
       <c r="I117" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="J117" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="K117" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="L117" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="M117" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="N117" t="s">
         <v>170</v>
       </c>
       <c r="O117" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="P117" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="Q117" t="s">
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="S117" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="T117" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="U117" t="s">
         <v>59</v>
@@ -12585,19 +12588,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C118" t="s">
         <v>75</v>
       </c>
       <c r="D118" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12606,40 +12609,40 @@
         <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="J118" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="K118" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="L118" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="M118" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="N118" t="s">
         <v>170</v>
       </c>
       <c r="O118" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="P118" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="Q118" t="s">
         <v>55</v>
       </c>
       <c r="R118" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="S118" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="T118" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="U118" t="s">
         <v>59</v>
@@ -12651,7 +12654,7 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C119" t="s">
         <v>75</v>
@@ -12663,7 +12666,7 @@
         <v>62</v>
       </c>
       <c r="F119" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12672,40 +12675,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="J119" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="K119" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="L119" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="M119" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="N119" t="s">
         <v>170</v>
       </c>
       <c r="O119" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="P119" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="Q119" t="s">
         <v>195</v>
       </c>
       <c r="R119" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="S119" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="T119" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="U119" t="s">
         <v>59</v>
@@ -12717,19 +12720,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C120" t="s">
         <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12738,28 +12741,28 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J120" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="K120" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="L120" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="M120" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="N120" t="s">
         <v>170</v>
       </c>
       <c r="O120" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="P120" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="Q120" t="s">
         <v>195</v>
@@ -12783,7 +12786,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C121" t="s">
         <v>75</v>
@@ -12795,7 +12798,7 @@
         <v>77</v>
       </c>
       <c r="F121" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12804,28 +12807,28 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="J121" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="K121" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L121" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="M121" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="N121" t="s">
         <v>170</v>
       </c>
       <c r="O121" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="P121" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="Q121" t="s">
         <v>55</v>
@@ -12849,19 +12852,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C122" t="s">
         <v>75</v>
       </c>
       <c r="D122" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E122" t="s">
         <v>62</v>
       </c>
       <c r="F122" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12870,28 +12873,28 @@
         <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="J122" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="K122" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="L122" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M122" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="N122" t="s">
         <v>170</v>
       </c>
       <c r="O122" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="P122" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="Q122" t="s">
         <v>55</v>
@@ -12915,19 +12918,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C123" t="s">
         <v>150</v>
       </c>
       <c r="D123" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E123" t="s">
         <v>62</v>
       </c>
       <c r="F123" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12936,28 +12939,28 @@
         <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="J123" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="K123" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="L123" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="M123" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="N123" t="s">
         <v>283</v>
       </c>
       <c r="O123" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="P123" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="Q123" t="s">
         <v>55</v>
@@ -12981,7 +12984,7 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C124" t="s">
         <v>163</v>
@@ -12993,7 +12996,7 @@
         <v>77</v>
       </c>
       <c r="F124" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -13002,26 +13005,26 @@
         <v>78</v>
       </c>
       <c r="I124" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="J124" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="M124" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="N124" t="s">
         <v>170</v>
       </c>
       <c r="O124" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="P124" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="Q124" t="s">
         <v>247</v>
@@ -13045,7 +13048,7 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C125" t="s">
         <v>163</v>
@@ -13057,7 +13060,7 @@
         <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13066,26 +13069,26 @@
         <v>78</v>
       </c>
       <c r="I125" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="J125" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="M125" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="N125" t="s">
         <v>170</v>
       </c>
       <c r="O125" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="P125" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="Q125" t="s">
         <v>55</v>
@@ -13109,17 +13112,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13128,40 +13131,40 @@
         <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="J126" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="K126" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="L126" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="M126" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="N126" t="s">
         <v>283</v>
       </c>
       <c r="O126" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="P126" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="Q126" t="s">
         <v>247</v>
       </c>
       <c r="R126" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="S126" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="T126" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="U126" t="s">
         <v>59</v>
@@ -13173,7 +13176,7 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C127" t="s">
         <v>75</v>
@@ -13185,7 +13188,7 @@
         <v>104</v>
       </c>
       <c r="F127" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13194,40 +13197,40 @@
         <v>78</v>
       </c>
       <c r="I127" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="J127" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="K127" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="L127" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="M127" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="N127" t="s">
         <v>170</v>
       </c>
       <c r="O127" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="P127" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="Q127" t="s">
         <v>195</v>
       </c>
       <c r="R127" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="S127" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="T127" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="U127" t="s">
         <v>59</v>
@@ -13239,7 +13242,7 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -13251,7 +13254,7 @@
         <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13260,40 +13263,40 @@
         <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="J128" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="K128" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="L128" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="M128" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="N128" t="s">
         <v>170</v>
       </c>
       <c r="O128" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="P128" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="Q128" t="s">
         <v>195</v>
       </c>
       <c r="R128" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="S128" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="T128" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="U128" t="s">
         <v>59</v>
@@ -13305,19 +13308,19 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E129" t="s">
         <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
@@ -13326,40 +13329,40 @@
         <v>688</v>
       </c>
       <c r="I129" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="J129" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="K129" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="L129" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="M129" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="N129" t="s">
         <v>170</v>
       </c>
       <c r="O129" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="P129" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="Q129" t="s">
         <v>195</v>
       </c>
       <c r="R129" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="S129" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="T129" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="U129" t="s">
         <v>59</v>
@@ -13371,7 +13374,7 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -13383,7 +13386,7 @@
         <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
@@ -13392,40 +13395,40 @@
         <v>688</v>
       </c>
       <c r="I130" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="J130" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="K130" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="L130" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="M130" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="N130" t="s">
         <v>170</v>
       </c>
       <c r="O130" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="P130" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="Q130" t="s">
         <v>195</v>
       </c>
       <c r="R130" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="S130" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="T130" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="U130" t="s">
         <v>59</v>
@@ -13437,19 +13440,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C131" t="s">
         <v>75</v>
       </c>
       <c r="D131" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="E131" t="s">
         <v>188</v>
       </c>
       <c r="F131" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13458,28 +13461,28 @@
         <v>105</v>
       </c>
       <c r="I131" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="J131" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="K131" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="L131" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="M131" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="N131" t="s">
         <v>170</v>
       </c>
       <c r="O131" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="P131" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="Q131" t="s">
         <v>195</v>
@@ -13503,7 +13506,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C132" t="s">
         <v>75</v>
@@ -13515,7 +13518,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13524,40 +13527,40 @@
         <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="J132" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="K132" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="L132" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="M132" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="N132" t="s">
         <v>170</v>
       </c>
       <c r="O132" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="P132" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="Q132" t="s">
         <v>55</v>
       </c>
       <c r="R132" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="S132" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="T132" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="U132" t="s">
         <v>59</v>
@@ -13569,7 +13572,7 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C133" t="s">
         <v>75</v>
@@ -13581,7 +13584,7 @@
         <v>77</v>
       </c>
       <c r="F133" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13590,40 +13593,40 @@
         <v>78</v>
       </c>
       <c r="I133" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="J133" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="K133" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="L133" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="M133" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="N133" t="s">
         <v>170</v>
       </c>
       <c r="O133" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="P133" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="Q133" t="s">
         <v>55</v>
       </c>
       <c r="R133" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="S133" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="T133" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="U133" t="s">
         <v>59</v>
@@ -13635,19 +13638,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C134" t="s">
         <v>163</v>
       </c>
       <c r="D134" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="E134" t="s">
         <v>104</v>
       </c>
       <c r="F134" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13656,38 +13659,38 @@
         <v>78</v>
       </c>
       <c r="I134" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="J134" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="M134" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="N134" t="s">
         <v>170</v>
       </c>
       <c r="O134" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="P134" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q134" t="s">
         <v>195</v>
       </c>
       <c r="R134" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="S134" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="T134" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="U134" t="s">
         <v>59</v>
@@ -13699,19 +13702,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C135" t="s">
         <v>163</v>
       </c>
       <c r="D135" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="E135" t="s">
         <v>104</v>
       </c>
       <c r="F135" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13720,38 +13723,38 @@
         <v>78</v>
       </c>
       <c r="I135" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="J135" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="M135" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="N135" t="s">
         <v>170</v>
       </c>
       <c r="O135" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="P135" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="Q135" t="s">
         <v>247</v>
       </c>
       <c r="R135" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="S135" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="T135" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="U135" t="s">
         <v>59</v>
@@ -13763,19 +13766,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C136" t="s">
         <v>163</v>
       </c>
       <c r="D136" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="E136" t="s">
         <v>188</v>
       </c>
       <c r="F136" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13784,26 +13787,26 @@
         <v>78</v>
       </c>
       <c r="I136" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="J136" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="M136" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="N136" t="s">
         <v>170</v>
       </c>
       <c r="O136" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="P136" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="Q136" t="s">
         <v>247</v>
@@ -13827,19 +13830,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C137" t="s">
         <v>163</v>
       </c>
       <c r="D137" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13848,38 +13851,38 @@
         <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="J137" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="M137" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="N137" t="s">
         <v>170</v>
       </c>
       <c r="O137" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="P137" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="Q137" t="s">
         <v>195</v>
       </c>
       <c r="R137" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="S137" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="T137" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="U137" t="s">
         <v>59</v>
@@ -13891,7 +13894,7 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C138" t="s">
         <v>525</v>
@@ -13901,47 +13904,47 @@
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>105</v>
       </c>
       <c r="I138" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="J138" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="K138" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="L138" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="M138" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="N138" t="s">
         <v>170</v>
       </c>
       <c r="O138" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="P138" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="Q138" t="s">
         <v>55</v>
       </c>
       <c r="R138" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="S138" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="T138" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="U138" t="s">
         <v>59</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -2354,358 +2354,358 @@
     <t xml:space="preserve">&lt;p&gt;Das Bundesparlament und der Bundesrat werden gebeten, die notwendigen Schritte zu unternehmen, damit unter dem Aspekt des Gebots der bundesstaatlichen und föderalen Rechtsgleichheit die ehemaligen Halbkantone Basel-Stadt und Basel-Landschaft den übrigen Kantonen im Hinblick auf die Vertretung im Ständerat gleichgestellt werden (Aufwertung als Kantone mit Vollem Ständerecht, Änderung von Art. 142 Abs. 4 und Art. 150 Abs. 1 und 2 der Bundesverfassung).&lt;/p&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission de gestion Conseil des États</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunaux fédéraux. Introduire un système disciplinaire pour renforcer la confiance à leur égard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunali della Confederazione. Introdurre un sistema disciplinare per rafforzare la fiducia in queste istituzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Il y a lieu d’élaborer les bases légales permettant d’introduire une surveillance disciplinaire des juges des tribunaux fédéraux. Les principes de l’indépendance des juges, de l’autonomie des tribunaux en matière d’organisation et de la séparation des pouvoirs devront être respectés.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Es seien die gesetzlichen Grundlagen zu erarbeiten, um eine Disziplinaraufsicht über die Richterinnen und Richter an den eidgenössischen Gerichten einzuführen. Dabei ist den Grundsätzen der richterlichen Unabhängigkeit, der Organisationsautonomie und der Gewaltentrennung Rechnung zu tragen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Gerichtswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Giustizia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrierter Ansatz für Service-Center des Service public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une approche intégrée des centres de services dans le service public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per un approccio integrato per i centri di servizio del servizio pubblico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale est chargée de créer les bases légales permettant de développer et de mettre en œuvre une approche intégrée des centres de services dans le service public. Ce faisant, elle intégrera l’infrastructure existante du réseau postal. L’objectif est de créer une infrastructure moderne et efficace pour la population et de garantir un réseau physique qui assure l’accès des personnes aux produits numériques et aux produits physiques.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung wird beauftragt, die gesetzlichen Grundlagen zu schaffen, um einen integrierten Ansatz für ServiceCenter des Service Public zu entwickeln und umzusetzen. Die bestehende Infrastruktur von PostNetz ist dabei einzubeziehen. Ziel ist es, eine moderne und effiziente Infrastruktur für die Bevölkerung zu schaffen, ein physisches Netz zu sichern, das den Zugang der Menschen zu digitalen und physischen Produkten sichert.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vieillissement de la population. Créer un mécanisme de compensation pour les primes de l’assurance-maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introdurre un meccanismo di compensazione intercantonale per i premi di cassa malati dovuti all’invecchiamento dalla popolazione </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Dans son avis sur la motion Quadri 24.4209, qui le charge «&amp;nbsp;de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population&amp;nbsp;», le Conseil fédéral affirme: «&amp;nbsp;Le Conseil fédéral reste d’avis que la péréquation financière nationale assure un équilibre entre les cantons&amp;nbsp;» et souligne notamment que «&amp;nbsp;... la compensation des charges dans le cadre de la péréquation financière nationale comprend une composante sociodémographique, qui tient compte des coûts liés à la structure de la population, notamment à la pyramide des âges. Le Canton du Tessin reçoit déjà des contributions fédérales dans ce cadre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;Malheureusement, ce n’est pas ce que disent les montants définitifs des paiements compensatoires pour 2025 récemment publiés. Au contraire, le canton du Tessin ne reçoit rien au titre de la compensation sociodémographique, bien qu’il compte le plus grand nombre de personnes de 80 ans ou plus (7,6 % de la population résidante permanente, contre 5,7&amp;nbsp;% pour la moyenne nationale). Le moment est donc venu de reconnaître la situation particulière du Tessin, qui compte une proportion non négligeable de retraités âgés originaires de la Suisse alémanique.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Confirme-t-il que le Tessin ne reçoit aucune contribution au titre de la compensation sociodémographique, contrairement à ce qu’il affirme dans son avis sur la motion 24.4209?&lt;/li&gt;&lt;li&gt;Au vu de ce qui précède, convient-il que la péréquation financière nationale n’atteint pas son but?&lt;/li&gt;&lt;li&gt;Par conséquent, ne pense-t-il pas que la création d’un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population, demandée par la motion 24.4209, soit à la fois opportune et nécessaire?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In der Stellungnahme zur Motion Quadri 24.4209, die den Bundesrat beauftragte, einen Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien einzuführen, hat der Bundesrat festgehalten: «Der Bundesrat ist weiterhin der Meinung, dass der nationale Finanzausgleich für ein Gleichgewicht zwischen den Kantonen sorgt. [...], insbesondere hat er ausgeführt, dass der nationale Finanzausgleich eine soziodemographische Komponente innerhalb des Lastenausgleichs enthält, der die Kosten aufgrund der Bevölkerungsstruktur, u. a. des Alters, berücksichtigt. Der Kanton [...] erhält bereits Beiträge vom Bund im Rahmen des Lastenausgleichs».&lt;/p&gt;&lt;p&gt;Leider decken sich aber die kürzlich veröffentlichten Berechnungen zu den Ausgleichszahlungen 2025 nicht mit diesen Aussagen. So erhält der Kanton Tessin keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich, obwohl er einen besonders hohen Anteil an Personen im Alter von 80 Jahren und mehr im Verhältnis zur ständigen Wohnbevölkerung aufweist (7,6 % gegenüber dem schweizerischen Durchschnitt von 5,7 %). Es ist daher an der Zeit, die besondere Situation des Kantons Tessin anzuerkennen, wo ein nicht unerheblicher Teil der älteren Menschen Rentnerinnen und Rentner aus der Deutschschweiz sind.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte deshalb den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bestätigt der Bundesrat, dass der Kanton Tessin – anders als in der Stellungnahme zur Motion 24.4209 behauptet – keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich erhält?&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat in Anbetracht der obigen Ausführungen die Ansicht, dass der nationale Finanzausgleich seinen Zweck nicht erfüllt?&lt;/li&gt;&lt;li&gt;Hält der Bundesrat die Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien, wie sie mit der Motion 24.4209 verlangt wird, nicht auch für sinnvoll und notwendig?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rechsteiner Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentlichkeitsarbeit des Bundes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relations publiques de la Confédération</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attività di pubbliche relazioni della Confederazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le chancelier de la Confédération a répondu le 16&amp;nbsp;décembre 2024 de manière relativement détaillée à ma question 24.7932 «&amp;nbsp;400 fonctionnaires médias. Y a-t-il un potentiel d’économies&amp;nbsp;?&amp;nbsp;». Certains points restent toutefois flous, et les réponses fournies soulèvent d’autres questions.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Meine Frage 24.7932 «400 Medienbeamte – Sparpotential erkannt?» wurde vom Bundeskanzler am 16. Dezember 2024 relativ ausführlich beantwortet. Trotzdem bleibt einiges im Unklaren und die Antworten werfen weiteren Fragen auf.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufhebung des Zentrumslastenausgleichs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppression de la compensation des charges des centres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliminare la compensazione degli oneri dei centri urbani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la législation relative à la péréquation financière et à la compensation des charges de sorte que la compensation des charges dues à des facteurs socio-démographiques (CCS) ne s’applique désormais plus qu’aux charges excessives liées à la structure de la population et que les charges des centres ne soient plus compensées.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Gesetzgebung zum Finanz- und Lastenausgleich dahingehend anzupassen, dass der soziodemografische Lastenausgleich künftig nur mehr Sonderlasten aufgrund der Bevölkerungsstruktur ausgleicht und keinen Zentrumslastenausgleich mehr vorsieht.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übernahme der EU-Richtlinie 2019/1158 zur Vereinbarkeit von Beruf und Privatleben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reprise de la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepimento della direttiva UE 2019/1158 relativa all’equilibrio tra attività professionale e vita familiare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de reprendre dans le droit suisse la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die EU-Richtlinie 2019/118 zur Vereinbarkeit von Beruf und Privatleben ins Schweizer Recht zu übernehmen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europapolitik|Soziale Fragen|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique européenne|Questions sociales|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica europea|Questioni sociali|Occupazione e lavoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widmer Céline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systemwechsel bei der Wohneigentumsbesteuerung. Steuerliche Folgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changement de système d’imposition du logement. Conséquences fiscales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambio di sistema nell'ambito dell'imposizione della proprietà abitativa. Conseguenze fiscali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les chambres fédérales ont adopté une réforme de l’imposition du logement le 20.12.2024, qui bouleverse les équilibres dans ce domaine tout en amenant de grandes pertes fiscales.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes, au sujet de la réforme telle qu’elle a été adoptée par le parlement et de l’introduction d’un impôt réel sur les résidences secondaires :&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;La BNS a annoncé une baisse des taux directeurs à 0.5%. Un scénario avec des taux hypothécaires moyens durablement en dessous de 1.5% devient de plus en plus crédibles. Quelles seraient les pertes fiscales liées à la réforme en cas de taux moyen à 1%&amp;nbsp; et à 1.25%?&amp;nbsp;&amp;nbsp;&lt;/li&gt;&lt;li&gt;Etant donné que la réforme entraine de grandes pertes fiscales, cela veut dire que certains contribuables vont être avantagés par rapport au reste de la population. Est-il correct de dire que les personnes qui toucheront la plus grande somme par rapport à la situation actuelle sont celles et ceux qui disposent de très grandes propriétés avec une énorme valeur et qui n’ont pas de dette liée à cette propriété ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Combien de baisse d’impôt peut attendre un propriétaire d’une maison de maître d’une valeur de CHF 10'000'000.- et qui finance aujourd’hui son bien entièrement en fonds propres ? Quelle serait le changement de la situation fiscale d’un propriétaire qui dispose d’un bien d’une valeur de CHF 500'000, hypothéqué à hauteur de CHF 400'000.- avec un taux hypothécaire de 3%, et devant faire des frais d’entretiens pour CHF 10'000.-, s’il dispose d’un revenu imposable de 100'000.- ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral peut-il expliquer quelle est la relation entre d’une part la valeur d’une bien immobilier utilisé comme résidence principale et d’autre part l’allègement fiscal obtenu suite à l’introduction du changement de système d’imposition du logement?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont les effets de la réforme de l’imposition du logement sur la péréquation financière? En particulier, quel est l’effet sur l’équilibre de cette péréquation à long terme?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung hat am 20. Dezember 2024 eine Reform der Wohneigentumsbesteuerung verabschiedet, die das Gleichgewicht in diesem Bereich erheblich stört und gleichzeitig grosse Steuerausfälle mit sich bringt.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, die folgenden Fragen zur Reform in der vom Parlament verabschiedeten Form und zur Einführung einer Objektsteuer auf Zweitwohnungen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Die Schweizerische Nationalbank (SNB) hat eine Senkung des Leitzinses auf 0,5&amp;nbsp;Prozent angekündigt. Es ist immer wahrscheinlicher, dass die durchschnittlichen Hypothekarzinsen dauerhaft unter 1,5&amp;nbsp;Prozent liegen. Wie hoch wären die Steuerausfälle aufgrund der Reform bei einem durchschnittlichen Zinssatz von 1 Prozent oder 1,25 Prozent?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Die Reform führt zu grossen Steuerausfällen. Das bedeutet, dass einige Steuerzahler und Steuerzahlerinnen gegenüber dem Rest der Bevölkerung begünstigt werden. Kann man sagen, dass die Personen, die über sehr grosse Immobilien mit einem enormen Wert verfügen und keine Schulden im Zusammenhang mit diesen Immobilien haben, im Vergleich zur aktuellen Situation am stärksten profitieren?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Mit welcher Steuersenkung kann ein Eigentümer einer herrschaftlichen Villa im Wert von 10&amp;nbsp;000&amp;nbsp;000 Franken rechnen, der seine Immobilie heute vollständig mit Eigenmitteln finanziert? Wie würde sich die steuerliche Situation einer Eigentümerin mit einem steuerpflichtigen Einkommen von 100 000 Franken ändern, wenn sie über eine Immobilie im Wert von 500&amp;nbsp;000 Franken verfügt, die mit einer Hypothek in Höhe von 400&amp;nbsp;000 Franken zu einem Hypothekarzins von 3&amp;nbsp;Prozent belastet ist, und sie Unterhaltskosten in Höhe von 10&amp;nbsp;000 Franken tragen muss?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. &amp;nbsp;Kann der Bundesrat erklären, in welchem Verhältnis der Wert einer Immobilie, die als Erstwohnung genutzt wird, zur Steuererleichterung steht, die durch den Systemwechsel bei der Wohneigentumsbesteuerung erreicht wird?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Wie wirkt sich die Reform der Wohneigentumsbesteuerung auf den Finanzausgleich aus?&lt;/p&gt;&lt;p&gt;Welches sind insbesondere die langfristigen Auswirkungen auf das Gleichgewicht des Finanzausgleichs?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuer|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscalité|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposte|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was ist die Umweltpolitik des ASTRA im Rahmen seiner Ausschreibungen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle est la politique environnementale de l'OFROU dans le cadre de ses appels d'offres?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual è la politica ambientale dell’USTRA in ambito appaltistico?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;L’OFROU réalise des travaux importants à la sortie de l'autoroute à Matran. Pour une question de prix uniquement, du gravier (grave de route principalement) est acheminé depuis un site du Jura français situé à environ 100km de Matran. Pour ne pas circuler à vide sur le retour, les poids-lourds transportent des éléments de chaussée rabotés et les amènent dans les décharges en France voisine. La distance aller-retour est de 200km environ alors que les mêmes matériaux sont disponibles dans un rayon de moins de 30km dans le canton de Fribourg ou 50km hors canton. Il s’ensuit des trajets et des engorgements supplémentaires, plus de CO2, plus de bruit, plus d’usure des infrastructures, de bruit et de poussières. De surcroit, des chauffeurs dont les conditions de travail sont très précaires remplacent des conducteurs domiciliés en Suisse qui bénéficient de bonnes conditions sociales. En utilisant des graviers locaux, on s'assure qu'ils sont exploités selon les normes locales avec du personnel local. Je remercie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Les soumissions provenant de l'OFROU prévoient-elles des filières d’approvisionnement et d’évacuation de graviers et autres matériaux minéraux&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si non, est-il prévu de prendre en compte rapidement les éléments précités?&lt;/li&gt;&lt;li&gt;Si oui, sachant que l’empreinte CO2 du transport de ces matériaux lourds est importante, comment cet élément est-il mis en valeur&amp;nbsp;dans la soumission&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces aspects sont-ils contrôlés en pratique, sur le terrain&amp;nbsp;?&lt;/li&gt;&lt;li&gt;En cas de faute, quelles sont les conséquences&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Das Bundesamt für Strassen (ASTRA) führt bei der Autobahnausfahrt Matran wichtige Bauarbeiten durch. Dabei wird einzig aus Kostengründen Kies (hauptsächlich als Strassenschotter) aus dem französischen Jura angeliefert, von einem Ort, der rund 100 Kilometer von Matran entfernt liegt. Um auf dem Rückweg Leerfahrten zu vermeiden, transportiert der Schwerverkehr von der Fahrbahn abgeschliffene Elemente ab und entsorgt diese im benachbarten Frankreich. Insgesamt werden rund 200 Kilometer zurückgelegt, obwohl dieselben Materialien in einem Umkreis von weniger als 30 Kilometern im Kanton Freiburg oder 50 Kilometern ausserhalb des Kantons verfügbar wären. Dies führt zu zusätzlichen Fahrten, mehr Stau, CO2, Lärm und Staub sowie zu einer verstärkten Abnutzung der Infrastrukturen. Zudem werden in der Schweiz wohnhafte Chauffeurinnen und Chauffeure, die von guten sozialen Bedingungen profitieren, durch solche mit sehr prekären Arbeitsbedingungen ersetzt. Die Verwendung von lokalem Kies stellt sicher, dass dieser nach lokalen Normen und mit lokalem Personal abgebaut wird. Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Sehen die Ausschreibungen des ASTRA Liefer- und Entsorgungswege für Kies und andere mineralische Materialien vor?&lt;/li&gt;&lt;li&gt;Wenn nein: Ist geplant, die obgenannten Punkte rasch zu berücksichtigen?&lt;/li&gt;&lt;li&gt;Wenn ja: Wie wird dieser Aspekt in der Ausschreibung hervorgehoben, zumal bekannt ist, dass der Transport von Schwergut einen grossen CO2-Fussabdruck hat?&lt;/li&gt;&lt;li&gt;Wie werden diese Aspekte in der Praxis vor Ort kontrolliert?&lt;/li&gt;&lt;li&gt;Was wären die Folgen, wenn sie nicht kontrolliert werden?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschäftigung und Arbeit|Verkehr|Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emploi et travail|Transports|Environnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupazione e lavoro|Trasporti|Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marti Min Li</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kann die Post einen Beitrag zur digitalen Inklusion leisten? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Poste peut-elle contribuer à l'inclusion numérique? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Posta può contribuire all'inclusione digitale? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Diverses études comme le Baromètre numérique&amp;nbsp;2024 de la Mobilière ont constaté que des compétences numériques de base font défaut à près d’un tiers de la population. Elles relèvent des disparités notables selon l’âge, le revenu et la formation. Même si l’âge joue un rôle en matière de compétences numériques, les personnes âgées ne sont en réalité pas les seules à connaître des difficultés dans l’utilisation des outils numériques comme les services bancaires et les billetteries en ligne ou les guichets virtuels des autorités. Ces lacunes vont souvent de pair avec un sentiment de gêne. &amp;nbsp;Certains, en particulier les jeunes, surestiment leurs propres compétences. De fait, le quotidien bascule toujours plus dans le numérique et exacerbe les lacunes en matière de compétences numériques. C’est pourquoi je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Que pense-t-il du problème des compétences numériques lacunaires&amp;nbsp;? Comment pourrait-on y remédier&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les pouvoirs publics et les entreprises proches de la Confédération, par exemple, numérisent de plus en plus leurs services, et ne les proposent parfois plus que sous cette forme. Comment garantir leur accessibilité à tout le monde&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans le cadre d’un projet pilote mené dans trois filiales, la Poste a proposé une assistance sur toutes sortes de problèmes relevant du numérique. Que pense le Conseil fédéral de ce projet&amp;nbsp;? La poste pourrait-elle contribuer à faire progresser l’inclusion numérique grâce à cette offre&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Est-ce qu’une telle offre de la Poste ou d’autres entreprises pourraient aussi alléger le travail des autorités&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Verschiedene Studien wie beispielsweise der Digitalbarometer 2024 der Mobiliar haben festgestellt, dass fast ein Drittel der Bevölkerung nicht über grundlegende digitale Kompetenzen verfügt. Dabei gibt es signifikante Unterschiede nach Alter, Einkommen und Bildung. Auch wenn das Alter bei den digitalen Kompetenzen eine Rolle spielt, sind es beileibe nicht nur ältere Menschen, die Mühe haben, digitale Anwendungen wie beispielsweise E-Banking, Billetkäufe oder digitale Behördengänge zu nutzen. Dies ist oft auch mit Scham verbunden. &amp;nbsp;Teilweise werden auch die eigenen Fähigkeiten überschätzt, gerade bei jüngeren Menschen. Da immer mehr Dinge des täglichen Lebens digitalisiert werden, stellt die mangelnde digitale Kompetenz ein zunehmendes Problem dar. In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie schätzt der Bundesrat das Problem der fehlenden digitalen Kompetenzen ein und wie könnten diese verbessert werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Auch Leistungen der öffentlichen Hand oder beispielsweise von bundesnahen Betrieben werden immer häufiger digitalisiert und teilweise nur noch digital angeboten. Wie kann sichergestellt werden, dass alle Personen Zugang zu diesen Leistungen haben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Im Rahmen eines Pilotprojekts hat die Post in drei Filialen ein Angebot geschaffen, um Menschen bei digitalen Problemen aller Art zu unterstützen. Wie beurteilt der Bundesrat dieses Projekt? Könnte die Post mit diesem Angebot einen Beitrag leisten, die digitale Inklusion voranzutreiben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Könnte eine entsprechende Dienstleistung der Post oder von anderen Betreibern auch dazu beitragen, Behörden zu entlasten?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Soziale Fragen|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Questions sociales|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Questioni sociali|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzielle Unterstützung für Imkerinnen und Imker bei geoklimatischen Ausnahmebedingungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soutien financier direct aux apiculteurs et apicultrices lors de situations géoclimatiques exceptionnelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sostegno finanziario diretto agli apicoltori in situazioni geoclimatiche eccezionali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale et à l'article 84, lettre o, de la Constitution cantonale, le Canton demande aux Chambres fédérales d'accorder un soutien financier direct, comme des subsides, aux apiculteurs et apicultrices pour l'achat de sucre nécessaire au nourrissement des abeilles mellifères, ceci lorsque les situations géoclimatiques rendent ce nourrissement indispensable à la survie des colonies d'abeilles.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o seiner Kantonsverfassung fordert der Kanton Jura die Bundesversammlung auf, den Imkerinnen und Imkern finanzielle Unterstützung, beispielsweise in Form von Subventionen, zu gewähren für den Kauf von Zucker, wenn dieser aufgrund der geoklimatischen Bedingungen an Honigbienen verfüttert werden muss, um deren Überleben sicherzustellen.&lt;/p&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beratung in Kommission des Nationalrates abgeschlossen / Fin des discussions en commission du Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commission de gestion Conseil des États</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunaux fédéraux. Introduire un système disciplinaire pour renforcer la confiance à leur égard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunali della Confederazione. Introdurre un sistema disciplinare per rafforzare la fiducia in queste istituzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Il y a lieu d’élaborer les bases légales permettant d’introduire une surveillance disciplinaire des juges des tribunaux fédéraux. Les principes de l’indépendance des juges, de l’autonomie des tribunaux en matière d’organisation et de la séparation des pouvoirs devront être respectés.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Es seien die gesetzlichen Grundlagen zu erarbeiten, um eine Disziplinaraufsicht über die Richterinnen und Richter an den eidgenössischen Gerichten einzuführen. Dabei ist den Grundsätzen der richterlichen Unabhängigkeit, der Organisationsautonomie und der Gewaltentrennung Rechnung zu tragen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20250401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Gerichtswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Justice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Giustizia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrierter Ansatz für Service-Center des Service public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une approche intégrée des centres de services dans le service public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per un approccio integrato per i centri di servizio del servizio pubblico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’Assemblée fédérale est chargée de créer les bases légales permettant de développer et de mettre en œuvre une approche intégrée des centres de services dans le service public. Ce faisant, elle intégrera l’infrastructure existante du réseau postal. L’objectif est de créer une infrastructure moderne et efficace pour la population et de garantir un réseau physique qui assure l’accès des personnes aux produits numériques et aux produits physiques.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung wird beauftragt, die gesetzlichen Grundlagen zu schaffen, um einen integrierten Ansatz für ServiceCenter des Service Public zu entwickeln und umzusetzen. Die bestehende Infrastruktur von PostNetz ist dabei einzubeziehen. Ziel ist es, eine moderne und effiziente Infrastruktur für die Bevölkerung zu schaffen, ein physisches Netz zu sichern, das den Zugang der Menschen zu digitalen und physischen Produkten sichert.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vieillissement de la population. Créer un mécanisme de compensation pour les primes de l’assurance-maladie </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introdurre un meccanismo di compensazione intercantonale per i premi di cassa malati dovuti all’invecchiamento dalla popolazione </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Dans son avis sur la motion Quadri 24.4209, qui le charge «&amp;nbsp;de proposer un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population&amp;nbsp;», le Conseil fédéral affirme: «&amp;nbsp;Le Conseil fédéral reste d’avis que la péréquation financière nationale assure un équilibre entre les cantons&amp;nbsp;» et souligne notamment que «&amp;nbsp;... la compensation des charges dans le cadre de la péréquation financière nationale comprend une composante sociodémographique, qui tient compte des coûts liés à la structure de la population, notamment à la pyramide des âges. Le Canton du Tessin reçoit déjà des contributions fédérales dans ce cadre.&amp;nbsp;»&lt;/p&gt;&lt;p&gt;Malheureusement, ce n’est pas ce que disent les montants définitifs des paiements compensatoires pour 2025 récemment publiés. Au contraire, le canton du Tessin ne reçoit rien au titre de la compensation sociodémographique, bien qu’il compte le plus grand nombre de personnes de 80 ans ou plus (7,6 % de la population résidante permanente, contre 5,7&amp;nbsp;% pour la moyenne nationale). Le moment est donc venu de reconnaître la situation particulière du Tessin, qui compte une proportion non négligeable de retraités âgés originaires de la Suisse alémanique.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Confirme-t-il que le Tessin ne reçoit aucune contribution au titre de la compensation sociodémographique, contrairement à ce qu’il affirme dans son avis sur la motion 24.4209?&lt;/li&gt;&lt;li&gt;Au vu de ce qui précède, convient-il que la péréquation financière nationale n’atteint pas son but?&lt;/li&gt;&lt;li&gt;Par conséquent, ne pense-t-il pas que la création d’un mécanisme de compensation intercantonale de l’augmentation des primes de l’assurance-maladie due au vieillissement de la population, demandée par la motion 24.4209, soit à la fois opportune et nécessaire?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In der Stellungnahme zur Motion Quadri 24.4209, die den Bundesrat beauftragte, einen Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien einzuführen, hat der Bundesrat festgehalten: «Der Bundesrat ist weiterhin der Meinung, dass der nationale Finanzausgleich für ein Gleichgewicht zwischen den Kantonen sorgt. [...], insbesondere hat er ausgeführt, dass der nationale Finanzausgleich eine soziodemographische Komponente innerhalb des Lastenausgleichs enthält, der die Kosten aufgrund der Bevölkerungsstruktur, u. a. des Alters, berücksichtigt. Der Kanton [...] erhält bereits Beiträge vom Bund im Rahmen des Lastenausgleichs».&lt;/p&gt;&lt;p&gt;Leider decken sich aber die kürzlich veröffentlichten Berechnungen zu den Ausgleichszahlungen 2025 nicht mit diesen Aussagen. So erhält der Kanton Tessin keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich, obwohl er einen besonders hohen Anteil an Personen im Alter von 80 Jahren und mehr im Verhältnis zur ständigen Wohnbevölkerung aufweist (7,6 % gegenüber dem schweizerischen Durchschnitt von 5,7 %). Es ist daher an der Zeit, die besondere Situation des Kantons Tessin anzuerkennen, wo ein nicht unerheblicher Teil der älteren Menschen Rentnerinnen und Rentner aus der Deutschschweiz sind.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte deshalb den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bestätigt der Bundesrat, dass der Kanton Tessin – anders als in der Stellungnahme zur Motion 24.4209 behauptet – keine Ausgleichszahlungen für den soziodemografischen Lastenausgleich erhält?&lt;/li&gt;&lt;li&gt;Teilt der Bundesrat in Anbetracht der obigen Ausführungen die Ansicht, dass der nationale Finanzausgleich seinen Zweck nicht erfüllt?&lt;/li&gt;&lt;li&gt;Hält der Bundesrat die Einführung eines Mechanismus zum interkantonalen Ausgleich des alterungsbedingten Anstiegs der Krankenkassenprämien, wie sie mit der Motion 24.4209 verlangt wird, nicht auch für sinnvoll und notwendig?&amp;nbsp;&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechsteiner Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlichkeitsarbeit des Bundes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relations publiques de la Confédération</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attività di pubbliche relazioni della Confederazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le chancelier de la Confédération a répondu le 16&amp;nbsp;décembre 2024 de manière relativement détaillée à ma question 24.7932 «&amp;nbsp;400 fonctionnaires médias. Y a-t-il un potentiel d’économies&amp;nbsp;?&amp;nbsp;». Certains points restent toutefois flous, et les réponses fournies soulèvent d’autres questions.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Meine Frage 24.7932 «400 Medienbeamte – Sparpotential erkannt?» wurde vom Bundeskanzler am 16. Dezember 2024 relativ ausführlich beantwortet. Trotzdem bleibt einiges im Unklaren und die Antworten werfen weiteren Fragen auf.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufhebung des Zentrumslastenausgleichs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suppression de la compensation des charges des centres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eliminare la compensazione degli oneri dei centri urbani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier la législation relative à la péréquation financière et à la compensation des charges de sorte que la compensation des charges dues à des facteurs socio-démographiques (CCS) ne s’applique désormais plus qu’aux charges excessives liées à la structure de la population et que les charges des centres ne soient plus compensées.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die Gesetzgebung zum Finanz- und Lastenausgleich dahingehend anzupassen, dass der soziodemografische Lastenausgleich künftig nur mehr Sonderlasten aufgrund der Bevölkerungsstruktur ausgleicht und keinen Zentrumslastenausgleich mehr vorsieht.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Soziale Fragen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Questions sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina Fabian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übernahme der EU-Richtlinie 2019/1158 zur Vereinbarkeit von Beruf und Privatleben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reprise de la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepimento della direttiva UE 2019/1158 relativa all’equilibrio tra attività professionale e vita familiare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de reprendre dans le droit suisse la directive (UE) 2019/1158 concernant l’équilibre entre vie professionnelle et vie privée.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die EU-Richtlinie 2019/118 zur Vereinbarkeit von Beruf und Privatleben ins Schweizer Recht zu übernehmen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europapolitik|Soziale Fragen|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique européenne|Questions sociales|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica europea|Questioni sociali|Occupazione e lavoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widmer Céline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systemwechsel bei der Wohneigentumsbesteuerung. Steuerliche Folgen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changement de système d’imposition du logement. Conséquences fiscales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cambio di sistema nell'ambito dell'imposizione della proprietà abitativa. Conseguenze fiscali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les chambres fédérales ont adopté une réforme de l’imposition du logement le 20.12.2024, qui bouleverse les équilibres dans ce domaine tout en amenant de grandes pertes fiscales.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le conseil fédéral est prié de répondre aux questions suivantes, au sujet de la réforme telle qu’elle a été adoptée par le parlement et de l’introduction d’un impôt réel sur les résidences secondaires :&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;La BNS a annoncé une baisse des taux directeurs à 0.5%. Un scénario avec des taux hypothécaires moyens durablement en dessous de 1.5% devient de plus en plus crédibles. Quelles seraient les pertes fiscales liées à la réforme en cas de taux moyen à 1%&amp;nbsp; et à 1.25%?&amp;nbsp;&amp;nbsp;&lt;/li&gt;&lt;li&gt;Etant donné que la réforme entraine de grandes pertes fiscales, cela veut dire que certains contribuables vont être avantagés par rapport au reste de la population. Est-il correct de dire que les personnes qui toucheront la plus grande somme par rapport à la situation actuelle sont celles et ceux qui disposent de très grandes propriétés avec une énorme valeur et qui n’ont pas de dette liée à cette propriété ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Combien de baisse d’impôt peut attendre un propriétaire d’une maison de maître d’une valeur de CHF 10'000'000.- et qui finance aujourd’hui son bien entièrement en fonds propres ? Quelle serait le changement de la situation fiscale d’un propriétaire qui dispose d’un bien d’une valeur de CHF 500'000, hypothéqué à hauteur de CHF 400'000.- avec un taux hypothécaire de 3%, et devant faire des frais d’entretiens pour CHF 10'000.-, s’il dispose d’un revenu imposable de 100'000.- ?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Le Conseil fédéral peut-il expliquer quelle est la relation entre d’une part la valeur d’une bien immobilier utilisé comme résidence principale et d’autre part l’allègement fiscal obtenu suite à l’introduction du changement de système d’imposition du logement?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;li&gt;Quels sont les effets de la réforme de l’imposition du logement sur la péréquation financière? En particulier, quel est l’effet sur l’équilibre de cette péréquation à long terme?&amp;nbsp; &amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die Bundesversammlung hat am 20. Dezember 2024 eine Reform der Wohneigentumsbesteuerung verabschiedet, die das Gleichgewicht in diesem Bereich erheblich stört und gleichzeitig grosse Steuerausfälle mit sich bringt.&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, die folgenden Fragen zur Reform in der vom Parlament verabschiedeten Form und zur Einführung einer Objektsteuer auf Zweitwohnungen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Die Schweizerische Nationalbank (SNB) hat eine Senkung des Leitzinses auf 0,5&amp;nbsp;Prozent angekündigt. Es ist immer wahrscheinlicher, dass die durchschnittlichen Hypothekarzinsen dauerhaft unter 1,5&amp;nbsp;Prozent liegen. Wie hoch wären die Steuerausfälle aufgrund der Reform bei einem durchschnittlichen Zinssatz von 1 Prozent oder 1,25 Prozent?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Die Reform führt zu grossen Steuerausfällen. Das bedeutet, dass einige Steuerzahler und Steuerzahlerinnen gegenüber dem Rest der Bevölkerung begünstigt werden. Kann man sagen, dass die Personen, die über sehr grosse Immobilien mit einem enormen Wert verfügen und keine Schulden im Zusammenhang mit diesen Immobilien haben, im Vergleich zur aktuellen Situation am stärksten profitieren?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Mit welcher Steuersenkung kann ein Eigentümer einer herrschaftlichen Villa im Wert von 10&amp;nbsp;000&amp;nbsp;000 Franken rechnen, der seine Immobilie heute vollständig mit Eigenmitteln finanziert? Wie würde sich die steuerliche Situation einer Eigentümerin mit einem steuerpflichtigen Einkommen von 100 000 Franken ändern, wenn sie über eine Immobilie im Wert von 500&amp;nbsp;000 Franken verfügt, die mit einer Hypothek in Höhe von 400&amp;nbsp;000 Franken zu einem Hypothekarzins von 3&amp;nbsp;Prozent belastet ist, und sie Unterhaltskosten in Höhe von 10&amp;nbsp;000 Franken tragen muss?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. &amp;nbsp;Kann der Bundesrat erklären, in welchem Verhältnis der Wert einer Immobilie, die als Erstwohnung genutzt wird, zur Steuererleichterung steht, die durch den Systemwechsel bei der Wohneigentumsbesteuerung erreicht wird?&amp;nbsp; &amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Wie wirkt sich die Reform der Wohneigentumsbesteuerung auf den Finanzausgleich aus?&lt;/p&gt;&lt;p&gt;Welches sind insbesondere die langfristigen Auswirkungen auf das Gleichgewicht des Finanzausgleichs?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuer|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscalité|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imposte|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Was ist die Umweltpolitik des ASTRA im Rahmen seiner Ausschreibungen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quelle est la politique environnementale de l'OFROU dans le cadre de ses appels d'offres?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual è la politica ambientale dell’USTRA in ambito appaltistico?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;L’OFROU réalise des travaux importants à la sortie de l'autoroute à Matran. Pour une question de prix uniquement, du gravier (grave de route principalement) est acheminé depuis un site du Jura français situé à environ 100km de Matran. Pour ne pas circuler à vide sur le retour, les poids-lourds transportent des éléments de chaussée rabotés et les amènent dans les décharges en France voisine. La distance aller-retour est de 200km environ alors que les mêmes matériaux sont disponibles dans un rayon de moins de 30km dans le canton de Fribourg ou 50km hors canton. Il s’ensuit des trajets et des engorgements supplémentaires, plus de CO2, plus de bruit, plus d’usure des infrastructures, de bruit et de poussières. De surcroit, des chauffeurs dont les conditions de travail sont très précaires remplacent des conducteurs domiciliés en Suisse qui bénéficient de bonnes conditions sociales. En utilisant des graviers locaux, on s'assure qu'ils sont exploités selon les normes locales avec du personnel local. Je remercie donc le Conseil fédéral de répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Les soumissions provenant de l'OFROU prévoient-elles des filières d’approvisionnement et d’évacuation de graviers et autres matériaux minéraux&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Si non, est-il prévu de prendre en compte rapidement les éléments précités?&lt;/li&gt;&lt;li&gt;Si oui, sachant que l’empreinte CO2 du transport de ces matériaux lourds est importante, comment cet élément est-il mis en valeur&amp;nbsp;dans la soumission&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment ces aspects sont-ils contrôlés en pratique, sur le terrain&amp;nbsp;?&lt;/li&gt;&lt;li&gt;En cas de faute, quelles sont les conséquences&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Das Bundesamt für Strassen (ASTRA) führt bei der Autobahnausfahrt Matran wichtige Bauarbeiten durch. Dabei wird einzig aus Kostengründen Kies (hauptsächlich als Strassenschotter) aus dem französischen Jura angeliefert, von einem Ort, der rund 100 Kilometer von Matran entfernt liegt. Um auf dem Rückweg Leerfahrten zu vermeiden, transportiert der Schwerverkehr von der Fahrbahn abgeschliffene Elemente ab und entsorgt diese im benachbarten Frankreich. Insgesamt werden rund 200 Kilometer zurückgelegt, obwohl dieselben Materialien in einem Umkreis von weniger als 30 Kilometern im Kanton Freiburg oder 50 Kilometern ausserhalb des Kantons verfügbar wären. Dies führt zu zusätzlichen Fahrten, mehr Stau, CO2, Lärm und Staub sowie zu einer verstärkten Abnutzung der Infrastrukturen. Zudem werden in der Schweiz wohnhafte Chauffeurinnen und Chauffeure, die von guten sozialen Bedingungen profitieren, durch solche mit sehr prekären Arbeitsbedingungen ersetzt. Die Verwendung von lokalem Kies stellt sicher, dass dieser nach lokalen Normen und mit lokalem Personal abgebaut wird. Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul style="list-style-type:disc;"&gt;&lt;li&gt;Sehen die Ausschreibungen des ASTRA Liefer- und Entsorgungswege für Kies und andere mineralische Materialien vor?&lt;/li&gt;&lt;li&gt;Wenn nein: Ist geplant, die obgenannten Punkte rasch zu berücksichtigen?&lt;/li&gt;&lt;li&gt;Wenn ja: Wie wird dieser Aspekt in der Ausschreibung hervorgehoben, zumal bekannt ist, dass der Transport von Schwergut einen grossen CO2-Fussabdruck hat?&lt;/li&gt;&lt;li&gt;Wie werden diese Aspekte in der Praxis vor Ort kontrolliert?&lt;/li&gt;&lt;li&gt;Was wären die Folgen, wenn sie nicht kontrolliert werden?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20241055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschäftigung und Arbeit|Verkehr|Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emploi et travail|Transports|Environnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupazione e lavoro|Trasporti|Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marti Min Li</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kann die Post einen Beitrag zur digitalen Inklusion leisten? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Poste peut-elle contribuer à l'inclusion numérique? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Posta può contribuire all'inclusione digitale? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Diverses études comme le Baromètre numérique&amp;nbsp;2024 de la Mobilière ont constaté que des compétences numériques de base font défaut à près d’un tiers de la population. Elles relèvent des disparités notables selon l’âge, le revenu et la formation. Même si l’âge joue un rôle en matière de compétences numériques, les personnes âgées ne sont en réalité pas les seules à connaître des difficultés dans l’utilisation des outils numériques comme les services bancaires et les billetteries en ligne ou les guichets virtuels des autorités. Ces lacunes vont souvent de pair avec un sentiment de gêne. &amp;nbsp;Certains, en particulier les jeunes, surestiment leurs propres compétences. De fait, le quotidien bascule toujours plus dans le numérique et exacerbe les lacunes en matière de compétences numériques. C’est pourquoi je prie le Conseil fédéral de répondre aux questions suivantes&amp;nbsp;:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Que pense-t-il du problème des compétences numériques lacunaires&amp;nbsp;? Comment pourrait-on y remédier&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Les pouvoirs publics et les entreprises proches de la Confédération, par exemple, numérisent de plus en plus leurs services, et ne les proposent parfois plus que sous cette forme. Comment garantir leur accessibilité à tout le monde&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Dans le cadre d’un projet pilote mené dans trois filiales, la Poste a proposé une assistance sur toutes sortes de problèmes relevant du numérique. Que pense le Conseil fédéral de ce projet&amp;nbsp;? La poste pourrait-elle contribuer à faire progresser l’inclusion numérique grâce à cette offre&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Est-ce qu’une telle offre de la Poste ou d’autres entreprises pourraient aussi alléger le travail des autorités&amp;nbsp;?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Verschiedene Studien wie beispielsweise der Digitalbarometer 2024 der Mobiliar haben festgestellt, dass fast ein Drittel der Bevölkerung nicht über grundlegende digitale Kompetenzen verfügt. Dabei gibt es signifikante Unterschiede nach Alter, Einkommen und Bildung. Auch wenn das Alter bei den digitalen Kompetenzen eine Rolle spielt, sind es beileibe nicht nur ältere Menschen, die Mühe haben, digitale Anwendungen wie beispielsweise E-Banking, Billetkäufe oder digitale Behördengänge zu nutzen. Dies ist oft auch mit Scham verbunden. &amp;nbsp;Teilweise werden auch die eigenen Fähigkeiten überschätzt, gerade bei jüngeren Menschen. Da immer mehr Dinge des täglichen Lebens digitalisiert werden, stellt die mangelnde digitale Kompetenz ein zunehmendes Problem dar. In diesem Zusammenhang bitte ich den Bundesrat um die Beantwortung folgender Fragen:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie schätzt der Bundesrat das Problem der fehlenden digitalen Kompetenzen ein und wie könnten diese verbessert werden?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Auch Leistungen der öffentlichen Hand oder beispielsweise von bundesnahen Betrieben werden immer häufiger digitalisiert und teilweise nur noch digital angeboten. Wie kann sichergestellt werden, dass alle Personen Zugang zu diesen Leistungen haben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Im Rahmen eines Pilotprojekts hat die Post in drei Filialen ein Angebot geschaffen, um Menschen bei digitalen Problemen aller Art zu unterstützen. Wie beurteilt der Bundesrat dieses Projekt? Könnte die Post mit diesem Angebot einen Beitrag leisten, die digitale Inklusion voranzutreiben?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Könnte eine entsprechende Dienstleistung der Post oder von anderen Betreibern auch dazu beitragen, Behörden zu entlasten?&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20244459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Soziale Fragen|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Questions sociales|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Questioni sociali|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzielle Unterstützung für Imkerinnen und Imker bei geoklimatischen Ausnahmebedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soutien financier direct aux apiculteurs et apicultrices lors de situations géoclimatiques exceptionnelles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sostegno finanziario diretto agli apicoltori in situazioni geoclimatiche eccezionali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Conformément à l'article 160, alinéa 1, de la Constitution fédérale et à l'article 84, lettre o, de la Constitution cantonale, le Canton demande aux Chambres fédérales d'accorder un soutien financier direct, comme des subsides, aux apiculteurs et apicultrices pour l'achat de sucre nécessaire au nourrissement des abeilles mellifères, ceci lorsque les situations géoclimatiques rendent ce nourrissement indispensable à la survie des colonies d'abeilles.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Gestützt auf Artikel&amp;nbsp;160 Absatz&amp;nbsp;1 der Bundesverfassung und Artikel&amp;nbsp;84 Buchstabe&amp;nbsp;o seiner Kantonsverfassung fordert der Kanton Jura die Bundesversammlung auf, den Imkerinnen und Imkern finanzielle Unterstützung, beispielsweise in Form von Subventionen, zu gewähren für den Kauf von Zucker, wenn dieser aufgrund der geoklimatischen Bedingungen an Honigbienen verfüttert werden muss, um deren Überleben sicherzustellen.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20240331</t>
@@ -9198,13 +9198,13 @@
         <v>779</v>
       </c>
       <c r="N65" t="s">
+        <v>170</v>
+      </c>
+      <c r="O65" t="s">
         <v>780</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P65" t="s">
         <v>781</v>
-      </c>
-      <c r="P65" t="s">
-        <v>782</v>
       </c>
       <c r="Q65" t="s">
         <v>55</v>
@@ -9222,17 +9222,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C66" t="s">
         <v>444</v>
       </c>
       <c r="D66" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9241,40 +9241,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
+        <v>785</v>
+      </c>
+      <c r="J66" t="s">
         <v>786</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>787</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>788</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>789</v>
-      </c>
-      <c r="M66" t="s">
-        <v>790</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
+        <v>790</v>
+      </c>
+      <c r="P66" t="s">
         <v>791</v>
-      </c>
-      <c r="P66" t="s">
-        <v>792</v>
       </c>
       <c r="Q66" t="s">
         <v>55</v>
       </c>
       <c r="R66" t="s">
+        <v>792</v>
+      </c>
+      <c r="S66" t="s">
         <v>793</v>
       </c>
-      <c r="S66" t="s">
+      <c r="T66" t="s">
         <v>794</v>
-      </c>
-      <c r="T66" t="s">
-        <v>795</v>
       </c>
       <c r="U66" t="s">
         <v>59</v>
@@ -9286,7 +9286,7 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C67" t="s">
         <v>444</v>
@@ -9298,7 +9298,7 @@
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9307,40 +9307,40 @@
         <v>78</v>
       </c>
       <c r="I67" t="s">
+        <v>797</v>
+      </c>
+      <c r="J67" t="s">
         <v>798</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>799</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>800</v>
       </c>
-      <c r="L67" t="s">
+      <c r="M67" t="s">
         <v>801</v>
-      </c>
-      <c r="M67" t="s">
-        <v>802</v>
       </c>
       <c r="N67" t="s">
         <v>170</v>
       </c>
       <c r="O67" t="s">
+        <v>802</v>
+      </c>
+      <c r="P67" t="s">
         <v>803</v>
-      </c>
-      <c r="P67" t="s">
-        <v>804</v>
       </c>
       <c r="Q67" t="s">
         <v>55</v>
       </c>
       <c r="R67" t="s">
+        <v>804</v>
+      </c>
+      <c r="S67" t="s">
         <v>805</v>
       </c>
-      <c r="S67" t="s">
+      <c r="T67" t="s">
         <v>806</v>
-      </c>
-      <c r="T67" t="s">
-        <v>807</v>
       </c>
       <c r="U67" t="s">
         <v>59</v>
@@ -9352,7 +9352,7 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
@@ -9364,7 +9364,7 @@
         <v>653</v>
       </c>
       <c r="F68" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9373,40 +9373,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
+        <v>808</v>
+      </c>
+      <c r="J68" t="s">
         <v>809</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>810</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>811</v>
       </c>
-      <c r="L68" t="s">
+      <c r="M68" t="s">
         <v>812</v>
-      </c>
-      <c r="M68" t="s">
-        <v>813</v>
       </c>
       <c r="N68" t="s">
         <v>244</v>
       </c>
       <c r="O68" t="s">
+        <v>813</v>
+      </c>
+      <c r="P68" t="s">
         <v>814</v>
-      </c>
-      <c r="P68" t="s">
-        <v>815</v>
       </c>
       <c r="Q68" t="s">
         <v>247</v>
       </c>
       <c r="R68" t="s">
+        <v>815</v>
+      </c>
+      <c r="S68" t="s">
         <v>816</v>
       </c>
-      <c r="S68" t="s">
+      <c r="T68" t="s">
         <v>817</v>
-      </c>
-      <c r="T68" t="s">
-        <v>818</v>
       </c>
       <c r="U68" t="s">
         <v>59</v>
@@ -9418,61 +9418,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
+        <v>820</v>
+      </c>
+      <c r="I69" t="s">
         <v>821</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>822</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>823</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>824</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>825</v>
-      </c>
-      <c r="M69" t="s">
-        <v>826</v>
       </c>
       <c r="N69" t="s">
         <v>170</v>
       </c>
       <c r="O69" t="s">
+        <v>826</v>
+      </c>
+      <c r="P69" t="s">
         <v>827</v>
-      </c>
-      <c r="P69" t="s">
-        <v>828</v>
       </c>
       <c r="Q69" t="s">
         <v>195</v>
       </c>
       <c r="R69" t="s">
+        <v>828</v>
+      </c>
+      <c r="S69" t="s">
         <v>829</v>
       </c>
-      <c r="S69" t="s">
+      <c r="T69" t="s">
         <v>830</v>
-      </c>
-      <c r="T69" t="s">
-        <v>831</v>
       </c>
       <c r="U69" t="s">
         <v>59</v>
@@ -9484,7 +9484,7 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -9496,7 +9496,7 @@
         <v>104</v>
       </c>
       <c r="F70" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9505,40 +9505,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
+        <v>832</v>
+      </c>
+      <c r="J70" t="s">
         <v>833</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>834</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>835</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>836</v>
-      </c>
-      <c r="M70" t="s">
-        <v>837</v>
       </c>
       <c r="N70" t="s">
         <v>568</v>
       </c>
       <c r="O70" t="s">
+        <v>837</v>
+      </c>
+      <c r="P70" t="s">
         <v>838</v>
-      </c>
-      <c r="P70" t="s">
-        <v>839</v>
       </c>
       <c r="Q70" t="s">
         <v>247</v>
       </c>
       <c r="R70" t="s">
+        <v>839</v>
+      </c>
+      <c r="S70" t="s">
         <v>840</v>
       </c>
-      <c r="S70" t="s">
+      <c r="T70" t="s">
         <v>841</v>
-      </c>
-      <c r="T70" t="s">
-        <v>842</v>
       </c>
       <c r="U70" t="s">
         <v>59</v>
@@ -9550,19 +9550,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9571,40 +9571,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
+        <v>844</v>
+      </c>
+      <c r="J71" t="s">
         <v>845</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>846</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>847</v>
       </c>
-      <c r="L71" t="s">
+      <c r="M71" t="s">
         <v>848</v>
-      </c>
-      <c r="M71" t="s">
-        <v>849</v>
       </c>
       <c r="N71" t="s">
         <v>244</v>
       </c>
       <c r="O71" t="s">
+        <v>849</v>
+      </c>
+      <c r="P71" t="s">
         <v>850</v>
-      </c>
-      <c r="P71" t="s">
-        <v>851</v>
       </c>
       <c r="Q71" t="s">
         <v>195</v>
       </c>
       <c r="R71" t="s">
+        <v>851</v>
+      </c>
+      <c r="S71" t="s">
         <v>852</v>
       </c>
-      <c r="S71" t="s">
+      <c r="T71" t="s">
         <v>853</v>
-      </c>
-      <c r="T71" t="s">
-        <v>854</v>
       </c>
       <c r="U71" t="s">
         <v>59</v>
@@ -9616,19 +9616,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C72" t="s">
         <v>75</v>
       </c>
       <c r="D72" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E72" t="s">
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9637,40 +9637,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
+        <v>856</v>
+      </c>
+      <c r="J72" t="s">
         <v>857</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>858</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>859</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>860</v>
-      </c>
-      <c r="M72" t="s">
-        <v>861</v>
       </c>
       <c r="N72" t="s">
         <v>244</v>
       </c>
       <c r="O72" t="s">
+        <v>861</v>
+      </c>
+      <c r="P72" t="s">
         <v>862</v>
-      </c>
-      <c r="P72" t="s">
-        <v>863</v>
       </c>
       <c r="Q72" t="s">
         <v>247</v>
       </c>
       <c r="R72" t="s">
+        <v>863</v>
+      </c>
+      <c r="S72" t="s">
         <v>864</v>
       </c>
-      <c r="S72" t="s">
+      <c r="T72" t="s">
         <v>865</v>
-      </c>
-      <c r="T72" t="s">
-        <v>866</v>
       </c>
       <c r="U72" t="s">
         <v>59</v>
@@ -9682,7 +9682,7 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C73" t="s">
         <v>163</v>
@@ -9694,7 +9694,7 @@
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9703,40 +9703,40 @@
         <v>78</v>
       </c>
       <c r="I73" t="s">
+        <v>868</v>
+      </c>
+      <c r="J73" t="s">
         <v>869</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>870</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>871</v>
       </c>
-      <c r="L73" t="s">
+      <c r="M73" t="s">
         <v>872</v>
-      </c>
-      <c r="M73" t="s">
-        <v>873</v>
       </c>
       <c r="N73" t="s">
         <v>170</v>
       </c>
       <c r="O73" t="s">
+        <v>873</v>
+      </c>
+      <c r="P73" t="s">
         <v>874</v>
-      </c>
-      <c r="P73" t="s">
-        <v>875</v>
       </c>
       <c r="Q73" t="s">
         <v>55</v>
       </c>
       <c r="R73" t="s">
+        <v>875</v>
+      </c>
+      <c r="S73" t="s">
         <v>876</v>
       </c>
-      <c r="S73" t="s">
+      <c r="T73" t="s">
         <v>877</v>
-      </c>
-      <c r="T73" t="s">
-        <v>878</v>
       </c>
       <c r="U73" t="s">
         <v>59</v>
@@ -9748,19 +9748,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C74" t="s">
         <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E74" t="s">
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9769,40 +9769,40 @@
         <v>78</v>
       </c>
       <c r="I74" t="s">
+        <v>880</v>
+      </c>
+      <c r="J74" t="s">
         <v>881</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>882</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>883</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>884</v>
-      </c>
-      <c r="M74" t="s">
-        <v>885</v>
       </c>
       <c r="N74" t="s">
         <v>244</v>
       </c>
       <c r="O74" t="s">
+        <v>885</v>
+      </c>
+      <c r="P74" t="s">
         <v>886</v>
-      </c>
-      <c r="P74" t="s">
-        <v>887</v>
       </c>
       <c r="Q74" t="s">
         <v>195</v>
       </c>
       <c r="R74" t="s">
+        <v>887</v>
+      </c>
+      <c r="S74" t="s">
         <v>888</v>
       </c>
-      <c r="S74" t="s">
+      <c r="T74" t="s">
         <v>889</v>
-      </c>
-      <c r="T74" t="s">
-        <v>890</v>
       </c>
       <c r="U74" t="s">
         <v>59</v>
@@ -9814,39 +9814,39 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C75" t="s">
         <v>525</v>
       </c>
       <c r="D75" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>78</v>
       </c>
       <c r="I75" t="s">
+        <v>892</v>
+      </c>
+      <c r="J75" t="s">
         <v>893</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>894</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>895</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>896</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>897</v>
-      </c>
-      <c r="N75" t="s">
-        <v>780</v>
       </c>
       <c r="O75" t="s">
         <v>898</v>
@@ -10046,13 +10046,13 @@
         <v>55</v>
       </c>
       <c r="R78" t="s">
+        <v>804</v>
+      </c>
+      <c r="S78" t="s">
         <v>805</v>
       </c>
-      <c r="S78" t="s">
+      <c r="T78" t="s">
         <v>806</v>
-      </c>
-      <c r="T78" t="s">
-        <v>807</v>
       </c>
       <c r="U78" t="s">
         <v>59</v>
@@ -10126,7 +10126,7 @@
         <v>525</v>
       </c>
       <c r="D80" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
@@ -10188,7 +10188,7 @@
         <v>525</v>
       </c>
       <c r="D81" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
@@ -10214,7 +10214,7 @@
         <v>956</v>
       </c>
       <c r="N81" t="s">
-        <v>780</v>
+        <v>897</v>
       </c>
       <c r="O81" t="s">
         <v>957</v>
@@ -11296,7 +11296,7 @@
         <v>525</v>
       </c>
       <c r="D98" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
@@ -11532,13 +11532,13 @@
         <v>247</v>
       </c>
       <c r="R101" t="s">
+        <v>815</v>
+      </c>
+      <c r="S101" t="s">
         <v>816</v>
       </c>
-      <c r="S101" t="s">
+      <c r="T101" t="s">
         <v>817</v>
-      </c>
-      <c r="T101" t="s">
-        <v>818</v>
       </c>
       <c r="U101" t="s">
         <v>59</v>
@@ -12070,7 +12070,7 @@
         <v>525</v>
       </c>
       <c r="D110" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
@@ -13380,7 +13380,7 @@
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E130" t="s">
         <v>62</v>
@@ -13900,7 +13900,7 @@
         <v>525</v>
       </c>
       <c r="D138" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -140,6 +140,102 @@
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuosto Brenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahnplanung. Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planification ferroviaire. Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pianificazione ferroviaria. Il Consiglio federale può ignorare i mandati del Parlamento?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat hat Ende Januar 2026 die Eckwerte für den Ausbau der Verkehrsinfrastruktur im Rahmen von «Verkehr 45» veröffentlicht. Obwohl die politischen Instanzen bereits klare Leitlinien festgelegt haben – insbesondere haben beide Kammern am 11. März 2026 die Motion &lt;strong&gt;24.4042&lt;/strong&gt; «Entwicklung eines Angebotskonzepts 2050 auf nationaler und internationaler Ebene» und am 11. März 2024 &lt;strong&gt;die Motion 23.3668&lt;/strong&gt; «Redundanz und Zuverlässigkeit auf der Eisenbahnachse Lausanne–Genf» angenommen – scheint dies im Dossier &lt;strong&gt;«Verkehr 45»&lt;/strong&gt; in keiner Weise berücksichtigt worden zu sein.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Wird sich die Botschaft 2027 auf diese beiden Motionen abstützen und klar aufzeigen, dass prioritär die Redundanz in der Genferseeregion sowie ein Angebotskonzept, das den nationalen Hauptstrecken Vorrang einräumt, schnellstmöglich geprüft und umgesetzt werden müssen? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Wird die Botschaft 2027 eine Erhöhung der Taktfrequenz, kürzere Fahrzeiten, mehr Kapazitäten und eine robustere Eisenbahninfrastruktur vorsehen, insbesondere für die Westschweiz?&lt;/p&gt;&lt;p&gt;3. Wie gedenkt der Bundesrat angesichts bestimmter neuer Projekte, die im Rahmen von «Verkehr&amp;nbsp;45» vorgesehen sind, die Tragfähigkeit des Bahninfrastrukturfonds zu gewährleisten, ohne dabei die Regionen zu benachteiligen, die bereits einen Investitionsrückstand aufweisen (Jura und Genferseeregion)?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Kann der Bundesrat die territorialen und wirtschaftlichen Auswirkungen eines mangelnden Ausbaus des Schienenverkehrs darlegen und die geplanten Massnahmen zur Gewährleistung der Gleichbehandlung erläutern?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Hält es der Bundesrat im Hinblick auf die Eindämmung der öffentlichen Ausgaben nicht für notwendig, die Baustandards der SBB zu vereinfachen?&lt;/p&gt;&lt;p&gt;6. Sind konkret Verbesserungen auf der Strecke Biel–Lausanne/Genf sowie die endgültige Wiederaufnahme der direkten (pünktlichen) Verbindung Basel/Zürich–Biel–Genf (ohne Umsteigen in Renens) vorgesehen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Ist der Bundesrat nicht der Ansicht, dass er neben den Grossprojekten auch Projekten mit hohem Mehrwert und geringen Kosten Vorrang einräumen sollte, wie beispielsweise der &lt;strong&gt;Bahnhaltestelle «Y-Parc» in Yverdon&lt;/strong&gt;? Die Investitionen sind für das Bundesamt für Verkehr lächerlich gering, gewährleisten jedoch eine Verkehrsverlagerung für Tausende von Arbeitsplätzen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Wenn die Beschlüsse des Parlaments bei der technischen Planung ausser Kraft gesetzt werden können, was bringen die Sessionen dann noch?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strafrecht|Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diritto penale|Migrazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3374</t>
   </si>
   <si>
@@ -170,9 +266,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Finanzwesen|Steuer</t>
   </si>
   <si>
@@ -191,9 +284,6 @@
     <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
   </si>
   <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
     <t xml:space="preserve">SR</t>
   </si>
   <si>
@@ -236,18 +326,12 @@
     <t xml:space="preserve">26.3454</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stettler Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">UDC</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verbesserte Lebensqualität dank den Umfahrungsprojekten entlang der N18</t>
   </si>
   <si>
@@ -335,9 +419,6 @@
     <t xml:space="preserve">2026-03-12</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rechtliche Abklärungen und Potenzial von künstlicher Intelligenz in den Bereichen Polizei und innere Sicherheit</t>
   </si>
   <si>
@@ -374,9 +455,6 @@
     <t xml:space="preserve">Wyssmann Rémy</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Streichung von Artikel 22 des Epidemiengesetzes</t>
   </si>
   <si>
@@ -398,9 +476,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Gesundheit</t>
   </si>
   <si>
@@ -416,7 +491,7 @@
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
-    <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse 18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
+    <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse N18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
   </si>
   <si>
     <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
@@ -437,15 +512,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
   </si>
   <si>
-    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3069</t>
   </si>
   <si>
@@ -518,36 +584,6 @@
     <t xml:space="preserve">2026-04-02</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuosto Brenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bahnplanung. Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planification ferroviaire. Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pianificazione ferroviaria. Il Consiglio federale può ignorare i mandati del Parlamento?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat hat Ende Januar 2026 die Eckwerte für den Ausbau der Verkehrsinfrastruktur im Rahmen von «Verkehr 45» veröffentlicht. Obwohl die politischen Instanzen bereits klare Leitlinien festgelegt haben – insbesondere haben beide Kammern am 11. März 2026 die Motion &lt;strong&gt;24.4042&lt;/strong&gt; «Entwicklung eines Angebotskonzepts 2050 auf nationaler und internationaler Ebene» und am 11. März 2024 &lt;strong&gt;die Motion 23.3668&lt;/strong&gt; «Redundanz und Zuverlässigkeit auf der Eisenbahnachse Lausanne–Genf» angenommen – scheint dies im Dossier &lt;strong&gt;«Verkehr 45»&lt;/strong&gt; in keiner Weise berücksichtigt worden zu sein.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Wird sich die Botschaft 2027 auf diese beiden Motionen abstützen und klar aufzeigen, dass prioritär die Redundanz in der Genferseeregion sowie ein Angebotskonzept, das den nationalen Hauptstrecken Vorrang einräumt, schnellstmöglich geprüft und umgesetzt werden müssen? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Wird die Botschaft 2027 eine Erhöhung der Taktfrequenz, kürzere Fahrzeiten, mehr Kapazitäten und eine robustere Eisenbahninfrastruktur vorsehen, insbesondere für die Westschweiz?&lt;/p&gt;&lt;p&gt;3. Wie gedenkt der Bundesrat angesichts bestimmter neuer Projekte, die im Rahmen von «Verkehr&amp;nbsp;45» vorgesehen sind, die Tragfähigkeit des Bahninfrastrukturfonds zu gewährleisten, ohne dabei die Regionen zu benachteiligen, die bereits einen Investitionsrückstand aufweisen (Jura und Genferseeregion)?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Kann der Bundesrat die territorialen und wirtschaftlichen Auswirkungen eines mangelnden Ausbaus des Schienenverkehrs darlegen und die geplanten Massnahmen zur Gewährleistung der Gleichbehandlung erläutern?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Hält es der Bundesrat im Hinblick auf die Eindämmung der öffentlichen Ausgaben nicht für notwendig, die Baustandards der SBB zu vereinfachen?&lt;/p&gt;&lt;p&gt;6. Sind konkret Verbesserungen auf der Strecke Biel–Lausanne/Genf sowie die endgültige Wiederaufnahme der direkten (pünktlichen) Verbindung Basel/Zürich–Biel–Genf (ohne Umsteigen in Renens) vorgesehen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Ist der Bundesrat nicht der Ansicht, dass er neben den Grossprojekten auch Projekten mit hohem Mehrwert und geringen Kosten Vorrang einräumen sollte, wie beispielsweise der &lt;strong&gt;Bahnhaltestelle «Y-Parc» in Yverdon&lt;/strong&gt;? Die Investitionen sind für das Bundesamt für Verkehr lächerlich gering, gewährleisten jedoch eine Verkehrsverlagerung für Tausende von Arbeitsplätzen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Wenn die Beschlüsse des Parlaments bei der technischen Planung ausser Kraft gesetzt werden können, was bringen die Sessionen dann noch?&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3323</t>
   </si>
   <si>
@@ -588,42 +624,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strafrecht|Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diritto penale|Migrazione</t>
   </si>
   <si>
     <t xml:space="preserve">26.7194</t>
@@ -5202,150 +5202,148 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263374</v>
+        <v>20263228</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3"/>
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
         <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
         <v>34</v>
       </c>
       <c r="O3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263411</v>
+        <v>20263131</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E4"/>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N4" t="s">
         <v>34</v>
       </c>
       <c r="O4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263454</v>
+        <v>20263374</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
       </c>
-      <c r="E5" t="s">
-        <v>76</v>
-      </c>
+      <c r="E5"/>
       <c r="F5" t="s">
         <v>26</v>
       </c>
@@ -5353,70 +5351,70 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s">
         <v>77</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>78</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>79</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>80</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>81</v>
-      </c>
-      <c r="M5" t="s">
-        <v>82</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
       </c>
       <c r="O5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" t="s">
         <v>83</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" t="s">
         <v>84</v>
       </c>
-      <c r="Q5" t="s">
-        <v>69</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>85</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>86</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>87</v>
-      </c>
-      <c r="U5" t="s">
-        <v>56</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263192</v>
+        <v>20263411</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
         <v>90</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
       </c>
       <c r="H6" t="s">
         <v>91</v>
@@ -5446,31 +5444,31 @@
         <v>98</v>
       </c>
       <c r="Q6" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="R6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U6" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263099</v>
+        <v>20263454</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>104</v>
@@ -5479,211 +5477,211 @@
         <v>105</v>
       </c>
       <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
         <v>106</v>
       </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>107</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>108</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>109</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>110</v>
-      </c>
-      <c r="L7" t="s">
-        <v>111</v>
-      </c>
-      <c r="M7" t="s">
-        <v>112</v>
       </c>
       <c r="N7" t="s">
         <v>34</v>
       </c>
       <c r="O7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" t="s">
         <v>113</v>
       </c>
-      <c r="P7" t="s">
+      <c r="S7" t="s">
         <v>114</v>
       </c>
-      <c r="Q7" t="s">
-        <v>69</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>115</v>
       </c>
-      <c r="S7" t="s">
-        <v>116</v>
-      </c>
-      <c r="T7" t="s">
-        <v>117</v>
-      </c>
       <c r="U7" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263120</v>
+        <v>20263192</v>
       </c>
       <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s">
         <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" t="s">
-        <v>120</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="I8" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" t="s">
         <v>121</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>122</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>123</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>124</v>
-      </c>
-      <c r="M8" t="s">
-        <v>125</v>
       </c>
       <c r="N8" t="s">
         <v>34</v>
       </c>
       <c r="O8" t="s">
+        <v>125</v>
+      </c>
+      <c r="P8" t="s">
         <v>126</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" t="s">
         <v>127</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="S8" t="s">
         <v>128</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>129</v>
       </c>
-      <c r="S8" t="s">
-        <v>130</v>
-      </c>
-      <c r="T8" t="s">
-        <v>131</v>
-      </c>
       <c r="U8" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263121</v>
+        <v>20263099</v>
       </c>
       <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" t="s">
         <v>133</v>
       </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" t="s">
-        <v>105</v>
-      </c>
       <c r="F9" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s">
         <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="S9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="T9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="U9" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263069</v>
+        <v>20263120</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>147</v>
@@ -5710,287 +5708,285 @@
         <v>153</v>
       </c>
       <c r="Q10" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="S10" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="T10" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="U10" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20254774</v>
+        <v>20263121</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M11" t="s">
+        <v>163</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" t="s">
+        <v>164</v>
+      </c>
+      <c r="P11" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" t="s">
+        <v>56</v>
+      </c>
+      <c r="S11" t="s">
+        <v>57</v>
+      </c>
+      <c r="T11" t="s">
+        <v>58</v>
+      </c>
+      <c r="U11" t="s">
         <v>157</v>
-      </c>
-      <c r="K11" t="s">
-        <v>158</v>
-      </c>
-      <c r="L11" t="s">
-        <v>159</v>
-      </c>
-      <c r="M11" t="s">
-        <v>160</v>
-      </c>
-      <c r="N11" t="s">
-        <v>161</v>
-      </c>
-      <c r="O11" t="s">
-        <v>162</v>
-      </c>
-      <c r="P11" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" t="s">
-        <v>164</v>
-      </c>
-      <c r="S11" t="s">
-        <v>165</v>
-      </c>
-      <c r="T11" t="s">
-        <v>166</v>
-      </c>
-      <c r="U11" t="s">
-        <v>167</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263228</v>
+        <v>20263069</v>
       </c>
       <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" t="s">
         <v>168</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>170</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" t="s">
         <v>171</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>172</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>173</v>
-      </c>
-      <c r="L12" t="s">
-        <v>174</v>
-      </c>
-      <c r="M12" t="s">
-        <v>175</v>
       </c>
       <c r="N12" t="s">
         <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R12" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="S12" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="T12" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="U12" t="s">
-        <v>41</v>
-      </c>
-      <c r="V12" t="s">
-        <v>41</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263323</v>
+        <v>20254774</v>
       </c>
       <c r="B13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" t="s">
         <v>178</v>
       </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="J13" t="s">
         <v>179</v>
       </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>180</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>181</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>182</v>
       </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
         <v>183</v>
       </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
         <v>184</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>185</v>
       </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
+        <v>99</v>
+      </c>
+      <c r="R13" t="s">
         <v>186</v>
       </c>
-      <c r="P13" t="s">
+      <c r="S13" t="s">
         <v>187</v>
       </c>
-      <c r="Q13" t="s">
-        <v>128</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
         <v>188</v>
       </c>
-      <c r="S13" t="s">
+      <c r="U13" t="s">
         <v>189</v>
-      </c>
-      <c r="T13" t="s">
-        <v>190</v>
-      </c>
-      <c r="U13" t="s">
-        <v>191</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263131</v>
+        <v>20263323</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14"/>
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
       <c r="F14" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" t="s">
         <v>194</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>195</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>196</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>197</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>198</v>
       </c>
-      <c r="N14" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>199</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>70</v>
+      </c>
+      <c r="R14" t="s">
         <v>200</v>
       </c>
-      <c r="Q14" t="s">
-        <v>128</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>201</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>202</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>203</v>
       </c>
-      <c r="U14" t="s">
-        <v>41</v>
-      </c>
-      <c r="V14" t="s">
-        <v>41</v>
-      </c>
+      <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6006,7 +6002,7 @@
         <v>206</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>207</v>
@@ -6040,7 +6036,7 @@
         <v>214</v>
       </c>
       <c r="Q15" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R15" t="s">
         <v>215</v>
@@ -6052,7 +6048,7 @@
         <v>217</v>
       </c>
       <c r="U15" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V15"/>
     </row>
@@ -6073,13 +6069,13 @@
         <v>220</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
         <v>221</v>
@@ -6116,7 +6112,7 @@
         <v>229</v>
       </c>
       <c r="U16" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V16"/>
     </row>
@@ -6137,7 +6133,7 @@
       </c>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
         <v>233</v>
@@ -6160,19 +6156,19 @@
         <v>238</v>
       </c>
       <c r="Q17" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R17" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="S17" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="T17" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="U17" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V17"/>
     </row>
@@ -6199,7 +6195,7 @@
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
         <v>241</v>
@@ -6224,7 +6220,7 @@
         <v>246</v>
       </c>
       <c r="Q18" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R18" t="s">
         <v>247</v>
@@ -6236,7 +6232,7 @@
         <v>249</v>
       </c>
       <c r="U18" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V18"/>
     </row>
@@ -6261,7 +6257,7 @@
         <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
         <v>253</v>
@@ -6288,7 +6284,7 @@
         <v>259</v>
       </c>
       <c r="Q19" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R19" t="s">
         <v>260</v>
@@ -6300,7 +6296,7 @@
         <v>262</v>
       </c>
       <c r="U19" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V19"/>
     </row>
@@ -6312,7 +6308,7 @@
         <v>263</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
         <v>264</v>
@@ -6321,13 +6317,13 @@
         <v>265</v>
       </c>
       <c r="F20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s">
         <v>266</v>
@@ -6354,7 +6350,7 @@
         <v>272</v>
       </c>
       <c r="Q20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R20" t="s">
         <v>273</v>
@@ -6366,7 +6362,7 @@
         <v>275</v>
       </c>
       <c r="U20" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V20"/>
     </row>
@@ -6378,22 +6374,22 @@
         <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
         <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
         <v>278</v>
@@ -6432,7 +6428,7 @@
         <v>287</v>
       </c>
       <c r="U21" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V21"/>
     </row>
@@ -6447,16 +6443,16 @@
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
         <v>289</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
         <v>290</v>
@@ -6486,7 +6482,7 @@
         <v>298</v>
       </c>
       <c r="Q22" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R22" t="s">
         <v>299</v>
@@ -6498,7 +6494,7 @@
         <v>301</v>
       </c>
       <c r="U22" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V22"/>
     </row>
@@ -6510,22 +6506,22 @@
         <v>302</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F23" t="s">
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="I23" t="s">
         <v>303</v>
@@ -6552,7 +6548,7 @@
         <v>310</v>
       </c>
       <c r="Q23" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R23" t="s">
         <v>311</v>
@@ -6564,7 +6560,7 @@
         <v>313</v>
       </c>
       <c r="U23" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V23"/>
     </row>
@@ -6576,22 +6572,22 @@
         <v>314</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
         <v>315</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F24" t="s">
         <v>316</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I24" t="s">
         <v>317</v>
@@ -6630,7 +6626,7 @@
         <v>326</v>
       </c>
       <c r="U24" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V24"/>
     </row>
@@ -6645,10 +6641,10 @@
         <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F25" t="s">
         <v>328</v>
@@ -6657,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s">
         <v>329</v>
@@ -6696,7 +6692,7 @@
         <v>262</v>
       </c>
       <c r="U25" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V25"/>
     </row>
@@ -6708,13 +6704,13 @@
         <v>336</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
         <v>206</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>328</v>
@@ -6723,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s">
         <v>337</v>
@@ -6750,7 +6746,7 @@
         <v>343</v>
       </c>
       <c r="Q26" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R26" t="s">
         <v>344</v>
@@ -6762,7 +6758,7 @@
         <v>346</v>
       </c>
       <c r="U26" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6780,7 +6776,7 @@
         <v>348</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>349</v>
@@ -6814,7 +6810,7 @@
         <v>355</v>
       </c>
       <c r="Q27" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R27" t="s">
         <v>356</v>
@@ -6826,7 +6822,7 @@
         <v>358</v>
       </c>
       <c r="U27" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V27"/>
     </row>
@@ -6841,10 +6837,10 @@
         <v>205</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
         <v>349</v>
@@ -6853,7 +6849,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="I28" t="s">
         <v>360</v>
@@ -6878,19 +6874,19 @@
         <v>365</v>
       </c>
       <c r="Q28" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R28" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="S28" t="s">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="T28" t="s">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s">
         <v>203</v>
-      </c>
-      <c r="U28" t="s">
-        <v>191</v>
       </c>
       <c r="V28"/>
     </row>
@@ -6902,7 +6898,7 @@
         <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
         <v>367</v>
@@ -6915,7 +6911,7 @@
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s">
         <v>369</v>
@@ -6942,7 +6938,7 @@
         <v>375</v>
       </c>
       <c r="Q29" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R29" t="s">
         <v>376</v>
@@ -6954,7 +6950,7 @@
         <v>378</v>
       </c>
       <c r="U29" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V29"/>
     </row>
@@ -6972,16 +6968,16 @@
         <v>380</v>
       </c>
       <c r="E30" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s">
         <v>381</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I30" t="s">
         <v>382</v>
@@ -7008,7 +7004,7 @@
         <v>388</v>
       </c>
       <c r="Q30" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="R30" t="s">
         <v>389</v>
@@ -7020,7 +7016,7 @@
         <v>391</v>
       </c>
       <c r="U30" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V30"/>
     </row>
@@ -7032,7 +7028,7 @@
         <v>392</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>393</v>
@@ -7047,7 +7043,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s">
         <v>394</v>
@@ -7074,19 +7070,19 @@
         <v>400</v>
       </c>
       <c r="Q31" t="s">
+        <v>70</v>
+      </c>
+      <c r="R31" t="s">
+        <v>127</v>
+      </c>
+      <c r="S31" t="s">
         <v>128</v>
       </c>
-      <c r="R31" t="s">
-        <v>99</v>
-      </c>
-      <c r="S31" t="s">
-        <v>100</v>
-      </c>
       <c r="T31" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V31"/>
     </row>
@@ -7098,13 +7094,13 @@
         <v>401</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>381</v>
@@ -7113,7 +7109,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
         <v>402</v>
@@ -7140,19 +7136,19 @@
         <v>408</v>
       </c>
       <c r="Q32" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R32" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="S32" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="T32" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="U32" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V32"/>
     </row>
@@ -7167,19 +7163,19 @@
         <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
         <v>381</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
         <v>410</v>
@@ -7206,7 +7202,7 @@
         <v>416</v>
       </c>
       <c r="Q33" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R33" t="s">
         <v>417</v>
@@ -7218,7 +7214,7 @@
         <v>419</v>
       </c>
       <c r="U33" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V33"/>
     </row>
@@ -7230,13 +7226,13 @@
         <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>421</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F34" t="s">
         <v>422</v>
@@ -7245,7 +7241,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I34" t="s">
         <v>423</v>
@@ -7272,7 +7268,7 @@
         <v>429</v>
       </c>
       <c r="Q34" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R34" t="s">
         <v>273</v>
@@ -7284,7 +7280,7 @@
         <v>275</v>
       </c>
       <c r="U34" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V34"/>
     </row>
@@ -7296,19 +7292,19 @@
         <v>430</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F35" t="s">
         <v>431</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s">
         <v>28</v>
@@ -7338,7 +7334,7 @@
         <v>438</v>
       </c>
       <c r="Q35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R35" t="s">
         <v>439</v>
@@ -7350,7 +7346,7 @@
         <v>441</v>
       </c>
       <c r="U35" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V35"/>
     </row>
@@ -7362,13 +7358,13 @@
         <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
         <v>443</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
         <v>431</v>
@@ -7416,7 +7412,7 @@
         <v>453</v>
       </c>
       <c r="U36" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V36"/>
     </row>
@@ -7428,22 +7424,22 @@
         <v>454</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
         <v>455</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s">
         <v>457</v>
@@ -7470,7 +7466,7 @@
         <v>463</v>
       </c>
       <c r="Q37" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R37" t="s">
         <v>464</v>
@@ -7482,7 +7478,7 @@
         <v>466</v>
       </c>
       <c r="U37" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="V37"/>
     </row>
@@ -7497,10 +7493,10 @@
         <v>468</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F38" t="s">
         <v>469</v>
@@ -7509,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I38" t="s">
         <v>470</v>
@@ -7536,7 +7532,7 @@
         <v>477</v>
       </c>
       <c r="Q38" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="R38" t="s">
         <v>478</v>
@@ -7548,7 +7544,7 @@
         <v>480</v>
       </c>
       <c r="U38" t="s